--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名にスバルとあるが、アップル1号店を開業した会社と紹介されている（春日井市）。トラック専門店も運営。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名にスバルとあるが、アップル1号店を開業した会社と紹介されている（春日井市）。トラック専門店も運営。 参考：店舗の連絡先（アップル春日井店）〒486-0849 愛知県春日井市八田町2丁目1-16 TEL 0568-85-0202 FAX 0568-85-0262。</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル坂戸鶴ヶ島インター店）〒350-2211 埼玉県鶴ヶ島市脚折町5-4-13 TEL 049-279-3500 FAX 049-279-3501。</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。軽四専門「メガタウン」（豊田市）も運営しており、実際の店舗数はこれより多い可能性。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。軽四専門「メガタウン」（豊田市）も運営しており、実際の店舗数はこれより多い可能性。 参考：店舗の連絡先（アップル江田駅前店）〒225-0013 神奈川県横浜市青葉区荏田町1236-7東急江田駅前ドエリング1F TEL 045-912-7560 FAX 045-912-7566。</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
         </is>
       </c>
     </row>
@@ -1677,33 +1677,98 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>株式会社パッション</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>岐阜県、愛知県</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>愛知県春日井市味美町2丁目122番地</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>買取専門店ラビット勝川店を運営</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>217名（2025年12月）</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1963passion.co.jp/company/outline/
+https://www.1963passion.co.jp/company/access/</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>株式会社アップルカーセールス</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0004/
@@ -1711,91 +1776,14 @@
 https://www.applenet.co.jp/shop/0046/</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ヨシダオートサービス</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>大阪府</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0301</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0302</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>吉田宜史</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/contact/</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>218名（2025年1月）</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
         </is>
       </c>
     </row>
@@ -1805,40 +1793,64 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -1848,7 +1860,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1870,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1866,15 +1878,19 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>浜松市内6店舗</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1886,20 +1902,18 @@
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1923,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>松下モータース</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1917,12 +1931,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1937,17 +1951,20 @@
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1974,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>松下モータース</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1965,57 +1982,37 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2022,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2033,30 +2030,47 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 石戸宏樹</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>26名</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/</t>
+          <t>https://www.apple-car.jp/company</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2066,7 +2080,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2090,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2084,12 +2098,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -2104,17 +2118,20 @@
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
         </is>
       </c>
     </row>
@@ -2124,77 +2141,45 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>human joint株式会社</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>03-4446-7735</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>03-5422-8006</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 齊藤博行</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>https://cococar-hp.net/</t>
-        </is>
-      </c>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>中古自動車の販売および買取（事業内容）</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>32名</t>
-        </is>
-      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/company/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2189,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>株式会社NIIZAWA</t>
+          <t>human joint株式会社</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2212,108 +2197,256 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>広島県、山口県</t>
+          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
+          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>広島県廿日市市大野原1丁目2-20</t>
+          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0829-30-8103</t>
+          <t>03-4446-7735</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0829-30-8104</t>
+          <t>03-5422-8006</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
+          <t>代表取締役 齊藤博行</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.kei-market.co.jp/</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kei-market.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://cococar-hp.net/</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>中古自動車の販売および買取（事業内容）</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>32名</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/company/</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>株式会社NIIZAWA</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>広島県、山口県</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>広島県廿日市市大野原1丁目2-20</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8103</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8104</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keimarket.k
 https://www.facebook.com/share/1AhR49eysR
 https://youtube.com/@keimarket398</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>95名（パート含む）</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/company/
 https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>株式会社Y's GARAGE</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>京都府、鳥取県、島根県</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>京都府宇治市槇島町三十五38-1</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0774-25-5557</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 桐畑勇志</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>158名（アルバイト含む、令和8年10月）</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/company/</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>株式会社横浜ユーポス</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>栃木県、神奈川県</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/kouhoku
@@ -2321,12 +2454,12 @@
 https://www.u-pohs.co.jp/tsuzuki</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
         </is>
@@ -2343,7 +2476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2506,7 +2639,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2526,7 +2659,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -2556,7 +2689,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2592,7 +2725,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2602,7 +2735,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2612,17 +2745,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>徳島県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2632,17 +2765,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>愛媛県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>高知県</t>
+          <t>徳島県</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2652,127 +2785,127 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>高知県</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>長崎県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>熊本県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>長崎県</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>鹿児島県</t>
+          <t>熊本県</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>大分県</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>鹿児島県</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>沖縄県</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B39" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>本社所在地の都道府県別の社数</t>
         </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>都道府県</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>千葉県</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2782,17 +2915,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2802,141 +2935,161 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B52" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>店舗数の分布</t>
         </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>5〜9店舗</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10〜19店舗</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>9</v>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20〜30店舗</t>
+          <t>5〜9店舗</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>10〜19店舗</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20〜30店舗</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="B59" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>確度別の社数</t>
         </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>確度</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>21</v>
+          <t>確度</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2950,7 +3103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3424,7 +3577,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>株式会社ダブルツリー</t>
+          <t>株式会社グローバンネット</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -3432,19 +3585,23 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
+          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://pa-cars.com/</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
@@ -3452,19 +3609,17 @@
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0288/
-https://www.applenet.co.jp/shop/0300/
-https://www.applenet.co.jp/shop/0309/</t>
+          <t>https://pa-cars.com/shopinfo.html</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3634,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビッグワン</t>
+          <t>株式会社ダブルツリー</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -3487,12 +3642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>販売店（千葉市内4店舗）</t>
+          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -3507,17 +3662,19 @@
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0288/
+https://www.applenet.co.jp/shop/0300/
+https://www.applenet.co.jp/shop/0309/</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3689,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミナミシマ自動車販売</t>
+          <t>株式会社ビッグワン</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -3540,12 +3697,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
+          <t>販売店（千葉市内4店舗）</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -3560,19 +3717,17 @@
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kashiba/
-https://www.u-pohs.co.jp/kashihara/
-https://www.u-pohs.co.jp/katuragi/</t>
+          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3742,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>株式会社沖縄ユーポス</t>
+          <t>株式会社ミナミシマ自動車販売</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -3595,12 +3750,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -3615,9 +3770,9 @@
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/misato/
-https://www.u-pohs.co.jp/naha-shintoshin
-https://www.u-pohs.co.jp/noborikawa/</t>
+          <t>https://www.u-pohs.co.jp/kashiba/
+https://www.u-pohs.co.jp/kashihara/
+https://www.u-pohs.co.jp/katuragi/</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -3642,7 +3797,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>株式会社鈴木モータース</t>
+          <t>株式会社ワークス</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -3650,12 +3805,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
+          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -3670,19 +3825,17 @@
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0065/
-https://www.applenet.co.jp/shop/0071/
-https://www.applenet.co.jp/shop/0080/</t>
+          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3697,39 +3850,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>株式会社沖縄ユーポス</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8844</t>
-        </is>
-      </c>
+          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.autogallery.co.jp/</t>
-        </is>
-      </c>
+      <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
@@ -3737,8 +3878,9 @@
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>https://www.u-pohs.co.jp/misato/
+https://www.u-pohs.co.jp/naha-shintoshin
+https://www.u-pohs.co.jp/noborikawa/</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -3748,7 +3890,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -3763,39 +3905,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>株式会社鈴木モータース</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
-        </is>
-      </c>
+          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.csauto.jp/</t>
-        </is>
-      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -3803,8 +3933,9 @@
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://www.applenet.co.jp/shop/0065/
+https://www.applenet.co.jp/shop/0071/
+https://www.applenet.co.jp/shop/0080/</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -3814,7 +3945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3960,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -3837,19 +3968,31 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.autogallery.co.jp/</t>
+        </is>
+      </c>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
@@ -3857,9 +4000,8 @@
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -3869,7 +4011,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
         </is>
       </c>
     </row>
@@ -3884,7 +4026,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -3892,29 +4034,29 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 上武英輝</t>
+          <t>代表取締役 河野修一</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/</t>
+          <t>https://www.csauto.jp/</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -3924,8 +4066,8 @@
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -3933,7 +4075,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -3946,7 +4092,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -3954,12 +4100,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -3974,9 +4120,9 @@
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -4001,7 +4147,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>株式会社カミタケモータース</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -4009,19 +4155,31 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>大阪府、奈良県、大分県</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>枚方本店、奈良店、大分店</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
@@ -4029,7 +4187,8 @@
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -4037,11 +4196,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス以外の事業は未確認。</t>
-        </is>
-      </c>
+      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -4054,7 +4209,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>株式会社シマダオート商事</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -4062,12 +4217,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -4082,9 +4237,9 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/</t>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -4104,12 +4259,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FC本部</t>
+          <t>4店舗以下</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーポス</t>
+          <t>株式会社フロンティアモータース</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -4117,35 +4272,19 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>大阪府、兵庫県</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>06-6532-6532</t>
-        </is>
-      </c>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 柏原隆宏</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-pohs.co.jp/</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
@@ -4153,18 +4292,17 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/about/company_info
-https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
+          <t>ユーポス以外の事業は未確認。</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4317,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>株式会社ベネフィット</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -4187,12 +4325,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -4207,9 +4345,9 @@
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -4229,12 +4367,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>4店舗以下</t>
+          <t>FC本部</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社ユーポス</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -4242,19 +4380,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>06-6532-6532</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 柏原隆宏</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
@@ -4262,19 +4416,18 @@
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/</t>
+          <t>https://www.u-pohs.co.jp/about/company_info
+https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
         </is>
       </c>
     </row>
@@ -4289,20 +4442,20 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎有限会社</t>
+          <t>株式会社リフトオフ</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>宮崎県</t>
+          <t>茨城県、千葉県、東京都</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -4317,8 +4470,9 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0056/
-https://www.applenet.co.jp/shop/0149/</t>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -4328,7 +4482,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4343,20 +4497,20 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>タイガー石油株式会社</t>
+          <t>株式会社中州自動車</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -4371,7 +4525,9 @@
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -4381,7 +4537,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4552,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>大谷自動車株式会社</t>
+          <t>アップル宮崎有限会社</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -4404,47 +4560,28 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>大阪府、和歌山県</t>
+          <t>宮崎県</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>大阪本店、和歌山店</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>大阪府泉佐野市長滝753</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>072-465-0492</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>072-465-3109</t>
-        </is>
-      </c>
+          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.otani-j.co.jp/</t>
-        </is>
-      </c>
+      <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>81名</t>
-        </is>
-      </c>
+      <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>https://www.otani-j.co.jp/company</t>
+          <t>https://www.applenet.co.jp/shop/0056/
+https://www.applenet.co.jp/shop/0149/</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -4452,7 +4589,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -4465,7 +4606,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>平岩石油販売株式会社</t>
+          <t>タイガー石油株式会社</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -4473,12 +4614,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>アップル練馬関町店、アップル板橋環8店</t>
+          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -4493,8 +4634,7 @@
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0175/
-https://www.applenet.co.jp/shop/0247/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -4504,7 +4644,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4659,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>株式会社B&amp;F</t>
+          <t>大谷自動車株式会社</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
@@ -4527,28 +4667,47 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>大阪府、和歌山県</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>アップル古河4号店、アップル守谷店</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t>大阪本店、和歌山店</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>大阪府泉佐野市長滝753</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>072-465-0492</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>072-465-3109</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.otani-j.co.jp/</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0140/
-https://www.applenet.co.jp/shop/0146/</t>
+          <t>https://www.otani-j.co.jp/company</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -4556,11 +4715,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="S27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -4573,7 +4728,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>株式会社NEXTモビィ</t>
+          <t>平岩石油販売株式会社</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -4581,12 +4736,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
+          <t>アップル練馬関町店、アップル板橋環8店</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -4601,8 +4756,8 @@
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukuoka-inter
-https://www.u-pohs.co.jp/kokurahigashi-inter</t>
+          <t>https://www.applenet.co.jp/shop/0175/
+https://www.applenet.co.jp/shop/0247/</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -4612,7 +4767,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4782,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>株式会社PlusOne</t>
+          <t>株式会社B&amp;F</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -4635,12 +4790,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>アップル安城南店、アップル弥富1号線店</t>
+          <t>アップル古河4号店、アップル守谷店</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -4655,8 +4810,8 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0129/
-https://www.applenet.co.jp/shop/0219/</t>
+          <t>https://www.applenet.co.jp/shop/0140/
+https://www.applenet.co.jp/shop/0146/</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -4681,7 +4836,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>株式会社SHIMAカーライフコネクテッド</t>
+          <t>株式会社NEXTモビィ</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -4689,12 +4844,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>アップル金沢店、アップル高岡店</t>
+          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -4709,8 +4864,8 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0313/
-https://www.applenet.co.jp/shop/0339/</t>
+          <t>https://www.u-pohs.co.jp/fukuoka-inter
+https://www.u-pohs.co.jp/kokurahigashi-inter</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
@@ -4720,7 +4875,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4890,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>株式会社WinWinサービス</t>
+          <t>株式会社PlusOne</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -4743,12 +4898,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>アップル盛岡盛南店、アップル盛岡北店</t>
+          <t>アップル安城南店、アップル弥富1号線店</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -4763,8 +4918,8 @@
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0117/
-https://www.applenet.co.jp/shop/0137/</t>
+          <t>https://www.applenet.co.jp/shop/0129/
+https://www.applenet.co.jp/shop/0219/</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -4789,7 +4944,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>株式会社イトー</t>
+          <t>株式会社SHIMAカーライフコネクテッド</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -4797,12 +4952,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>アップル岸和田店、アップル河内長野中央店</t>
+          <t>アップル金沢店、アップル高岡店</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -4817,8 +4972,8 @@
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0258/
-https://www.applenet.co.jp/shop/0278/</t>
+          <t>https://www.applenet.co.jp/shop/0313/
+https://www.applenet.co.jp/shop/0339/</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -4828,7 +4983,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>アップル以外の店舗は未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4998,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>株式会社インデックス</t>
+          <t>株式会社WinWinサービス</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -4851,12 +5006,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
+          <t>アップル盛岡盛南店、アップル盛岡北店</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -4871,8 +5026,8 @@
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0018/
-https://www.applenet.co.jp/shop/0029/</t>
+          <t>https://www.applenet.co.jp/shop/0117/
+https://www.applenet.co.jp/shop/0137/</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -4897,7 +5052,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>株式会社イーグルオートサービス</t>
+          <t>株式会社イトー</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -4905,12 +5060,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
+          <t>アップル岸和田店、アップル河内長野中央店</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -4925,8 +5080,8 @@
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0032/
-https://www.applenet.co.jp/shop/0063/</t>
+          <t>https://www.applenet.co.jp/shop/0258/
+https://www.applenet.co.jp/shop/0278/</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -4936,7 +5091,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップル以外の店舗は未確認。</t>
         </is>
       </c>
     </row>
@@ -4951,7 +5106,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>株式会社エムエフノースジャパン</t>
+          <t>株式会社インデックス</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -4959,12 +5114,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -4979,8 +5134,8 @@
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0035/
-https://www.applenet.co.jp/shop/0043/</t>
+          <t>https://www.applenet.co.jp/shop/0018/
+https://www.applenet.co.jp/shop/0029/</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -5005,7 +5160,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>株式会社オカモト</t>
+          <t>株式会社イーグルオートサービス</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -5013,12 +5168,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>アップル西帯広店、アップル帯広店</t>
+          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -5033,8 +5188,8 @@
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0307/
-https://www.applenet.co.jp/shop/0334/</t>
+          <t>https://www.applenet.co.jp/shop/0032/
+https://www.applenet.co.jp/shop/0063/</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -5059,7 +5214,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>株式会社オリンピアオート</t>
+          <t>株式会社エムエフノースジャパン</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -5067,12 +5222,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>アップルひたちなか店、アップル那珂中央店</t>
+          <t>、</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -5087,8 +5242,8 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0208/
-https://www.applenet.co.jp/shop/0280/</t>
+          <t>https://www.applenet.co.jp/shop/0035/
+https://www.applenet.co.jp/shop/0043/</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -5113,7 +5268,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートグローリー</t>
+          <t>株式会社オカモト</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -5121,12 +5276,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福重店、ユーポス直方店</t>
+          <t>アップル西帯広店、アップル帯広店</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -5141,8 +5296,8 @@
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukushige
-https://www.u-pohs.co.jp/nogata</t>
+          <t>https://www.applenet.co.jp/shop/0307/
+https://www.applenet.co.jp/shop/0334/</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5152,7 +5307,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5322,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>株式会社クインオート</t>
+          <t>株式会社オリンピアオート</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -5175,12 +5330,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>京都府、兵庫県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>ユーポス亀岡店、ユーポス三田店</t>
+          <t>アップルひたちなか店、アップル那珂中央店</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -5195,8 +5350,8 @@
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kameoka
-https://www.u-pohs.co.jp/sanda/</t>
+          <t>https://www.applenet.co.jp/shop/0208/
+https://www.applenet.co.jp/shop/0280/</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -5206,7 +5361,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5376,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>株式会社サコダ車輛</t>
+          <t>株式会社オートグローリー</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -5229,12 +5384,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>アップル海田店、アップル東広島店</t>
+          <t>ユーポス福重店、ユーポス直方店</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -5249,8 +5404,8 @@
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0297/
-https://www.applenet.co.jp/shop/0298/</t>
+          <t>https://www.u-pohs.co.jp/fukushige
+https://www.u-pohs.co.jp/nogata</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -5260,7 +5415,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5430,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>株式会社シブヤエネックスホールディングス</t>
+          <t>株式会社クインオート</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -5283,12 +5438,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>京都府、兵庫県</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>アップル相模原城山店、アップル大井松田インター店</t>
+          <t>ユーポス亀岡店、ユーポス三田店</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -5303,8 +5458,8 @@
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0266/
-https://www.applenet.co.jp/shop/0292/</t>
+          <t>https://www.u-pohs.co.jp/kameoka
+https://www.u-pohs.co.jp/sanda/</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -5314,7 +5469,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5484,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>株式会社スズキアリーナ瑞穂</t>
+          <t>株式会社サコダ車輛</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -5337,12 +5492,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>アップル青梅店、アップル西東京店</t>
+          <t>アップル海田店、アップル東広島店</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -5357,8 +5512,8 @@
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0057/
-https://www.applenet.co.jp/shop/0100/</t>
+          <t>https://www.applenet.co.jp/shop/0297/
+https://www.applenet.co.jp/shop/0298/</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
@@ -5383,7 +5538,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>株式会社トップワン</t>
+          <t>株式会社シブヤエネックスホールディングス</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -5391,12 +5546,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>アップル豊田梅坪店、アップル豊田南店</t>
+          <t>アップル相模原城山店、アップル大井松田インター店</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -5411,8 +5566,8 @@
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0075/
-https://www.applenet.co.jp/shop/0126/</t>
+          <t>https://www.applenet.co.jp/shop/0266/
+https://www.applenet.co.jp/shop/0292/</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -5437,7 +5592,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社スズキアリーナ瑞穂</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -5445,12 +5600,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>アップル大和店、アップル相模原店</t>
+          <t>アップル青梅店、アップル西東京店</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -5465,8 +5620,8 @@
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0306/
-https://www.applenet.co.jp/shop/0340/</t>
+          <t>https://www.applenet.co.jp/shop/0057/
+https://www.applenet.co.jp/shop/0100/</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -5491,7 +5646,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビーインプレスト</t>
+          <t>株式会社トップワン</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -5499,12 +5654,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>アップル宇都宮北店、アップル大田原店</t>
+          <t>アップル豊田梅坪店、アップル豊田南店</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -5519,8 +5674,8 @@
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0211/
-https://www.applenet.co.jp/shop/0303/</t>
+          <t>https://www.applenet.co.jp/shop/0075/
+https://www.applenet.co.jp/shop/0126/</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -5545,7 +5700,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミヤチ</t>
+          <t>株式会社トータス</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -5553,12 +5708,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>アップル岐阜長良店、アップル関店</t>
+          <t>アップル大和店、アップル相模原店</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -5573,8 +5728,8 @@
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0101/
-https://www.applenet.co.jp/shop/0155/</t>
+          <t>https://www.applenet.co.jp/shop/0306/
+https://www.applenet.co.jp/shop/0340/</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -5599,7 +5754,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>株式会社メーカーズ</t>
+          <t>株式会社ビーインプレスト</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -5607,12 +5762,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>アップル福岡東店、アップル福岡八幡店</t>
+          <t>アップル宇都宮北店、アップル大田原店</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -5627,8 +5782,8 @@
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0238/
-https://www.applenet.co.jp/shop/0255/</t>
+          <t>https://www.applenet.co.jp/shop/0211/
+https://www.applenet.co.jp/shop/0303/</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -5653,7 +5808,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>株式会社湯浅</t>
+          <t>株式会社ファミリー</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -5661,12 +5816,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>アップル白井店、アップル松戸本店</t>
+          <t>ファミリー可児店、ファミリー各務原店</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -5681,18 +5836,17 @@
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0287/
-https://www.applenet.co.jp/shop/0293/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5861,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>株式会社関西オート</t>
+          <t>株式会社ミヤチ</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -5715,27 +5869,19 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>八尾店、平野店</t>
+          <t>アップル岐阜長良店、アップル関店</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 大川純平</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kansai-auto.jp/</t>
-        </is>
-      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
@@ -5743,7 +5889,8 @@
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>https://www.kansai-auto.jp/company/outline/</t>
+          <t>https://www.applenet.co.jp/shop/0101/
+https://www.applenet.co.jp/shop/0155/</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -5751,7 +5898,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -5764,20 +5915,20 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Re-BOOT株式会社</t>
+          <t>株式会社メーカーズ</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>アップル大阪平野店</t>
+          <t>アップル福岡東店、アップル福岡八幡店</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -5792,7 +5943,8 @@
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0284/</t>
+          <t>https://www.applenet.co.jp/shop/0238/
+https://www.applenet.co.jp/shop/0255/</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -5800,7 +5952,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -5813,43 +5969,27 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>北摂オート株式会社</t>
+          <t>株式会社湯浅</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>大阪府箕面市桜井2-16-17</t>
-        </is>
-      </c>
+          <t>アップル白井店、アップル松戸本店</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>072-723-1102</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 喜多克之</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>https://hokusetu-auto.com/</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
@@ -5857,7 +5997,8 @@
       <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>https://hokusetu-auto.com/company.php</t>
+          <t>https://www.applenet.co.jp/shop/0287/
+https://www.applenet.co.jp/shop/0293/</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
@@ -5865,7 +6006,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -5878,11 +6023,11 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>有限会社タイヨウ</t>
+          <t>株式会社関西オート</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -5891,14 +6036,22 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>ユーポス富田林店</t>
+          <t>八尾店、平野店</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 大川純平</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kansai-auto.jp/</t>
+        </is>
+      </c>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
@@ -5906,7 +6059,7 @@
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.kansai-auto.jp/company/outline/</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
@@ -5914,11 +6067,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -5931,7 +6080,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>株式会社We Car CORE</t>
+          <t>Re-BOOT株式会社</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -5944,7 +6093,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>ユーポス貝塚店</t>
+          <t>アップル大阪平野店</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -5959,7 +6108,7 @@
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0284/</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -5967,11 +6116,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -5984,7 +6129,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>株式会社cantera</t>
+          <t>北摂オート株式会社</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -5997,14 +6142,30 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環四條畷店</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>大阪府箕面市桜井2-16-17</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>072-723-1102</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 喜多克之</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>https://hokusetu-auto.com/</t>
+        </is>
+      </c>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
@@ -6012,7 +6173,7 @@
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://hokusetu-auto.com/company.php</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -6020,11 +6181,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -6037,7 +6194,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>株式会社プロンザ</t>
+          <t>有限会社タイヨウ</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -6050,7 +6207,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>ユーポス枚方店</t>
+          <t>ユーポス富田林店</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -6090,7 +6247,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>株式会社ポロ</t>
+          <t>株式会社We Car CORE</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -6103,30 +6260,14 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>大阪府高槻市富田町6丁目15-13</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>072-694-6641</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>072-694-9913</t>
-        </is>
-      </c>
+          <t>ユーポス貝塚店</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.polojp.com/</t>
-        </is>
-      </c>
+      <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
@@ -6134,7 +6275,7 @@
       <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>https://www.polojp.com/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
@@ -6142,7 +6283,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -6155,7 +6300,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>豊栄モータース</t>
+          <t>株式会社cantera</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -6168,7 +6313,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>ユーポス寝屋川店</t>
+          <t>ユーポス外環四條畷店</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -6193,6 +6338,177 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>株式会社プロンザ</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス枚方店</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ポロ</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>大阪府高槻市富田町6丁目15-13</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>072-694-6641</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>072-694-9913</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>豊栄モータース</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス寝屋川店</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
           <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。（法人格の表示なし）</t>
         </is>
       </c>
@@ -6208,7 +6524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6264,22 +6580,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>株式会社パッション（旧サンアイ自動車）</t>
+          <t>車のせんいち</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>軽届出済未使用車専門店。南大高・豊田・春日井（パッションプラス・4U）・土岐。2022年時点で4拠点</t>
+          <t>群馬（みどり・伊勢崎・桐生・太田・前橋）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>公式サイトが見つからず店舗数が確定できない（5店舗前後）</t>
+          <t>公式の店舗一覧が見つからない</t>
         </is>
       </c>
     </row>
@@ -6289,22 +6605,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>車のせんいち</t>
+          <t>株式会社くるまのハチオウジ</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>群馬（みどり・伊勢崎・桐生・太田・前橋）</t>
+          <t>八王子、グループ会社あり</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>公式の店舗一覧が見つからない</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -6314,22 +6630,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>株式会社グローバンネット（Pa!Cars・車検の速太郎）</t>
+          <t>エジソングループ</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>川越・所沢、親会社ウェルビングループ</t>
+          <t>岐阜市、新車・登録済未使用車専門店</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>運営会社・店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -6339,22 +6655,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファミリー</t>
+          <t>プラスパージャパン（NEW CARS）</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>岐阜、売上高107億円、届出済未使用車（ファミリー可児店ほか）</t>
+          <t>あきる野</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>公式サイト・店舗数未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -6364,22 +6680,18 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>株式会社くるまのハチオウジ</t>
+          <t>フレックス・ドリーム株式会社</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>八王子、グループ会社あり</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>東京都</t>
-        </is>
-      </c>
+          <t>ランクル・ハイエース専門。調布・仙台東・小牧ほか（検索結果）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>公式サイトが503で取得不可</t>
         </is>
       </c>
     </row>
@@ -6389,22 +6701,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>エジソングループ</t>
+          <t>株式会社アクティブコレクション</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>岐阜市、新車・登録済未使用車専門店</t>
+          <t>リバティの子会社。横浜・大和、グループ総在庫4,000台</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>運営会社・店舗数未確認</t>
+          <t>店舗数未確認。リバティとの関係（子会社）をどう扱うか要判断</t>
         </is>
       </c>
     </row>
@@ -6414,22 +6726,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>プラスパージャパン（NEW CARS）</t>
+          <t>株式会社クレタ（北海道軽パーク）</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>あきる野</t>
+          <t>苫小牧</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -6439,18 +6751,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>フレックス・ドリーム株式会社</t>
+          <t>軽プラザサンライズ</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ランクル・ハイエース専門、10店舗以上の可能性</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>弘前・八戸</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>公式サイトが503で取得不可</t>
+          <t>未確認（2店舗の可能性）</t>
         </is>
       </c>
     </row>
@@ -6460,22 +6776,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>株式会社アクティブコレクション</t>
+          <t>良質車専門店ネクスト</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>リバティの子会社。横浜・大和、グループ総在庫4,000台</t>
+          <t>会津若松・いわき・白河</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認。リバティとの関係（子会社）をどう扱うか要判断</t>
+          <t>運営会社未確認</t>
         </is>
       </c>
     </row>
@@ -6485,17 +6801,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>株式会社クレタ（北海道軽パーク）</t>
+          <t>興和自動車販売（KOWA飯田）</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>苫小牧</t>
+          <t>南信地区</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -6510,22 +6826,18 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>軽プラザサンライズ</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>弘前・八戸</t>
-        </is>
-      </c>
+          <t>株式会社佐野自動車商会（トラスト新潟）</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>未確認（2店舗の可能性）</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -6535,22 +6847,18 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>良質車専門店ネクスト</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>会津若松・いわき・白河</t>
-        </is>
-      </c>
+          <t>株式会社光野自動車（ヒカリノ）</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>運営会社未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -6560,17 +6868,13 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>興和自動車販売（KOWA飯田）</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>南信地区</t>
-        </is>
-      </c>
+          <t>株式会社Smile Carz</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6585,15 +6889,15 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>株式会社佐野自動車商会（トラスト新潟）</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>新潟県</t>
-        </is>
-      </c>
+          <t>株式会社BIG BRIDGE／株式会社five star</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>自社ローン</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
@@ -6606,22 +6910,14 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>株式会社Y'S GARAGE（K-smile）</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>京都2・出雲1・鳥取1（2022年）</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>京都府</t>
-        </is>
-      </c>
+          <t>株式会社ヤマト（島根）／共盛自動車グループ（広島）／株式会社日本カードック（尼崎）／株式会社グランドエンタープライズ（京都）</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>現在の店舗数未確認（4店舗前後）</t>
+          <t>業態・店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -6631,15 +6927,15 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>株式会社光野自動車（ヒカリノ）</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
+          <t>株式会社ルートシックス</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー専門、水戸・埼玉</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
@@ -6652,18 +6948,18 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>株式会社Smile Carz</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>山口県</t>
-        </is>
-      </c>
+          <t>株式会社タックス横浜／株式会社タックス宮城野／株式会社キリン自動車（ONIX）</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>FC加盟店</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>タックス・オニキス本部の店舗一覧が取得できず店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -6673,117 +6969,16 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ワークス／白沢自動車／れもんオート／ABCcars／軽マート</t>
+          <t>株式会社OSG（ミニバン専門店OSG）／OSINC.／株式会社N.T ART</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店グループ（グーネットのグループ店一覧に掲載）</t>
+          <t>大阪</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>株式会社BIG BRIDGE／株式会社five star</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>自社ローン</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ヤマト（島根）／共盛自動車グループ（広島）／株式会社日本カードック（尼崎）／株式会社グランドエンタープライズ（京都）</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>業態・店舗数未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ルートシックス</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>キャンピングカー専門、水戸・埼玉</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>株式会社タックス横浜／株式会社タックス宮城野／株式会社キリン自動車（ONIX）</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>FC加盟店</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>タックス・オニキス本部の店舗一覧が取得できず店舗数未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>株式会社OSG（ミニバン専門店OSG）／OSINC.／株式会社N.T ART</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>大阪</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>店舗数未確認（1〜2店舗の可能性）</t>
         </is>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -965,179 +965,229 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>株式会社KSファクトリー</t>
+          <t>株式会社ナオイオート</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>宮城県、茨城県、栃木県、群馬県、千葉県、愛知県、福岡県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>仙台店、ランクル宇都宮店、アップル宇都宮外環若草店、前橋インター店、アップル前橋店、アップルつくば学園店、つくば店、アップル土浦学園東大通り店、千葉北店、ハイエース名古屋店、ハイエース福岡店、アップル福岡南バイパス店、福岡須恵インター店、アップル福岡久留米店</t>
+          <t>牛久店、戸頭店、守谷店、つくば吉瀬店、下館店、下妻店、6号取手店、ひたちなか店、水戸吉田店、土浦中貫店、サンキュッパ下妻店、龍ヶ岡店、坂東店、ラビットイオンタウン水戸南店、ラビットつくば吉瀬、GarageTricolore（ガレージトリコロール）</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>千葉県佐倉市ユーカリが丘7-21-3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>茨城県取手市桑原680-1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>029-874-2233</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>043-376-9195</t>
+          <t>029-874-2363</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>代表取締役社長 遠藤和広</t>
+          <t>代表取締役 直井清正</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://ksfactory.jp/</t>
+          <t>https://sale.naoiauto.jp/</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>https://ksfactory.jp/contact/</t>
+          <t>https://sale.naoiauto.jp/contact/</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/naoiauto/
+https://www.instagram.com/naoiauto_car/
+https://www.youtube.com/channel/UCqkEz6s5HrxxnCPQPsME1FA</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>354名</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>https://sale.naoiauto.jp/company/
+https://sale.naoiauto.jp/store/</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>軽未使用車・39.8万円車専門店。公式の店舗一覧16件で、ラビット（買取FC）2店舗とGarageTricolore（業態未確認）を含む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>株式会社フジカーズジャパン</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>北海道、宮城県、茨城県、埼玉県、千葉県、神奈川県、新潟県、石川県、岐阜県、静岡県、兵庫県、広島県、香川県、佐賀県</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>札幌店、仙台店、新潟店、茨城店、つくば店、柏店、狭山店、寄居店、厚木店、石川店、浜松店、岐阜店、神戸西宮店、広島店、高松店、鳥栖店</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>東京都江戸川区西小岩2丁目11番6号</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0120-007-560</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.campnofuji.jp/</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>車両全般の買取事業・買取専門店「カープライスセンター」あり</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>220名</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.campnofuji.jp/company/
+https://www.campnofuji.jp/shop/</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>ブランドは「キャンピングカーのフジ」。キャンピングカーの新車・中古車の販売と買取が中心で、一般の中古車販売店とは業態がやや異なる（対象に含めるか要判断）。店舗数はキャンピングカー販売店16店舗で、買取専門店カープライスセンターは含めていない。店舗名はURLから付けた。電話はフリーダイヤル。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>株式会社KSファクトリー</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、茨城県、栃木県、群馬県、千葉県、愛知県、福岡県</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>仙台店、ランクル宇都宮店、アップル宇都宮外環若草店、前橋インター店、アップル前橋店、アップルつくば学園店、つくば店、アップル土浦学園東大通り店、千葉北店、ハイエース名古屋店、ハイエース福岡店、アップル福岡南バイパス店、福岡須恵インター店、アップル福岡久留米店</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>千葉県佐倉市ユーカリが丘7-21-3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>043-376-9195</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 遠藤和広</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>https://ksfactory.jp/</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>https://ksfactory.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/ksfactory_carshop/
 https://www.youtube.com/@KS_factory
 https://www.tiktok.com/@ksfactory4wd</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>77名</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>https://ksfactory.jp/company/
 https://ksfactory.jp/shop/head-office/
 https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>ランクル・ハイエース専門店とアップル加盟店を運営。公式サイトの店舗一覧13件に、アップル本部サイトでKSファクトリー運営と表示される「アップル福岡久留米店」（公式サイトの一覧には無し）を加えて14店舗。本社ページの電話番号欄は空欄。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>株式会社アタックス</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県、愛知県、三重県</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>アップル津島中央道店、アップル厚木・北129号店、アップル富田302号店、アップル小田原飯泉店、アップル昭和橋通店、アップル桑名七和店、アップル中村畑江通店、アップル稲沢店、アップル西・康生通店、アップル南23号店、アップル桑名大桑店、アップル黒川北41号店</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0008/
-https://www.applenet.co.jp/shop/0021/
-https://www.applenet.co.jp/shop/0022/</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ジェイ・ピー</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>宮城県、福島県、栃木県、群馬県、埼玉県</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>アップル坂戸鶴ヶ島インター店、アップル太田店、アップル川越16号店、アップル郡山インター店、アップル深谷17号店、アップル西那須野店、アップル朝霞店、アップル仙台六丁目店、アップル東松山店、アップル白河店、アップル所沢店、アップル鴻巣店</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0015/
-https://www.applenet.co.jp/shop/0037/
-https://www.applenet.co.jp/shop/0044/</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル坂戸鶴ヶ島インター店）〒350-2211 埼玉県鶴ヶ島市脚折町5-4-13 TEL 049-279-3500 FAX 049-279-3501。</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1197,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>高橋自動車販売株式会社</t>
+          <t>株式会社アタックス</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1155,12 +1205,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>東京都、神奈川県、愛知県</t>
+          <t>神奈川県、愛知県、三重県</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>アップル江田駅前店、アップル江戸川環七店、アップル豊橋佐藤店、アップル248岡崎店、アップル平塚田村店、アップル中山宮の下店、アップル町田南店、アップル岡崎六ッ美店、アップル東戸塚店、アップル蒲郡店、アップル豊川インター店、アップル岡崎緑丘店</t>
+          <t>アップル津島中央道店、アップル厚木・北129号店、アップル富田302号店、アップル小田原飯泉店、アップル昭和橋通店、アップル桑名七和店、アップル中村畑江通店、アップル稲沢店、アップル西・康生通店、アップル南23号店、アップル桑名大桑店、アップル黒川北41号店</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1176,180 +1226,121 @@
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0008/
+https://www.applenet.co.jp/shop/0021/
+https://www.applenet.co.jp/shop/0022/</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ジェイ・ピー</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、福島県、栃木県、群馬県、埼玉県</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>アップル坂戸鶴ヶ島インター店、アップル太田店、アップル川越16号店、アップル郡山インター店、アップル深谷17号店、アップル西那須野店、アップル朝霞店、アップル仙台六丁目店、アップル東松山店、アップル白河店、アップル所沢店、アップル鴻巣店</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0015/
+https://www.applenet.co.jp/shop/0037/
+https://www.applenet.co.jp/shop/0044/</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル坂戸鶴ヶ島インター店）〒350-2211 埼玉県鶴ヶ島市脚折町5-4-13 TEL 049-279-3500 FAX 049-279-3501。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>高橋自動車販売株式会社</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>東京都、神奈川県、愛知県</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>アップル江田駅前店、アップル江戸川環七店、アップル豊橋佐藤店、アップル248岡崎店、アップル平塚田村店、アップル中山宮の下店、アップル町田南店、アップル岡崎六ッ美店、アップル東戸塚店、アップル蒲郡店、アップル豊川インター店、アップル岡崎緑丘店</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0013/
 https://www.applenet.co.jp/shop/0014/
 https://www.applenet.co.jp/shop/0024/</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。軽四専門「メガタウン」（豊田市）も運営しており、実際の店舗数はこれより多い可能性。 参考：店舗の連絡先（アップル江田駅前店）〒225-0013 神奈川県横浜市青葉区荏田町1236-7東急江田駅前ドエリング1F TEL 045-912-7560 FAX 045-912-7566。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>株式会社軽自動車館</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>北海道、宮城県</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>札幌本店、札幌東店、新さっぽろ店、札幌清田店、北見店、旭川店、函館店、苫小牧店、帯広店、釧路店、せんだい店</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>北海道札幌市中央区北5条西6丁目2-2</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>011-200-0312</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>011-200-0357</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 阿部章一</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>https://keijidousyakan.com/</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>https://keijidousyakan.com/contact/（現在お問い合わせ見合わせ中の表示あり）</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCtYVtXtEHCIxOCia6QF0nBw</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>自動車の買取（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>117名（2026年1月）</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>https://keijidousyakan.com/about/company/
-https://keijidousyakan.com/shops/</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>店舗名は公式の店舗ページから。札幌本店と札幌東店はURL（sapporo / satsuhigashi）から推定した店舗名。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ジョブカーズ</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>大阪府</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>ジョブカーズ本店、南港店、枚方東店、枚方南店、枚方北店、枚方インポート店、八尾店、守口店、COOL店、バイパス店</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市茄子作2-33-25</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>072-852-8500</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>072-852-8501</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>吉村浩二</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/contact/</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>70名</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/company/</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>同じ名前の別会社に注意：jobcars.jp は札幌の「ジョブカーズ株式会社」で別会社。枚方の会社の公式サイトは jobcars.net。枚方北店は大型トラック・バス、COOL店とバイパス店は会社概要に住所の記載がない。</t>
         </is>
       </c>
     </row>
@@ -1359,380 +1350,466 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>株式会社シースペース</t>
+          <t>株式会社メーカーズ</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>京都府、大阪府、兵庫県</t>
+          <t>福岡県、佐賀県</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
+          <t>ケイカフェ おおのじょう店、ケイカフェ しんぐう店、ケイカフェ こくらみなみ店、ケイカフェ くるめ店、ケイカフェ ちくしの店、ケイカフェ いいづか店、ケイカフェ やはた店、ケイカフェ ふくおかにし店、ケイカフェ とす店、アップル福岡東店、アップル福岡八幡店</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>大阪府柏原市国分市場2丁目13番1号</t>
+          <t>福岡県福岡市西区石丸4丁目5-53</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>072-978-1263</t>
+          <t>092-753-6611</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>072-978-1283</t>
+          <t>092-753-6622</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>代表取締役社長 平松宗彦</t>
+          <t>代表取締役社長 白井剛</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/</t>
+          <t>https://www.k-cafe.com/</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/contact/</t>
+          <t>https://www.k-cafe.com/contact/</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://twitter.com/C_SPACE_U_POHS</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス事業（車買取）</t>
-        </is>
-      </c>
+          <t>https://twitter.com/kcafe_official
+https://www.facebook.com/kcarandcafe
+https://www.instagram.com/kcafe_car_fukuoka/
+https://www.tiktok.com/@k_cafe.fukuoka?lang=ja-JP
+https://www.youtube.com/@kcafe_fukuoka/videos</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.k-cafe.com/company/
+https://www.k-cafe.com/
+https://www.applenet.co.jp/shop/</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>軽自動車専門店ケイカフェ9店舗（公式サイトの店舗情報）と、アップル加盟店2店舗（本部サイトで運営会社を確認）の合計。ONIXフランチャイズにも加盟（沿革）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>株式会社軽自動車館</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>北海道、宮城県</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>札幌本店、札幌東店、新さっぽろ店、札幌清田店、北見店、旭川店、函館店、苫小牧店、帯広店、釧路店、せんだい店</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>北海道札幌市中央区北5条西6丁目2-2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>011-200-0312</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>011-200-0357</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 阿部章一</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>https://keijidousyakan.com/</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>https://keijidousyakan.com/contact/（現在お問い合わせ見合わせ中の表示あり）</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCtYVtXtEHCIxOCia6QF0nBw</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>自動車の買取（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>117名（2026年1月）</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>https://keijidousyakan.com/about/company/
+https://keijidousyakan.com/shops/</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>店舗名は公式の店舗ページから。札幌本店と札幌東店はURL（sapporo / satsuhigashi）から推定した店舗名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>日免オートシステム株式会社</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>美使用軽専門店 江別店、美使用軽専門店 静内店（新ひだか）、美使用軽専門店 小樽店、美使用軽専門店 旭川店、美使用軽専門店 十勝音更店、美使用軽専門店 イオンスーパーセンター三笠店、美使用軽専門店 スーパーアークス新琴似店、カーセブン札幌北店、カーセブン北見店、カーセブン十勝音更店</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>北海道札幌市北区東茨戸1条1丁目8番5号</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>011-774-3111</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>011-775-8906</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 安部直人</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nichimen-g.co.jp/</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nichimen-g.co.jp/company/contact/</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nichimen_mishiyou/
+https://www.youtube.com/channel/UC-iuDCLbQ6px8P3WISQrLdg</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>ニチメン買取（買取・査定）あり</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>210名（グループ全体・パート含む）</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nichimen-g.co.jp/company/
+https://www.nichimen-g.co.jp/company/stores/
+https://www.nichimen-g.co.jp/mishiyou/</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>ニチメングループ。会社概要の「総店舗数31店舗（北海道内グループ全体）」には、スズキ販売店・レンタカー・整備工場・板金・建機なども含まれる。中古車の販売・買取の店舗として、美使用軽専門店7店舗とカーセブン加盟店3店舗を数えた。新琴似本店・札幌本店の位置づけは未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ジョブカーズ</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>ジョブカーズ本店、南港店、枚方東店、枚方南店、枚方北店、枚方インポート店、八尾店、守口店、COOL店、バイパス店</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市茄子作2-33-25</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>072-852-8500</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>072-852-8501</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>吉村浩二</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>https://jobcars.net/</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://jobcars.net/contact/</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>70名</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>https://jobcars.net/company/</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>同じ名前の別会社に注意：jobcars.jp は札幌の「ジョブカーズ株式会社」で別会社。枚方の会社の公式サイトは jobcars.net。枚方北店は大型トラック・バス、COOL店とバイパス店は会社概要に住所の記載がない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>株式会社川内自動車</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>https://k-bacca.com/</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/k_bacca_kawauchi/</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>https://k-bacca.com/contents/store/index.html
+https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>株式会社シースペース</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>京都府、大阪府、兵庫県</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>大阪府柏原市国分市場2丁目13番1号</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1263</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1283</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 平松宗彦</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/C_SPACE_U_POHS</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス事業（車買取）</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>https://www.c-space.co.jp/company/
 https://www.c-space.co.jp/shop/
 https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>会社概要に「ユーポス（関西にて現在8店舗）」とある。ユーポス本部のサイトでシースペース運営と表示されるのは7店舗で、久御山店は表示されていない。本社のC-SPACE.（中古車販売）を1店舗として数え、合計9店舗。ほかにニコニコレンタカー5店舗とコバック1店舗（いずれも対象外）を運営。X(Twitter)のURLは検索結果から取得。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>株式会社リトラス</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 津田猛</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.retrus.co.jp/</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.retrus.co.jp/about/office.asp
-https://www.retrus.co.jp/about/</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>株式会社九州ユーポス</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/hikarinomori/
-https://www.u-pohs.co.jp/kagoshima
-https://www.u-pohs.co.jp/kumamotominami</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>株式会社原ホンダ</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>長野県</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0031/
-https://www.applenet.co.jp/shop/0033/
-https://www.applenet.co.jp/shop/0042/</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>株式会社TRUCK-ONE</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>山口県下松市生野屋南3-3-40</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-1100</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-5660</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.truck-one.com/</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/truckone_official/</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>買取専用窓口あり（0120-751-519）</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.truck-one.com/officelist/
-https://www.truck-one.com/company/</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>株式会社パッション</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>岐阜県、愛知県</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>愛知県春日井市味美町2丁目122番地</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>買取専門店ラビット勝川店を運営</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>217名（2025年12月）</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.1963passion.co.jp/company/outline/
-https://www.1963passion.co.jp/company/access/</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -1742,27 +1819,39 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>株式会社リトラス</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 津田猛</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.retrus.co.jp/</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
@@ -1770,20 +1859,18 @@
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0004/
-https://www.applenet.co.jp/shop/0007/
-https://www.applenet.co.jp/shop/0046/</t>
+          <t>https://www.retrus.co.jp/about/office.asp
+https://www.retrus.co.jp/about/</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
+          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
         </is>
       </c>
     </row>
@@ -1793,74 +1880,48 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヨシダオートサービス</t>
+          <t>株式会社九州ユーポス</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0301</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0302</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>吉田宜史</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/contact/</t>
-        </is>
-      </c>
+          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>218名（2025年1月）</t>
-        </is>
-      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/hikarinomori/
+https://www.u-pohs.co.jp/kagoshima
+https://www.u-pohs.co.jp/kumamotominami</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
         </is>
       </c>
     </row>
@@ -1870,27 +1931,23 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>株式会社原ホンダ</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
-        </is>
-      </c>
+          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1902,18 +1959,20 @@
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0031/
+https://www.applenet.co.jp/shop/0033/
+https://www.applenet.co.jp/shop/0042/</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
         </is>
       </c>
     </row>
@@ -1923,38 +1982,60 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>株式会社TRUCK-ONE</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
+          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>山口県下松市生野屋南3-3-40</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-1100</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-5660</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.truck-one.com/</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/truckone_official/</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>買取専用窓口あり（0120-751-519）</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/</t>
+          <t>https://www.truck-one.com/officelist/
+https://www.truck-one.com/company/</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -1964,7 +2045,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
+          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
         </is>
       </c>
     </row>
@@ -1974,45 +2055,62 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>松下モータース</t>
+          <t>株式会社パッション</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県、愛知県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
+          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>愛知県春日井市味美町2丁目122番地</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>買取専門店ラビット勝川店を運営</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>217名（2025年12月）</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://www.1963passion.co.jp/company/outline/
+https://www.1963passion.co.jp/company/access/</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
+          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -2022,55 +2120,38 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>株式会社アップルカーセールス</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0004/
+https://www.applenet.co.jp/shop/0007/
+https://www.applenet.co.jp/shop/0046/</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2080,7 +2161,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
         </is>
       </c>
     </row>
@@ -2090,48 +2171,74 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2248,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2149,15 +2256,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
+          <t>浜松市内6店舗</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2169,7 +2280,8 @@
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -2179,7 +2291,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2189,67 +2301,38 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>human joint株式会社</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>03-4446-7735</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>03-5422-8006</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 齊藤博行</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>https://cococar-hp.net/</t>
-        </is>
-      </c>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>中古自動車の販売および買取（事業内容）</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>32名</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/company/</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -2259,7 +2342,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
         </is>
       </c>
     </row>
@@ -2269,80 +2352,45 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>株式会社NIIZAWA</t>
+          <t>松下モータース</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>広島県、山口県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>広島県廿日市市大野原1丁目2-20</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>0829-30-8103</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0829-30-8104</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kei-market.co.jp/</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kei-market.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/keimarket.k
-https://www.facebook.com/share/1AhR49eysR
-https://youtube.com/@keimarket398</t>
-        </is>
-      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>95名（パート含む）</t>
-        </is>
-      </c>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>https://www.kei-market.co.jp/company/
-https://www.kei-market.co.jp/store/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
         </is>
       </c>
     </row>
@@ -2352,55 +2400,55 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>株式会社Y's GARAGE</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>京都府、鳥取県、島根県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>京都府宇治市槇島町三十五38-1</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>0774-25-5557</t>
-        </is>
-      </c>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 桐畑勇志</t>
+          <t>代表取締役 石戸宏樹</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://k-smile.jp/</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>158名（アルバイト含む、令和8年10月）</t>
+          <t>26名</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://k-smile.jp/company/</t>
+          <t>https://www.apple-car.jp/company</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -2410,7 +2458,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
         </is>
       </c>
     </row>
@@ -2420,20 +2468,20 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>株式会社横浜ユーポス</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>栃木県、神奈川県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
@@ -2448,18 +2496,480 @@
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ダブルツリー</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>岡山県、香川県</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店、軽自動車専門店 ハヤシ 高松店、軽自動車専門店 ハヤシ 丸亀店</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/
+https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
+https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）に加え、軽自動車専門店「くるまのハヤシ」（1972年創業、年間販売約6,100台と求人情報に記載）を運営。ハヤシの店舗は検索結果で高松店・丸亀店を確認。求人情報には倉敷・東岡山の勤務地もあり、実際の店舗数はこれより多い可能性。公式サイト未確認。 注意：別の掲載では「株式会社ハヤシ 倉敷店（本社）」とあり、ハヤシの店舗は別法人（株式会社ハヤシ）の運営の可能性がある。その場合ダブルツリー単体はアップル4店舗で4店舗以下になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ファインソレイユ</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>福岡県、佐賀県、長崎県</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>human joint株式会社</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>03-4446-7735</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>03-5422-8006</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 齊藤博行</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>中古自動車の販売および買取（事業内容）</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>32名</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/company/</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>株式会社NIIZAWA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>広島県、山口県</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>広島県廿日市市大野原1丁目2-20</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8103</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8104</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/keimarket.k
+https://www.facebook.com/share/1AhR49eysR
+https://youtube.com/@keimarket398</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>95名（パート含む）</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/company/
+https://www.kei-market.co.jp/store/</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>株式会社Y's GARAGE</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>京都府、鳥取県、島根県</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>京都府宇治市槇島町三十五38-1</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0774-25-5557</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 桐畑勇志</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>158名（アルバイト含む、令和8年10月）</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/company/</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ロイヤルオートサービス</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>長野県松本市村井町南2-1-5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0120-107-817</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 中田忠章</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>https://carstation.royal-auto.jp/</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>https://carstation.royal-auto.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/royal_auto_
+https://www.instagram.com/royal_auto_service/?hl=ja
+https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>187名</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>https://carstation.royal-auto.jp/company/</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>株式会社横浜ユーポス</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>栃木県、神奈川県</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/kouhoku
 https://www.u-pohs.co.jp/shonanhiratsuka
 https://www.u-pohs.co.jp/tsuzuki</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
         </is>
@@ -2476,7 +2986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2509,7 +3019,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2529,7 +3039,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2549,7 +3059,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2579,7 +3089,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2589,7 +3099,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2609,13 +3119,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>福井県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2625,7 +3135,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>石川県</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2635,77 +3145,77 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>福井県</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2715,37 +3225,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>鳥取県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>島根県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2755,7 +3265,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2765,37 +3275,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>徳島県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>愛媛県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>高知県</t>
+          <t>徳島県</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2805,157 +3315,157 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>香川県</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>長崎県</t>
+          <t>高知県</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>熊本県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>鹿児島県</t>
+          <t>長崎県</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>熊本県</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>大分県</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>本社所在地の都道府県別の社数</t>
-        </is>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>鹿児島県</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>都道府県</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-    </row>
+          <t>沖縄県</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>千葉県</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>本社所在地の都道府県別の社数</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>東京都</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3</v>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2965,7 +3475,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2975,7 +3485,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2985,111 +3495,171 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+    </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>店舗数の分布</t>
-        </is>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5〜9店舗</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10〜19店舗</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20〜30店舗</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>店舗数の分布</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>確度別の社数</t>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>確度</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
+          <t>5〜9店舗</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>10〜19店舗</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>20〜30店舗</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>23</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>確度別の社数</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>確度</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -3634,7 +4204,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>株式会社ダブルツリー</t>
+          <t>株式会社ビッグワン</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -3642,12 +4212,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
+          <t>販売店（千葉市内4店舗）</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -3662,19 +4232,17 @@
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0288/
-https://www.applenet.co.jp/shop/0300/
-https://www.applenet.co.jp/shop/0309/</t>
+          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3689,7 +4257,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビッグワン</t>
+          <t>株式会社ミナミシマ自動車販売</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -3697,12 +4265,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>販売店（千葉市内4店舗）</t>
+          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -3717,17 +4285,19 @@
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
+          <t>https://www.u-pohs.co.jp/kashiba/
+https://www.u-pohs.co.jp/kashihara/
+https://www.u-pohs.co.jp/katuragi/</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。</t>
         </is>
       </c>
     </row>
@@ -3742,7 +4312,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミナミシマ自動車販売</t>
+          <t>株式会社ワークス</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -3750,12 +4320,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
+          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -3770,19 +4340,17 @@
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kashiba/
-https://www.u-pohs.co.jp/kashihara/
-https://www.u-pohs.co.jp/katuragi/</t>
+          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3797,7 +4365,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>株式会社ワークス</t>
+          <t>株式会社沖縄ユーポス</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -3805,12 +4373,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
+          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -3825,17 +4393,19 @@
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
+          <t>https://www.u-pohs.co.jp/misato/
+https://www.u-pohs.co.jp/naha-shintoshin
+https://www.u-pohs.co.jp/noborikawa/</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -3850,7 +4420,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>株式会社沖縄ユーポス</t>
+          <t>株式会社鈴木モータース</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -3858,12 +4428,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -3878,9 +4448,9 @@
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/misato/
-https://www.u-pohs.co.jp/naha-shintoshin
-https://www.u-pohs.co.jp/noborikawa/</t>
+          <t>https://www.applenet.co.jp/shop/0065/
+https://www.applenet.co.jp/shop/0071/
+https://www.applenet.co.jp/shop/0080/</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -3890,7 +4460,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -3905,27 +4475,31 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>株式会社鈴木モータース</t>
+          <t>Dash（運営会社未確認）</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
+          <t>名古屋本店、西三河店、三重鈴鹿店</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.car-dash.jp/</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -3933,19 +4507,17 @@
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0065/
-https://www.applenet.co.jp/shop/0071/
-https://www.applenet.co.jp/shop/0080/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>自社ローン専門店。</t>
         </is>
       </c>
     </row>
@@ -3960,7 +4532,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>ポケットカーズ（運営会社未確認）</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -3968,29 +4540,21 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8844</t>
-        </is>
-      </c>
+          <t>女池店、三条店、長岡店</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/</t>
+          <t>https://www.pocketcars.jp/</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -4000,18 +4564,17 @@
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>https://www.pocketcars.jp/shop/</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
+          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4589,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -4034,29 +4597,29 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/</t>
+          <t>https://www.autogallery.co.jp/</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -4066,8 +4629,8 @@
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -4077,7 +4640,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4655,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -4100,19 +4663,31 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 河野修一</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.csauto.jp/</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
@@ -4120,9 +4695,8 @@
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -4132,7 +4706,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4721,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -4155,31 +4729,19 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
-        </is>
-      </c>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 上武英輝</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kamitake.net/</t>
-        </is>
-      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
@@ -4187,8 +4749,9 @@
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -4196,7 +4759,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -4209,7 +4776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>株式会社カミタケモータース</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -4217,19 +4784,31 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>大阪府、奈良県、大分県</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t>枚方本店、奈良店、大分店</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
@@ -4237,9 +4816,8 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -4247,11 +4825,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="S19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -4264,7 +4838,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>株式会社シマダオート商事</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -4272,12 +4846,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -4292,7 +4866,9 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -4302,7 +4878,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>ユーポス以外の事業は未確認。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4893,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>株式会社フロンティアモータース</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -4325,12 +4901,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>大阪府、兵庫県</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -4345,9 +4921,7 @@
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -4357,7 +4931,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポス以外の事業は未確認。</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4941,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FC本部</t>
+          <t>4店舗以下</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーポス</t>
+          <t>株式会社ベネフィット</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -4380,35 +4954,19 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>06-6532-6532</t>
-        </is>
-      </c>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 柏原隆宏</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-pohs.co.jp/</t>
-        </is>
-      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
@@ -4416,18 +4974,19 @@
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/about/company_info
-https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4437,12 +4996,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>4店舗以下</t>
+          <t>FC本部</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>株式会社ユーポス</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -4450,19 +5009,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
+          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>06-6532-6532</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 柏原隆宏</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
@@ -4470,19 +5045,18 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://www.u-pohs.co.jp/about/company_info
+https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
         </is>
       </c>
     </row>
@@ -4497,7 +5071,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社リフトオフ</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -4505,12 +5079,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>茨城県、千葉県、東京都</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -4525,9 +5099,9 @@
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/</t>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -4552,20 +5126,20 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎有限会社</t>
+          <t>株式会社中州自動車</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>宮崎県</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -4580,8 +5154,9 @@
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0056/
-https://www.applenet.co.jp/shop/0149/</t>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -4591,7 +5166,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4606,7 +5181,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>タイガー石油株式会社</t>
+          <t>アップル宮崎有限会社</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -4614,12 +5189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>宮崎県</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
+          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -4634,7 +5209,8 @@
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0056/
+https://www.applenet.co.jp/shop/0149/</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -4644,7 +5220,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4659,7 +5235,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>大谷自動車株式会社</t>
+          <t>タイガー石油株式会社</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
@@ -4667,47 +5243,27 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>大阪府、和歌山県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>大阪本店、和歌山店</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>大阪府泉佐野市長滝753</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>072-465-0492</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>072-465-3109</t>
-        </is>
-      </c>
+          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.otani-j.co.jp/</t>
-        </is>
-      </c>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>81名</t>
-        </is>
-      </c>
+      <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>https://www.otani-j.co.jp/company</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -4715,7 +5271,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -4728,7 +5288,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>平岩石油販売株式会社</t>
+          <t>大谷自動車株式会社</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -4736,28 +5296,47 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>大阪府、和歌山県</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>アップル練馬関町店、アップル板橋環8店</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>大阪本店、和歌山店</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>大阪府泉佐野市長滝753</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>072-465-0492</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>072-465-3109</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.otani-j.co.jp/</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0175/
-https://www.applenet.co.jp/shop/0247/</t>
+          <t>https://www.otani-j.co.jp/company</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -4765,11 +5344,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -4782,7 +5357,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>株式会社B&amp;F</t>
+          <t>平岩石油販売株式会社</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -4790,12 +5365,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>アップル古河4号店、アップル守谷店</t>
+          <t>アップル練馬関町店、アップル板橋環8店</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -4810,8 +5385,8 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0140/
-https://www.applenet.co.jp/shop/0146/</t>
+          <t>https://www.applenet.co.jp/shop/0175/
+https://www.applenet.co.jp/shop/0247/</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -4836,7 +5411,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>株式会社NEXTモビィ</t>
+          <t>株式会社B&amp;F</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -4844,12 +5419,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
+          <t>アップル古河4号店、アップル守谷店</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -4864,8 +5439,8 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukuoka-inter
-https://www.u-pohs.co.jp/kokurahigashi-inter</t>
+          <t>https://www.applenet.co.jp/shop/0140/
+https://www.applenet.co.jp/shop/0146/</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
@@ -4875,7 +5450,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4890,7 +5465,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>株式会社PlusOne</t>
+          <t>株式会社NEXTモビィ</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -4898,12 +5473,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>アップル安城南店、アップル弥富1号線店</t>
+          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -4918,8 +5493,8 @@
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0129/
-https://www.applenet.co.jp/shop/0219/</t>
+          <t>https://www.u-pohs.co.jp/fukuoka-inter
+https://www.u-pohs.co.jp/kokurahigashi-inter</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -4929,7 +5504,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4944,7 +5519,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>株式会社SHIMAカーライフコネクテッド</t>
+          <t>株式会社PlusOne</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -4952,12 +5527,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>アップル金沢店、アップル高岡店</t>
+          <t>アップル安城南店、アップル弥富1号線店</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -4972,8 +5547,8 @@
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0313/
-https://www.applenet.co.jp/shop/0339/</t>
+          <t>https://www.applenet.co.jp/shop/0129/
+https://www.applenet.co.jp/shop/0219/</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -4998,7 +5573,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>株式会社WinWinサービス</t>
+          <t>株式会社SHIMAカーライフコネクテッド</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -5006,12 +5581,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>アップル盛岡盛南店、アップル盛岡北店</t>
+          <t>アップル金沢店、アップル高岡店</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -5026,8 +5601,8 @@
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0117/
-https://www.applenet.co.jp/shop/0137/</t>
+          <t>https://www.applenet.co.jp/shop/0313/
+https://www.applenet.co.jp/shop/0339/</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -5052,7 +5627,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>株式会社イトー</t>
+          <t>株式会社WinWinサービス</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -5060,12 +5635,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>アップル岸和田店、アップル河内長野中央店</t>
+          <t>アップル盛岡盛南店、アップル盛岡北店</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -5080,8 +5655,8 @@
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0258/
-https://www.applenet.co.jp/shop/0278/</t>
+          <t>https://www.applenet.co.jp/shop/0117/
+https://www.applenet.co.jp/shop/0137/</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -5091,7 +5666,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>アップル以外の店舗は未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5681,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>株式会社インデックス</t>
+          <t>株式会社イトー</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -5114,12 +5689,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
+          <t>アップル岸和田店、アップル河内長野中央店</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -5134,8 +5709,8 @@
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0018/
-https://www.applenet.co.jp/shop/0029/</t>
+          <t>https://www.applenet.co.jp/shop/0258/
+https://www.applenet.co.jp/shop/0278/</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -5145,7 +5720,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップル以外の店舗は未確認。</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5735,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>株式会社イーグルオートサービス</t>
+          <t>株式会社インデックス</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -5168,12 +5743,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
+          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -5188,8 +5763,8 @@
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0032/
-https://www.applenet.co.jp/shop/0063/</t>
+          <t>https://www.applenet.co.jp/shop/0018/
+https://www.applenet.co.jp/shop/0029/</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -5214,7 +5789,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>株式会社エムエフノースジャパン</t>
+          <t>株式会社イーグルオートサービス</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -5222,12 +5797,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -5242,8 +5817,8 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0035/
-https://www.applenet.co.jp/shop/0043/</t>
+          <t>https://www.applenet.co.jp/shop/0032/
+https://www.applenet.co.jp/shop/0063/</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -5268,7 +5843,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>株式会社オカモト</t>
+          <t>株式会社エムエフノースジャパン</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -5276,12 +5851,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>アップル西帯広店、アップル帯広店</t>
+          <t>、</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -5296,8 +5871,8 @@
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0307/
-https://www.applenet.co.jp/shop/0334/</t>
+          <t>https://www.applenet.co.jp/shop/0035/
+https://www.applenet.co.jp/shop/0043/</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5322,7 +5897,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>株式会社オリンピアオート</t>
+          <t>株式会社オカモト</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -5330,12 +5905,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>アップルひたちなか店、アップル那珂中央店</t>
+          <t>アップル西帯広店、アップル帯広店</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -5350,8 +5925,8 @@
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0208/
-https://www.applenet.co.jp/shop/0280/</t>
+          <t>https://www.applenet.co.jp/shop/0307/
+https://www.applenet.co.jp/shop/0334/</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -5376,7 +5951,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートグローリー</t>
+          <t>株式会社オリンピアオート</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -5384,12 +5959,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福重店、ユーポス直方店</t>
+          <t>アップルひたちなか店、アップル那珂中央店</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -5404,8 +5979,8 @@
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukushige
-https://www.u-pohs.co.jp/nogata</t>
+          <t>https://www.applenet.co.jp/shop/0208/
+https://www.applenet.co.jp/shop/0280/</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -5415,7 +5990,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5430,7 +6005,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>株式会社クインオート</t>
+          <t>株式会社オートグローリー</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -5438,12 +6013,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>京都府、兵庫県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>ユーポス亀岡店、ユーポス三田店</t>
+          <t>ユーポス福重店、ユーポス直方店</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -5458,8 +6033,8 @@
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kameoka
-https://www.u-pohs.co.jp/sanda/</t>
+          <t>https://www.u-pohs.co.jp/fukushige
+https://www.u-pohs.co.jp/nogata</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -5484,7 +6059,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>株式会社サコダ車輛</t>
+          <t>株式会社クインオート</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -5492,12 +6067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>京都府、兵庫県</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>アップル海田店、アップル東広島店</t>
+          <t>ユーポス亀岡店、ユーポス三田店</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -5512,8 +6087,8 @@
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0297/
-https://www.applenet.co.jp/shop/0298/</t>
+          <t>https://www.u-pohs.co.jp/kameoka
+https://www.u-pohs.co.jp/sanda/</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
@@ -5523,7 +6098,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5538,7 +6113,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>株式会社シブヤエネックスホールディングス</t>
+          <t>株式会社サコダ車輛</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -5546,12 +6121,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>アップル相模原城山店、アップル大井松田インター店</t>
+          <t>アップル海田店、アップル東広島店</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -5566,8 +6141,8 @@
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0266/
-https://www.applenet.co.jp/shop/0292/</t>
+          <t>https://www.applenet.co.jp/shop/0297/
+https://www.applenet.co.jp/shop/0298/</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -5577,7 +6152,7 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 社名の正式表記は「サコダ車輌」の可能性。本社は広島市中区舟入南、売上高158億円・従業員240名（求人情報）。自社店舗の海田店（軽自動車専門）と佐伯区五日市の拠点もあり、合計4か所以上。自社サイト未確認のため境界扱い。</t>
         </is>
       </c>
     </row>
@@ -5592,7 +6167,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>株式会社スズキアリーナ瑞穂</t>
+          <t>株式会社シブヤエネックスホールディングス</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -5600,12 +6175,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>アップル青梅店、アップル西東京店</t>
+          <t>アップル相模原城山店、アップル大井松田インター店</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -5620,8 +6195,8 @@
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0057/
-https://www.applenet.co.jp/shop/0100/</t>
+          <t>https://www.applenet.co.jp/shop/0266/
+https://www.applenet.co.jp/shop/0292/</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -5646,7 +6221,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>株式会社トップワン</t>
+          <t>株式会社スズキアリーナ瑞穂</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -5654,12 +6229,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>アップル豊田梅坪店、アップル豊田南店</t>
+          <t>アップル青梅店、アップル西東京店</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -5674,8 +6249,8 @@
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0075/
-https://www.applenet.co.jp/shop/0126/</t>
+          <t>https://www.applenet.co.jp/shop/0057/
+https://www.applenet.co.jp/shop/0100/</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -5700,7 +6275,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社トップワン</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -5708,12 +6283,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>アップル大和店、アップル相模原店</t>
+          <t>アップル豊田梅坪店、アップル豊田南店</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -5728,8 +6303,8 @@
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0306/
-https://www.applenet.co.jp/shop/0340/</t>
+          <t>https://www.applenet.co.jp/shop/0075/
+https://www.applenet.co.jp/shop/0126/</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -5754,7 +6329,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビーインプレスト</t>
+          <t>株式会社トータス</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -5762,12 +6337,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>アップル宇都宮北店、アップル大田原店</t>
+          <t>アップル大和店、アップル相模原店</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -5782,8 +6357,8 @@
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0211/
-https://www.applenet.co.jp/shop/0303/</t>
+          <t>https://www.applenet.co.jp/shop/0306/
+https://www.applenet.co.jp/shop/0340/</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -5808,7 +6383,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファミリー</t>
+          <t>株式会社ビーインプレスト</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -5816,12 +6391,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>ファミリー可児店、ファミリー各務原店</t>
+          <t>アップル宇都宮北店、アップル大田原店</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -5836,17 +6411,18 @@
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0211/
+https://www.applenet.co.jp/shop/0303/</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5861,7 +6437,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミヤチ</t>
+          <t>株式会社ファミリー</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -5874,7 +6450,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>アップル岐阜長良店、アップル関店</t>
+          <t>ファミリー可児店、ファミリー各務原店</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -5889,18 +6465,17 @@
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0101/
-https://www.applenet.co.jp/shop/0155/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -5915,7 +6490,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>株式会社メーカーズ</t>
+          <t>株式会社ミヤチ</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -5923,12 +6498,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>アップル福岡東店、アップル福岡八幡店</t>
+          <t>アップル岐阜長良店、アップル関店</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -5943,8 +6518,8 @@
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0238/
-https://www.applenet.co.jp/shop/0255/</t>
+          <t>https://www.applenet.co.jp/shop/0101/
+https://www.applenet.co.jp/shop/0155/</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -6524,7 +7099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6984,6 +7559,202 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>LACモービル（アネックス・キャンピングカーランド・デルタリンクの3社）</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー。宮城・横浜・埼玉・入間・千葉・名古屋・京都・大阪・倉敷・岐阜・新潟（直営9店舗＋FC）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3社の共通ブランドで、どの会社が何店舗を運営しているか未確認（各社4店舗以下の可能性）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>東和モータース販売</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー。東京本店・埼玉入間・所沢・本庄・横浜・千葉・世田谷・札幌</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>公式サイトに接続できず（接続エラー）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Yacco（株式会社ホワイトハウス系）</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー。守谷本店・水海道・仙台・横浜・名古屋買取センター</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>運営会社と店舗数が未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ケイカフェ</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>福岡県内に複数店舗、軽の新車・届出済未使用車</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>プチモ軽自動車専門店</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>唐津店・佐賀店、総在庫500台</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ハヤシ（くるまのハヤシ）</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>倉敷本社。高松・丸亀・倉敷ほか。ダブルツリー（代表 林和樹）と同じグループの可能性</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>ダブルツリーとの関係（同一法人か別法人か）が未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>株式会社クロカワ</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>軽届出済未使用車専門店</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>オートプラネット名古屋</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>輸入中古車</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>店舗数未確認</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>ツチヤ自動車株式会社</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2128,15 +2128,19 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
+          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>千葉県市川市北方町4-1441-8</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2148,97 +2152,69 @@
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
+https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>株式会社アップルカーセールス</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0004/
 https://www.applenet.co.jp/shop/0007/
 https://www.applenet.co.jp/shop/0046/</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ヨシダオートサービス</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>大阪府</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0301</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0302</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>吉田宜史</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/contact/</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>218名（2025年1月）</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -2248,40 +2224,64 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2309,15 +2309,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t>浜松市内6店舗</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2329,20 +2333,18 @@
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2354,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>松下モータース</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2360,12 +2362,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -2380,17 +2382,20 @@
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2405,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>松下モータース</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2408,57 +2413,37 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2453,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2476,30 +2461,47 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 石戸宏樹</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>26名</t>
+        </is>
+      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/</t>
+          <t>https://www.apple-car.jp/company</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -2509,7 +2511,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2521,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>株式会社ダブルツリー</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2527,22 +2529,18 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店、軽自動車専門店 ハヤシ 高松店、軽自動車専門店 ハヤシ 丸亀店</t>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
@@ -2552,18 +2550,19 @@
       <c r="P32" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
-https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
-https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）に加え、軽自動車専門店「くるまのハヤシ」（1972年創業、年間販売約6,100台と求人情報に記載）を運営。ハヤシの店舗は検索結果で高松店・丸亀店を確認。求人情報には倉敷・東岡山の勤務地もあり、実際の店舗数はこれより多い可能性。公式サイト未確認。 注意：別の掲載では「株式会社ハヤシ 倉敷店（本社）」とあり、ハヤシの店舗は別法人（株式会社ハヤシ）の運営の可能性がある。その場合ダブルツリー単体はアップル4店舗で4店舗以下になる。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2572,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社ダブルツリー</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2581,18 +2580,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店、軽自動車専門店 ハヤシ 高松店、軽自動車専門店 ハヤシ 丸亀店</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
@@ -2601,7 +2604,9 @@
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
+https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -2611,7 +2616,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）に加え、軽自動車専門店「くるまのハヤシ」（1972年創業、年間販売約6,100台と求人情報に記載）を運営。ハヤシの店舗は検索結果で高松店・丸亀店を確認。求人情報には倉敷・東岡山の勤務地もあり、実際の店舗数はこれより多い可能性。公式サイト未確認。 注意：別の掲載では「株式会社ハヤシ 倉敷店（本社）」とあり、ハヤシの店舗は別法人（株式会社ハヤシ）の運営の可能性がある。その場合ダブルツリー単体はアップル4店舗で4店舗以下になる。</t>
         </is>
       </c>
     </row>
@@ -2621,77 +2626,45 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>human joint株式会社</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>03-4446-7735</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>03-5422-8006</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 齊藤博行</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>https://cococar-hp.net/</t>
-        </is>
-      </c>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>中古自動車の販売および買取（事業内容）</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>32名</t>
-        </is>
-      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/company/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2674,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>株式会社NIIZAWA</t>
+          <t>human joint株式会社</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2709,140 +2682,152 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>広島県、山口県</t>
+          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
+          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>広島県廿日市市大野原1丁目2-20</t>
+          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0829-30-8103</t>
+          <t>03-4446-7735</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0829-30-8104</t>
+          <t>03-5422-8006</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
+          <t>代表取締役 齊藤博行</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.kei-market.co.jp/</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kei-market.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://cococar-hp.net/</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>中古自動車の販売および買取（事業内容）</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>32名</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/company/</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>株式会社NIIZAWA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>広島県、山口県</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>広島県廿日市市大野原1丁目2-20</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8103</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8104</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keimarket.k
 https://www.facebook.com/share/1AhR49eysR
 https://youtube.com/@keimarket398</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>95名（パート含む）</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/company/
 https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>株式会社Y's GARAGE</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>京都府、鳥取県、島根県</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>京都府宇治市槇島町三十五38-1</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>0774-25-5557</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 桐畑勇志</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>158名（アルバイト含む、令和8年10月）</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/company/</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2837,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロイヤルオートサービス</t>
+          <t>株式会社Y's GARAGE</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2860,103 +2845,171 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>京都府、鳥取県、島根県</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>長野県松本市村井町南2-1-5</t>
+          <t>京都府宇治市槇島町三十五38-1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0120-107-817</t>
+          <t>0774-25-5557</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
+          <t>代表取締役 桐畑勇志</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>158名（アルバイト含む、令和8年10月）</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/company/</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ロイヤルオートサービス</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>長野県松本市村井町南2-1-5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>0120-107-817</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
           <t>代表取締役 中田忠章</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/contact/</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/royal_auto_
 https://www.instagram.com/royal_auto_service/?hl=ja
 https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>187名</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>株式会社横浜ユーポス</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>栃木県、神奈川県</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/kouhoku
@@ -2964,12 +3017,12 @@
 https://www.u-pohs.co.jp/tsuzuki</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
         </is>
@@ -3099,7 +3152,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -3109,7 +3162,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -3459,7 +3512,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3589,7 +3642,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
@@ -3619,7 +3672,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66"/>
@@ -3649,7 +3702,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -3673,7 +3726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3982,7 +4035,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>昭和礦油株式会社</t>
+          <t>プルミエ（軽届出済未使用車専門店、運営会社未確認）</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -3990,12 +4043,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
+          <t>豊田、安城、豊橋、四日市</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -4010,21 +4063,15 @@
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0282/
-https://www.applenet.co.jp/shop/0290/
-https://www.applenet.co.jp/shop/0291/</t>
+          <t>検索結果の抜粋</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -4037,7 +4084,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>株式会社MARE</t>
+          <t>昭和礦油株式会社</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -4045,12 +4092,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>愛知県、兵庫県、広島県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
+          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -4065,9 +4112,9 @@
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0289/
-https://www.applenet.co.jp/shop/0296/
-https://www.applenet.co.jp/shop/0308/</t>
+          <t>https://www.applenet.co.jp/shop/0282/
+https://www.applenet.co.jp/shop/0290/
+https://www.applenet.co.jp/shop/0291/</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -4092,7 +4139,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>株式会社オリンピア</t>
+          <t>株式会社MARE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -4100,12 +4147,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>栃木県、群馬県、埼玉県</t>
+          <t>愛知県、兵庫県、広島県</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
+          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -4120,9 +4167,9 @@
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0138/
-https://www.applenet.co.jp/shop/0141/
-https://www.applenet.co.jp/shop/0143/</t>
+          <t>https://www.applenet.co.jp/shop/0289/
+https://www.applenet.co.jp/shop/0296/
+https://www.applenet.co.jp/shop/0308/</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -4147,7 +4194,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>株式会社グローバンネット</t>
+          <t>株式会社オリンピア</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -4155,23 +4202,19 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>栃木県、群馬県、埼玉県</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
+          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>https://pa-cars.com/</t>
-        </is>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
@@ -4179,17 +4222,19 @@
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>https://pa-cars.com/shopinfo.html</t>
+          <t>https://www.applenet.co.jp/shop/0138/
+https://www.applenet.co.jp/shop/0141/
+https://www.applenet.co.jp/shop/0143/</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4249,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビッグワン</t>
+          <t>株式会社グローバンネット</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -4212,19 +4257,23 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>販売店（千葉市内4店舗）</t>
+          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>https://pa-cars.com/</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
@@ -4232,7 +4281,7 @@
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
+          <t>https://pa-cars.com/shopinfo.html</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -4242,7 +4291,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
+          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4306,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミナミシマ自動車販売</t>
+          <t>株式会社ビッグワン</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -4265,12 +4314,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
+          <t>販売店（千葉市内4店舗）</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -4285,19 +4334,17 @@
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kashiba/
-https://www.u-pohs.co.jp/kashihara/
-https://www.u-pohs.co.jp/katuragi/</t>
+          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。</t>
+          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4359,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>株式会社ワークス</t>
+          <t>株式会社ミナミシマ自動車販売</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -4320,12 +4367,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
+          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -4340,17 +4387,19 @@
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
+          <t>https://www.u-pohs.co.jp/kashiba/
+https://www.u-pohs.co.jp/kashihara/
+https://www.u-pohs.co.jp/katuragi/</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4414,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>株式会社沖縄ユーポス</t>
+          <t>株式会社ワークス</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -4373,12 +4422,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -4393,19 +4442,17 @@
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/misato/
-https://www.u-pohs.co.jp/naha-shintoshin
-https://www.u-pohs.co.jp/noborikawa/</t>
+          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4467,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>株式会社鈴木モータース</t>
+          <t>株式会社沖縄ユーポス</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -4428,12 +4475,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
+          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -4448,9 +4495,9 @@
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0065/
-https://www.applenet.co.jp/shop/0071/
-https://www.applenet.co.jp/shop/0080/</t>
+          <t>https://www.u-pohs.co.jp/misato/
+https://www.u-pohs.co.jp/naha-shintoshin
+https://www.u-pohs.co.jp/noborikawa/</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -4460,7 +4507,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4475,31 +4522,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Dash（運営会社未確認）</t>
+          <t>株式会社鈴木モータース</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>名古屋本店、西三河店、三重鈴鹿店</t>
+          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.car-dash.jp/</t>
-        </is>
-      </c>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -4507,17 +4550,19 @@
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>https://www.car-dash.jp/</t>
+          <t>https://www.applenet.co.jp/shop/0065/
+https://www.applenet.co.jp/shop/0071/
+https://www.applenet.co.jp/shop/0080/</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4577,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ポケットカーズ（運営会社未確認）</t>
+          <t>Dash（運営会社未確認）</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -4540,12 +4585,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>女池店、三条店、長岡店</t>
+          <t>名古屋本店、西三河店、三重鈴鹿店</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -4554,7 +4599,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -4564,7 +4609,7 @@
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/shop/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -4574,7 +4619,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
+          <t>自社ローン専門店。</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4634,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>ポケットカーズ（運営会社未確認）</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -4597,29 +4642,21 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8844</t>
-        </is>
-      </c>
+          <t>女池店、三条店、長岡店</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/</t>
+          <t>https://www.pocketcars.jp/</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -4629,18 +4666,17 @@
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>https://www.pocketcars.jp/shop/</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
+          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4691,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>古城モータース</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -4663,29 +4699,21 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
-        </is>
-      </c>
+          <t>高岡本店、富山店、石川白山店</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
+      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -4695,20 +4723,15 @@
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://www.kojyo-motors.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -4721,7 +4744,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -4729,19 +4752,31 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.autogallery.co.jp/</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
@@ -4749,9 +4784,8 @@
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -4761,7 +4795,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4810,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -4784,29 +4818,29 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 上武英輝</t>
+          <t>代表取締役 河野修一</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/</t>
+          <t>https://www.csauto.jp/</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -4816,8 +4850,8 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -4825,7 +4859,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -4838,7 +4876,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -4846,12 +4884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -4866,9 +4904,9 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -4893,7 +4931,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>株式会社カミタケモータース</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -4901,19 +4939,31 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>大阪府、奈良県、大分県</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>枚方本店、奈良店、大分店</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
@@ -4921,7 +4971,8 @@
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -4929,11 +4980,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス以外の事業は未確認。</t>
-        </is>
-      </c>
+      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -4946,7 +4993,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>株式会社シマダオート商事</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -4954,12 +5001,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -4974,9 +5021,9 @@
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/</t>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -4996,12 +5043,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FC本部</t>
+          <t>4店舗以下</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーポス</t>
+          <t>株式会社フロンティアモータース</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -5009,35 +5056,19 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>大阪府、兵庫県</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>06-6532-6532</t>
-        </is>
-      </c>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 柏原隆宏</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-pohs.co.jp/</t>
-        </is>
-      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
@@ -5045,18 +5076,17 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/about/company_info
-https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
+          <t>ユーポス以外の事業は未確認。</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5101,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>株式会社ベネフィット</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -5079,12 +5109,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -5099,9 +5129,9 @@
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -5121,12 +5151,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>4店舗以下</t>
+          <t>FC本部</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社ユーポス</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -5134,19 +5164,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
+          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>06-6532-6532</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 柏原隆宏</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
@@ -5154,19 +5200,18 @@
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/</t>
+          <t>https://www.u-pohs.co.jp/about/company_info
+https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
         </is>
       </c>
     </row>
@@ -5181,20 +5226,20 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎有限会社</t>
+          <t>株式会社リフトオフ</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>宮崎県</t>
+          <t>茨城県、千葉県、東京都</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -5209,8 +5254,9 @@
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0056/
-https://www.applenet.co.jp/shop/0149/</t>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -5220,7 +5266,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5235,20 +5281,20 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>タイガー石油株式会社</t>
+          <t>株式会社中州自動車</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -5263,7 +5309,9 @@
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -5273,7 +5321,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5288,60 +5336,44 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>大谷自動車株式会社</t>
+          <t>阿部勝自動車工業株式会社</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>大阪府、和歌山県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>大阪本店、和歌山店</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>大阪府泉佐野市長滝753</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>072-465-0492</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>072-465-3109</t>
-        </is>
-      </c>
+          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>https://www.otani-j.co.jp/</t>
+          <t>https://k-mishiyo.abekatu.co.jp/</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>81名</t>
-        </is>
-      </c>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>https://www.otani-j.co.jp/company</t>
+          <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr"/>
@@ -5357,7 +5389,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>平岩石油販売株式会社</t>
+          <t>アップル宮崎有限会社</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -5365,12 +5397,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>宮崎県</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>アップル練馬関町店、アップル板橋環8店</t>
+          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -5385,8 +5417,8 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0175/
-https://www.applenet.co.jp/shop/0247/</t>
+          <t>https://www.applenet.co.jp/shop/0056/
+https://www.applenet.co.jp/shop/0149/</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -5411,7 +5443,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>株式会社B&amp;F</t>
+          <t>タイガー石油株式会社</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -5419,12 +5451,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>アップル古河4号店、アップル守谷店</t>
+          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -5439,8 +5471,7 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0140/
-https://www.applenet.co.jp/shop/0146/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
@@ -5450,7 +5481,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5496,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>株式会社NEXTモビィ</t>
+          <t>大谷自動車株式会社</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -5473,28 +5504,47 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>大阪府、和歌山県</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+          <t>大阪本店、和歌山店</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>大阪府泉佐野市長滝753</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>072-465-0492</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>072-465-3109</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.otani-j.co.jp/</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukuoka-inter
-https://www.u-pohs.co.jp/kokurahigashi-inter</t>
+          <t>https://www.otani-j.co.jp/company</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -5502,11 +5552,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -5519,7 +5565,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>株式会社PlusOne</t>
+          <t>平岩石油販売株式会社</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -5527,12 +5573,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>アップル安城南店、アップル弥富1号線店</t>
+          <t>アップル練馬関町店、アップル板橋環8店</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -5547,8 +5593,8 @@
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0129/
-https://www.applenet.co.jp/shop/0219/</t>
+          <t>https://www.applenet.co.jp/shop/0175/
+https://www.applenet.co.jp/shop/0247/</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -5573,7 +5619,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>株式会社SHIMAカーライフコネクテッド</t>
+          <t>株式会社B&amp;F</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -5581,12 +5627,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>アップル金沢店、アップル高岡店</t>
+          <t>アップル古河4号店、アップル守谷店</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -5601,8 +5647,8 @@
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0313/
-https://www.applenet.co.jp/shop/0339/</t>
+          <t>https://www.applenet.co.jp/shop/0140/
+https://www.applenet.co.jp/shop/0146/</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -5627,7 +5673,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>株式会社WinWinサービス</t>
+          <t>株式会社NEXTモビィ</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -5635,12 +5681,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>アップル盛岡盛南店、アップル盛岡北店</t>
+          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -5655,8 +5701,8 @@
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0117/
-https://www.applenet.co.jp/shop/0137/</t>
+          <t>https://www.u-pohs.co.jp/fukuoka-inter
+https://www.u-pohs.co.jp/kokurahigashi-inter</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -5666,7 +5712,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5727,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>株式会社イトー</t>
+          <t>株式会社PlusOne</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -5689,12 +5735,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>アップル岸和田店、アップル河内長野中央店</t>
+          <t>アップル安城南店、アップル弥富1号線店</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -5709,8 +5755,8 @@
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0258/
-https://www.applenet.co.jp/shop/0278/</t>
+          <t>https://www.applenet.co.jp/shop/0129/
+https://www.applenet.co.jp/shop/0219/</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -5720,7 +5766,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>アップル以外の店舗は未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5781,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>株式会社インデックス</t>
+          <t>株式会社SHIMAカーライフコネクテッド</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -5743,12 +5789,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
+          <t>アップル金沢店、アップル高岡店</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -5763,8 +5809,8 @@
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0018/
-https://www.applenet.co.jp/shop/0029/</t>
+          <t>https://www.applenet.co.jp/shop/0313/
+https://www.applenet.co.jp/shop/0339/</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -5789,7 +5835,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>株式会社イーグルオートサービス</t>
+          <t>株式会社WinWinサービス</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -5797,12 +5843,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
+          <t>アップル盛岡盛南店、アップル盛岡北店</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -5817,8 +5863,8 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0032/
-https://www.applenet.co.jp/shop/0063/</t>
+          <t>https://www.applenet.co.jp/shop/0117/
+https://www.applenet.co.jp/shop/0137/</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -5843,7 +5889,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>株式会社エムエフノースジャパン</t>
+          <t>株式会社イトー</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -5851,12 +5897,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>アップル岸和田店、アップル河内長野中央店</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -5871,8 +5917,8 @@
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0035/
-https://www.applenet.co.jp/shop/0043/</t>
+          <t>https://www.applenet.co.jp/shop/0258/
+https://www.applenet.co.jp/shop/0278/</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5882,7 +5928,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップル以外の店舗は未確認。</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5943,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>株式会社オカモト</t>
+          <t>株式会社インデックス</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -5905,12 +5951,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>アップル西帯広店、アップル帯広店</t>
+          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -5925,8 +5971,8 @@
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0307/
-https://www.applenet.co.jp/shop/0334/</t>
+          <t>https://www.applenet.co.jp/shop/0018/
+https://www.applenet.co.jp/shop/0029/</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -5951,7 +5997,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>株式会社オリンピアオート</t>
+          <t>株式会社イーグルオートサービス</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -5959,12 +6005,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>アップルひたちなか店、アップル那珂中央店</t>
+          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -5979,8 +6025,8 @@
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0208/
-https://www.applenet.co.jp/shop/0280/</t>
+          <t>https://www.applenet.co.jp/shop/0032/
+https://www.applenet.co.jp/shop/0063/</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -6005,7 +6051,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートグローリー</t>
+          <t>株式会社エムエフノースジャパン</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -6013,12 +6059,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福重店、ユーポス直方店</t>
+          <t>、</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -6033,8 +6079,8 @@
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukushige
-https://www.u-pohs.co.jp/nogata</t>
+          <t>https://www.applenet.co.jp/shop/0035/
+https://www.applenet.co.jp/shop/0043/</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -6044,7 +6090,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6105,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>株式会社クインオート</t>
+          <t>株式会社オカモト</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -6067,12 +6113,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>京都府、兵庫県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>ユーポス亀岡店、ユーポス三田店</t>
+          <t>アップル西帯広店、アップル帯広店</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -6087,8 +6133,8 @@
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kameoka
-https://www.u-pohs.co.jp/sanda/</t>
+          <t>https://www.applenet.co.jp/shop/0307/
+https://www.applenet.co.jp/shop/0334/</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
@@ -6098,7 +6144,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6159,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>株式会社サコダ車輛</t>
+          <t>株式会社オリンピアオート</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -6121,12 +6167,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>アップル海田店、アップル東広島店</t>
+          <t>アップルひたちなか店、アップル那珂中央店</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -6141,8 +6187,8 @@
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0297/
-https://www.applenet.co.jp/shop/0298/</t>
+          <t>https://www.applenet.co.jp/shop/0208/
+https://www.applenet.co.jp/shop/0280/</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -6152,7 +6198,7 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 社名の正式表記は「サコダ車輌」の可能性。本社は広島市中区舟入南、売上高158億円・従業員240名（求人情報）。自社店舗の海田店（軽自動車専門）と佐伯区五日市の拠点もあり、合計4か所以上。自社サイト未確認のため境界扱い。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6213,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>株式会社シブヤエネックスホールディングス</t>
+          <t>株式会社オートグローリー</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -6175,12 +6221,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>アップル相模原城山店、アップル大井松田インター店</t>
+          <t>ユーポス福重店、ユーポス直方店</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -6195,8 +6241,8 @@
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0266/
-https://www.applenet.co.jp/shop/0292/</t>
+          <t>https://www.u-pohs.co.jp/fukushige
+https://www.u-pohs.co.jp/nogata</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -6206,7 +6252,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6267,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>株式会社スズキアリーナ瑞穂</t>
+          <t>株式会社クインオート</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -6229,12 +6275,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>京都府、兵庫県</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>アップル青梅店、アップル西東京店</t>
+          <t>ユーポス亀岡店、ユーポス三田店</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -6249,8 +6295,8 @@
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0057/
-https://www.applenet.co.jp/shop/0100/</t>
+          <t>https://www.u-pohs.co.jp/kameoka
+https://www.u-pohs.co.jp/sanda/</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -6260,7 +6306,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6321,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>株式会社トップワン</t>
+          <t>株式会社サコダ車輛</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -6283,12 +6329,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>アップル豊田梅坪店、アップル豊田南店</t>
+          <t>アップル海田店、アップル東広島店</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -6303,8 +6349,8 @@
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0075/
-https://www.applenet.co.jp/shop/0126/</t>
+          <t>https://www.applenet.co.jp/shop/0297/
+https://www.applenet.co.jp/shop/0298/</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -6314,7 +6360,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 社名の正式表記は「サコダ車輌」の可能性。本社は広島市中区舟入南、売上高158億円・従業員240名（求人情報）。自社店舗の海田店（軽自動車専門）と佐伯区五日市の拠点もあり、合計4か所以上。自社サイト未確認のため境界扱い。</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6375,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社シブヤエネックスホールディングス</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -6342,7 +6388,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>アップル大和店、アップル相模原店</t>
+          <t>アップル相模原城山店、アップル大井松田インター店</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -6357,8 +6403,8 @@
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0306/
-https://www.applenet.co.jp/shop/0340/</t>
+          <t>https://www.applenet.co.jp/shop/0266/
+https://www.applenet.co.jp/shop/0292/</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -6383,7 +6429,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビーインプレスト</t>
+          <t>株式会社スズキアリーナ瑞穂</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -6391,12 +6437,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>アップル宇都宮北店、アップル大田原店</t>
+          <t>アップル青梅店、アップル西東京店</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -6411,8 +6457,8 @@
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0211/
-https://www.applenet.co.jp/shop/0303/</t>
+          <t>https://www.applenet.co.jp/shop/0057/
+https://www.applenet.co.jp/shop/0100/</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
@@ -6437,7 +6483,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファミリー</t>
+          <t>株式会社トップワン</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -6445,12 +6491,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>ファミリー可児店、ファミリー各務原店</t>
+          <t>アップル豊田梅坪店、アップル豊田南店</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -6465,17 +6511,18 @@
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0075/
+https://www.applenet.co.jp/shop/0126/</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6537,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミヤチ</t>
+          <t>株式会社トータス</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -6498,12 +6545,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>アップル岐阜長良店、アップル関店</t>
+          <t>アップル大和店、アップル相模原店</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -6518,8 +6565,8 @@
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0101/
-https://www.applenet.co.jp/shop/0155/</t>
+          <t>https://www.applenet.co.jp/shop/0306/
+https://www.applenet.co.jp/shop/0340/</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -6544,7 +6591,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>株式会社湯浅</t>
+          <t>株式会社ビーインプレスト</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -6552,12 +6599,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>アップル白井店、アップル松戸本店</t>
+          <t>アップル宇都宮北店、アップル大田原店</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -6572,8 +6619,8 @@
       <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0287/
-https://www.applenet.co.jp/shop/0293/</t>
+          <t>https://www.applenet.co.jp/shop/0211/
+https://www.applenet.co.jp/shop/0303/</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
@@ -6598,7 +6645,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>株式会社関西オート</t>
+          <t>株式会社ファミリー</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -6606,27 +6653,19 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>八尾店、平野店</t>
+          <t>ファミリー可児店、ファミリー各務原店</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 大川純平</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kansai-auto.jp/</t>
-        </is>
-      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
@@ -6634,15 +6673,19 @@
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>https://www.kansai-auto.jp/company/outline/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr"/>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -6655,20 +6698,20 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Re-BOOT株式会社</t>
+          <t>株式会社ミヤチ</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>アップル大阪平野店</t>
+          <t>アップル岐阜長良店、アップル関店</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -6683,7 +6726,8 @@
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0284/</t>
+          <t>https://www.applenet.co.jp/shop/0101/
+https://www.applenet.co.jp/shop/0155/</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -6691,7 +6735,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -6704,43 +6752,27 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>北摂オート株式会社</t>
+          <t>株式会社湯浅</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>大阪府箕面市桜井2-16-17</t>
-        </is>
-      </c>
+          <t>アップル白井店、アップル松戸本店</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>072-723-1102</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 喜多克之</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>https://hokusetu-auto.com/</t>
-        </is>
-      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
@@ -6748,7 +6780,8 @@
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>https://hokusetu-auto.com/company.php</t>
+          <t>https://www.applenet.co.jp/shop/0287/
+https://www.applenet.co.jp/shop/0293/</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -6756,7 +6789,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -6769,11 +6806,11 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>有限会社タイヨウ</t>
+          <t>株式会社関西オート</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -6782,14 +6819,22 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>ユーポス富田林店</t>
+          <t>八尾店、平野店</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 大川純平</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kansai-auto.jp/</t>
+        </is>
+      </c>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
@@ -6797,7 +6842,7 @@
       <c r="P55" s="2" t="inlineStr"/>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.kansai-auto.jp/company/outline/</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -6805,11 +6850,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -6822,7 +6863,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>株式会社We Car CORE</t>
+          <t>Re-BOOT株式会社</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -6835,7 +6876,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>ユーポス貝塚店</t>
+          <t>アップル大阪平野店</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -6850,7 +6891,7 @@
       <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0284/</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
@@ -6858,11 +6899,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -6875,7 +6912,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>株式会社cantera</t>
+          <t>北摂オート株式会社</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -6888,14 +6925,30 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環四條畷店</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>大阪府箕面市桜井2-16-17</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>072-723-1102</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 喜多克之</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>https://hokusetu-auto.com/</t>
+        </is>
+      </c>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
@@ -6903,7 +6956,7 @@
       <c r="P57" s="2" t="inlineStr"/>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://hokusetu-auto.com/company.php</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
@@ -6911,11 +6964,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -6928,7 +6977,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>株式会社プロンザ</t>
+          <t>有限会社タイヨウ</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -6941,7 +6990,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>ユーポス枚方店</t>
+          <t>ユーポス富田林店</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -6981,7 +7030,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>株式会社ポロ</t>
+          <t>株式会社We Car CORE</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -6994,30 +7043,14 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>大阪府高槻市富田町6丁目15-13</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>072-694-6641</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>072-694-9913</t>
-        </is>
-      </c>
+          <t>ユーポス貝塚店</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.polojp.com/</t>
-        </is>
-      </c>
+      <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
@@ -7025,7 +7058,7 @@
       <c r="P59" s="2" t="inlineStr"/>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>https://www.polojp.com/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
@@ -7033,7 +7066,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -7046,7 +7083,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>豊栄モータース</t>
+          <t>株式会社cantera</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -7059,7 +7096,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>ユーポス寝屋川店</t>
+          <t>ユーポス外環四條畷店</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -7084,6 +7121,177 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>株式会社プロンザ</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス枚方店</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ポロ</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>大阪府高槻市富田町6丁目15-13</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>072-694-6641</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>072-694-9913</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>豊栄モータース</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス寝屋川店</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
           <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。（法人格の表示なし）</t>
         </is>
       </c>
@@ -7099,7 +7307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7422,13 +7630,13 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>株式会社光野自動車（ヒカリノ）</t>
+          <t>株式会社Smile Carz</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7443,15 +7651,15 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>株式会社Smile Carz</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>山口県</t>
-        </is>
-      </c>
+          <t>株式会社BIG BRIDGE／株式会社five star</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>自社ローン</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
@@ -7464,18 +7672,14 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>株式会社BIG BRIDGE／株式会社five star</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>自社ローン</t>
-        </is>
-      </c>
+          <t>株式会社ヤマト（島根）／共盛自動車グループ（広島）／株式会社日本カードック（尼崎）／株式会社グランドエンタープライズ（京都）</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>業態・店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7485,14 +7689,18 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヤマト（島根）／共盛自動車グループ（広島）／株式会社日本カードック（尼崎）／株式会社グランドエンタープライズ（京都）</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>株式会社ルートシックス</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー専門、水戸・埼玉</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>業態・店舗数未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -7502,18 +7710,18 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>株式会社ルートシックス</t>
+          <t>株式会社タックス横浜／株式会社タックス宮城野／株式会社キリン自動車（ONIX）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー専門、水戸・埼玉</t>
+          <t>FC加盟店</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>タックス・オニキス本部の店舗一覧が取得できず店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7523,18 +7731,18 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>株式会社タックス横浜／株式会社タックス宮城野／株式会社キリン自動車（ONIX）</t>
+          <t>株式会社OSG（ミニバン専門店OSG）／OSINC.／株式会社N.T ART</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>FC加盟店</t>
+          <t>大阪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>タックス・オニキス本部の店舗一覧が取得できず店舗数未確認</t>
+          <t>店舗数未確認（1〜2店舗の可能性）</t>
         </is>
       </c>
     </row>
@@ -7544,18 +7752,18 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>株式会社OSG（ミニバン専門店OSG）／OSINC.／株式会社N.T ART</t>
+          <t>LACモービル（アネックス・キャンピングカーランド・デルタリンクの3社）</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>大阪</t>
+          <t>キャンピングカー。宮城・横浜・埼玉・入間・千葉・名古屋・京都・大阪・倉敷・岐阜・新潟（直営9店舗＋FC）</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認（1〜2店舗の可能性）</t>
+          <t>3社の共通ブランドで、どの会社が何店舗を運営しているか未確認（各社4店舗以下の可能性）</t>
         </is>
       </c>
     </row>
@@ -7565,18 +7773,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>LACモービル（アネックス・キャンピングカーランド・デルタリンクの3社）</t>
+          <t>東和モータース販売</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー。宮城・横浜・埼玉・入間・千葉・名古屋・京都・大阪・倉敷・岐阜・新潟（直営9店舗＋FC）</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>キャンピングカー。東京本店・埼玉入間・所沢・本庄・横浜・千葉・世田谷・札幌</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3社の共通ブランドで、どの会社が何店舗を運営しているか未確認（各社4店舗以下の可能性）</t>
+          <t>公式サイトに接続できず（接続エラー）</t>
         </is>
       </c>
     </row>
@@ -7586,22 +7798,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>東和モータース販売</t>
+          <t>Yacco（株式会社ホワイトハウス系）</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー。東京本店・埼玉入間・所沢・本庄・横浜・千葉・世田谷・札幌</t>
+          <t>キャンピングカー。守谷本店・水海道・仙台・横浜・名古屋買取センター</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>公式サイトに接続できず（接続エラー）</t>
+          <t>運営会社と店舗数が未確認</t>
         </is>
       </c>
     </row>
@@ -7611,22 +7823,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Yacco（株式会社ホワイトハウス系）</t>
+          <t>プチモ軽自動車専門店</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー。守谷本店・水海道・仙台・横浜・名古屋買取センター</t>
+          <t>唐津店・佐賀店、総在庫500台</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>運営会社と店舗数が未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -7636,22 +7848,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ケイカフェ</t>
+          <t>株式会社ハヤシ（くるまのハヤシ）</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>福岡県内に複数店舗、軽の新車・届出済未使用車</t>
+          <t>倉敷本社。高松・丸亀・倉敷ほか。ダブルツリー（代表 林和樹）と同じグループの可能性</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>ダブルツリーとの関係（同一法人か別法人か）が未確認</t>
         </is>
       </c>
     </row>
@@ -7661,17 +7873,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>プチモ軽自動車専門店</t>
+          <t>株式会社クロカワ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>唐津店・佐賀店、総在庫500台</t>
+          <t>軽届出済未使用車専門店</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>香川県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -7686,22 +7898,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社ハヤシ（くるまのハヤシ）</t>
+          <t>オートプラネット名古屋</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>倉敷本社。高松・丸亀・倉敷ほか。ダブルツリー（代表 林和樹）と同じグループの可能性</t>
+          <t>輸入中古車</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ダブルツリーとの関係（同一法人か別法人か）が未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7711,22 +7923,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社クロカワ</t>
+          <t>株式会社ネクスト（軽スマイル）</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>軽届出済未使用車専門店</t>
+          <t>北九州、39.8万円専門店</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>香川県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7736,22 +7948,156 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>オートプラネット名古屋</t>
+          <t>株式会社モトヤモビリティーズ（軽モール）</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>輸入中古車</t>
+          <t>倉敷</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>店舗数未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>カーズ松尾自動車</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>小郡・朝倉ほか</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>店舗数未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>軽ステ</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>熊本（けんぐん東・うと・しみず）、総在庫1,300台</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>熊本県</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>運営会社・店舗数未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ネクスト系／ニシオ自販（静岡西部4店舗）／綿仁株式会社（パッカーズ沼津・三島）</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>株式会社Car Service FRIENDS（軽マート）</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>トヨオカ自動車グループ（軽市場）</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>新生オートプラザグループ</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>飯能・坂戸、グループ300台</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>公式サイトから店舗数を判定できず（2〜3店舗の可能性）</t>
         </is>
       </c>
     </row>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>株式会社川内自動車</t>
+          <t>株式会社フレックス・ドリーム</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>宮城県、群馬県、埼玉県、東京都、神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
+          <t>ランクル調布店、ランクルさいたま北店、ランクル小牧店、ランクル湘南厚木店、ランクル仙台東店、ハイエース小牧店、ハイエース湘南厚木店、ハイエース高崎店、ハイエース仙台東店、ハイエース三郷店</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1702,22 +1702,18 @@
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://k-bacca.com/</t>
+          <t>https://www.flexdream.jp/</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/k_bacca_kawauchi/</t>
-        </is>
-      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>https://k-bacca.com/contents/store/index.html
-https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
+          <t>https://www.flexdream.jp/（503で取得不可。検索結果に表示された店舗一覧の抜粋）
+https://compalyze.co.jp/company/2012401009864（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -1727,7 +1723,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
+          <t>ランクル・ハイエース・USトヨタ専門店。店舗名は検索結果に表示された公式サイトの店舗一覧の抜粋による（10店舗、これ以上ある可能性）。公式サイトは503で確認できず。フレックス株式会社（FLEX、31店舗以上で除外）とは別会社。同じ敷地のランクル店・ハイエース店を別々に数えている。</t>
         </is>
       </c>
     </row>
@@ -1737,140 +1733,136 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>株式会社シースペース</t>
+          <t>株式会社川内自動車</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>京都府、大阪府、兵庫県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>大阪府柏原市国分市場2丁目13番1号</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>072-978-1263</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>072-978-1283</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 平松宗彦</t>
-        </is>
-      </c>
+          <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.c-space.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://k-bacca.com/</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>https://twitter.com/C_SPACE_U_POHS</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス事業（車買取）</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/k_bacca_kawauchi/</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>https://k-bacca.com/contents/store/index.html
+https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>株式会社シースペース</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>京都府、大阪府、兵庫県</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>大阪府柏原市国分市場2丁目13番1号</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1263</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1283</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 平松宗彦</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/C_SPACE_U_POHS</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス事業（車買取）</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>https://www.c-space.co.jp/company/
 https://www.c-space.co.jp/shop/
 https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>会社概要に「ユーポス（関西にて現在8店舗）」とある。ユーポス本部のサイトでシースペース運営と表示されるのは7店舗で、久御山店は表示されていない。本社のC-SPACE.（中古車販売）を1店舗として数え、合計9店舗。ほかにニコニコレンタカー5店舗とコバック1店舗（いずれも対象外）を運営。X(Twitter)のURLは検索結果から取得。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>株式会社リトラス</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 津田猛</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.retrus.co.jp/</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.retrus.co.jp/about/office.asp
-https://www.retrus.co.jp/about/</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1872,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>株式会社九州ユーポス</t>
+          <t>株式会社リトラス</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1888,19 +1880,31 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
+          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 津田猛</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.retrus.co.jp/</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
@@ -1908,20 +1912,18 @@
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/hikarinomori/
-https://www.u-pohs.co.jp/kagoshima
-https://www.u-pohs.co.jp/kumamotominami</t>
+          <t>https://www.retrus.co.jp/about/office.asp
+https://www.retrus.co.jp/about/</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
+          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1933,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>株式会社原ホンダ</t>
+          <t>株式会社九州ユーポス</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1939,12 +1941,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
+          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -1959,93 +1961,71 @@
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/hikarinomori/
+https://www.u-pohs.co.jp/kagoshima
+https://www.u-pohs.co.jp/kumamotominami</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>株式会社原ホンダ</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0031/
 https://www.applenet.co.jp/shop/0033/
 https://www.applenet.co.jp/shop/0042/</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>株式会社TRUCK-ONE</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>山口県下松市生野屋南3-3-40</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-1100</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-5660</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.truck-one.com/</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/truckone_official/</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>買取専用窓口あり（0120-751-519）</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.truck-one.com/officelist/
-https://www.truck-one.com/company/</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2035,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>株式会社パッション</t>
+          <t>株式会社TRUCK-ONE</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -2063,44 +2043,52 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、愛知県</t>
+          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>愛知県春日井市味美町2丁目122番地</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>山口県下松市生野屋南3-3-40</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-1100</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-5660</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+          <t>https://www.truck-one.com/</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/truckone_official/</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>買取専門店ラビット勝川店を運営</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>217名（2025年12月）</t>
-        </is>
-      </c>
+          <t>買取専用窓口あり（0120-751-519）</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/company/outline/
-https://www.1963passion.co.jp/company/access/</t>
+          <t>https://www.truck-one.com/officelist/
+https://www.truck-one.com/company/</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2110,7 +2098,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
+          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
         </is>
       </c>
     </row>
@@ -2120,31 +2108,39 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ツチヤ自動車株式会社</t>
+          <t>株式会社ハヤシ</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>千葉県市川市北方町4-1441-8</t>
+          <t>岡山県倉敷市加須山334-4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>http://www.c-hayashi.com/</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
@@ -2152,8 +2148,8 @@
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
-https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
+          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
+https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2163,7 +2159,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
+          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -2173,38 +2169,52 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>株式会社パッション</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>岐阜県、愛知県</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>愛知県春日井市味美町2丁目122番地</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>買取専門店ラビット勝川店を運営</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>217名（2025年12月）</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0004/
-https://www.applenet.co.jp/shop/0007/
-https://www.applenet.co.jp/shop/0046/</t>
+          <t>https://www.1963passion.co.jp/company/outline/
+https://www.1963passion.co.jp/company/access/</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2214,7 +2224,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
+          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -2224,74 +2234,78 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヨシダオートサービス</t>
+          <t>株式会社東和モータース販売</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+          <t>東京都杉並区上高井戸1-21-18</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>072-246-0301</t>
+          <t>03-3303-1146</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>072-246-0302</t>
+          <t>03-3302-6600</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>吉田宜史</t>
+          <t>代表取締役社長 稲葉弘幸</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+          <t>https://towa-motors.com/</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/contact/</t>
+          <t>https://towa-motors.com/contact.html</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/towa.motors</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>218名（2025年1月）</t>
+          <t>50名</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
+          <t>https://towa-motors.com/company.html
+https://towa-motors.com/shop/</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
+          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
         </is>
       </c>
     </row>
@@ -2301,25 +2315,25 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>ツチヤ自動車株式会社</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
+          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
+          <t>千葉県市川市北方町4-1441-8</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -2333,8 +2347,8 @@
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
+https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -2344,7 +2358,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
         </is>
       </c>
     </row>
@@ -2354,20 +2368,20 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>株式会社アップルカーセールス</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -2383,9 +2397,9 @@
       <c r="P29" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/</t>
+https://www.applenet.co.jp/shop/0004/
+https://www.applenet.co.jp/shop/0007/
+https://www.applenet.co.jp/shop/0046/</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -2395,7 +2409,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
         </is>
       </c>
     </row>
@@ -2405,35 +2419,64 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>松下モータース</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -2443,7 +2486,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2496,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2461,57 +2504,42 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
+          <t>浜松市内6店舗</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2549,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2529,12 +2557,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
@@ -2550,9 +2578,9 @@
       <c r="P32" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/</t>
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -2562,7 +2590,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2600,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>株式会社ダブルツリー</t>
+          <t>松下モータース</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2580,22 +2608,18 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店、軽自動車専門店 ハヤシ 高松店、軽自動車専門店 ハヤシ 丸亀店</t>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
@@ -2604,9 +2628,7 @@
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
-https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -2616,7 +2638,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）に加え、軽自動車専門店「くるまのハヤシ」（1972年創業、年間販売約6,100台と求人情報に記載）を運営。ハヤシの店舗は検索結果で高松店・丸亀店を確認。求人情報には倉敷・東岡山の勤務地もあり、実際の店舗数はこれより多い可能性。公式サイト未確認。 注意：別の掲載では「株式会社ハヤシ 倉敷店（本社）」とあり、ハヤシの店舗は別法人（株式会社ハヤシ）の運営の可能性がある。その場合ダブルツリー単体はアップル4店舗で4店舗以下になる。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2648,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2634,37 +2656,57 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 石戸宏樹</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>26名</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://www.apple-car.jp/company</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
         </is>
       </c>
     </row>
@@ -2674,67 +2716,38 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>human joint株式会社</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>03-4446-7735</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>03-5422-8006</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 齊藤博行</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>https://cococar-hp.net/</t>
-        </is>
-      </c>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>中古自動車の販売および買取（事業内容）</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>32名</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/company/</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -2744,7 +2757,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
         </is>
       </c>
     </row>
@@ -2754,262 +2767,458 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>株式会社ファインソレイユ</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>福岡県、佐賀県、長崎県</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>human joint株式会社</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>03-4446-7735</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>03-5422-8006</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 齊藤博行</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>中古自動車の販売および買取（事業内容）</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>32名</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/company/</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>株式会社CIA</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 大内康弘</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー買取（買取センター4か所）</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/company/</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>株式会社NIIZAWA</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>広島県、山口県</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>広島県廿日市市大野原1丁目2-20</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>0829-30-8103</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>0829-30-8104</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/contact/</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keimarket.k
 https://www.facebook.com/share/1AhR49eysR
 https://youtube.com/@keimarket398</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>95名（パート含む）</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/company/
 https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>株式会社Y's GARAGE</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>京都府、鳥取県、島根県</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>京都府宇治市槇島町三十五38-1</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>0774-25-5557</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>代表取締役 桐畑勇志</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>https://k-smile.jp/</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>158名（アルバイト含む、令和8年10月）</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>https://k-smile.jp/company/</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>株式会社ロイヤルオートサービス</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>長野県</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>長野県松本市村井町南2-1-5</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>0120-107-817</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>代表取締役 中田忠章</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/contact/</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/royal_auto_
 https://www.instagram.com/royal_auto_service/?hl=ja
 https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>187名</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>株式会社横浜ユーポス</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>栃木県、神奈川県</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/kouhoku
@@ -3017,12 +3226,12 @@
 https://www.u-pohs.co.jp/tsuzuki</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
         </is>
@@ -3039,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3072,7 +3281,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3092,7 +3301,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3112,7 +3321,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3132,7 +3341,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3142,7 +3351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -3152,7 +3361,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -3162,7 +3371,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3172,7 +3381,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -3242,7 +3451,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -3412,7 +3621,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -3502,7 +3711,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3522,7 +3731,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -3578,7 +3787,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3588,7 +3797,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3598,7 +3807,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3608,111 +3817,121 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B59" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>店舗数の分布</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5〜9店舗</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>21</v>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10〜19店舗</t>
+          <t>5〜9店舗</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20〜30店舗</t>
+          <t>10〜19店舗</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>20〜30店舗</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="B66" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>確度別の社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>確度</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>12</v>
+          <t>確度</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>26</v>
+      <c r="B71" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3726,7 +3945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S63"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4306,7 +4525,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビッグワン</t>
+          <t>株式会社ダブルツリー</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -4314,18 +4533,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>販売店（千葉市内4店舗）</t>
+          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
@@ -4334,17 +4557,17 @@
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
+          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4582,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミナミシマ自動車販売</t>
+          <t>株式会社ビッグワン</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -4367,12 +4590,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
+          <t>販売店（千葉市内4店舗）</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -4387,19 +4610,17 @@
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kashiba/
-https://www.u-pohs.co.jp/kashihara/
-https://www.u-pohs.co.jp/katuragi/</t>
+          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。</t>
+          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4635,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>株式会社ワークス</t>
+          <t>株式会社ミナミシマ自動車販売</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -4422,12 +4643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
+          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -4442,17 +4663,19 @@
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
+          <t>https://www.u-pohs.co.jp/kashiba/
+https://www.u-pohs.co.jp/kashihara/
+https://www.u-pohs.co.jp/katuragi/</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4690,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>株式会社沖縄ユーポス</t>
+          <t>株式会社ワークス</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -4475,12 +4698,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -4495,19 +4718,17 @@
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/misato/
-https://www.u-pohs.co.jp/naha-shintoshin
-https://www.u-pohs.co.jp/noborikawa/</t>
+          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4743,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>株式会社鈴木モータース</t>
+          <t>株式会社沖縄ユーポス</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -4530,12 +4751,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
+          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -4550,9 +4771,9 @@
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0065/
-https://www.applenet.co.jp/shop/0071/
-https://www.applenet.co.jp/shop/0080/</t>
+          <t>https://www.u-pohs.co.jp/misato/
+https://www.u-pohs.co.jp/naha-shintoshin
+https://www.u-pohs.co.jp/noborikawa/</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -4562,7 +4783,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4577,31 +4798,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Dash（運営会社未確認）</t>
+          <t>株式会社鈴木モータース</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>名古屋本店、西三河店、三重鈴鹿店</t>
+          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.car-dash.jp/</t>
-        </is>
-      </c>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
@@ -4609,17 +4826,19 @@
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>https://www.car-dash.jp/</t>
+          <t>https://www.applenet.co.jp/shop/0065/
+https://www.applenet.co.jp/shop/0071/
+https://www.applenet.co.jp/shop/0080/</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4853,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ポケットカーズ（運営会社未確認）</t>
+          <t>Dash（運営会社未確認）</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -4642,12 +4861,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>女池店、三条店、長岡店</t>
+          <t>名古屋本店、西三河店、三重鈴鹿店</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -4656,7 +4875,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -4666,7 +4885,7 @@
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/shop/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -4676,7 +4895,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
+          <t>自社ローン専門店。</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4910,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>古城モータース</t>
+          <t>ポケットカーズ（運営会社未確認）</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -4699,12 +4918,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>高岡本店、富山店、石川白山店</t>
+          <t>女池店、三条店、長岡店</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -4713,7 +4932,7 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/</t>
+          <t>https://www.pocketcars.jp/</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -4723,7 +4942,7 @@
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/（検索結果の抜粋）</t>
+          <t>https://www.pocketcars.jp/shop/</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -4731,7 +4950,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -4744,7 +4967,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>古城モータース</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -4752,29 +4975,21 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8844</t>
-        </is>
-      </c>
+          <t>高岡本店、富山店、石川白山店</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -4784,20 +4999,15 @@
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>https://www.kojyo-motors.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -4810,7 +5020,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -4818,29 +5028,29 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/</t>
+          <t>https://www.autogallery.co.jp/</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -4850,8 +5060,8 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -4861,7 +5071,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
         </is>
       </c>
     </row>
@@ -4876,7 +5086,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -4884,19 +5094,31 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 河野修一</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.csauto.jp/</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
@@ -4904,9 +5126,8 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -4916,7 +5137,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
         </is>
       </c>
     </row>
@@ -4931,7 +5152,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -4939,31 +5160,19 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
-        </is>
-      </c>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 上武英輝</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kamitake.net/</t>
-        </is>
-      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
@@ -4971,8 +5180,9 @@
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -4980,7 +5190,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -4993,7 +5207,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>株式会社カミタケモータース</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -5001,19 +5215,31 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>大阪府、奈良県、大分県</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>枚方本店、奈良店、大分店</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
@@ -5021,9 +5247,8 @@
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -5031,11 +5256,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="S22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -5048,7 +5269,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>株式会社シマダオート商事</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -5056,12 +5277,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -5076,7 +5297,9 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -5086,7 +5309,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>ユーポス以外の事業は未確認。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5324,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>株式会社フロンティアモータース</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -5109,12 +5332,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>大阪府、兵庫県</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -5129,9 +5352,7 @@
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -5141,7 +5362,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポス以外の事業は未確認。</t>
         </is>
       </c>
     </row>
@@ -5151,12 +5372,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FC本部</t>
+          <t>4店舗以下</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーポス</t>
+          <t>株式会社ベネフィット</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -5164,35 +5385,19 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>06-6532-6532</t>
-        </is>
-      </c>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 柏原隆宏</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-pohs.co.jp/</t>
-        </is>
-      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
@@ -5200,18 +5405,19 @@
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/about/company_info
-https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5221,12 +5427,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>4店舗以下</t>
+          <t>FC本部</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>株式会社ユーポス</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -5234,19 +5440,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>06-6532-6532</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 柏原隆宏</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
@@ -5254,19 +5476,18 @@
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://www.u-pohs.co.jp/about/company_info
+https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5502,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社リフトオフ</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
@@ -5289,12 +5510,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>茨城県、千葉県、東京都</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -5309,9 +5530,9 @@
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/</t>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -5336,7 +5557,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>阿部勝自動車工業株式会社</t>
+          <t>株式会社中州自動車</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -5344,23 +5565,19 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>https://k-mishiyo.abekatu.co.jp/</t>
-        </is>
-      </c>
+      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
@@ -5368,15 +5585,21 @@
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr"/>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -5389,27 +5612,31 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎有限会社</t>
+          <t>阿部勝自動車工業株式会社</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>宮崎県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
+          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>https://k-mishiyo.abekatu.co.jp/</t>
+        </is>
+      </c>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
@@ -5417,20 +5644,15 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0056/
-https://www.applenet.co.jp/shop/0149/</t>
+          <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -5443,7 +5665,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>タイガー石油株式会社</t>
+          <t>アップル宮崎有限会社</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -5451,12 +5673,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>宮崎県</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
+          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -5471,7 +5693,8 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0056/
+https://www.applenet.co.jp/shop/0149/</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
@@ -5481,7 +5704,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5719,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>大谷自動車株式会社</t>
+          <t>タイガー石油株式会社</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -5504,47 +5727,27 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>大阪府、和歌山県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>大阪本店、和歌山店</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>大阪府泉佐野市長滝753</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>072-465-0492</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>072-465-3109</t>
-        </is>
-      </c>
+          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.otani-j.co.jp/</t>
-        </is>
-      </c>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>81名</t>
-        </is>
-      </c>
+      <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>https://www.otani-j.co.jp/company</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -5552,7 +5755,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -5565,7 +5772,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>平岩石油販売株式会社</t>
+          <t>大谷自動車株式会社</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -5573,28 +5780,47 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>大阪府、和歌山県</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>アップル練馬関町店、アップル板橋環8店</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>大阪本店、和歌山店</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>大阪府泉佐野市長滝753</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>072-465-0492</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>072-465-3109</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.otani-j.co.jp/</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0175/
-https://www.applenet.co.jp/shop/0247/</t>
+          <t>https://www.otani-j.co.jp/company</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -5602,11 +5828,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -5619,7 +5841,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>株式会社B&amp;F</t>
+          <t>平岩石油販売株式会社</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -5627,12 +5849,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>アップル古河4号店、アップル守谷店</t>
+          <t>アップル練馬関町店、アップル板橋環8店</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -5647,8 +5869,8 @@
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0140/
-https://www.applenet.co.jp/shop/0146/</t>
+          <t>https://www.applenet.co.jp/shop/0175/
+https://www.applenet.co.jp/shop/0247/</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -5673,7 +5895,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>株式会社NEXTモビィ</t>
+          <t>株式会社B&amp;F</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -5681,12 +5903,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
+          <t>アップル古河4号店、アップル守谷店</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -5701,8 +5923,8 @@
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukuoka-inter
-https://www.u-pohs.co.jp/kokurahigashi-inter</t>
+          <t>https://www.applenet.co.jp/shop/0140/
+https://www.applenet.co.jp/shop/0146/</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -5712,7 +5934,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5949,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>株式会社PlusOne</t>
+          <t>株式会社NEXTモビィ</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -5735,12 +5957,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>アップル安城南店、アップル弥富1号線店</t>
+          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -5755,8 +5977,8 @@
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0129/
-https://www.applenet.co.jp/shop/0219/</t>
+          <t>https://www.u-pohs.co.jp/fukuoka-inter
+https://www.u-pohs.co.jp/kokurahigashi-inter</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -5766,7 +5988,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5781,7 +6003,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>株式会社SHIMAカーライフコネクテッド</t>
+          <t>株式会社PlusOne</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -5789,12 +6011,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>アップル金沢店、アップル高岡店</t>
+          <t>アップル安城南店、アップル弥富1号線店</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -5809,8 +6031,8 @@
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0313/
-https://www.applenet.co.jp/shop/0339/</t>
+          <t>https://www.applenet.co.jp/shop/0129/
+https://www.applenet.co.jp/shop/0219/</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -5835,7 +6057,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>株式会社WinWinサービス</t>
+          <t>株式会社SHIMAカーライフコネクテッド</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -5843,12 +6065,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>アップル盛岡盛南店、アップル盛岡北店</t>
+          <t>アップル金沢店、アップル高岡店</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -5863,8 +6085,8 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0117/
-https://www.applenet.co.jp/shop/0137/</t>
+          <t>https://www.applenet.co.jp/shop/0313/
+https://www.applenet.co.jp/shop/0339/</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -5889,7 +6111,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>株式会社イトー</t>
+          <t>株式会社WinWinサービス</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -5897,12 +6119,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>アップル岸和田店、アップル河内長野中央店</t>
+          <t>アップル盛岡盛南店、アップル盛岡北店</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -5917,8 +6139,8 @@
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0258/
-https://www.applenet.co.jp/shop/0278/</t>
+          <t>https://www.applenet.co.jp/shop/0117/
+https://www.applenet.co.jp/shop/0137/</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5928,7 +6150,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>アップル以外の店舗は未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5943,7 +6165,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>株式会社インデックス</t>
+          <t>株式会社イトー</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -5951,12 +6173,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
+          <t>アップル岸和田店、アップル河内長野中央店</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -5971,8 +6193,8 @@
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0018/
-https://www.applenet.co.jp/shop/0029/</t>
+          <t>https://www.applenet.co.jp/shop/0258/
+https://www.applenet.co.jp/shop/0278/</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -5982,7 +6204,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップル以外の店舗は未確認。</t>
         </is>
       </c>
     </row>
@@ -5997,7 +6219,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>株式会社イーグルオートサービス</t>
+          <t>株式会社インデックス</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -6005,12 +6227,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
+          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -6025,8 +6247,8 @@
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0032/
-https://www.applenet.co.jp/shop/0063/</t>
+          <t>https://www.applenet.co.jp/shop/0018/
+https://www.applenet.co.jp/shop/0029/</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -6051,7 +6273,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>株式会社エムエフノースジャパン</t>
+          <t>株式会社イーグルオートサービス</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -6059,12 +6281,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -6079,8 +6301,8 @@
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0035/
-https://www.applenet.co.jp/shop/0043/</t>
+          <t>https://www.applenet.co.jp/shop/0032/
+https://www.applenet.co.jp/shop/0063/</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -6105,7 +6327,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>株式会社オカモト</t>
+          <t>株式会社エムエフノースジャパン</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -6113,12 +6335,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>アップル西帯広店、アップル帯広店</t>
+          <t>、</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -6133,8 +6355,8 @@
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0307/
-https://www.applenet.co.jp/shop/0334/</t>
+          <t>https://www.applenet.co.jp/shop/0035/
+https://www.applenet.co.jp/shop/0043/</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
@@ -6159,7 +6381,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>株式会社オリンピアオート</t>
+          <t>株式会社オカモト</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -6167,12 +6389,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>アップルひたちなか店、アップル那珂中央店</t>
+          <t>アップル西帯広店、アップル帯広店</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -6187,8 +6409,8 @@
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0208/
-https://www.applenet.co.jp/shop/0280/</t>
+          <t>https://www.applenet.co.jp/shop/0307/
+https://www.applenet.co.jp/shop/0334/</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -6213,7 +6435,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートグローリー</t>
+          <t>株式会社オリンピアオート</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -6221,12 +6443,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福重店、ユーポス直方店</t>
+          <t>アップルひたちなか店、アップル那珂中央店</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -6241,8 +6463,8 @@
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukushige
-https://www.u-pohs.co.jp/nogata</t>
+          <t>https://www.applenet.co.jp/shop/0208/
+https://www.applenet.co.jp/shop/0280/</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -6252,7 +6474,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6489,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>株式会社クインオート</t>
+          <t>株式会社オートグローリー</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -6275,12 +6497,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>京都府、兵庫県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>ユーポス亀岡店、ユーポス三田店</t>
+          <t>ユーポス福重店、ユーポス直方店</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -6295,8 +6517,8 @@
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kameoka
-https://www.u-pohs.co.jp/sanda/</t>
+          <t>https://www.u-pohs.co.jp/fukushige
+https://www.u-pohs.co.jp/nogata</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -6321,7 +6543,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>株式会社サコダ車輛</t>
+          <t>株式会社クインオート</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -6329,12 +6551,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>京都府、兵庫県</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>アップル海田店、アップル東広島店</t>
+          <t>ユーポス亀岡店、ユーポス三田店</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -6349,8 +6571,8 @@
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0297/
-https://www.applenet.co.jp/shop/0298/</t>
+          <t>https://www.u-pohs.co.jp/kameoka
+https://www.u-pohs.co.jp/sanda/</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -6360,7 +6582,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 社名の正式表記は「サコダ車輌」の可能性。本社は広島市中区舟入南、売上高158億円・従業員240名（求人情報）。自社店舗の海田店（軽自動車専門）と佐伯区五日市の拠点もあり、合計4か所以上。自社サイト未確認のため境界扱い。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6597,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>株式会社シブヤエネックスホールディングス</t>
+          <t>株式会社サコダ車輛</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -6383,12 +6605,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>アップル相模原城山店、アップル大井松田インター店</t>
+          <t>アップル海田店、アップル東広島店</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -6403,8 +6625,8 @@
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0266/
-https://www.applenet.co.jp/shop/0292/</t>
+          <t>https://www.applenet.co.jp/shop/0297/
+https://www.applenet.co.jp/shop/0298/</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -6414,7 +6636,7 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 社名の正式表記は「サコダ車輌」の可能性。本社は広島市中区舟入南、売上高158億円・従業員240名（求人情報）。自社店舗の海田店（軽自動車専門）と佐伯区五日市の拠点もあり、合計4か所以上。自社サイト未確認のため境界扱い。</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6651,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>株式会社スズキアリーナ瑞穂</t>
+          <t>株式会社シブヤエネックスホールディングス</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -6437,12 +6659,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>アップル青梅店、アップル西東京店</t>
+          <t>アップル相模原城山店、アップル大井松田インター店</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -6457,8 +6679,8 @@
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0057/
-https://www.applenet.co.jp/shop/0100/</t>
+          <t>https://www.applenet.co.jp/shop/0266/
+https://www.applenet.co.jp/shop/0292/</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
@@ -6483,7 +6705,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>株式会社トップワン</t>
+          <t>株式会社スズキアリーナ瑞穂</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -6491,12 +6713,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>アップル豊田梅坪店、アップル豊田南店</t>
+          <t>アップル青梅店、アップル西東京店</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -6511,8 +6733,8 @@
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0075/
-https://www.applenet.co.jp/shop/0126/</t>
+          <t>https://www.applenet.co.jp/shop/0057/
+https://www.applenet.co.jp/shop/0100/</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -6537,7 +6759,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社トップワン</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -6545,12 +6767,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>アップル大和店、アップル相模原店</t>
+          <t>アップル豊田梅坪店、アップル豊田南店</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -6565,8 +6787,8 @@
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0306/
-https://www.applenet.co.jp/shop/0340/</t>
+          <t>https://www.applenet.co.jp/shop/0075/
+https://www.applenet.co.jp/shop/0126/</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -6591,7 +6813,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビーインプレスト</t>
+          <t>株式会社トータス</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -6599,12 +6821,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>アップル宇都宮北店、アップル大田原店</t>
+          <t>アップル大和店、アップル相模原店</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -6619,8 +6841,8 @@
       <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0211/
-https://www.applenet.co.jp/shop/0303/</t>
+          <t>https://www.applenet.co.jp/shop/0306/
+https://www.applenet.co.jp/shop/0340/</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
@@ -6645,7 +6867,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファミリー</t>
+          <t>株式会社ビーインプレスト</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -6653,12 +6875,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>ファミリー可児店、ファミリー各務原店</t>
+          <t>アップル宇都宮北店、アップル大田原店</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -6673,17 +6895,18 @@
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0211/
+https://www.applenet.co.jp/shop/0303/</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6921,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミヤチ</t>
+          <t>株式会社ファミリー</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -6711,7 +6934,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>アップル岐阜長良店、アップル関店</t>
+          <t>ファミリー可児店、ファミリー各務原店</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -6726,18 +6949,17 @@
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0101/
-https://www.applenet.co.jp/shop/0155/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6974,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>株式会社湯浅</t>
+          <t>株式会社ミヤチ</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -6760,12 +6982,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>アップル白井店、アップル松戸本店</t>
+          <t>アップル岐阜長良店、アップル関店</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -6780,8 +7002,8 @@
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0287/
-https://www.applenet.co.jp/shop/0293/</t>
+          <t>https://www.applenet.co.jp/shop/0101/
+https://www.applenet.co.jp/shop/0155/</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -6806,7 +7028,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>株式会社関西オート</t>
+          <t>株式会社湯浅</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -6814,27 +7036,19 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>八尾店、平野店</t>
+          <t>アップル白井店、アップル松戸本店</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 大川純平</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kansai-auto.jp/</t>
-        </is>
-      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
@@ -6842,7 +7056,8 @@
       <c r="P55" s="2" t="inlineStr"/>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>https://www.kansai-auto.jp/company/outline/</t>
+          <t>https://www.applenet.co.jp/shop/0287/
+https://www.applenet.co.jp/shop/0293/</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -6850,7 +7065,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -6863,20 +7082,20 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Re-BOOT株式会社</t>
+          <t>株式会社車のせんいち</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>アップル大阪平野店</t>
+          <t>みどり本店、伊勢崎店</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -6891,15 +7110,19 @@
       <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0284/</t>
+          <t>求人情報（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr"/>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>軽自動車39.8万円専門店ほか。確認できたのは2店舗と新店舗（みどり市笠懸町、オープン予定）。公式サイト未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -6912,11 +7135,11 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>北摂オート株式会社</t>
+          <t>株式会社関西オート</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -6925,28 +7148,20 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>大阪府箕面市桜井2-16-17</t>
-        </is>
-      </c>
+          <t>八尾店、平野店</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>072-723-1102</t>
-        </is>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 喜多克之</t>
+          <t>代表取締役社長 大川純平</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>https://hokusetu-auto.com/</t>
+          <t>https://www.kansai-auto.jp/</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
@@ -6956,7 +7171,7 @@
       <c r="P57" s="2" t="inlineStr"/>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>https://hokusetu-auto.com/company.php</t>
+          <t>https://www.kansai-auto.jp/company/outline/</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
@@ -6977,7 +7192,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>有限会社タイヨウ</t>
+          <t>Re-BOOT株式会社</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -6990,7 +7205,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>ユーポス富田林店</t>
+          <t>アップル大阪平野店</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -7005,7 +7220,7 @@
       <c r="P58" s="2" t="inlineStr"/>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0284/</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
@@ -7013,11 +7228,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -7030,7 +7241,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>株式会社We Car CORE</t>
+          <t>北摂オート株式会社</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -7043,14 +7254,30 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>ユーポス貝塚店</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>大阪府箕面市桜井2-16-17</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>072-723-1102</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 喜多克之</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>https://hokusetu-auto.com/</t>
+        </is>
+      </c>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
@@ -7058,7 +7285,7 @@
       <c r="P59" s="2" t="inlineStr"/>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://hokusetu-auto.com/company.php</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
@@ -7066,11 +7293,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -7083,7 +7306,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>株式会社cantera</t>
+          <t>有限会社タイヨウ</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -7096,7 +7319,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環四條畷店</t>
+          <t>ユーポス富田林店</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -7136,7 +7359,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>株式会社プロンザ</t>
+          <t>株式会社We Car CORE</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -7149,7 +7372,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>ユーポス枚方店</t>
+          <t>ユーポス貝塚店</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -7189,7 +7412,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>株式会社ポロ</t>
+          <t>株式会社cantera</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -7202,30 +7425,14 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>大阪府高槻市富田町6丁目15-13</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>072-694-6641</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>072-694-9913</t>
-        </is>
-      </c>
+          <t>ユーポス外環四條畷店</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.polojp.com/</t>
-        </is>
-      </c>
+      <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
@@ -7233,7 +7440,7 @@
       <c r="P62" s="2" t="inlineStr"/>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>https://www.polojp.com/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -7241,7 +7448,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -7254,7 +7465,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>豊栄モータース</t>
+          <t>株式会社プロンザ</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -7267,7 +7478,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>ユーポス寝屋川店</t>
+          <t>ユーポス枚方店</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -7292,6 +7503,124 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ポロ</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>大阪府高槻市富田町6丁目15-13</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>072-694-6641</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>072-694-9913</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>豊栄モータース</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス寝屋川店</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
           <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。（法人格の表示なし）</t>
         </is>
       </c>
@@ -7307,7 +7636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7363,22 +7692,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>車のせんいち</t>
+          <t>株式会社くるまのハチオウジ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>群馬（みどり・伊勢崎・桐生・太田・前橋）</t>
+          <t>八王子、グループ会社あり</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>公式の店舗一覧が見つからない</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7388,22 +7717,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>株式会社くるまのハチオウジ</t>
+          <t>エジソングループ</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>八王子、グループ会社あり</t>
+          <t>岐阜市、新車・登録済未使用車専門店</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>運営会社・店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7413,22 +7742,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>エジソングループ</t>
+          <t>プラスパージャパン（NEW CARS）</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>岐阜市、新車・登録済未使用車専門店</t>
+          <t>あきる野</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>運営会社・店舗数未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7438,22 +7767,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>プラスパージャパン（NEW CARS）</t>
+          <t>株式会社アクティブコレクション</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>あきる野</t>
+          <t>リバティの子会社。横浜・大和、グループ総在庫4,000台</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>店舗数未確認。リバティとの関係（子会社）をどう扱うか要判断</t>
         </is>
       </c>
     </row>
@@ -7463,18 +7792,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>フレックス・ドリーム株式会社</t>
+          <t>株式会社クレタ（北海道軽パーク）</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ランクル・ハイエース専門。調布・仙台東・小牧ほか（検索結果）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>苫小牧</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>公式サイトが503で取得不可</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -7484,22 +7817,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>株式会社アクティブコレクション</t>
+          <t>軽プラザサンライズ</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>リバティの子会社。横浜・大和、グループ総在庫4,000台</t>
+          <t>弘前・八戸</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認。リバティとの関係（子会社）をどう扱うか要判断</t>
+          <t>未確認（2店舗の可能性）</t>
         </is>
       </c>
     </row>
@@ -7509,22 +7842,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>株式会社クレタ（北海道軽パーク）</t>
+          <t>良質車専門店ネクスト</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>苫小牧</t>
+          <t>会津若松・いわき・白河</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>運営会社未確認</t>
         </is>
       </c>
     </row>
@@ -7534,22 +7867,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>軽プラザサンライズ</t>
+          <t>興和自動車販売（KOWA飯田）</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>弘前・八戸</t>
+          <t>南信地区</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>未確認（2店舗の可能性）</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -7559,22 +7892,18 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>良質車専門店ネクスト</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>会津若松・いわき・白河</t>
-        </is>
-      </c>
+          <t>株式会社佐野自動車商会（トラスト新潟）</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>運営会社未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -7584,17 +7913,13 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>興和自動車販売（KOWA飯田）</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>南信地区</t>
-        </is>
-      </c>
+          <t>株式会社Smile Carz</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7609,15 +7934,15 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>株式会社佐野自動車商会（トラスト新潟）</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>新潟県</t>
-        </is>
-      </c>
+          <t>株式会社BIG BRIDGE／株式会社five star</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>自社ローン</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
@@ -7630,18 +7955,14 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>株式会社Smile Carz</t>
+          <t>株式会社ヤマト（島根）／共盛自動車グループ（広島）／株式会社日本カードック（尼崎）／株式会社グランドエンタープライズ（京都）</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>山口県</t>
-        </is>
-      </c>
+      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>業態・店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7651,12 +7972,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>株式会社BIG BRIDGE／株式会社five star</t>
+          <t>株式会社ルートシックス</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>自社ローン</t>
+          <t>キャンピングカー専門、水戸・埼玉</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -7672,14 +7993,18 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヤマト（島根）／共盛自動車グループ（広島）／株式会社日本カードック（尼崎）／株式会社グランドエンタープライズ（京都）</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
+          <t>株式会社タックス横浜／株式会社タックス宮城野／株式会社キリン自動車（ONIX）</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>FC加盟店</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>業態・店舗数未確認</t>
+          <t>タックス・オニキス本部の店舗一覧が取得できず店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7689,18 +8014,18 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>株式会社ルートシックス</t>
+          <t>株式会社OSG（ミニバン専門店OSG）／OSINC.／株式会社N.T ART</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー専門、水戸・埼玉</t>
+          <t>大阪</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>店舗数未確認（1〜2店舗の可能性）</t>
         </is>
       </c>
     </row>
@@ -7710,18 +8035,18 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>株式会社タックス横浜／株式会社タックス宮城野／株式会社キリン自動車（ONIX）</t>
+          <t>LACモービル（アネックス・キャンピングカーランド・デルタリンクの3社）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>FC加盟店</t>
+          <t>キャンピングカー。宮城・横浜・埼玉・入間・千葉・名古屋・京都・大阪・倉敷・岐阜・新潟（直営9店舗＋FC）</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>タックス・オニキス本部の店舗一覧が取得できず店舗数未確認</t>
+          <t>3社の共通ブランドで、どの会社が何店舗を運営しているか未確認（各社4店舗以下の可能性）</t>
         </is>
       </c>
     </row>
@@ -7731,18 +8056,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>株式会社OSG（ミニバン専門店OSG）／OSINC.／株式会社N.T ART</t>
+          <t>プチモ軽自動車専門店</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>大阪</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>佐賀店・唐津店・佐世保店（2025年12月開店）。運営は株式会社ヒューベストオートの可能性</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認（1〜2店舗の可能性）</t>
+          <t>3店舗前後で境界未満の可能性</t>
         </is>
       </c>
     </row>
@@ -7752,18 +8081,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LACモービル（アネックス・キャンピングカーランド・デルタリンクの3社）</t>
+          <t>株式会社クロカワ</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー。宮城・横浜・埼玉・入間・千葉・名古屋・京都・大阪・倉敷・岐阜・新潟（直営9店舗＋FC）</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
+          <t>軽届出済未使用車専門店</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3社の共通ブランドで、どの会社が何店舗を運営しているか未確認（各社4店舗以下の可能性）</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -7773,22 +8106,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>東和モータース販売</t>
+          <t>オートプラネット名古屋</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー。東京本店・埼玉入間・所沢・本庄・横浜・千葉・世田谷・札幌</t>
+          <t>輸入中古車</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>公式サイトに接続できず（接続エラー）</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7798,22 +8131,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Yacco（株式会社ホワイトハウス系）</t>
+          <t>株式会社ネクスト（軽スマイル）</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー。守谷本店・水海道・仙台・横浜・名古屋買取センター</t>
+          <t>北九州、39.8万円専門店</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>運営会社と店舗数が未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7823,22 +8156,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>プチモ軽自動車専門店</t>
+          <t>株式会社モトヤモビリティーズ（軽モール）</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>唐津店・佐賀店、総在庫500台</t>
+          <t>倉敷</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7848,22 +8181,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>株式会社ハヤシ（くるまのハヤシ）</t>
+          <t>カーズ松尾自動車</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>倉敷本社。高松・丸亀・倉敷ほか。ダブルツリー（代表 林和樹）と同じグループの可能性</t>
+          <t>小郡・朝倉ほか</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ダブルツリーとの関係（同一法人か別法人か）が未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -7873,22 +8206,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>株式会社クロカワ</t>
+          <t>軽ステ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>軽届出済未使用車専門店</t>
+          <t>熊本（けんぐん東・うと・しみず）、総在庫1,300台</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>香川県</t>
+          <t>熊本県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>運営会社・公式サイト未確認（3店舗前後）</t>
         </is>
       </c>
     </row>
@@ -7898,22 +8231,14 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>オートプラネット名古屋</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>輸入中古車</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>愛知県</t>
-        </is>
-      </c>
+          <t>株式会社ネクスト系／ニシオ自販（静岡西部4店舗）／綿仁株式会社（パッカーズ沼津・三島）</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -7923,22 +8248,18 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社ネクスト（軽スマイル）</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>北九州、39.8万円専門店</t>
-        </is>
-      </c>
+          <t>株式会社Car Service FRIENDS（軽マート）</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -7948,22 +8269,18 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社モトヤモビリティーズ（軽モール）</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>倉敷</t>
-        </is>
-      </c>
+          <t>トヨオカ自動車グループ（軽市場）</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -7973,129 +8290,20 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>カーズ松尾自動車</t>
+          <t>新生オートプラザグループ</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>小郡・朝倉ほか</t>
+          <t>飯能・坂戸、グループ300台</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>店舗数未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>軽ステ</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>熊本（けんぐん東・うと・しみず）、総在庫1,300台</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>熊本県</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>運営会社・店舗数未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ネクスト系／ニシオ自販（静岡西部4店舗）／綿仁株式会社（パッカーズ沼津・三島）</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>株式会社Car Service FRIENDS（軽マート）</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>兵庫県</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>トヨオカ自動車グループ（軽市場）</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>兵庫県</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>新生オートプラザグループ</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>飯能・坂戸、グループ300台</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>公式サイトから店舗数を判定できず（2〜3店舗の可能性）</t>
         </is>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1117,128 +1117,130 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>株式会社アビックスコーポレーション</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、千葉県、東京都、神奈川県、愛知県</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>AVIX IMPORT 府中店、AVIX IMPORT 多摩センター店、AVIX IMPORT 川崎生田店、AVIX IMPORT 木更津金田インター店、ほか関東9店舗、仙台東インター店、名古屋北店</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avix.co.jp/</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>https://car.motor-fan.jp/ucar/shop/9510200（検索結果の抜粋）
+https://www.goo-net.com/user_review/0500520/（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>輸入車専門店AVIX IMPORT。店舗紹介文の「関東地区13店舗＆関西地区3店舗＆仙台東インター＆名古屋北店」から、関西3店舗（アビックス大阪株式会社の運営）を除いて15店舗とした。仙台・名古屋の運営会社は未確認。公式サイトは接続できず。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>株式会社KSファクトリー</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>宮城県、茨城県、栃木県、群馬県、千葉県、愛知県、福岡県</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>仙台店、ランクル宇都宮店、アップル宇都宮外環若草店、前橋インター店、アップル前橋店、アップルつくば学園店、つくば店、アップル土浦学園東大通り店、千葉北店、ハイエース名古屋店、ハイエース福岡店、アップル福岡南バイパス店、福岡須恵インター店、アップル福岡久留米店</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>千葉県佐倉市ユーカリが丘7-21-3</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>043-376-9195</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>代表取締役社長 遠藤和広</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>https://ksfactory.jp/</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>https://ksfactory.jp/contact/</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/ksfactory_carshop/
 https://www.youtube.com/@KS_factory
 https://www.tiktok.com/@ksfactory4wd</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>77名</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>https://ksfactory.jp/company/
 https://ksfactory.jp/shop/head-office/
 https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>ランクル・ハイエース専門店とアップル加盟店を運営。公式サイトの店舗一覧13件に、アップル本部サイトでKSファクトリー運営と表示される「アップル福岡久留米店」（公式サイトの一覧には無し）を加えて14店舗。本社ページの電話番号欄は空欄。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>株式会社アタックス</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県、愛知県、三重県</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>アップル津島中央道店、アップル厚木・北129号店、アップル富田302号店、アップル小田原飯泉店、アップル昭和橋通店、アップル桑名七和店、アップル中村畑江通店、アップル稲沢店、アップル西・康生通店、アップル南23号店、アップル桑名大桑店、アップル黒川北41号店</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0008/
-https://www.applenet.co.jp/shop/0021/
-https://www.applenet.co.jp/shop/0022/</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1250,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>株式会社ジェイ・ピー</t>
+          <t>株式会社アタックス</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1256,12 +1258,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>宮城県、福島県、栃木県、群馬県、埼玉県</t>
+          <t>神奈川県、愛知県、三重県</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>アップル坂戸鶴ヶ島インター店、アップル太田店、アップル川越16号店、アップル郡山インター店、アップル深谷17号店、アップル西那須野店、アップル朝霞店、アップル仙台六丁目店、アップル東松山店、アップル白河店、アップル所沢店、アップル鴻巣店</t>
+          <t>アップル津島中央道店、アップル厚木・北129号店、アップル富田302号店、アップル小田原飯泉店、アップル昭和橋通店、アップル桑名七和店、アップル中村畑江通店、アップル稲沢店、アップル西・康生通店、アップル南23号店、アップル桑名大桑店、アップル黒川北41号店</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
@@ -1277,9 +1279,9 @@
       <c r="P12" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0015/
-https://www.applenet.co.jp/shop/0037/
-https://www.applenet.co.jp/shop/0044/</t>
+https://www.applenet.co.jp/shop/0008/
+https://www.applenet.co.jp/shop/0021/
+https://www.applenet.co.jp/shop/0022/</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1289,7 +1291,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル坂戸鶴ヶ島インター店）〒350-2211 埼玉県鶴ヶ島市脚折町5-4-13 TEL 049-279-3500 FAX 049-279-3501。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1301,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>高橋自動車販売株式会社</t>
+          <t>株式会社ジェイ・ピー</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1307,12 +1309,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>東京都、神奈川県、愛知県</t>
+          <t>宮城県、福島県、栃木県、群馬県、埼玉県</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>アップル江田駅前店、アップル江戸川環七店、アップル豊橋佐藤店、アップル248岡崎店、アップル平塚田村店、アップル中山宮の下店、アップル町田南店、アップル岡崎六ッ美店、アップル東戸塚店、アップル蒲郡店、アップル豊川インター店、アップル岡崎緑丘店</t>
+          <t>アップル坂戸鶴ヶ島インター店、アップル太田店、アップル川越16号店、アップル郡山インター店、アップル深谷17号店、アップル西那須野店、アップル朝霞店、アップル仙台六丁目店、アップル東松山店、アップル白河店、アップル所沢店、アップル鴻巣店</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1328,76 +1330,127 @@
       <c r="P13" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0015/
+https://www.applenet.co.jp/shop/0037/
+https://www.applenet.co.jp/shop/0044/</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル坂戸鶴ヶ島インター店）〒350-2211 埼玉県鶴ヶ島市脚折町5-4-13 TEL 049-279-3500 FAX 049-279-3501。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>高橋自動車販売株式会社</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>東京都、神奈川県、愛知県</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>アップル江田駅前店、アップル江戸川環七店、アップル豊橋佐藤店、アップル248岡崎店、アップル平塚田村店、アップル中山宮の下店、アップル町田南店、アップル岡崎六ッ美店、アップル東戸塚店、アップル蒲郡店、アップル豊川インター店、アップル岡崎緑丘店</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0013/
 https://www.applenet.co.jp/shop/0014/
 https://www.applenet.co.jp/shop/0024/</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。軽四専門「メガタウン」（豊田市）も運営しており、実際の店舗数はこれより多い可能性。 参考：店舗の連絡先（アップル江田駅前店）〒225-0013 神奈川県横浜市青葉区荏田町1236-7東急江田駅前ドエリング1F TEL 045-912-7560 FAX 045-912-7566。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>株式会社メーカーズ</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>福岡県、佐賀県</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>ケイカフェ おおのじょう店、ケイカフェ しんぐう店、ケイカフェ こくらみなみ店、ケイカフェ くるめ店、ケイカフェ ちくしの店、ケイカフェ いいづか店、ケイカフェ やはた店、ケイカフェ ふくおかにし店、ケイカフェ とす店、アップル福岡東店、アップル福岡八幡店</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>福岡県福岡市西区石丸4丁目5-53</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>092-753-6611</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>092-753-6622</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>代表取締役社長 白井剛</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>https://www.k-cafe.com/</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>https://www.k-cafe.com/contact/</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/kcafe_official
 https://www.facebook.com/kcarandcafe
@@ -1406,108 +1459,23 @@
 https://www.youtube.com/@kcafe_fukuoka/videos</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>https://www.k-cafe.com/company/
 https://www.k-cafe.com/
 https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ケイカフェ9店舗（公式サイトの店舗情報）と、アップル加盟店2店舗（本部サイトで運営会社を確認）の合計。ONIXフランチャイズにも加盟（沿革）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>株式会社軽自動車館</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>北海道、宮城県</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>札幌本店、札幌東店、新さっぽろ店、札幌清田店、北見店、旭川店、函館店、苫小牧店、帯広店、釧路店、せんだい店</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>北海道札幌市中央区北5条西6丁目2-2</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>011-200-0312</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>011-200-0357</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 阿部章一</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>https://keijidousyakan.com/</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>https://keijidousyakan.com/contact/（現在お問い合わせ見合わせ中の表示あり）</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCtYVtXtEHCIxOCia6QF0nBw</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>自動車の買取（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>117名（2026年1月）</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>https://keijidousyakan.com/about/company/
-https://keijidousyakan.com/shops/</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>店舗名は公式の店舗ページから。札幌本店と札幌東店はURL（sapporo / satsuhigashi）から推定した店舗名。</t>
         </is>
       </c>
     </row>
@@ -1517,160 +1485,169 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>日免オートシステム株式会社</t>
+          <t>株式会社軽自動車館</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>北海道、宮城県</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>美使用軽専門店 江別店、美使用軽専門店 静内店（新ひだか）、美使用軽専門店 小樽店、美使用軽専門店 旭川店、美使用軽専門店 十勝音更店、美使用軽専門店 イオンスーパーセンター三笠店、美使用軽専門店 スーパーアークス新琴似店、カーセブン札幌北店、カーセブン北見店、カーセブン十勝音更店</t>
+          <t>札幌本店、札幌東店、新さっぽろ店、札幌清田店、北見店、旭川店、函館店、苫小牧店、帯広店、釧路店、せんだい店</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>北海道札幌市北区東茨戸1条1丁目8番5号</t>
+          <t>北海道札幌市中央区北5条西6丁目2-2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>011-774-3111</t>
+          <t>011-200-0312</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>011-775-8906</t>
+          <t>011-200-0357</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>代表取締役社長 安部直人</t>
+          <t>代表取締役社長 阿部章一</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.nichimen-g.co.jp/</t>
+          <t>https://keijidousyakan.com/</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://www.nichimen-g.co.jp/company/contact/</t>
+          <t>https://keijidousyakan.com/contact/（現在お問い合わせ見合わせ中の表示あり）</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/channel/UCtYVtXtEHCIxOCia6QF0nBw</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>自動車の買取（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>117名（2026年1月）</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>https://keijidousyakan.com/about/company/
+https://keijidousyakan.com/shops/</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>店舗名は公式の店舗ページから。札幌本店と札幌東店はURL（sapporo / satsuhigashi）から推定した店舗名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>日免オートシステム株式会社</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>美使用軽専門店 江別店、美使用軽専門店 静内店（新ひだか）、美使用軽専門店 小樽店、美使用軽専門店 旭川店、美使用軽専門店 十勝音更店、美使用軽専門店 イオンスーパーセンター三笠店、美使用軽専門店 スーパーアークス新琴似店、カーセブン札幌北店、カーセブン北見店、カーセブン十勝音更店</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>北海道札幌市北区東茨戸1条1丁目8番5号</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>011-774-3111</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>011-775-8906</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 安部直人</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nichimen-g.co.jp/</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nichimen-g.co.jp/company/contact/</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/nichimen_mishiyou/
 https://www.youtube.com/channel/UC-iuDCLbQ6px8P3WISQrLdg</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>ニチメン買取（買取・査定）あり</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>210名（グループ全体・パート含む）</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>https://www.nichimen-g.co.jp/company/
 https://www.nichimen-g.co.jp/company/stores/
 https://www.nichimen-g.co.jp/mishiyou/</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>ニチメングループ。会社概要の「総店舗数31店舗（北海道内グループ全体）」には、スズキ販売店・レンタカー・整備工場・板金・建機なども含まれる。中古車の販売・買取の店舗として、美使用軽専門店7店舗とカーセブン加盟店3店舗を数えた。新琴似本店・札幌本店の位置づけは未確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ジョブカーズ</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>大阪府</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>ジョブカーズ本店、南港店、枚方東店、枚方南店、枚方北店、枚方インポート店、八尾店、守口店、COOL店、バイパス店</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市茄子作2-33-25</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>072-852-8500</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>072-852-8501</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>吉村浩二</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/contact/</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>70名</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/company/</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>同じ名前の別会社に注意：jobcars.jp は札幌の「ジョブカーズ株式会社」で別会社。枚方の会社の公式サイトは jobcars.net。枚方北店は大型トラック・バス、COOL店とバイパス店は会社概要に住所の記載がない。</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1657,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>株式会社フレックス・ドリーム</t>
+          <t>株式会社ジョブカーズ</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1688,42 +1665,65 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>宮城県、群馬県、埼玉県、東京都、神奈川県、愛知県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ランクル調布店、ランクルさいたま北店、ランクル小牧店、ランクル湘南厚木店、ランクル仙台東店、ハイエース小牧店、ハイエース湘南厚木店、ハイエース高崎店、ハイエース仙台東店、ハイエース三郷店</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>ジョブカーズ本店、南港店、枚方東店、枚方南店、枚方北店、枚方インポート店、八尾店、守口店、COOL店、バイパス店</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市茄子作2-33-25</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>072-852-8500</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>072-852-8501</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>吉村浩二</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.flexdream.jp/</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t>https://jobcars.net/</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://jobcars.net/contact/</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>70名</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>https://www.flexdream.jp/（503で取得不可。検索結果に表示された店舗一覧の抜粋）
-https://compalyze.co.jp/company/2012401009864（検索結果の抜粋）</t>
+          <t>https://jobcars.net/company/</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>ランクル・ハイエース・USトヨタ専門店。店舗名は検索結果に表示された公式サイトの店舗一覧の抜粋による（10店舗、これ以上ある可能性）。公式サイトは503で確認できず。フレックス株式会社（FLEX、31店舗以上で除外）とは別会社。同じ敷地のランクル店・ハイエース店を別々に数えている。</t>
+          <t>同じ名前の別会社に注意：jobcars.jp は札幌の「ジョブカーズ株式会社」で別会社。枚方の会社の公式サイトは jobcars.net。枚方北店は大型トラック・バス、COOL店とバイパス店は会社概要に住所の記載がない。</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>株式会社川内自動車</t>
+          <t>株式会社フレックス・ドリーム</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>宮城県、群馬県、埼玉県、東京都、神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
+          <t>ランクル調布店、ランクルさいたま北店、ランクル小牧店、ランクル湘南厚木店、ランクル仙台東店、ハイエース小牧店、ハイエース湘南厚木店、ハイエース高崎店、ハイエース仙台東店、ハイエース三郷店</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -1755,22 +1755,18 @@
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://k-bacca.com/</t>
+          <t>https://www.flexdream.jp/</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/k_bacca_kawauchi/</t>
-        </is>
-      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>https://k-bacca.com/contents/store/index.html
-https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
+          <t>https://www.flexdream.jp/（503で取得不可。検索結果に表示された店舗一覧の抜粋）
+https://compalyze.co.jp/company/2012401009864（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -1780,7 +1776,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
+          <t>ランクル・ハイエース・USトヨタ専門店。店舗名は検索結果に表示された公式サイトの店舗一覧の抜粋による（10店舗、これ以上ある可能性）。公式サイトは503で確認できず。フレックス株式会社（FLEX、31店舗以上で除外）とは別会社。同じ敷地のランクル店・ハイエース店を別々に数えている。</t>
         </is>
       </c>
     </row>
@@ -1790,79 +1786,54 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>株式会社シースペース</t>
+          <t>株式会社川内自動車</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>京都府、大阪府、兵庫県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>大阪府柏原市国分市場2丁目13番1号</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>072-978-1263</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>072-978-1283</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 平松宗彦</t>
-        </is>
-      </c>
+          <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.c-space.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://k-bacca.com/</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>https://twitter.com/C_SPACE_U_POHS</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス事業（車買取）</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/k_bacca_kawauchi/</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/company/
-https://www.c-space.co.jp/shop/
-https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://k-bacca.com/contents/store/index.html
+https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>会社概要に「ユーポス（関西にて現在8店舗）」とある。ユーポス本部のサイトでシースペース運営と表示されるのは7店舗で、久御山店は表示されていない。本社のC-SPACE.（中古車販売）を1店舗として数え、合計9店舗。ほかにニコニコレンタカー5店舗とコバック1店舗（いずれも対象外）を運営。X(Twitter)のURLは検索結果から取得。</t>
+          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1843,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>株式会社リトラス</t>
+          <t>株式会社サークルエム</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1880,29 +1851,25 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
+          <t>埼玉県、千葉県、東京都、神奈川県、愛知県、福岡県</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>カートルズ越谷店、カートルズ鶴ヶ島店、カートルズ草加店、カートルズ青梅インター店、カートルズ相模原店、カートルズ千葉店、カートルズ岡崎店、カートルズ名古屋店、カートルズ北九州店</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>048-970-2444</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 津田猛</t>
-        </is>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.retrus.co.jp/</t>
+          <t>https://1190.jp/</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -1912,8 +1879,8 @@
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>https://www.retrus.co.jp/about/office.asp
-https://www.retrus.co.jp/about/</t>
+          <t>https://1190.jp/shop/
+求人情報（検索結果の抜粋：カートルズ草加店【株式会社サークルエム】）</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -1923,7 +1890,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
+          <t>自社ローン専門店「カートルズ」。公式サイトの店舗一覧で販売店9店舗（ほかに整備工場とBlackbunny）。求人では「直営13店舗」とも。運営会社名は草加店の求人表記によるもので、全店が同じ法人かは未確認。</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1900,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>株式会社九州ユーポス</t>
+          <t>株式会社シースペース</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1941,30 +1908,61 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
+          <t>京都府、大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>大阪府柏原市国分市場2丁目13番1号</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1263</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1283</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 平松宗彦</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/contact/</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/C_SPACE_U_POHS</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス事業（車買取）</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/hikarinomori/
-https://www.u-pohs.co.jp/kagoshima
-https://www.u-pohs.co.jp/kumamotominami</t>
+          <t>https://www.c-space.co.jp/company/
+https://www.c-space.co.jp/shop/
+https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -1974,7 +1972,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
+          <t>会社概要に「ユーポス（関西にて現在8店舗）」とある。ユーポス本部のサイトでシースペース運営と表示されるのは7店舗で、久御山店は表示されていない。本社のC-SPACE.（中古車販売）を1店舗として数え、合計9店舗。ほかにニコニコレンタカー5店舗とコバック1店舗（いずれも対象外）を運営。X(Twitter)のURLは検索結果から取得。</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1982,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>株式会社原ホンダ</t>
+          <t>株式会社リトラス</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1992,19 +1990,31 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
+          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 津田猛</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.retrus.co.jp/</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
@@ -2012,20 +2022,18 @@
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0031/
-https://www.applenet.co.jp/shop/0033/
-https://www.applenet.co.jp/shop/0042/</t>
+          <t>https://www.retrus.co.jp/about/office.asp
+https://www.retrus.co.jp/about/</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
+          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
         </is>
       </c>
     </row>
@@ -2035,60 +2043,38 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>株式会社TRUCK-ONE</t>
+          <t>株式会社九州ユーポス</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
+          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>山口県下松市生野屋南3-3-40</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-1100</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-5660</t>
-        </is>
-      </c>
+          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.truck-one.com/</t>
-        </is>
-      </c>
+      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/truckone_official/</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>買取専用窓口あり（0120-751-519）</t>
-        </is>
-      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-one.com/officelist/
-https://www.truck-one.com/company/</t>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/hikarinomori/
+https://www.u-pohs.co.jp/kagoshima
+https://www.u-pohs.co.jp/kumamotominami</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2098,7 +2084,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
         </is>
       </c>
     </row>
@@ -2108,39 +2094,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社ハヤシ</t>
+          <t>株式会社原ホンダ</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>岡山県倉敷市加須山334-4</t>
-        </is>
-      </c>
+          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>http://www.c-hayashi.com/</t>
-        </is>
-      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
@@ -2148,18 +2122,20 @@
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
-https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0031/
+https://www.applenet.co.jp/shop/0033/
+https://www.applenet.co.jp/shop/0042/</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2145,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社パッション</t>
+          <t>株式会社TRUCK-ONE</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2177,44 +2153,52 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、愛知県</t>
+          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>愛知県春日井市味美町2丁目122番地</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t>山口県下松市生野屋南3-3-40</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-1100</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-5660</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+          <t>https://www.truck-one.com/</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/truckone_official/</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>買取専門店ラビット勝川店を運営</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>217名（2025年12月）</t>
-        </is>
-      </c>
+          <t>買取専用窓口あり（0120-751-519）</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/company/outline/
-https://www.1963passion.co.jp/company/access/</t>
+          <t>https://www.truck-one.com/officelist/
+https://www.truck-one.com/company/</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2224,7 +2208,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
+          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2218,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社東和モータース販売</t>
+          <t>株式会社ハヤシ</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2242,70 +2226,50 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
+          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>東京都杉並区上高井戸1-21-18</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>03-3303-1146</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>03-3302-6600</t>
-        </is>
-      </c>
+          <t>岡山県倉敷市加須山334-4</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>代表取締役社長 稲葉弘幸</t>
+          <t>代表取締役 林和樹</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>https://towa-motors.com/contact.html</t>
-        </is>
-      </c>
+          <t>http://www.c-hayashi.com/</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/towa.motors</t>
-        </is>
-      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/company.html
-https://towa-motors.com/shop/</t>
+          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
+https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
+          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -2315,50 +2279,62 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ツチヤ自動車株式会社</t>
+          <t>株式会社パッション</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>岐阜県、愛知県</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>千葉県市川市北方町4-1441-8</t>
+          <t>愛知県春日井市味美町2丁目122番地</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>買取専門店ラビット勝川店を運営</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>217名（2025年12月）</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
-https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
+          <t>https://www.1963passion.co.jp/company/outline/
+https://www.1963passion.co.jp/company/access/</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
+          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -2368,38 +2344,68 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>株式会社東和モータース販売</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
+          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>東京都杉並区上高井戸1-21-18</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>03-3303-1146</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>03-3302-6600</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 稲葉弘幸</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>https://towa-motors.com/</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>https://towa-motors.com/contact.html</t>
+        </is>
+      </c>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/towa.motors</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0004/
-https://www.applenet.co.jp/shop/0007/
-https://www.applenet.co.jp/shop/0046/</t>
+          <t>https://towa-motors.com/company.html
+https://towa-motors.com/shop/</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -2409,7 +2415,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
+          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2425,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヨシダオートサービス</t>
+          <t>ツチヤ自動車株式会社</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2427,56 +2433,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0301</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0302</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>吉田宜史</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/contact/</t>
-        </is>
-      </c>
+          <t>千葉県市川市北方町4-1441-8</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>218名（2025年1月）</t>
-        </is>
-      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
+          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
+https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -2486,7 +2468,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
+          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
         </is>
       </c>
     </row>
@@ -2496,27 +2478,23 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>株式会社アップルカーセールス</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
-        </is>
-      </c>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2528,18 +2506,20 @@
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0004/
+https://www.applenet.co.jp/shop/0007/
+https://www.applenet.co.jp/shop/0046/</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
         </is>
       </c>
     </row>
@@ -2549,48 +2529,74 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2606,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>松下モータース</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2613,10 +2619,14 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
+          <t>浜松市内6店舗</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2628,7 +2638,8 @@
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -2638,7 +2649,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2659,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2656,47 +2667,30 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -2706,7 +2700,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2710,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>松下モータース</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2724,12 +2718,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -2744,20 +2738,17 @@
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2758,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社AOZORA COMPANY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2775,15 +2766,19 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>東京都、新潟県、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
+          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>新潟県新潟市西区黒鳥5243番地1</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2795,7 +2790,8 @@
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
+厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -2805,7 +2801,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2815,67 +2811,55 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>human joint株式会社</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>03-4446-7735</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>03-5422-8006</t>
-        </is>
-      </c>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 齊藤博行</t>
+          <t>代表取締役 石戸宏樹</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>中古自動車の販売および買取（事業内容）</t>
+          <t>自動車買取サービス（事業内容に記載）</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32名</t>
+          <t>26名</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/company/</t>
+          <t>https://www.apple-car.jp/company</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -2885,7 +2869,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
         </is>
       </c>
     </row>
@@ -2895,55 +2879,38 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>株式会社CIA</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
-        </is>
-      </c>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 大内康弘</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.yacco.cc/</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>キャンピングカー買取（買取センター4か所）</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/company/</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -2953,7 +2920,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
         </is>
       </c>
     </row>
@@ -2963,80 +2930,50 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>株式会社NIIZAWA</t>
+          <t>株式会社トータス</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>広島県、山口県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>広島県廿日市市大野原1丁目2-20</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>0829-30-8103</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0829-30-8104</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
-        </is>
-      </c>
+          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://www.kei-market.co.jp/</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kei-market.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://www.tortoise-k-carlife.com/</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/keimarket.k
-https://www.facebook.com/share/1AhR49eysR
-https://youtube.com/@keimarket398</t>
-        </is>
-      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>95名（パート含む）</t>
-        </is>
-      </c>
+      <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>https://www.kei-market.co.jp/company/
-https://www.kei-market.co.jp/store/</t>
+          <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
+https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
+          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。</t>
         </is>
       </c>
     </row>
@@ -3046,65 +2983,45 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>株式会社Y's GARAGE</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>京都府、鳥取県、島根県</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>京都府宇治市槇島町三十五38-1</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>0774-25-5557</t>
-        </is>
-      </c>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 桐畑勇志</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/</t>
-        </is>
-      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>158名（アルバイト含む、令和8年10月）</t>
-        </is>
-      </c>
+      <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://k-smile.jp/company/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
         </is>
       </c>
     </row>
@@ -3114,111 +3031,479 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
+          <t>株式会社ユー・パーク</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>048-798-9566</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>048-798-9590</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-parknet.com/</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>買取無料査定あり</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-parknet.com/about-us/
+https://www.u-parknet.com/</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>human joint株式会社</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>03-4446-7735</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>03-5422-8006</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 齊藤博行</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>中古自動車の販売および買取（事業内容）</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>32名</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/company/</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>株式会社CIA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 大内康弘</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー買取（買取センター4か所）</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/company/</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>株式会社NIIZAWA</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>広島県、山口県</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>広島県廿日市市大野原1丁目2-20</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8103</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8104</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/keimarket.k
+https://www.facebook.com/share/1AhR49eysR
+https://youtube.com/@keimarket398</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>95名（パート含む）</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/company/
+https://www.kei-market.co.jp/store/</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>株式会社Y's GARAGE</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>京都府、鳥取県、島根県</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>京都府宇治市槇島町三十五38-1</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>0774-25-5557</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 桐畑勇志</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>158名（アルバイト含む、令和8年10月）</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/company/</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>株式会社ロイヤルオートサービス</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>長野県</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>長野県松本市村井町南2-1-5</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>0120-107-817</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>代表取締役 中田忠章</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/contact/</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/royal_auto_
 https://www.instagram.com/royal_auto_service/?hl=ja
 https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>187名</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>株式会社横浜ユーポス</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>栃木県、神奈川県</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/kouhoku
@@ -3226,12 +3511,12 @@
 https://www.u-pohs.co.jp/tsuzuki</t>
         </is>
       </c>
-      <c r="Q42" s="2" t="inlineStr">
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
         <is>
           <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
         </is>
@@ -3248,7 +3533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3301,7 +3586,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -3351,7 +3636,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -3361,7 +3646,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -3371,7 +3656,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -3381,7 +3666,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -3391,7 +3676,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -3451,7 +3736,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -3491,7 +3776,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -3611,7 +3896,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -3717,37 +4002,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3757,57 +4042,57 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3817,7 +4102,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3827,111 +4112,131 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="B61" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>店舗数の分布</t>
         </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>5〜9店舗</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10〜19店舗</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>15</v>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20〜30店舗</t>
+          <t>5〜9店舗</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>10〜19店舗</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20〜30店舗</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="B68" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>確度別の社数</t>
         </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>確度</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>確度</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>28</v>
+      <c r="B73" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3945,7 +4250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4910,7 +5215,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ポケットカーズ（運営会社未確認）</t>
+          <t>アビックス大阪株式会社</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -4918,23 +5223,19 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>女池店、三条店、長岡店</t>
+          <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pocketcars.jp/</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
@@ -4942,7 +5243,7 @@
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/shop/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -4952,7 +5253,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
+          <t>アビックスコーポレーションのグループ会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -4967,7 +5268,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>古城モータース</t>
+          <t>ポケットカーズ（運営会社未確認）</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -4975,12 +5276,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>高岡本店、富山店、石川白山店</t>
+          <t>女池店、三条店、長岡店</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -4989,7 +5290,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/</t>
+          <t>https://www.pocketcars.jp/</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -4999,7 +5300,7 @@
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/（検索結果の抜粋）</t>
+          <t>https://www.pocketcars.jp/shop/</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -5007,7 +5308,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -5020,7 +5325,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>古城モータース</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -5028,29 +5333,29 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
+          <t>高岡本店、富山店、石川白山店</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
+          <t>富山県高岡市二塚425番地</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>06-6538-8844</t>
+          <t>0120-540-118</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -5060,20 +5365,15 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -5086,7 +5386,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -5094,29 +5394,29 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/</t>
+          <t>https://www.autogallery.co.jp/</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
@@ -5126,8 +5426,8 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -5137,7 +5437,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5452,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -5160,19 +5460,31 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 河野修一</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.csauto.jp/</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
@@ -5180,9 +5492,8 @@
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -5192,7 +5503,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5518,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -5215,31 +5526,19 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
-        </is>
-      </c>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 上武英輝</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kamitake.net/</t>
-        </is>
-      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
@@ -5247,8 +5546,9 @@
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -5256,7 +5556,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -5269,7 +5573,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>株式会社カミタケモータース</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -5277,19 +5581,31 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>大阪府、奈良県、大分県</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>枚方本店、奈良店、大分店</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
@@ -5297,9 +5613,8 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -5307,11 +5622,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="S23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -5324,7 +5635,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>株式会社シマダオート商事</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -5332,12 +5643,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -5352,7 +5663,9 @@
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -5362,7 +5675,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>ユーポス以外の事業は未確認。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5690,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>株式会社フロンティアモータース</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -5385,12 +5698,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>大阪府、兵庫県</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -5405,9 +5718,7 @@
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -5417,7 +5728,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポス以外の事業は未確認。</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5738,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FC本部</t>
+          <t>4店舗以下</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーポス</t>
+          <t>株式会社ベネフィット</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -5440,35 +5751,19 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>06-6532-6532</t>
-        </is>
-      </c>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 柏原隆宏</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-pohs.co.jp/</t>
-        </is>
-      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
@@ -5476,18 +5771,19 @@
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/about/company_info
-https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5497,12 +5793,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>4店舗以下</t>
+          <t>FC本部</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>株式会社ユーポス</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
@@ -5510,19 +5806,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
+          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>06-6532-6532</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 柏原隆宏</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
@@ -5530,19 +5842,18 @@
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://www.u-pohs.co.jp/about/company_info
+https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5868,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社リフトオフ</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -5565,12 +5876,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>茨城県、千葉県、東京都</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -5585,9 +5896,9 @@
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/</t>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -5612,7 +5923,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>阿部勝自動車工業株式会社</t>
+          <t>株式会社中州自動車</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -5620,23 +5931,19 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>https://k-mishiyo.abekatu.co.jp/</t>
-        </is>
-      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
@@ -5644,15 +5951,21 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr"/>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -5665,27 +5978,31 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎有限会社</t>
+          <t>阿部勝自動車工業株式会社</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>宮崎県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
+          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>https://k-mishiyo.abekatu.co.jp/</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
@@ -5693,20 +6010,15 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0056/
-https://www.applenet.co.jp/shop/0149/</t>
+          <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -5719,7 +6031,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>タイガー石油株式会社</t>
+          <t>アップル宮崎有限会社</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -5727,12 +6039,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>宮崎県</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
+          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -5747,7 +6059,8 @@
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0056/
+https://www.applenet.co.jp/shop/0149/</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -5757,7 +6070,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5772,7 +6085,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>大谷自動車株式会社</t>
+          <t>タイガー石油株式会社</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -5780,47 +6093,27 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>大阪府、和歌山県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>大阪本店、和歌山店</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>大阪府泉佐野市長滝753</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>072-465-0492</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>072-465-3109</t>
-        </is>
-      </c>
+          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.otani-j.co.jp/</t>
-        </is>
-      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>81名</t>
-        </is>
-      </c>
+      <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>https://www.otani-j.co.jp/company</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -5828,7 +6121,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -5841,7 +6138,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>平岩石油販売株式会社</t>
+          <t>大谷自動車株式会社</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -5849,28 +6146,47 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>大阪府、和歌山県</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>アップル練馬関町店、アップル板橋環8店</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>大阪本店、和歌山店</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>大阪府泉佐野市長滝753</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>072-465-0492</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>072-465-3109</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.otani-j.co.jp/</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0175/
-https://www.applenet.co.jp/shop/0247/</t>
+          <t>https://www.otani-j.co.jp/company</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -5878,11 +6194,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="S33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -5895,7 +6207,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>株式会社B&amp;F</t>
+          <t>平岩石油販売株式会社</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -5903,12 +6215,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>アップル古河4号店、アップル守谷店</t>
+          <t>アップル練馬関町店、アップル板橋環8店</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -5923,8 +6235,8 @@
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0140/
-https://www.applenet.co.jp/shop/0146/</t>
+          <t>https://www.applenet.co.jp/shop/0175/
+https://www.applenet.co.jp/shop/0247/</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -5949,7 +6261,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>株式会社NEXTモビィ</t>
+          <t>月原自動車株式会社</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -5957,19 +6269,35 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
+          <t>ハピット 今治、ハピット 新居浜</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>愛媛県今治市小泉4丁目1-2</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0898-35-4488</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>月原正志</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>https://hapit-car.com/</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
@@ -5977,18 +6305,17 @@
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukuoka-inter
-https://www.u-pohs.co.jp/kokurahigashi-inter</t>
+          <t>https://hapit-car.com/</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ハピット軽未使用車専門店。</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6330,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>株式会社PlusOne</t>
+          <t>株式会社B&amp;F</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -6011,12 +6338,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>アップル安城南店、アップル弥富1号線店</t>
+          <t>アップル古河4号店、アップル守谷店</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -6031,8 +6358,8 @@
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0129/
-https://www.applenet.co.jp/shop/0219/</t>
+          <t>https://www.applenet.co.jp/shop/0140/
+https://www.applenet.co.jp/shop/0146/</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -6057,7 +6384,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>株式会社SHIMAカーライフコネクテッド</t>
+          <t>株式会社NEXTモビィ</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -6065,12 +6392,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>アップル金沢店、アップル高岡店</t>
+          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -6085,8 +6412,8 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0313/
-https://www.applenet.co.jp/shop/0339/</t>
+          <t>https://www.u-pohs.co.jp/fukuoka-inter
+https://www.u-pohs.co.jp/kokurahigashi-inter</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -6096,7 +6423,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6438,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>株式会社WinWinサービス</t>
+          <t>株式会社PlusOne</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -6119,12 +6446,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>アップル盛岡盛南店、アップル盛岡北店</t>
+          <t>アップル安城南店、アップル弥富1号線店</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -6139,8 +6466,8 @@
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0117/
-https://www.applenet.co.jp/shop/0137/</t>
+          <t>https://www.applenet.co.jp/shop/0129/
+https://www.applenet.co.jp/shop/0219/</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -6165,7 +6492,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>株式会社イトー</t>
+          <t>株式会社SHIMAカーライフコネクテッド</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -6173,12 +6500,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>アップル岸和田店、アップル河内長野中央店</t>
+          <t>アップル金沢店、アップル高岡店</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -6193,8 +6520,8 @@
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0258/
-https://www.applenet.co.jp/shop/0278/</t>
+          <t>https://www.applenet.co.jp/shop/0313/
+https://www.applenet.co.jp/shop/0339/</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -6204,7 +6531,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>アップル以外の店舗は未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6546,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>株式会社インデックス</t>
+          <t>株式会社WinWinサービス</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -6227,12 +6554,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
+          <t>アップル盛岡盛南店、アップル盛岡北店</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -6247,8 +6574,8 @@
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0018/
-https://www.applenet.co.jp/shop/0029/</t>
+          <t>https://www.applenet.co.jp/shop/0117/
+https://www.applenet.co.jp/shop/0137/</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -6273,7 +6600,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>株式会社イーグルオートサービス</t>
+          <t>株式会社イトー</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -6281,12 +6608,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
+          <t>アップル岸和田店、アップル河内長野中央店</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -6301,8 +6628,8 @@
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0032/
-https://www.applenet.co.jp/shop/0063/</t>
+          <t>https://www.applenet.co.jp/shop/0258/
+https://www.applenet.co.jp/shop/0278/</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -6312,7 +6639,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップル以外の店舗は未確認。</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6654,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>株式会社エムエフノースジャパン</t>
+          <t>株式会社インデックス</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -6335,12 +6662,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -6355,8 +6682,8 @@
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0035/
-https://www.applenet.co.jp/shop/0043/</t>
+          <t>https://www.applenet.co.jp/shop/0018/
+https://www.applenet.co.jp/shop/0029/</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
@@ -6381,7 +6708,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>株式会社オカモト</t>
+          <t>株式会社イーグルオートサービス</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -6389,12 +6716,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>アップル西帯広店、アップル帯広店</t>
+          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -6409,8 +6736,8 @@
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0307/
-https://www.applenet.co.jp/shop/0334/</t>
+          <t>https://www.applenet.co.jp/shop/0032/
+https://www.applenet.co.jp/shop/0063/</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -6435,7 +6762,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>株式会社オリンピアオート</t>
+          <t>株式会社エムエフノースジャパン</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -6443,12 +6770,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>アップルひたちなか店、アップル那珂中央店</t>
+          <t>、</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -6463,8 +6790,8 @@
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0208/
-https://www.applenet.co.jp/shop/0280/</t>
+          <t>https://www.applenet.co.jp/shop/0035/
+https://www.applenet.co.jp/shop/0043/</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -6489,7 +6816,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートグローリー</t>
+          <t>株式会社オカモト</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -6497,12 +6824,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福重店、ユーポス直方店</t>
+          <t>アップル西帯広店、アップル帯広店</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -6517,8 +6844,8 @@
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukushige
-https://www.u-pohs.co.jp/nogata</t>
+          <t>https://www.applenet.co.jp/shop/0307/
+https://www.applenet.co.jp/shop/0334/</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -6528,7 +6855,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6870,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>株式会社クインオート</t>
+          <t>株式会社オリンピアオート</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -6551,12 +6878,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>京都府、兵庫県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>ユーポス亀岡店、ユーポス三田店</t>
+          <t>アップルひたちなか店、アップル那珂中央店</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -6571,8 +6898,8 @@
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kameoka
-https://www.u-pohs.co.jp/sanda/</t>
+          <t>https://www.applenet.co.jp/shop/0208/
+https://www.applenet.co.jp/shop/0280/</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -6582,7 +6909,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6924,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>株式会社サコダ車輛</t>
+          <t>株式会社オートグローリー</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -6605,12 +6932,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>アップル海田店、アップル東広島店</t>
+          <t>ユーポス福重店、ユーポス直方店</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -6625,8 +6952,8 @@
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0297/
-https://www.applenet.co.jp/shop/0298/</t>
+          <t>https://www.u-pohs.co.jp/fukushige
+https://www.u-pohs.co.jp/nogata</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -6636,7 +6963,7 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 社名の正式表記は「サコダ車輌」の可能性。本社は広島市中区舟入南、売上高158億円・従業員240名（求人情報）。自社店舗の海田店（軽自動車専門）と佐伯区五日市の拠点もあり、合計4か所以上。自社サイト未確認のため境界扱い。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6978,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>株式会社シブヤエネックスホールディングス</t>
+          <t>株式会社カーボ</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -6659,19 +6986,31 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>福井県</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>アップル相模原城山店、アップル大井松田インター店</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
+          <t>開発店、鯖江店</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>福井県福井市開発町6-15</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0776-52-7515</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cavo-kei.jp/</t>
+        </is>
+      </c>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
@@ -6679,8 +7018,7 @@
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0266/
-https://www.applenet.co.jp/shop/0292/</t>
+          <t>https://www.cavo-kei.jp/</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
@@ -6690,7 +7028,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>グループ全体の従業員141名（グループ会社の店舗は未確認）。</t>
         </is>
       </c>
     </row>
@@ -6705,7 +7043,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>株式会社スズキアリーナ瑞穂</t>
+          <t>株式会社クインオート</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -6713,12 +7051,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>京都府、兵庫県</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>アップル青梅店、アップル西東京店</t>
+          <t>ユーポス亀岡店、ユーポス三田店</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -6733,8 +7071,8 @@
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0057/
-https://www.applenet.co.jp/shop/0100/</t>
+          <t>https://www.u-pohs.co.jp/kameoka
+https://www.u-pohs.co.jp/sanda/</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -6744,7 +7082,7 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6759,7 +7097,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>株式会社トップワン</t>
+          <t>株式会社サコダ車輛</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -6767,12 +7105,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>アップル豊田梅坪店、アップル豊田南店</t>
+          <t>アップル海田店、アップル東広島店</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -6787,8 +7125,8 @@
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0075/
-https://www.applenet.co.jp/shop/0126/</t>
+          <t>https://www.applenet.co.jp/shop/0297/
+https://www.applenet.co.jp/shop/0298/</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -6798,7 +7136,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 社名の正式表記は「サコダ車輌」の可能性。本社は広島市中区舟入南、売上高158億円・従業員240名（求人情報）。自社店舗の海田店（軽自動車専門）と佐伯区五日市の拠点もあり、合計4か所以上。自社サイト未確認のため境界扱い。</t>
         </is>
       </c>
     </row>
@@ -6813,7 +7151,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社シブヤエネックスホールディングス</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -6826,7 +7164,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>アップル大和店、アップル相模原店</t>
+          <t>アップル相模原城山店、アップル大井松田インター店</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -6841,8 +7179,8 @@
       <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0306/
-https://www.applenet.co.jp/shop/0340/</t>
+          <t>https://www.applenet.co.jp/shop/0266/
+https://www.applenet.co.jp/shop/0292/</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
@@ -6867,7 +7205,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビーインプレスト</t>
+          <t>株式会社スズキアリーナ瑞穂</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -6875,12 +7213,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>アップル宇都宮北店、アップル大田原店</t>
+          <t>アップル青梅店、アップル西東京店</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -6895,8 +7233,8 @@
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0211/
-https://www.applenet.co.jp/shop/0303/</t>
+          <t>https://www.applenet.co.jp/shop/0057/
+https://www.applenet.co.jp/shop/0100/</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
@@ -6921,7 +7259,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファミリー</t>
+          <t>株式会社トップワン</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -6929,12 +7267,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>ファミリー可児店、ファミリー各務原店</t>
+          <t>アップル豊田梅坪店、アップル豊田南店</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -6949,17 +7287,18 @@
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0075/
+https://www.applenet.co.jp/shop/0126/</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6974,7 +7313,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミヤチ</t>
+          <t>株式会社ビーインプレスト</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -6982,12 +7321,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>アップル岐阜長良店、アップル関店</t>
+          <t>アップル宇都宮北店、アップル大田原店</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -7002,8 +7341,8 @@
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0101/
-https://www.applenet.co.jp/shop/0155/</t>
+          <t>https://www.applenet.co.jp/shop/0211/
+https://www.applenet.co.jp/shop/0303/</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -7028,7 +7367,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>株式会社湯浅</t>
+          <t>株式会社ファミリー</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -7036,12 +7375,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>アップル白井店、アップル松戸本店</t>
+          <t>ファミリー可児店、ファミリー各務原店</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -7056,18 +7395,17 @@
       <c r="P55" s="2" t="inlineStr"/>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0287/
-https://www.applenet.co.jp/shop/0293/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7420,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>株式会社車のせんいち</t>
+          <t>株式会社ミヤチ</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -7090,12 +7428,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>みどり本店、伊勢崎店</t>
+          <t>アップル岐阜長良店、アップル関店</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -7110,17 +7448,18 @@
       <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>求人情報（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0101/
+https://www.applenet.co.jp/shop/0155/</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>軽自動車39.8万円専門店ほか。確認できたのは2店舗と新店舗（みどり市笠懸町、オープン予定）。公式サイト未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7474,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>株式会社関西オート</t>
+          <t>株式会社ユアーズ</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -7143,25 +7482,29 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>八尾店、平野店</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
+          <t>森町店、下郡店</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>大分県大分市森437-1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>097-578-9499</t>
+        </is>
+      </c>
       <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 大川純平</t>
-        </is>
-      </c>
+      <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>https://www.kansai-auto.jp/</t>
+          <t>https://kei-mishiyousya.com/</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
@@ -7171,12 +7514,12 @@
       <c r="P57" s="2" t="inlineStr"/>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>https://www.kansai-auto.jp/company/outline/</t>
+          <t>https://kei-mishiyousya.com/</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr"/>
@@ -7192,20 +7535,20 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Re-BOOT株式会社</t>
+          <t>株式会社湯浅</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>アップル大阪平野店</t>
+          <t>アップル白井店、アップル松戸本店</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -7220,7 +7563,8 @@
       <c r="P58" s="2" t="inlineStr"/>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0284/</t>
+          <t>https://www.applenet.co.jp/shop/0287/
+https://www.applenet.co.jp/shop/0293/</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
@@ -7228,7 +7572,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -7241,43 +7589,27 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>北摂オート株式会社</t>
+          <t>株式会社車のせんいち</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>大阪府箕面市桜井2-16-17</t>
-        </is>
-      </c>
+          <t>みどり本店、伊勢崎店</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>072-723-1102</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 喜多克之</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>https://hokusetu-auto.com/</t>
-        </is>
-      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
@@ -7285,15 +7617,19 @@
       <c r="P59" s="2" t="inlineStr"/>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>https://hokusetu-auto.com/company.php</t>
+          <t>求人情報（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr"/>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>軽自動車39.8万円専門店ほか。確認できたのは2店舗と新店舗（みどり市笠懸町、オープン予定）。公式サイト未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -7306,11 +7642,11 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>有限会社タイヨウ</t>
+          <t>株式会社関西オート</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -7319,14 +7655,22 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>ユーポス富田林店</t>
+          <t>八尾店、平野店</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 大川純平</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kansai-auto.jp/</t>
+        </is>
+      </c>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr"/>
@@ -7334,7 +7678,7 @@
       <c r="P60" s="2" t="inlineStr"/>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.kansai-auto.jp/company/outline/</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
@@ -7342,11 +7686,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -7359,7 +7699,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>株式会社We Car CORE</t>
+          <t>GARIREO（ガリレオ、愛媛）</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -7367,19 +7707,27 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>ユーポス貝塚店</t>
+          <t>軽自動車専門店 ガリレオケイランド</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0800-200-3440</t>
+        </is>
+      </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>https://garireo.co.jp/</t>
+        </is>
+      </c>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
@@ -7387,17 +7735,17 @@
       <c r="P61" s="2" t="inlineStr"/>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://garireo.co.jp/shops/</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+          <t>「松山市と東温市に5店舗」の表記だが、販売店はケイランドで、ほかは整備工場（サービステラス）とコバック併設店（谷町・余戸・重信）。コバック併設店で販売もしていれば5店舗になる。運営会社の正式名称は未確認（GARIREO Corporation）。</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7760,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>株式会社cantera</t>
+          <t>Re-BOOT株式会社</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -7425,7 +7773,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環四條畷店</t>
+          <t>アップル大阪平野店</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -7440,7 +7788,7 @@
       <c r="P62" s="2" t="inlineStr"/>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0284/</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -7448,11 +7796,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -7465,7 +7809,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>株式会社プロンザ</t>
+          <t>北摂オート株式会社</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -7478,14 +7822,30 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>ユーポス枚方店</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>大阪府箕面市桜井2-16-17</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>072-723-1102</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 喜多克之</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>https://hokusetu-auto.com/</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
@@ -7493,7 +7853,7 @@
       <c r="P63" s="2" t="inlineStr"/>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://hokusetu-auto.com/company.php</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -7501,11 +7861,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -7518,7 +7874,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>株式会社ポロ</t>
+          <t>有限会社タイヨウ</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -7531,30 +7887,14 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>大阪府高槻市富田町6丁目15-13</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>072-694-6641</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>072-694-9913</t>
-        </is>
-      </c>
+          <t>ユーポス富田林店</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.polojp.com/</t>
-        </is>
-      </c>
+      <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
@@ -7562,7 +7902,7 @@
       <c r="P64" s="2" t="inlineStr"/>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>https://www.polojp.com/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -7570,7 +7910,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -7583,7 +7927,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>豊栄モータース</t>
+          <t>株式会社We Car CORE</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -7596,7 +7940,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>ユーポス寝屋川店</t>
+          <t>ユーポス貝塚店</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -7621,6 +7965,352 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>株式会社cantera</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス外環四條畷店</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>株式会社world of star</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>軽ワールド 和歌山湊店</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>和歌山県和歌山市湊1820-160</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>073-488-9199</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>中谷和弘</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>https://kworld.jp/</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>https://kworld.jp/</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>株式会社サンアイク</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>茂原店</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>千葉県茂原市腰当526-1</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sunaiku.com/</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sunaiku.com/</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>株式会社プロンザ</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス枚方店</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ポロ</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>大阪府高槻市富田町6丁目15-13</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>072-694-6641</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>072-694-9913</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>豊栄モータース</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス寝屋川店</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
           <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。（法人格の表示なし）</t>
         </is>
       </c>
@@ -7636,7 +8326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8309,6 +8999,73 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>GTNET（スポーツカー専門店）</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>GT-R買取・スポーツカー専門、埼玉ほか複数店舗</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>公式サイトが403で取得できず、運営会社・店舗数未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>株式会社クイックモーション（カラーズ、4WD・SUV専門店）</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>埼玉中心に3店舗</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3店舗前後で境界未満の可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>株式会社RIP-OFF／株式会社STK（マーキュリー八王子）</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>輸入車</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>店舗数未確認</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1250,38 +1250,60 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>株式会社アタックス</t>
+          <t>株式会社オートベル</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県、三重県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>アップル津島中央道店、アップル厚木・北129号店、アップル富田302号店、アップル小田原飯泉店、アップル昭和橋通店、アップル桑名七和店、アップル中村畑江通店、アップル稲沢店、アップル西・康生通店、アップル南23号店、アップル桑名大桑店、アップル黒川北41号店</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>なでしこ店、三島店、富士宮バイパス店、富士旧国一店、御殿場店、掛川店、沼津ぐるめ街道店、浜松入野店、浜松和田店、浜松西ヶ崎店、清水インター店、藤枝店、静岡流通通り店、静岡見瀬店</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>静岡県沼津市岡宮1266-87</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>055-922-6007</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 牧野太一郎</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>https://autobell.co.jp/</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>車の買取（主業）</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>130名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0008/
-https://www.applenet.co.jp/shop/0021/
-https://www.applenet.co.jp/shop/0022/</t>
+          <t>https://autobell.co.jp/company/about/index.html
+https://autobell.co.jp/</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1291,7 +1313,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。</t>
+          <t>車買取・販売（新車・中古車）。サイトの表記は「静岡県内13店舗」、店舗リンクは14件（なでしこ店を含む）。千葉のオートベル・ジャパンとは別会社の可能性（未確認）。</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1323,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>株式会社ジェイ・ピー</t>
+          <t>株式会社アタックス</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1309,12 +1331,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>宮城県、福島県、栃木県、群馬県、埼玉県</t>
+          <t>神奈川県、愛知県、三重県</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>アップル坂戸鶴ヶ島インター店、アップル太田店、アップル川越16号店、アップル郡山インター店、アップル深谷17号店、アップル西那須野店、アップル朝霞店、アップル仙台六丁目店、アップル東松山店、アップル白河店、アップル所沢店、アップル鴻巣店</t>
+          <t>アップル津島中央道店、アップル厚木・北129号店、アップル富田302号店、アップル小田原飯泉店、アップル昭和橋通店、アップル桑名七和店、アップル中村畑江通店、アップル稲沢店、アップル西・康生通店、アップル南23号店、アップル桑名大桑店、アップル黒川北41号店</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1330,55 +1352,175 @@
       <c r="P13" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0008/
+https://www.applenet.co.jp/shop/0021/
+https://www.applenet.co.jp/shop/0022/</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>株式会社コヤマ・ミライエ</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>KOYAMA 富士宮店、KOYAMA 富士平垣店、KOYAMA 富士店、KOYAMA 新富士店、KOYAMA 御前崎店、KOYAMA 柿田川店、KOYAMA 浜松東店、KOYAMA 浜松西店、KOYAMA 藤枝店、KOYAMA 袋井上山梨店、KOYAMA 静岡中原店、KOYAMA 静岡池田店</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>静岡県富士市伝法878-15</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 小山武</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koyama-miraie.co.jp/</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取業務（主業）</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>48名</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koyama-miraie.co.jp/company/
+https://www.koyama-miraie.co.jp/shop/</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>車買取専門店KOYAMA。店舗数は公式サイトの店舗一覧12件。LINE公式アカウントあり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ジェイ・ピー</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、福島県、栃木県、群馬県、埼玉県</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>アップル坂戸鶴ヶ島インター店、アップル太田店、アップル川越16号店、アップル郡山インター店、アップル深谷17号店、アップル西那須野店、アップル朝霞店、アップル仙台六丁目店、アップル東松山店、アップル白河店、アップル所沢店、アップル鴻巣店</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0015/
 https://www.applenet.co.jp/shop/0037/
 https://www.applenet.co.jp/shop/0044/</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル坂戸鶴ヶ島インター店）〒350-2211 埼玉県鶴ヶ島市脚折町5-4-13 TEL 049-279-3500 FAX 049-279-3501。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>高橋自動車販売株式会社</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C16" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>東京都、神奈川県、愛知県</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>アップル江田駅前店、アップル江戸川環七店、アップル豊橋佐藤店、アップル248岡崎店、アップル平塚田村店、アップル中山宮の下店、アップル町田南店、アップル岡崎六ッ美店、アップル東戸塚店、アップル蒲郡店、アップル豊川インター店、アップル岡崎緑丘店</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0013/
@@ -1386,71 +1528,71 @@
 https://www.applenet.co.jp/shop/0024/</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。軽四専門「メガタウン」（豊田市）も運営しており、実際の店舗数はこれより多い可能性。 参考：店舗の連絡先（アップル江田駅前店）〒225-0013 神奈川県横浜市青葉区荏田町1236-7東急江田駅前ドエリング1F TEL 045-912-7560 FAX 045-912-7566。</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>株式会社メーカーズ</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C17" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>福岡県、佐賀県</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>ケイカフェ おおのじょう店、ケイカフェ しんぐう店、ケイカフェ こくらみなみ店、ケイカフェ くるめ店、ケイカフェ ちくしの店、ケイカフェ いいづか店、ケイカフェ やはた店、ケイカフェ ふくおかにし店、ケイカフェ とす店、アップル福岡東店、アップル福岡八幡店</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>福岡県福岡市西区石丸4丁目5-53</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>092-753-6611</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>092-753-6622</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>代表取締役社長 白井剛</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>https://www.k-cafe.com/</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>https://www.k-cafe.com/contact/</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/kcafe_official
 https://www.facebook.com/kcarandcafe
@@ -1459,324 +1601,195 @@
 https://www.youtube.com/@kcafe_fukuoka/videos</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>https://www.k-cafe.com/company/
 https://www.k-cafe.com/
 https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ケイカフェ9店舗（公式サイトの店舗情報）と、アップル加盟店2店舗（本部サイトで運営会社を確認）の合計。ONIXフランチャイズにも加盟（沿革）。</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>株式会社軽自動車館</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C18" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>北海道、宮城県</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>札幌本店、札幌東店、新さっぽろ店、札幌清田店、北見店、旭川店、函館店、苫小牧店、帯広店、釧路店、せんだい店</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>北海道札幌市中央区北5条西6丁目2-2</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>011-200-0312</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>011-200-0357</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>代表取締役社長 阿部章一</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>https://keijidousyakan.com/</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>https://keijidousyakan.com/contact/（現在お問い合わせ見合わせ中の表示あり）</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>https://www.youtube.com/channel/UCtYVtXtEHCIxOCia6QF0nBw</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>自動車の買取（事業内容に記載）</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>117名（2026年1月）</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>https://keijidousyakan.com/about/company/
 https://keijidousyakan.com/shops/</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>店舗名は公式の店舗ページから。札幌本店と札幌東店はURL（sapporo / satsuhigashi）から推定した店舗名。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>日免オートシステム株式会社</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>美使用軽専門店 江別店、美使用軽専門店 静内店（新ひだか）、美使用軽専門店 小樽店、美使用軽専門店 旭川店、美使用軽専門店 十勝音更店、美使用軽専門店 イオンスーパーセンター三笠店、美使用軽専門店 スーパーアークス新琴似店、カーセブン札幌北店、カーセブン北見店、カーセブン十勝音更店</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>北海道札幌市北区東茨戸1条1丁目8番5号</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>011-774-3111</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>011-775-8906</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>代表取締役社長 安部直人</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>https://www.nichimen-g.co.jp/</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>https://www.nichimen-g.co.jp/company/contact/</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/nichimen_mishiyou/
 https://www.youtube.com/channel/UC-iuDCLbQ6px8P3WISQrLdg</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>ニチメン買取（買取・査定）あり</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>210名（グループ全体・パート含む）</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>https://www.nichimen-g.co.jp/company/
 https://www.nichimen-g.co.jp/company/stores/
 https://www.nichimen-g.co.jp/mishiyou/</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>ニチメングループ。会社概要の「総店舗数31店舗（北海道内グループ全体）」には、スズキ販売店・レンタカー・整備工場・板金・建機なども含まれる。中古車の販売・買取の店舗として、美使用軽専門店7店舗とカーセブン加盟店3店舗を数えた。新琴似本店・札幌本店の位置づけは未確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ジョブカーズ</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>大阪府</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>ジョブカーズ本店、南港店、枚方東店、枚方南店、枚方北店、枚方インポート店、八尾店、守口店、COOL店、バイパス店</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市茄子作2-33-25</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>072-852-8500</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>072-852-8501</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>吉村浩二</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/contact/</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>70名</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/company/</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>同じ名前の別会社に注意：jobcars.jp は札幌の「ジョブカーズ株式会社」で別会社。枚方の会社の公式サイトは jobcars.net。枚方北店は大型トラック・バス、COOL店とバイパス店は会社概要に住所の記載がない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>株式会社フレックス・ドリーム</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>宮城県、群馬県、埼玉県、東京都、神奈川県、愛知県</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>ランクル調布店、ランクルさいたま北店、ランクル小牧店、ランクル湘南厚木店、ランクル仙台東店、ハイエース小牧店、ハイエース湘南厚木店、ハイエース高崎店、ハイエース仙台東店、ハイエース三郷店</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flexdream.jp/</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flexdream.jp/（503で取得不可。検索結果に表示された店舗一覧の抜粋）
-https://compalyze.co.jp/company/2012401009864（検索結果の抜粋）</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>ランクル・ハイエース・USトヨタ専門店。店舗名は検索結果に表示された公式サイトの店舗一覧の抜粋による（10店舗、これ以上ある可能性）。公式サイトは503で確認できず。フレックス株式会社（FLEX、31店舗以上で除外）とは別会社。同じ敷地のランクル店・ハイエース店を別々に数えている。</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1799,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>株式会社川内自動車</t>
+          <t>株式会社ジョブカーズ</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1794,46 +1807,65 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>ジョブカーズ本店、南港店、枚方東店、枚方南店、枚方北店、枚方インポート店、八尾店、守口店、COOL店、バイパス店</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市茄子作2-33-25</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>072-852-8500</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>072-852-8501</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>吉村浩二</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://k-bacca.com/</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>https://jobcars.net/</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>https://jobcars.net/contact/</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/k_bacca_kawauchi/</t>
-        </is>
-      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>70名</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>https://k-bacca.com/contents/store/index.html
-https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
+          <t>https://jobcars.net/company/</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
+          <t>同じ名前の別会社に注意：jobcars.jp は札幌の「ジョブカーズ株式会社」で別会社。枚方の会社の公式サイトは jobcars.net。枚方北店は大型トラック・バス、COOL店とバイパス店は会社概要に住所の記載がない。</t>
         </is>
       </c>
     </row>
@@ -1843,33 +1875,29 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>株式会社サークルエム</t>
+          <t>株式会社フレックス・ドリーム</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県、東京都、神奈川県、愛知県、福岡県</t>
+          <t>宮城県、群馬県、埼玉県、東京都、神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>カートルズ越谷店、カートルズ鶴ヶ島店、カートルズ草加店、カートルズ青梅インター店、カートルズ相模原店、カートルズ千葉店、カートルズ岡崎店、カートルズ名古屋店、カートルズ北九州店</t>
+          <t>ランクル調布店、ランクルさいたま北店、ランクル小牧店、ランクル湘南厚木店、ランクル仙台東店、ハイエース小牧店、ハイエース湘南厚木店、ハイエース高崎店、ハイエース仙台東店、ハイエース三郷店</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>048-970-2444</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://1190.jp/</t>
+          <t>https://www.flexdream.jp/</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -1879,8 +1907,8 @@
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>https://1190.jp/shop/
-求人情報（検索結果の抜粋：カートルズ草加店【株式会社サークルエム】）</t>
+          <t>https://www.flexdream.jp/（503で取得不可。検索結果に表示された店舗一覧の抜粋）
+https://compalyze.co.jp/company/2012401009864（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -1890,7 +1918,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店「カートルズ」。公式サイトの店舗一覧で販売店9店舗（ほかに整備工場とBlackbunny）。求人では「直営13店舗」とも。運営会社名は草加店の求人表記によるもので、全店が同じ法人かは未確認。</t>
+          <t>ランクル・ハイエース・USトヨタ専門店。店舗名は検索結果に表示された公式サイトの店舗一覧の抜粋による（10店舗、これ以上ある可能性）。公式サイトは503で確認できず。フレックス株式会社（FLEX、31店舗以上で除外）とは別会社。同じ敷地のランクル店・ハイエース店を別々に数えている。</t>
         </is>
       </c>
     </row>
@@ -1900,79 +1928,54 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>株式会社シースペース</t>
+          <t>株式会社川内自動車</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>京都府、大阪府、兵庫県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>大阪府柏原市国分市場2丁目13番1号</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>072-978-1263</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>072-978-1283</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 平松宗彦</t>
-        </is>
-      </c>
+          <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.c-space.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://k-bacca.com/</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>https://twitter.com/C_SPACE_U_POHS</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス事業（車買取）</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/k_bacca_kawauchi/</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/company/
-https://www.c-space.co.jp/shop/
-https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://k-bacca.com/contents/store/index.html
+https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>会社概要に「ユーポス（関西にて現在8店舗）」とある。ユーポス本部のサイトでシースペース運営と表示されるのは7店舗で、久御山店は表示されていない。本社のC-SPACE.（中古車販売）を1店舗として数え、合計9店舗。ほかにニコニコレンタカー5店舗とコバック1店舗（いずれも対象外）を運営。X(Twitter)のURLは検索結果から取得。</t>
+          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1985,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>株式会社リトラス</t>
+          <t>株式会社サークルエム</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1990,29 +1993,25 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
+          <t>埼玉県、千葉県、東京都、神奈川県、愛知県、福岡県</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>カートルズ越谷店、カートルズ鶴ヶ島店、カートルズ草加店、カートルズ青梅インター店、カートルズ相模原店、カートルズ千葉店、カートルズ岡崎店、カートルズ名古屋店、カートルズ北九州店</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>048-970-2444</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 津田猛</t>
-        </is>
-      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://www.retrus.co.jp/</t>
+          <t>https://1190.jp/</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
@@ -2022,8 +2021,8 @@
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>https://www.retrus.co.jp/about/office.asp
-https://www.retrus.co.jp/about/</t>
+          <t>https://1190.jp/shop/
+求人情報（検索結果の抜粋：カートルズ草加店【株式会社サークルエム】）</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2033,7 +2032,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
+          <t>自社ローン専門店「カートルズ」。公式サイトの店舗一覧で販売店9店舗（ほかに整備工場とBlackbunny）。求人では「直営13店舗」とも。運営会社名は草加店の求人表記によるもので、全店が同じ法人かは未確認。</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2042,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>株式会社九州ユーポス</t>
+          <t>株式会社シースペース</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -2051,30 +2050,61 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
+          <t>京都府、大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>大阪府柏原市国分市場2丁目13番1号</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1263</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1283</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 平松宗彦</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/contact/</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/C_SPACE_U_POHS</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス事業（車買取）</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/hikarinomori/
-https://www.u-pohs.co.jp/kagoshima
-https://www.u-pohs.co.jp/kumamotominami</t>
+          <t>https://www.c-space.co.jp/company/
+https://www.c-space.co.jp/shop/
+https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2084,7 +2114,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
+          <t>会社概要に「ユーポス（関西にて現在8店舗）」とある。ユーポス本部のサイトでシースペース運営と表示されるのは7店舗で、久御山店は表示されていない。本社のC-SPACE.（中古車販売）を1店舗として数え、合計9店舗。ほかにニコニコレンタカー5店舗とコバック1店舗（いずれも対象外）を運営。X(Twitter)のURLは検索結果から取得。</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2124,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社原ホンダ</t>
+          <t>株式会社リトラス</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2102,19 +2132,31 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
+          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 津田猛</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.retrus.co.jp/</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
@@ -2122,20 +2164,18 @@
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0031/
-https://www.applenet.co.jp/shop/0033/
-https://www.applenet.co.jp/shop/0042/</t>
+          <t>https://www.retrus.co.jp/about/office.asp
+https://www.retrus.co.jp/about/</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
+          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
         </is>
       </c>
     </row>
@@ -2145,60 +2185,38 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社TRUCK-ONE</t>
+          <t>株式会社九州ユーポス</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
+          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>山口県下松市生野屋南3-3-40</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-1100</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-5660</t>
-        </is>
-      </c>
+          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.truck-one.com/</t>
-        </is>
-      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/truckone_official/</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>買取専用窓口あり（0120-751-519）</t>
-        </is>
-      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-one.com/officelist/
-https://www.truck-one.com/company/</t>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/hikarinomori/
+https://www.u-pohs.co.jp/kagoshima
+https://www.u-pohs.co.jp/kumamotominami</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2208,7 +2226,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
         </is>
       </c>
     </row>
@@ -2218,39 +2236,27 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社ハヤシ</t>
+          <t>株式会社原ホンダ</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>岡山県倉敷市加須山334-4</t>
-        </is>
-      </c>
+          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>http://www.c-hayashi.com/</t>
-        </is>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
@@ -2258,18 +2264,20 @@
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
-https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0031/
+https://www.applenet.co.jp/shop/0033/
+https://www.applenet.co.jp/shop/0042/</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2287,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>株式会社パッション</t>
+          <t>株式会社TRUCK-ONE</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2287,44 +2295,52 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、愛知県</t>
+          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>愛知県春日井市味美町2丁目122番地</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>山口県下松市生野屋南3-3-40</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-1100</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-5660</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+          <t>https://www.truck-one.com/</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/truckone_official/</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>買取専門店ラビット勝川店を運営</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>217名（2025年12月）</t>
-        </is>
-      </c>
+          <t>買取専用窓口あり（0120-751-519）</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/company/outline/
-https://www.1963passion.co.jp/company/access/</t>
+          <t>https://www.truck-one.com/officelist/
+https://www.truck-one.com/company/</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -2334,7 +2350,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
+          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2360,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>株式会社東和モータース販売</t>
+          <t>株式会社ジャンプジャパン</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2352,70 +2368,38 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>東京都杉並区上高井戸1-21-18</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>03-3303-1146</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>03-3302-6600</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 稲葉弘幸</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>https://towa-motors.com/</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>https://towa-motors.com/contact.html</t>
-        </is>
-      </c>
+          <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/towa.motors</t>
-        </is>
-      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/company.html
-https://towa-motors.com/shop/</t>
+          <t>検索結果の抜粋（日立市・東海村・那珂市・水戸市・つくば市・牛久市・守谷市・龍ヶ崎市に店舗を構えるとの案内）
+https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
+          <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2425,31 +2409,39 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ツチヤ自動車株式会社</t>
+          <t>株式会社ハヤシ</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>千葉県市川市北方町4-1441-8</t>
+          <t>岡山県倉敷市加須山334-4</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>http://www.c-hayashi.com/</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
@@ -2457,8 +2449,8 @@
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
-https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
+          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
+https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -2468,7 +2460,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
+          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -2478,38 +2470,52 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>株式会社パッション</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>岐阜県、愛知県</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
+          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>愛知県春日井市味美町2丁目122番地</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>買取専門店ラビット勝川店を運営</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>217名（2025年12月）</t>
+        </is>
+      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0004/
-https://www.applenet.co.jp/shop/0007/
-https://www.applenet.co.jp/shop/0046/</t>
+          <t>https://www.1963passion.co.jp/company/outline/
+https://www.1963passion.co.jp/company/access/</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -2519,7 +2525,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
+          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -2529,74 +2535,78 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヨシダオートサービス</t>
+          <t>株式会社東和モータース販売</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+          <t>東京都杉並区上高井戸1-21-18</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>072-246-0301</t>
+          <t>03-3303-1146</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>072-246-0302</t>
+          <t>03-3302-6600</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>吉田宜史</t>
+          <t>代表取締役社長 稲葉弘幸</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+          <t>https://towa-motors.com/</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/contact/</t>
+          <t>https://towa-motors.com/contact.html</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/towa.motors</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>218名（2025年1月）</t>
+          <t>50名</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
+          <t>https://towa-motors.com/company.html
+https://towa-motors.com/shop/</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
+          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
         </is>
       </c>
     </row>
@@ -2606,25 +2616,25 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>ツチヤ自動車株式会社</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
+          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
+          <t>千葉県市川市北方町4-1441-8</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -2638,8 +2648,8 @@
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
+https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -2649,7 +2659,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
         </is>
       </c>
     </row>
@@ -2659,20 +2669,20 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>株式会社アップルカーセールス</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -2688,9 +2698,9 @@
       <c r="P34" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/</t>
+https://www.applenet.co.jp/shop/0004/
+https://www.applenet.co.jp/shop/0007/
+https://www.applenet.co.jp/shop/0046/</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -2700,7 +2710,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
         </is>
       </c>
     </row>
@@ -2710,35 +2720,64 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>松下モータース</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -2748,7 +2787,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2797,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>株式会社AOZORA COMPANY</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2766,17 +2805,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>東京都、新潟県、大阪府、福岡県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
+          <t>浜松市内6店舗</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>新潟県新潟市西区黒鳥5243番地1</t>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -2790,8 +2829,8 @@
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
-厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -2801,7 +2840,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2850,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2819,47 +2858,30 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -2869,7 +2891,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2901,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>松下モータース</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2887,12 +2909,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2907,20 +2929,17 @@
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2949,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社AOZORA COMPANY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2938,23 +2957,23 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都、新潟県、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
+          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>新潟県新潟市西区黒鳥5243番地1</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tortoise-k-carlife.com/</t>
-        </is>
-      </c>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
@@ -2962,8 +2981,8 @@
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
-https://www.applenet.co.jp/shop/</t>
+          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
+厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -2973,7 +2992,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。</t>
+          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2983,7 +3002,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -2991,37 +3010,57 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 石戸宏樹</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>26名</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://www.apple-car.jp/company</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3070,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユー・パーク</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -3039,48 +3078,30 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9566</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9590</t>
-        </is>
-      </c>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-parknet.com/</t>
-        </is>
-      </c>
+      <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>買取無料査定あり</t>
-        </is>
-      </c>
+      <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/about-us/
-https://www.u-parknet.com/</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -3090,7 +3111,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
         </is>
       </c>
     </row>
@@ -3100,77 +3121,50 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>human joint株式会社</t>
+          <t>株式会社トータス</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>03-4446-7735</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>03-5422-8006</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 齊藤博行</t>
-        </is>
-      </c>
+          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/</t>
+          <t>https://www.tortoise-k-carlife.com/</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>中古自動車の販売および買取（事業内容）</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>32名</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/company/</t>
+          <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
+https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。</t>
         </is>
       </c>
     </row>
@@ -3180,65 +3174,45 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>株式会社CIA</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
-        </is>
-      </c>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 大内康弘</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.yacco.cc/</t>
-        </is>
-      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>キャンピングカー買取（買取センター4か所）</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/company/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
         </is>
       </c>
     </row>
@@ -3248,262 +3222,479 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
+          <t>株式会社ユー・パーク</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>048-798-9566</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>048-798-9590</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-parknet.com/</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>買取無料査定あり</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-parknet.com/about-us/
+https://www.u-parknet.com/</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>human joint株式会社</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>03-4446-7735</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>03-5422-8006</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 齊藤博行</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>中古自動車の販売および買取（事業内容）</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>32名</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>https://cococar-hp.net/company/</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>株式会社CIA</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 大内康弘</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー買取（買取センター4か所）</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/company/</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>株式会社NIIZAWA</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>広島県、山口県</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>広島県廿日市市大野原1丁目2-20</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>0829-30-8103</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>0829-30-8104</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/contact/</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keimarket.k
 https://www.facebook.com/share/1AhR49eysR
 https://youtube.com/@keimarket398</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>95名（パート含む）</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/company/
 https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
-      <c r="Q44" s="2" t="inlineStr">
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
         <is>
           <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>株式会社Y's GARAGE</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>京都府、鳥取県、島根県</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>京都府宇治市槇島町三十五38-1</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>0774-25-5557</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>代表取締役 桐畑勇志</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>https://k-smile.jp/</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>158名（アルバイト含む、令和8年10月）</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>https://k-smile.jp/company/</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>株式会社ロイヤルオートサービス</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C49" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>長野県</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>長野県松本市村井町南2-1-5</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>0120-107-817</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>代表取締役 中田忠章</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/contact/</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/royal_auto_
 https://www.instagram.com/royal_auto_service/?hl=ja
 https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>187名</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="inlineStr">
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>株式会社横浜ユーポス</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C50" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>栃木県、神奈川県</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/kouhoku
@@ -3511,12 +3702,12 @@
 https://www.u-pohs.co.jp/tsuzuki</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
         </is>
@@ -3606,7 +3797,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -3726,7 +3917,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -4056,7 +4247,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -4136,7 +4327,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62"/>
@@ -4166,7 +4357,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66">
@@ -4176,7 +4367,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -4196,7 +4387,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69"/>
@@ -4226,7 +4417,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73">
@@ -4236,7 +4427,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4250,7 +4441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4595,7 +4786,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>同じ4店舗（豊橋・岡崎安城・豊田・四日市）で「CAST」の名称の掲載もあり、同一の運営会社の可能性。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -5268,7 +5463,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ポケットカーズ（運営会社未確認）</t>
+          <t>カーライフステーション（埼玉）</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -5276,31 +5471,47 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>女池店、三条店、長岡店</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>上尾店、久喜店、岩槻インター店</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県さいたま市見沼区宮ケ谷塔91-1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0120-344-713</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>048-681-5088</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/</t>
+          <t>https://344860.net/</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>158人（2019年度）</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/shop/</t>
+          <t>https://344860.net/</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -5310,7 +5521,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
+          <t>軽・普通車の未使用車専門店。従業員158人の規模から、ほかの業態の店舗がある可能性。運営会社名未確認。</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5536,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>古城モータース</t>
+          <t>ポケットカーズ（運営会社未確認）</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -5333,29 +5544,21 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>高岡本店、富山店、石川白山店</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>富山県高岡市二塚425番地</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0120-540-118</t>
-        </is>
-      </c>
+          <t>女池店、三条店、長岡店</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/</t>
+          <t>https://www.pocketcars.jp/</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -5365,7 +5568,7 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/</t>
+          <t>https://www.pocketcars.jp/shop/</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -5373,7 +5576,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -5386,7 +5593,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>古城モータース</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -5394,29 +5601,29 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
+          <t>高岡本店、富山店、石川白山店</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
+          <t>富山県高岡市二塚425番地</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>06-6538-8844</t>
+          <t>0120-540-118</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
@@ -5426,20 +5633,15 @@
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -5452,7 +5654,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -5460,29 +5662,29 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/</t>
+          <t>https://www.autogallery.co.jp/</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
@@ -5492,8 +5694,8 @@
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -5503,7 +5705,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5720,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -5526,19 +5728,31 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 河野修一</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.csauto.jp/</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
@@ -5546,9 +5760,8 @@
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -5558,7 +5771,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5786,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -5581,31 +5794,19 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
-        </is>
-      </c>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 上武英輝</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kamitake.net/</t>
-        </is>
-      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
@@ -5613,8 +5814,9 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -5622,7 +5824,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -5635,7 +5841,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>株式会社カミタケモータース</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -5643,19 +5849,31 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>大阪府、奈良県、大分県</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>枚方本店、奈良店、大分店</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
@@ -5663,9 +5881,8 @@
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -5673,11 +5890,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="S24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -5690,7 +5903,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>株式会社シマダオート商事</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -5698,12 +5911,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -5718,7 +5931,9 @@
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -5728,7 +5943,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>ユーポス以外の事業は未確認。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5958,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>株式会社フロンティアモータース</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -5751,12 +5966,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>大阪府、兵庫県</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -5771,9 +5986,7 @@
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -5783,7 +5996,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポス以外の事業は未確認。</t>
         </is>
       </c>
     </row>
@@ -5793,12 +6006,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FC本部</t>
+          <t>4店舗以下</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーポス</t>
+          <t>株式会社ベネフィット</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
@@ -5806,35 +6019,19 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>06-6532-6532</t>
-        </is>
-      </c>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 柏原隆宏</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-pohs.co.jp/</t>
-        </is>
-      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
@@ -5842,18 +6039,19 @@
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/about/company_info
-https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5863,12 +6061,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>4店舗以下</t>
+          <t>FC本部</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>株式会社ユーポス</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -5876,19 +6074,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>ユーポス外環河内長野店、ユーポス高石店、ユーポス岸和田南店</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区新町1-28-3 四ツ橋グランスクエア3F</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>06-6532-6532</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 柏原隆宏</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
@@ -5896,19 +6110,18 @@
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://www.u-pohs.co.jp/about/company_info
+https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>FC本部。大阪府内でFCオーナーの表示がない3店舗を直営と推定した。ロードカーと代表者が同じ。</t>
         </is>
       </c>
     </row>
@@ -5923,7 +6136,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社ユーリンクス</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -5931,12 +6144,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
+          <t>アラジン二又瀬店、アラジン小倉南店、アラジン飯塚店</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -5951,19 +6164,17 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/</t>
+          <t>https://autoc-one.jp/ullo/shop/3142/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>車買取りネットワーク「アラジン」の運営会社の一つ。アラジンは九州中心に複数の運営会社がある（久留米南店は株式会社Alive）。他店舗の運営会社は未確認。</t>
         </is>
       </c>
     </row>
@@ -5978,7 +6189,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>阿部勝自動車工業株式会社</t>
+          <t>株式会社リフトオフ</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -5986,23 +6197,19 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>茨城県、千葉県、東京都</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>https://k-mishiyo.abekatu.co.jp/</t>
-        </is>
-      </c>
+      <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
@@ -6010,15 +6217,21 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr"/>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -6031,20 +6244,20 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎有限会社</t>
+          <t>株式会社中州自動車</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>宮崎県</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -6059,8 +6272,9 @@
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0056/
-https://www.applenet.co.jp/shop/0149/</t>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -6070,7 +6284,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6085,27 +6299,31 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>タイガー石油株式会社</t>
+          <t>阿部勝自動車工業株式会社</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
+          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>https://k-mishiyo.abekatu.co.jp/</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
@@ -6113,19 +6331,15 @@
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -6138,7 +6352,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>大谷自動車株式会社</t>
+          <t>アップル宮崎有限会社</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -6146,47 +6360,28 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>大阪府、和歌山県</t>
+          <t>宮崎県</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>大阪本店、和歌山店</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>大阪府泉佐野市長滝753</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>072-465-0492</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>072-465-3109</t>
-        </is>
-      </c>
+          <t>アップル宮崎新名爪店、アップル宮崎空港店</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.otani-j.co.jp/</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>81名</t>
-        </is>
-      </c>
+      <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>https://www.otani-j.co.jp/company</t>
+          <t>https://www.applenet.co.jp/shop/0056/
+https://www.applenet.co.jp/shop/0149/</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -6194,7 +6389,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -6207,7 +6406,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>平岩石油販売株式会社</t>
+          <t>タイガー石油株式会社</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -6215,12 +6414,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>アップル練馬関町店、アップル板橋環8店</t>
+          <t>ユーポス香里ヶ丘店、ユーポス高槻上牧店</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -6235,8 +6434,7 @@
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0175/
-https://www.applenet.co.jp/shop/0247/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -6246,7 +6444,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>高槻上牧店のページには「タイガーエナジー株式会社」の表記もあり、名寄せに迷った。燃料会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6459,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>月原自動車株式会社</t>
+          <t>大谷自動車株式会社</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -6269,55 +6467,55 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>愛媛県</t>
+          <t>大阪府、和歌山県</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>ハピット 今治、ハピット 新居浜</t>
+          <t>大阪本店、和歌山店</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>愛媛県今治市小泉4丁目1-2</t>
+          <t>大阪府泉佐野市長滝753</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0898-35-4488</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>月原正志</t>
-        </is>
-      </c>
+          <t>072-465-0492</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>072-465-3109</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>https://hapit-car.com/</t>
+          <t>https://www.otani-j.co.jp/</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>https://hapit-car.com/</t>
+          <t>https://www.otani-j.co.jp/company</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>ハピット軽未使用車専門店。</t>
-        </is>
-      </c>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -6330,7 +6528,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>株式会社B&amp;F</t>
+          <t>平岩石油販売株式会社</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -6338,12 +6536,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>アップル古河4号店、アップル守谷店</t>
+          <t>アップル練馬関町店、アップル板橋環8店</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -6358,8 +6556,8 @@
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0140/
-https://www.applenet.co.jp/shop/0146/</t>
+          <t>https://www.applenet.co.jp/shop/0175/
+https://www.applenet.co.jp/shop/0247/</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -6384,7 +6582,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>株式会社NEXTモビィ</t>
+          <t>月原自動車株式会社</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -6392,19 +6590,35 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
+          <t>ハピット 今治、ハピット 新居浜</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>愛媛県今治市小泉4丁目1-2</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0898-35-4488</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>月原正志</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>https://hapit-car.com/</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
@@ -6412,18 +6626,17 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukuoka-inter
-https://www.u-pohs.co.jp/kokurahigashi-inter</t>
+          <t>https://hapit-car.com/</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ハピット軽未使用車専門店。</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6651,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>株式会社PlusOne</t>
+          <t>株式会社B&amp;F</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -6446,12 +6659,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>アップル安城南店、アップル弥富1号線店</t>
+          <t>アップル古河4号店、アップル守谷店</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -6466,8 +6679,8 @@
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0129/
-https://www.applenet.co.jp/shop/0219/</t>
+          <t>https://www.applenet.co.jp/shop/0140/
+https://www.applenet.co.jp/shop/0146/</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -6492,7 +6705,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>株式会社SHIMAカーライフコネクテッド</t>
+          <t>株式会社NEXTモビィ</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -6500,12 +6713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>アップル金沢店、アップル高岡店</t>
+          <t>ユーポス福岡インター店、ユーポス小倉東インター店</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -6520,8 +6733,8 @@
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0313/
-https://www.applenet.co.jp/shop/0339/</t>
+          <t>https://www.u-pohs.co.jp/fukuoka-inter
+https://www.u-pohs.co.jp/kokurahigashi-inter</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -6531,7 +6744,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6759,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>株式会社WinWinサービス</t>
+          <t>株式会社PlusOne</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -6554,12 +6767,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>アップル盛岡盛南店、アップル盛岡北店</t>
+          <t>アップル安城南店、アップル弥富1号線店</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -6574,8 +6787,8 @@
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0117/
-https://www.applenet.co.jp/shop/0137/</t>
+          <t>https://www.applenet.co.jp/shop/0129/
+https://www.applenet.co.jp/shop/0219/</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -6600,7 +6813,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>株式会社イトー</t>
+          <t>株式会社SHIMAカーライフコネクテッド</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -6608,12 +6821,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>アップル岸和田店、アップル河内長野中央店</t>
+          <t>アップル金沢店、アップル高岡店</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -6628,8 +6841,8 @@
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0258/
-https://www.applenet.co.jp/shop/0278/</t>
+          <t>https://www.applenet.co.jp/shop/0313/
+https://www.applenet.co.jp/shop/0339/</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -6639,7 +6852,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>アップル以外の店舗は未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6867,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>株式会社インデックス</t>
+          <t>株式会社WinWinサービス</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -6662,12 +6875,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
+          <t>アップル盛岡盛南店、アップル盛岡北店</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -6682,8 +6895,8 @@
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0018/
-https://www.applenet.co.jp/shop/0029/</t>
+          <t>https://www.applenet.co.jp/shop/0117/
+https://www.applenet.co.jp/shop/0137/</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
@@ -6708,7 +6921,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>株式会社イーグルオートサービス</t>
+          <t>株式会社イトー</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -6716,12 +6929,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
+          <t>アップル岸和田店、アップル河内長野中央店</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -6736,8 +6949,8 @@
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0032/
-https://www.applenet.co.jp/shop/0063/</t>
+          <t>https://www.applenet.co.jp/shop/0258/
+https://www.applenet.co.jp/shop/0278/</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -6747,7 +6960,7 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップル以外の店舗は未確認。</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6975,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>株式会社エムエフノースジャパン</t>
+          <t>株式会社インデックス</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -6770,12 +6983,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>、</t>
+          <t>アップル美女木バイパス店、アップル水戸バイパス店</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -6790,8 +7003,8 @@
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0035/
-https://www.applenet.co.jp/shop/0043/</t>
+          <t>https://www.applenet.co.jp/shop/0018/
+https://www.applenet.co.jp/shop/0029/</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -6816,7 +7029,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>株式会社オカモト</t>
+          <t>株式会社イーグルオートサービス</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -6824,12 +7037,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>アップル西帯広店、アップル帯広店</t>
+          <t>アップル木更津長須賀店、アップル千葉桜木店</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -6844,8 +7057,8 @@
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0307/
-https://www.applenet.co.jp/shop/0334/</t>
+          <t>https://www.applenet.co.jp/shop/0032/
+https://www.applenet.co.jp/shop/0063/</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -6870,7 +7083,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>株式会社オリンピアオート</t>
+          <t>株式会社エムエフノースジャパン</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -6878,12 +7091,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>アップルひたちなか店、アップル那珂中央店</t>
+          <t>、</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -6898,8 +7111,8 @@
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0208/
-https://www.applenet.co.jp/shop/0280/</t>
+          <t>https://www.applenet.co.jp/shop/0035/
+https://www.applenet.co.jp/shop/0043/</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -6924,7 +7137,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートグローリー</t>
+          <t>株式会社オカモト</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -6932,12 +7145,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>ユーポス福重店、ユーポス直方店</t>
+          <t>アップル西帯広店、アップル帯広店</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -6952,8 +7165,8 @@
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/fukushige
-https://www.u-pohs.co.jp/nogata</t>
+          <t>https://www.applenet.co.jp/shop/0307/
+https://www.applenet.co.jp/shop/0334/</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -6963,7 +7176,7 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6978,7 +7191,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>株式会社カーボ</t>
+          <t>株式会社オリンピアオート</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -6986,31 +7199,19 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>福井県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>開発店、鯖江店</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>福井県福井市開発町6-15</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0776-52-7515</t>
-        </is>
-      </c>
+          <t>アップルひたちなか店、アップル那珂中央店</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cavo-kei.jp/</t>
-        </is>
-      </c>
+      <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
@@ -7018,7 +7219,8 @@
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>https://www.cavo-kei.jp/</t>
+          <t>https://www.applenet.co.jp/shop/0208/
+https://www.applenet.co.jp/shop/0280/</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
@@ -7028,7 +7230,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>グループ全体の従業員141名（グループ会社の店舗は未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7245,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>株式会社クインオート</t>
+          <t>株式会社オートグローリー</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -7051,12 +7253,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>京都府、兵庫県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>ユーポス亀岡店、ユーポス三田店</t>
+          <t>ユーポス福重店、ユーポス直方店</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -7071,8 +7273,8 @@
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kameoka
-https://www.u-pohs.co.jp/sanda/</t>
+          <t>https://www.u-pohs.co.jp/fukushige
+https://www.u-pohs.co.jp/nogata</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -7097,7 +7299,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>株式会社サコダ車輛</t>
+          <t>株式会社カーボ</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -7105,19 +7307,31 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>福井県</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>アップル海田店、アップル東広島店</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
+          <t>開発店、鯖江店</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>福井県福井市開発町6-15</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0776-52-7515</t>
+        </is>
+      </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cavo-kei.jp/</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
@@ -7125,8 +7339,7 @@
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0297/
-https://www.applenet.co.jp/shop/0298/</t>
+          <t>https://www.cavo-kei.jp/</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -7136,7 +7349,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 社名の正式表記は「サコダ車輌」の可能性。本社は広島市中区舟入南、売上高158億円・従業員240名（求人情報）。自社店舗の海田店（軽自動車専門）と佐伯区五日市の拠点もあり、合計4か所以上。自社サイト未確認のため境界扱い。</t>
+          <t>グループ全体の従業員141名（グループ会社の店舗は未確認）。</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7364,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>株式会社シブヤエネックスホールディングス</t>
+          <t>株式会社クインオート</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -7159,12 +7372,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>京都府、兵庫県</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>アップル相模原城山店、アップル大井松田インター店</t>
+          <t>ユーポス亀岡店、ユーポス三田店</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -7179,8 +7392,8 @@
       <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0266/
-https://www.applenet.co.jp/shop/0292/</t>
+          <t>https://www.u-pohs.co.jp/kameoka
+https://www.u-pohs.co.jp/sanda/</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
@@ -7190,7 +7403,7 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7418,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>株式会社スズキアリーナ瑞穂</t>
+          <t>株式会社サコダ車輛</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -7213,12 +7426,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>アップル青梅店、アップル西東京店</t>
+          <t>アップル海田店、アップル東広島店</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -7233,8 +7446,8 @@
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0057/
-https://www.applenet.co.jp/shop/0100/</t>
+          <t>https://www.applenet.co.jp/shop/0297/
+https://www.applenet.co.jp/shop/0298/</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
@@ -7244,7 +7457,7 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 社名の正式表記は「サコダ車輌」の可能性。本社は広島市中区舟入南、売上高158億円・従業員240名（求人情報）。自社店舗の海田店（軽自動車専門）と佐伯区五日市の拠点もあり、合計4か所以上。自社サイト未確認のため境界扱い。</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7472,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>株式会社トップワン</t>
+          <t>株式会社シブヤエネックスホールディングス</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -7267,12 +7480,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>アップル豊田梅坪店、アップル豊田南店</t>
+          <t>アップル相模原城山店、アップル大井松田インター店</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -7287,8 +7500,8 @@
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0075/
-https://www.applenet.co.jp/shop/0126/</t>
+          <t>https://www.applenet.co.jp/shop/0266/
+https://www.applenet.co.jp/shop/0292/</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -7313,7 +7526,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビーインプレスト</t>
+          <t>株式会社スズキアリーナ瑞穂</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -7321,12 +7534,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>アップル宇都宮北店、アップル大田原店</t>
+          <t>アップル青梅店、アップル西東京店</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -7341,8 +7554,8 @@
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0211/
-https://www.applenet.co.jp/shop/0303/</t>
+          <t>https://www.applenet.co.jp/shop/0057/
+https://www.applenet.co.jp/shop/0100/</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -7367,7 +7580,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファミリー</t>
+          <t>株式会社トップワン</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -7375,12 +7588,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>ファミリー可児店、ファミリー各務原店</t>
+          <t>アップル豊田梅坪店、アップル豊田南店</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -7395,17 +7608,18 @@
       <c r="P55" s="2" t="inlineStr"/>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0075/
+https://www.applenet.co.jp/shop/0126/</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7634,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミヤチ</t>
+          <t>株式会社ビーインプレスト</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -7428,12 +7642,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>アップル岐阜長良店、アップル関店</t>
+          <t>アップル宇都宮北店、アップル大田原店</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -7448,8 +7662,8 @@
       <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0101/
-https://www.applenet.co.jp/shop/0155/</t>
+          <t>https://www.applenet.co.jp/shop/0211/
+https://www.applenet.co.jp/shop/0303/</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
@@ -7474,7 +7688,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユアーズ</t>
+          <t>株式会社ファミリー</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -7482,31 +7696,19 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>森町店、下郡店</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>大分県大分市森437-1</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>097-578-9499</t>
-        </is>
-      </c>
+          <t>ファミリー可児店、ファミリー各務原店</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>https://kei-mishiyousya.com/</t>
-        </is>
-      </c>
+      <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
@@ -7514,7 +7716,7 @@
       <c r="P57" s="2" t="inlineStr"/>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>https://kei-mishiyousya.com/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0202095/map.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
@@ -7522,7 +7724,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>届出済未使用車専門店。確認できたのは2店舗だけだが、売上高107億円（採用サイト）の規模から、ほかに店舗がある可能性あり。公式サイト未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -7535,7 +7741,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>株式会社湯浅</t>
+          <t>株式会社ミヤチ</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -7543,12 +7749,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>アップル白井店、アップル松戸本店</t>
+          <t>アップル岐阜長良店、アップル関店</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -7563,8 +7769,8 @@
       <c r="P58" s="2" t="inlineStr"/>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0287/
-https://www.applenet.co.jp/shop/0293/</t>
+          <t>https://www.applenet.co.jp/shop/0101/
+https://www.applenet.co.jp/shop/0155/</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
@@ -7589,7 +7795,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>株式会社車のせんいち</t>
+          <t>株式会社ユアーズ</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -7597,19 +7803,31 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>みどり本店、伊勢崎店</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
+          <t>森町店、下郡店</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>大分県大分市森437-1</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>097-578-9499</t>
+        </is>
+      </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>https://kei-mishiyousya.com/</t>
+        </is>
+      </c>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
@@ -7617,7 +7835,7 @@
       <c r="P59" s="2" t="inlineStr"/>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>求人情報（検索結果の抜粋）</t>
+          <t>https://kei-mishiyousya.com/</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
@@ -7625,11 +7843,7 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>軽自動車39.8万円専門店ほか。確認できたのは2店舗と新店舗（みどり市笠懸町、オープン予定）。公式サイト未確認。</t>
-        </is>
-      </c>
+      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -7642,7 +7856,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>株式会社関西オート</t>
+          <t>株式会社湯浅</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -7650,27 +7864,19 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>八尾店、平野店</t>
+          <t>アップル白井店、アップル松戸本店</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 大川純平</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kansai-auto.jp/</t>
-        </is>
-      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr"/>
@@ -7678,7 +7884,8 @@
       <c r="P60" s="2" t="inlineStr"/>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>https://www.kansai-auto.jp/company/outline/</t>
+          <t>https://www.applenet.co.jp/shop/0287/
+https://www.applenet.co.jp/shop/0293/</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
@@ -7686,7 +7893,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として2店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -7699,35 +7910,27 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>GARIREO（ガリレオ、愛媛）</t>
+          <t>株式会社車のせんいち</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>愛媛県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店 ガリレオケイランド</t>
+          <t>みどり本店、伊勢崎店</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0800-200-3440</t>
-        </is>
-      </c>
+      <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>https://garireo.co.jp/</t>
-        </is>
-      </c>
+      <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
@@ -7735,7 +7938,7 @@
       <c r="P61" s="2" t="inlineStr"/>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>https://garireo.co.jp/shops/</t>
+          <t>求人情報（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
@@ -7745,7 +7948,7 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>「松山市と東温市に5店舗」の表記だが、販売店はケイランドで、ほかは整備工場（サービステラス）とコバック併設店（谷町・余戸・重信）。コバック併設店で販売もしていれば5店舗になる。運営会社の正式名称は未確認（GARIREO Corporation）。</t>
+          <t>軽自動車39.8万円専門店ほか。確認できたのは2店舗と新店舗（みどり市笠懸町、オープン予定）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -7760,11 +7963,11 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Re-BOOT株式会社</t>
+          <t>株式会社関西オート</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -7773,14 +7976,22 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>アップル大阪平野店</t>
+          <t>八尾店、平野店</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 大川純平</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kansai-auto.jp/</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
@@ -7788,7 +7999,7 @@
       <c r="P62" s="2" t="inlineStr"/>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0284/</t>
+          <t>https://www.kansai-auto.jp/company/outline/</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -7809,7 +8020,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>北摂オート株式会社</t>
+          <t>GARIREO（ガリレオ、愛媛）</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -7817,33 +8028,25 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>大阪府箕面市桜井2-16-17</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>072-723-1102</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 喜多克之</t>
-        </is>
-      </c>
+          <t>軽自動車専門店 ガリレオケイランド</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0800-200-3440</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>https://hokusetu-auto.com/</t>
+          <t>https://garireo.co.jp/</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr"/>
@@ -7853,15 +8056,19 @@
       <c r="P63" s="2" t="inlineStr"/>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>https://hokusetu-auto.com/company.php</t>
+          <t>https://garireo.co.jp/shops/</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="inlineStr"/>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>「松山市と東温市に5店舗」の表記だが、販売店はケイランドで、ほかは整備工場（サービステラス）とコバック併設店（谷町・余戸・重信）。コバック併設店で販売もしていれば5店舗になる。運営会社の正式名称は未確認（GARIREO Corporation）。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -7874,7 +8081,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>有限会社タイヨウ</t>
+          <t>Re-BOOT株式会社</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -7887,7 +8094,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>ユーポス富田林店</t>
+          <t>アップル大阪平野店</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -7902,7 +8109,7 @@
       <c r="P64" s="2" t="inlineStr"/>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.applenet.co.jp/shop/0284/</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -7910,11 +8117,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -7927,7 +8130,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>株式会社We Car CORE</t>
+          <t>北摂オート株式会社</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -7940,14 +8143,30 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>ユーポス貝塚店</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>大阪府箕面市桜井2-16-17</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>072-723-1102</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 喜多克之</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>https://hokusetu-auto.com/</t>
+        </is>
+      </c>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr"/>
@@ -7955,7 +8174,7 @@
       <c r="P65" s="2" t="inlineStr"/>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://hokusetu-auto.com/company.php</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -7963,11 +8182,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -7980,7 +8195,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>株式会社cantera</t>
+          <t>有限会社タイヨウ</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -7993,7 +8208,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>ユーポス外環四條畷店</t>
+          <t>ユーポス富田林店</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -8033,7 +8248,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>株式会社world of star</t>
+          <t>株式会社We Car CORE</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
@@ -8041,35 +8256,19 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>軽ワールド 和歌山湊店</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>和歌山県和歌山市湊1820-160</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>073-488-9199</t>
-        </is>
-      </c>
+          <t>ユーポス貝塚店</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>中谷和弘</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>https://kworld.jp/</t>
-        </is>
-      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr"/>
@@ -8077,15 +8276,19 @@
       <c r="P67" s="2" t="inlineStr"/>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>https://kworld.jp/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="inlineStr"/>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -8098,7 +8301,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>株式会社サンアイク</t>
+          <t>株式会社cantera</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
@@ -8106,27 +8309,19 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>茂原店</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>千葉県茂原市腰当526-1</t>
-        </is>
-      </c>
+          <t>ユーポス外環四條畷店</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sunaiku.com/</t>
-        </is>
-      </c>
+      <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr"/>
@@ -8134,15 +8329,19 @@
       <c r="P68" s="2" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>https://www.sunaiku.com/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="S68" s="2" t="inlineStr"/>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -8155,7 +8354,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>株式会社プロンザ</t>
+          <t>株式会社world of star</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
@@ -8163,19 +8362,35 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>和歌山県</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>ユーポス枚方店</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
+          <t>軽ワールド 和歌山湊店</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>和歌山県和歌山市湊1820-160</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>073-488-9199</t>
+        </is>
+      </c>
       <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>中谷和弘</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>https://kworld.jp/</t>
+        </is>
+      </c>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
@@ -8183,19 +8398,15 @@
       <c r="P69" s="2" t="inlineStr"/>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://kworld.jp/</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="S69" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -8208,7 +8419,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>株式会社ポロ</t>
+          <t>株式会社サンアイク</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
@@ -8216,33 +8427,25 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>本社</t>
+          <t>茂原店</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>大阪府高槻市富田町6丁目15-13</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>072-694-6641</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>072-694-9913</t>
-        </is>
-      </c>
+          <t>千葉県茂原市腰当526-1</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>https://www.polojp.com/</t>
+          <t>https://www.sunaiku.com/</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr"/>
@@ -8252,12 +8455,12 @@
       <c r="P70" s="2" t="inlineStr"/>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>https://www.polojp.com/</t>
+          <t>https://www.sunaiku.com/</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr"/>
@@ -8273,7 +8476,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>豊栄モータース</t>
+          <t>株式会社プロンザ</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -8286,7 +8489,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>ユーポス寝屋川店</t>
+          <t>ユーポス枚方店</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -8310,6 +8513,124 @@
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ポロ</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>大阪府高槻市富田町6丁目15-13</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>072-694-6641</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>072-694-9913</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.polojp.com/</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>4店舗以下</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>豊栄モータース</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス寝屋川店</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
         <is>
           <t>ユーポス本部の店舗ページによる。ユーポス以外の店舗は未確認。（法人格の表示なし）</t>
         </is>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社ナック（ジャック査定センター）</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3182,37 +3182,58 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>京都府、大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
+          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>078-685-0066</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 難波克年</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>https://jacnet.jp/</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>中古車の査定買取（主業）</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://jacnet.jp/site/company/?pt=detail
+https://jacnet.jp/site/company/?pt=shop_list</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3243,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユー・パーク</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3230,58 +3251,37 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9566</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9590</t>
-        </is>
-      </c>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-parknet.com/</t>
-        </is>
-      </c>
+      <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>買取無料査定あり</t>
-        </is>
-      </c>
+      <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/about-us/
-https://www.u-parknet.com/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
         </is>
       </c>
     </row>
@@ -3291,67 +3291,56 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>human joint株式会社</t>
+          <t>株式会社ユー・パーク</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
+          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
+          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>03-4446-7735</t>
+          <t>048-798-9566</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>03-5422-8006</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 齊藤博行</t>
-        </is>
-      </c>
+          <t>048-798-9590</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/</t>
+          <t>https://www.u-parknet.com/</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
-        </is>
-      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>中古自動車の販売および買取（事業内容）</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>32名</t>
-        </is>
-      </c>
+          <t>買取無料査定あり</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/company/</t>
+          <t>https://www.u-parknet.com/about-us/
+https://www.u-parknet.com/</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -3361,7 +3350,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3360,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>株式会社CIA</t>
+          <t>human joint株式会社</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3379,47 +3368,59 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
+          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>03-4446-7735</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>03-5422-8006</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 大内康弘</t>
+          <t>代表取締役 齊藤博行</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/</t>
+          <t>https://cococar-hp.net/</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー買取（買取センター4か所）</t>
+          <t>中古自動車の販売および買取（事業内容）</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>50名</t>
+          <t>32名</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/company/</t>
+          <t>https://cococar-hp.net/company/</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -3429,7 +3430,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3440,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>株式会社NIIZAWA</t>
+          <t>株式会社CIA</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3447,140 +3448,140 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 大内康弘</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー買取（買取センター4か所）</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/company/</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>株式会社NIIZAWA</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
           <t>広島県、山口県</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>広島県廿日市市大野原1丁目2-20</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>0829-30-8103</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>0829-30-8104</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/contact/</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keimarket.k
 https://www.facebook.com/share/1AhR49eysR
 https://youtube.com/@keimarket398</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>95名（パート含む）</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/company/
 https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr">
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>株式会社Y's GARAGE</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>京都府、鳥取県、島根県</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>京都府宇治市槇島町三十五38-1</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>0774-25-5557</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 桐畑勇志</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>158名（アルバイト含む、令和8年10月）</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/company/</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3591,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロイヤルオートサービス</t>
+          <t>株式会社Y's GARAGE</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3598,103 +3599,171 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>京都府、鳥取県、島根県</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>長野県松本市村井町南2-1-5</t>
+          <t>京都府宇治市槇島町三十五38-1</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0120-107-817</t>
+          <t>0774-25-5557</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
+          <t>代表取締役 桐畑勇志</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>158名（アルバイト含む、令和8年10月）</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/company/</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ロイヤルオートサービス</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>長野県松本市村井町南2-1-5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>0120-107-817</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
           <t>代表取締役 中田忠章</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/contact/</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/royal_auto_
 https://www.instagram.com/royal_auto_service/?hl=ja
 https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>187名</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr">
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
-      <c r="Q49" s="2" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>株式会社横浜ユーポス</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>栃木県、神奈川県</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/kouhoku
@@ -3702,12 +3771,12 @@
 https://www.u-pohs.co.jp/tsuzuki</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="inlineStr">
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="R51" s="2" t="inlineStr">
         <is>
           <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
         </is>
@@ -3724,7 +3793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3957,7 +4026,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -3967,7 +4036,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -3977,7 +4046,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -4283,7 +4352,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -4293,7 +4362,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -4303,7 +4372,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -4313,7 +4382,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -4323,111 +4392,121 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B62" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>店舗数の分布</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5〜9店舗</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>28</v>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10〜19店舗</t>
+          <t>5〜9店舗</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20〜30店舗</t>
+          <t>10〜19店舗</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>20〜30店舗</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="B69" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>確度別の社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>確度</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>18</v>
+          <t>確度</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>31</v>
+      <c r="B74" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -8647,7 +8726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9387,6 +9466,102 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ティーバイティーガレージ（TxTGARAGE）</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>北海道8店舗（比較記事）、岩手にも店舗</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>運営会社・公式店舗一覧未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>ミスターシャーマン</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>長野県内4店舗（比較記事）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>境界（4店舗）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>買取マウス</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>新潟市内4店舗（比較記事）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>境界（4店舗）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>アップルワールド</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>豊田市、1972年設立</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>店舗数未確認</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社リトラス</t>
+          <t>株式会社ジーアフター</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2132,50 +2132,58 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
+          <t>宮城県、栃木県、埼玉県、千葉県、新潟県、岡山県</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
+          <t>MEGA仙台新港店、MEGA佐野厄除大師店、MEGA越谷レイクタウン店、MEGA千葉北インター店、G-BORDER千葉北インター店、成田店、木更津店、MEGA新潟店、MEGA東岡山店</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
+          <t>東京都中央区日本橋2-12-6 高島屋THビル北館4階</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>代表取締役社長 津田猛</t>
+          <t>代表取締役社長 西川佳吾</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://www.retrus.co.jp/</t>
+          <t>https://www.g-after.co.jp/</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>車買取専門店（主業）</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>210名（2023年6月期実績）</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>https://www.retrus.co.jp/about/office.asp
-https://www.retrus.co.jp/about/</t>
+          <t>https://www.g-after.co.jp/company
+https://www.g-after.co.jp/shop/</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
+          <t>車買取専門店ジーアフター（MEGA店など）。店舗数は公式サイトの店舗一覧9件。都道府県は店舗名から判断。</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2193,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社九州ユーポス</t>
+          <t>株式会社リトラス</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2193,19 +2201,31 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
+          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 津田猛</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.retrus.co.jp/</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
@@ -2213,20 +2233,18 @@
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/hikarinomori/
-https://www.u-pohs.co.jp/kagoshima
-https://www.u-pohs.co.jp/kumamotominami</t>
+          <t>https://www.retrus.co.jp/about/office.asp
+https://www.retrus.co.jp/about/</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
+          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2254,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社原ホンダ</t>
+          <t>株式会社九州ユーポス</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2244,12 +2262,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
+          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -2264,93 +2282,71 @@
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/hikarinomori/
+https://www.u-pohs.co.jp/kagoshima
+https://www.u-pohs.co.jp/kumamotominami</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>株式会社原ホンダ</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0031/
 https://www.applenet.co.jp/shop/0033/
 https://www.applenet.co.jp/shop/0042/</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>株式会社TRUCK-ONE</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>山口県下松市生野屋南3-3-40</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-1100</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-5660</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.truck-one.com/</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/truckone_official/</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>買取専用窓口あり（0120-751-519）</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.truck-one.com/officelist/
-https://www.truck-one.com/company/</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2356,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>株式会社ジャンプジャパン</t>
+          <t>株式会社TRUCK-ONE</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2368,38 +2364,62 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>山口県下松市生野屋南3-3-40</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-1100</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-5660</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.truck-one.com/</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/truckone_official/</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>買取専用窓口あり（0120-751-519）</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（日立市・東海村・那珂市・水戸市・つくば市・牛久市・守谷市・龍ヶ崎市に店舗を構えるとの案内）
-https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-</t>
+          <t>https://www.truck-one.com/officelist/
+https://www.truck-one.com/company/</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。</t>
+          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2429,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>株式会社ハヤシ</t>
+          <t>株式会社ジャンプジャパン</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2417,31 +2437,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>岡山県倉敷市加須山334-4</t>
-        </is>
-      </c>
+          <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>http://www.c-hayashi.com/</t>
-        </is>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
@@ -2449,8 +2457,8 @@
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
-https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
+          <t>検索結果の抜粋（日立市・東海村・那珂市・水戸市・つくば市・牛久市・守谷市・龍ヶ崎市に店舗を構えるとの案内）
+https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -2460,7 +2468,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
+          <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2478,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>株式会社パッション</t>
+          <t>株式会社ハヤシ</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2478,54 +2486,50 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、愛知県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>愛知県春日井市味美町2丁目122番地</t>
+          <t>岡山県倉敷市加須山334-4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+          <t>http://www.c-hayashi.com/</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>買取専門店ラビット勝川店を運営</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>217名（2025年12月）</t>
-        </is>
-      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/company/outline/
-https://www.1963passion.co.jp/company/access/</t>
+          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
+https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
+          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2539,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>株式会社東和モータース販売</t>
+          <t>株式会社パッション</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2543,60 +2547,44 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
+          <t>岐阜県、愛知県</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
+          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>東京都杉並区上高井戸1-21-18</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>03-3303-1146</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>03-3302-6600</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 稲葉弘幸</t>
-        </is>
-      </c>
+          <t>愛知県春日井市味美町2丁目122番地</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>https://towa-motors.com/contact.html</t>
-        </is>
-      </c>
+          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/towa.motors</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>買取専門店ラビット勝川店を運営</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50名</t>
+          <t>217名（2025年12月）</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/company.html
-https://towa-motors.com/shop/</t>
+          <t>https://www.1963passion.co.jp/company/outline/
+https://www.1963passion.co.jp/company/access/</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -2606,7 +2594,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
+          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -2616,50 +2604,78 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ツチヤ自動車株式会社</t>
+          <t>株式会社東和モータース販売</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>千葉県市川市北方町4-1441-8</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
+          <t>東京都杉並区上高井戸1-21-18</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>03-3303-1146</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>03-3302-6600</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 稲葉弘幸</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>https://towa-motors.com/</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>https://towa-motors.com/contact.html</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/towa.motors</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
-https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
+          <t>https://towa-motors.com/company.html
+https://towa-motors.com/shop/</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
+          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2685,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>ツチヤ自動車株式会社</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2677,15 +2693,19 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>千葉県市川市北方町4-1441-8</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2697,97 +2717,69 @@
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
+          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
+https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>株式会社アップルカーセールス</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0004/
 https://www.applenet.co.jp/shop/0007/
 https://www.applenet.co.jp/shop/0046/</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ヨシダオートサービス</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>大阪府</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0301</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0302</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>吉田宜史</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/contact/</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>218名（2025年1月）</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -2797,40 +2789,64 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -2840,7 +2856,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2866,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2858,15 +2874,19 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
+          <t>浜松市内6店舗</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2878,20 +2898,18 @@
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2919,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>松下モータース</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2909,12 +2927,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2929,17 +2947,20 @@
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2970,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>株式会社AOZORA COMPANY</t>
+          <t>松下モータース</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2957,19 +2978,15 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>東京都、新潟県、大阪府、福岡県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>新潟県新潟市西区黒鳥5243番地1</t>
-        </is>
-      </c>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2981,8 +2998,7 @@
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
-厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -2992,7 +3008,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3018,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>株式会社AOZORA COMPANY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -3010,57 +3026,42 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>東京都、新潟県、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>新潟県新潟市西区黒鳥5243番地1</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company</t>
+          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
+厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
+          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3071,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -3078,30 +3079,47 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 石戸宏樹</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>26名</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/</t>
+          <t>https://www.apple-car.jp/company</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -3111,7 +3129,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3139,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3129,23 +3147,19 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tortoise-k-carlife.com/</t>
-        </is>
-      </c>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
@@ -3153,18 +3167,20 @@
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
-https://www.applenet.co.jp/shop/</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3190,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>株式会社ナック（ジャック査定センター）</t>
+          <t>株式会社トータス</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3182,58 +3198,42 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>京都府、大阪府、兵庫県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
-        </is>
-      </c>
+          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>078-685-0066</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 難波克年</t>
-        </is>
-      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://jacnet.jp/</t>
+          <t>https://www.tortoise-k-carlife.com/</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>中古車の査定買取（主業）</t>
-        </is>
-      </c>
+      <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>https://jacnet.jp/site/company/?pt=detail
-https://jacnet.jp/site/company/?pt=shop_list</t>
+          <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
+https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
+          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社ナック（ジャック査定センター）</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3251,37 +3251,58 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>京都府、大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
+          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>078-685-0066</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 難波克年</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>https://jacnet.jp/</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>中古車の査定買取（主業）</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://jacnet.jp/site/company/?pt=detail
+https://jacnet.jp/site/company/?pt=shop_list</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3312,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユー・パーク</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3299,58 +3320,37 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9566</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9590</t>
-        </is>
-      </c>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-parknet.com/</t>
-        </is>
-      </c>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>買取無料査定あり</t>
-        </is>
-      </c>
+      <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/about-us/
-https://www.u-parknet.com/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
         </is>
       </c>
     </row>
@@ -3360,67 +3360,56 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>human joint株式会社</t>
+          <t>株式会社ユー・パーク</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
+          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
+          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>03-4446-7735</t>
+          <t>048-798-9566</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>03-5422-8006</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 齊藤博行</t>
-        </is>
-      </c>
+          <t>048-798-9590</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/</t>
+          <t>https://www.u-parknet.com/</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
-        </is>
-      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>中古自動車の販売および買取（事業内容）</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>32名</t>
-        </is>
-      </c>
+          <t>買取無料査定あり</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/company/</t>
+          <t>https://www.u-parknet.com/about-us/
+https://www.u-parknet.com/</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -3430,7 +3419,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3429,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>株式会社CIA</t>
+          <t>human joint株式会社</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3448,47 +3437,59 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
+          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>03-4446-7735</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>03-5422-8006</t>
+        </is>
+      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 大内康弘</t>
+          <t>代表取締役 齊藤博行</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/</t>
+          <t>https://cococar-hp.net/</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー買取（買取センター4か所）</t>
+          <t>中古自動車の販売および買取（事業内容）</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>50名</t>
+          <t>32名</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/company/</t>
+          <t>https://cococar-hp.net/company/</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -3498,7 +3499,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3509,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>株式会社NIIZAWA</t>
+          <t>株式会社CIA</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3516,140 +3517,140 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 大内康弘</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー買取（買取センター4か所）</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/company/</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>株式会社NIIZAWA</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
           <t>広島県、山口県</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>広島県廿日市市大野原1丁目2-20</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>0829-30-8103</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>0829-30-8104</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/contact/</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keimarket.k
 https://www.facebook.com/share/1AhR49eysR
 https://youtube.com/@keimarket398</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>95名（パート含む）</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/company/
 https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="inlineStr">
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>株式会社Y's GARAGE</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>京都府、鳥取県、島根県</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>京都府宇治市槇島町三十五38-1</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>0774-25-5557</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 桐畑勇志</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>158名（アルバイト含む、令和8年10月）</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/company/</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3660,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロイヤルオートサービス</t>
+          <t>株式会社Y's GARAGE</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3667,103 +3668,171 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>京都府、鳥取県、島根県</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>長野県松本市村井町南2-1-5</t>
+          <t>京都府宇治市槇島町三十五38-1</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0120-107-817</t>
+          <t>0774-25-5557</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
+          <t>代表取締役 桐畑勇志</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>158名（アルバイト含む、令和8年10月）</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/company/</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ロイヤルオートサービス</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>長野県松本市村井町南2-1-5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>0120-107-817</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
           <t>代表取締役 中田忠章</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/contact/</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/royal_auto_
 https://www.instagram.com/royal_auto_service/?hl=ja
 https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>187名</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="inlineStr">
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="R51" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>株式会社横浜ユーポス</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>栃木県、神奈川県</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/kouhoku
@@ -3771,12 +3840,12 @@
 https://www.u-pohs.co.jp/tsuzuki</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="inlineStr">
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
         </is>
@@ -3846,7 +3915,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -3876,7 +3945,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -3896,7 +3965,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -3906,7 +3975,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -3936,7 +4005,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -4086,7 +4155,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4286,7 +4355,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -4436,7 +4505,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67">
@@ -4466,7 +4535,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70"/>
@@ -4506,7 +4575,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -8726,7 +8795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9562,6 +9631,31 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Car Shop IKKI</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>さいたま市北区本社、埼玉県内に複数店舗</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>公式サイトに接続できず、運営会社・店舗数未確認</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -965,149 +965,145 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>オートコミュニケーションズ株式会社（オニキス）</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>北海道、埼玉県、千葉県、東京都、熊本県</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>ONIXモビリティタウン千葉（オニキス・フラット7千葉16号／八千代千葉）、オニキス・フラット7松戸、オニキス・フラット7成田、オニキス・フラット7市原、北海道2店舗（店名未確認）、東京1店舗（店名未確認）、埼玉1店舗（店名未確認）、熊本3店舗（店名未確認）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>東京都品川区東五反田2-3-1 損保ジャパン五反田共同ビル6階</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>03-5475-7140</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>玉野 寛明</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>193名（2025年10月現在）</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>https://job.mynavi.jp/27/pc/search/corp269787/outline.html
+https://unusedcar.onix-ns.com/</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>【要判断】事業内容は「新車販売中心（中古車販売も）」で、中古車は販売台数の約2割。オニキス（新車定額リース・未使用車）の直営。拠点数は就職情報サイトの「北海道2店舗、千葉10店舗、東京1店舗、埼玉1店舗、熊本3店舗」の合計17（整備工場を含む可能性あり）。以前は「オニキス千葉（運営会社未確認）3店舗」として掲載していたものを運営会社で更新。売上92億円（2025年9月期）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>株式会社ナオイオート</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C9" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>牛久店、戸頭店、守谷店、つくば吉瀬店、下館店、下妻店、6号取手店、ひたちなか店、水戸吉田店、土浦中貫店、サンキュッパ下妻店、龍ヶ岡店、坂東店、ラビットイオンタウン水戸南店、ラビットつくば吉瀬、GarageTricolore（ガレージトリコロール）</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>茨城県取手市桑原680-1</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>029-874-2233</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>029-874-2363</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>代表取締役 直井清正</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>https://sale.naoiauto.jp/</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>https://sale.naoiauto.jp/contact/</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/naoiauto/
 https://www.instagram.com/naoiauto_car/
 https://www.youtube.com/channel/UCqkEz6s5HrxxnCPQPsME1FA</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>354名</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>https://sale.naoiauto.jp/company/
 https://sale.naoiauto.jp/store/</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>軽未使用車・39.8万円車専門店。公式の店舗一覧16件で、ラビット（買取FC）2店舗とGarageTricolore（業態未確認）を含む。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>株式会社フジカーズジャパン</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>北海道、宮城県、茨城県、埼玉県、千葉県、神奈川県、新潟県、石川県、岐阜県、静岡県、兵庫県、広島県、香川県、佐賀県</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>札幌店、仙台店、新潟店、茨城店、つくば店、柏店、狭山店、寄居店、厚木店、石川店、浜松店、岐阜店、神戸西宮店、広島店、高松店、鳥栖店</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>東京都江戸川区西小岩2丁目11番6号</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0120-007-560</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.campnofuji.jp/</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>車両全般の買取事業・買取専門店「カープライスセンター」あり</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>220名</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.campnofuji.jp/company/
-https://www.campnofuji.jp/shop/</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>ブランドは「キャンピングカーのフジ」。キャンピングカーの新車・中古車の販売と買取が中心で、一般の中古車販売店とは業態がやや異なる（対象に含めるか要判断）。店舗数はキャンピングカー販売店16店舗で、買取専門店カープライスセンターは含めていない。店舗名はURLから付けた。電話はフリーダイヤル。</t>
         </is>
       </c>
     </row>
@@ -1117,50 +1113,66 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>株式会社アビックスコーポレーション</t>
+          <t>株式会社フジカーズジャパン</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>宮城県、千葉県、東京都、神奈川県、愛知県</t>
+          <t>北海道、宮城県、茨城県、埼玉県、千葉県、神奈川県、新潟県、石川県、岐阜県、静岡県、兵庫県、広島県、香川県、佐賀県</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>AVIX IMPORT 府中店、AVIX IMPORT 多摩センター店、AVIX IMPORT 川崎生田店、AVIX IMPORT 木更津金田インター店、ほか関東9店舗、仙台東インター店、名古屋北店</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>札幌店、仙台店、新潟店、茨城店、つくば店、柏店、狭山店、寄居店、厚木店、石川店、浜松店、岐阜店、神戸西宮店、広島店、高松店、鳥栖店</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>東京都江戸川区西小岩2丁目11番6号</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0120-007-560</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.avix.co.jp/</t>
+          <t>https://www.campnofuji.jp/</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>車両全般の買取事業・買取専門店「カープライスセンター」あり</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>220名</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/9510200（検索結果の抜粋）
-https://www.goo-net.com/user_review/0500520/（検索結果の抜粋）</t>
+          <t>https://www.campnofuji.jp/company/
+https://www.campnofuji.jp/shop/</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店AVIX IMPORT。店舗紹介文の「関東地区13店舗＆関西地区3店舗＆仙台東インター＆名古屋北店」から、関西3店舗（アビックス大阪株式会社の運営）を除いて15店舗とした。仙台・名古屋の運営会社は未確認。公式サイトは接続できず。</t>
+          <t>ブランドは「キャンピングカーのフジ」。キャンピングカーの新車・中古車の販売と買取が中心で、一般の中古車販売店とは業態がやや異なる（対象に含めるか要判断）。店舗数はキャンピングカー販売店16店舗で、買取専門店カープライスセンターは含めていない。店舗名はURLから付けた。電話はフリーダイヤル。</t>
         </is>
       </c>
     </row>
@@ -1170,150 +1182,130 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>株式会社アビックスコーポレーション</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、千葉県、東京都、神奈川県、愛知県</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>AVIX IMPORT 府中店、AVIX IMPORT 多摩センター店、AVIX IMPORT 川崎生田店、AVIX IMPORT 木更津金田インター店、ほか関東9店舗、仙台東インター店、名古屋北店</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avix.co.jp/</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>https://car.motor-fan.jp/ucar/shop/9510200（検索結果の抜粋）
+https://www.goo-net.com/user_review/0500520/（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>輸入車専門店AVIX IMPORT。店舗紹介文の「関東地区13店舗＆関西地区3店舗＆仙台東インター＆名古屋北店」から、関西3店舗（アビックス大阪株式会社の運営）を除いて15店舗とした。仙台・名古屋の運営会社は未確認。公式サイトは接続できず。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>株式会社KSファクトリー</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C12" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>宮城県、茨城県、栃木県、群馬県、千葉県、愛知県、福岡県</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>仙台店、ランクル宇都宮店、アップル宇都宮外環若草店、前橋インター店、アップル前橋店、アップルつくば学園店、つくば店、アップル土浦学園東大通り店、千葉北店、ハイエース名古屋店、ハイエース福岡店、アップル福岡南バイパス店、福岡須恵インター店、アップル福岡久留米店</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>千葉県佐倉市ユーカリが丘7-21-3</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>043-376-9195</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>代表取締役社長 遠藤和広</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>https://ksfactory.jp/</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>https://ksfactory.jp/contact/</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/ksfactory_carshop/
 https://www.youtube.com/@KS_factory
 https://www.tiktok.com/@ksfactory4wd</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>77名</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>https://ksfactory.jp/company/
 https://ksfactory.jp/shop/head-office/
 https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>ランクル・ハイエース専門店とアップル加盟店を運営。公式サイトの店舗一覧13件に、アップル本部サイトでKSファクトリー運営と表示される「アップル福岡久留米店」（公式サイトの一覧には無し）を加えて14店舗。本社ページの電話番号欄は空欄。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>株式会社オートベル</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>静岡県</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>なでしこ店、三島店、富士宮バイパス店、富士旧国一店、御殿場店、掛川店、沼津ぐるめ街道店、浜松入野店、浜松和田店、浜松西ヶ崎店、清水インター店、藤枝店、静岡流通通り店、静岡見瀬店</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>静岡県沼津市岡宮1266-87</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>055-922-6007</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 牧野太一郎</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>https://autobell.co.jp/</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>車の買取（主業）</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>130名（2025年1月）</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>https://autobell.co.jp/company/about/index.html
-https://autobell.co.jp/</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>車買取・販売（新車・中古車）。サイトの表記は「静岡県内13店舗」、店舗リンクは14件（なでしこ店を含む）。千葉のオートベル・ジャパンとは別会社の可能性（未確認）。</t>
         </is>
       </c>
     </row>
@@ -1323,33 +1315,106 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>株式会社アタックス</t>
+          <t>株式会社オートベル</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県、三重県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>アップル津島中央道店、アップル厚木・北129号店、アップル富田302号店、アップル小田原飯泉店、アップル昭和橋通店、アップル桑名七和店、アップル中村畑江通店、アップル稲沢店、アップル西・康生通店、アップル南23号店、アップル桑名大桑店、アップル黒川北41号店</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+          <t>なでしこ店、三島店、富士宮バイパス店、富士旧国一店、御殿場店、掛川店、沼津ぐるめ街道店、浜松入野店、浜松和田店、浜松西ヶ崎店、清水インター店、藤枝店、静岡流通通り店、静岡見瀬店</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>静岡県沼津市岡宮1266-87</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>055-922-6007</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 牧野太一郎</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>https://autobell.co.jp/</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>車の買取（主業）</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>130名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>https://autobell.co.jp/company/about/index.html
+https://autobell.co.jp/</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>車買取・販売（新車・中古車）。サイトの表記は「静岡県内13店舗」、店舗リンクは14件（なでしこ店を含む）。千葉のオートベル・ジャパンとは別会社の可能性（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>株式会社アタックス</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県、愛知県、三重県</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>アップル津島中央道店、アップル厚木・北129号店、アップル富田302号店、アップル小田原飯泉店、アップル昭和橋通店、アップル桑名七和店、アップル中村畑江通店、アップル稲沢店、アップル西・康生通店、アップル南23号店、アップル桑名大桑店、アップル黒川北41号店</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0008/
@@ -1357,83 +1422,14 @@
 https://www.applenet.co.jp/shop/0022/</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>株式会社コヤマ・ミライエ</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>静岡県</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>KOYAMA 富士宮店、KOYAMA 富士平垣店、KOYAMA 富士店、KOYAMA 新富士店、KOYAMA 御前崎店、KOYAMA 柿田川店、KOYAMA 浜松東店、KOYAMA 浜松西店、KOYAMA 藤枝店、KOYAMA 袋井上山梨店、KOYAMA 静岡中原店、KOYAMA 静岡池田店</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>静岡県富士市伝法878-15</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 小山武</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.koyama-miraie.co.jp/</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取業務（主業）</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>48名</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.koyama-miraie.co.jp/company/
-https://www.koyama-miraie.co.jp/shop/</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>車買取専門店KOYAMA。店舗数は公式サイトの店舗一覧12件。LINE公式アカウントあり。</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1439,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>株式会社ジェイ・ピー</t>
+          <t>株式会社コヤマ・ミライエ</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1451,25 +1447,94 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>宮城県、福島県、栃木県、群馬県、埼玉県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>アップル坂戸鶴ヶ島インター店、アップル太田店、アップル川越16号店、アップル郡山インター店、アップル深谷17号店、アップル西那須野店、アップル朝霞店、アップル仙台六丁目店、アップル東松山店、アップル白河店、アップル所沢店、アップル鴻巣店</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>KOYAMA 富士宮店、KOYAMA 富士平垣店、KOYAMA 富士店、KOYAMA 新富士店、KOYAMA 御前崎店、KOYAMA 柿田川店、KOYAMA 浜松東店、KOYAMA 浜松西店、KOYAMA 藤枝店、KOYAMA 袋井上山梨店、KOYAMA 静岡中原店、KOYAMA 静岡池田店</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>静岡県富士市伝法878-15</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 小山武</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koyama-miraie.co.jp/</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取業務（主業）</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>48名</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.koyama-miraie.co.jp/company/
+https://www.koyama-miraie.co.jp/shop/</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>車買取専門店KOYAMA。店舗数は公式サイトの店舗一覧12件。LINE公式アカウントあり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ジェイ・ピー</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、福島県、栃木県、群馬県、埼玉県</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>アップル坂戸鶴ヶ島インター店、アップル太田店、アップル川越16号店、アップル郡山インター店、アップル深谷17号店、アップル西那須野店、アップル朝霞店、アップル仙台六丁目店、アップル東松山店、アップル白河店、アップル所沢店、アップル鴻巣店</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0015/
@@ -1477,95 +1542,14 @@
 https://www.applenet.co.jp/shop/0044/</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル坂戸鶴ヶ島インター店）〒350-2211 埼玉県鶴ヶ島市脚折町5-4-13 TEL 049-279-3500 FAX 049-279-3501。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>株式会社リバーサイド</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>本社ショールーム（海老名）、RS BASE湘南、RS ANEX湘南、湘南店、フルタイム店（SUV・ワゴン専門）、RSユーロカーズ（レクサス・輸入車）、エルザ藤沢ショールーム、RS藤沢バイパス店、エルザ246号店、エルザ横浜店、エルザ町田ショールーム／ANEX町田店</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県海老名市門沢橋6-9-29</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>046-233-8000</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>046-237-3223</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>田島 明</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rs-riverside.com/</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rs-riverside.com/contact/</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>rs101@rs-riverside.com</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>106名（2023年4月現在）</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rs-riverside.com/shop/
-https://job.mynavi.jp/27/pc/search/corp81423/outline.html</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>会社の説明は「神奈川県下12店舗、総在庫850台」。事業所一覧で確認できた販売拠点は11（ほかに車検工場・鈑金・カーコンビニ倶楽部加盟2店舗）。売上76億円（2023年11月期）。公式サイトの会社概要ページは503で取得できず、本社電話・代表者・従業員数は就職情報サイトの会社概要から。FAXは店舗ページ記載。</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1559,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>高橋自動車販売株式会社</t>
+          <t>株式会社リバーサイド</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1583,25 +1567,106 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>東京都、神奈川県、愛知県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>アップル江田駅前店、アップル江戸川環七店、アップル豊橋佐藤店、アップル248岡崎店、アップル平塚田村店、アップル中山宮の下店、アップル町田南店、アップル岡崎六ッ美店、アップル東戸塚店、アップル蒲郡店、アップル豊川インター店、アップル岡崎緑丘店</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>本社ショールーム（海老名）、RS BASE湘南、RS ANEX湘南、湘南店、フルタイム店（SUV・ワゴン専門）、RSユーロカーズ（レクサス・輸入車）、エルザ藤沢ショールーム、RS藤沢バイパス店、エルザ246号店、エルザ横浜店、エルザ町田ショールーム／ANEX町田店</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県海老名市門沢橋6-9-29</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>046-233-8000</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>046-237-3223</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>田島 明</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rs-riverside.com/</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rs-riverside.com/contact/</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>rs101@rs-riverside.com</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>106名（2023年4月現在）</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rs-riverside.com/shop/
+https://job.mynavi.jp/27/pc/search/corp81423/outline.html</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>会社の説明は「神奈川県下12店舗、総在庫850台」。事業所一覧で確認できた販売拠点は11（ほかに車検工場・鈑金・カーコンビニ倶楽部加盟2店舗）。売上76億円（2023年11月期）。公式サイトの会社概要ページは503で取得できず、本社電話・代表者・従業員数は就職情報サイトの会社概要から。FAXは店舗ページ記載。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>高橋自動車販売株式会社</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>東京都、神奈川県、愛知県</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>アップル江田駅前店、アップル江戸川環七店、アップル豊橋佐藤店、アップル248岡崎店、アップル平塚田村店、アップル中山宮の下店、アップル町田南店、アップル岡崎六ッ美店、アップル東戸塚店、アップル蒲郡店、アップル豊川インター店、アップル岡崎緑丘店</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0013/
@@ -1609,71 +1674,71 @@
 https://www.applenet.co.jp/shop/0024/</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。軽四専門「メガタウン」（豊田市）も運営しており、実際の店舗数はこれより多い可能性。 参考：店舗の連絡先（アップル江田駅前店）〒225-0013 神奈川県横浜市青葉区荏田町1236-7東急江田駅前ドエリング1F TEL 045-912-7560 FAX 045-912-7566。</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>株式会社メーカーズ</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C19" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>福岡県、佐賀県</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>ケイカフェ おおのじょう店、ケイカフェ しんぐう店、ケイカフェ こくらみなみ店、ケイカフェ くるめ店、ケイカフェ ちくしの店、ケイカフェ いいづか店、ケイカフェ やはた店、ケイカフェ ふくおかにし店、ケイカフェ とす店、アップル福岡東店、アップル福岡八幡店</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>福岡県福岡市西区石丸4丁目5-53</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>092-753-6611</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>092-753-6622</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>代表取締役社長 白井剛</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>https://www.k-cafe.com/</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>https://www.k-cafe.com/contact/</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/kcafe_official
 https://www.facebook.com/kcarandcafe
@@ -1682,108 +1747,23 @@
 https://www.youtube.com/@kcafe_fukuoka/videos</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>https://www.k-cafe.com/company/
 https://www.k-cafe.com/
 https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ケイカフェ9店舗（公式サイトの店舗情報）と、アップル加盟店2店舗（本部サイトで運営会社を確認）の合計。ONIXフランチャイズにも加盟（沿革）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>株式会社軽自動車館</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>北海道、宮城県</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>札幌本店、札幌東店、新さっぽろ店、札幌清田店、北見店、旭川店、函館店、苫小牧店、帯広店、釧路店、せんだい店</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>北海道札幌市中央区北5条西6丁目2-2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>011-200-0312</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>011-200-0357</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 阿部章一</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>https://keijidousyakan.com/</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>https://keijidousyakan.com/contact/（現在お問い合わせ見合わせ中の表示あり）</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCtYVtXtEHCIxOCia6QF0nBw</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>自動車の買取（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>117名（2026年1月）</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>https://keijidousyakan.com/about/company/
-https://keijidousyakan.com/shops/</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>店舗名は公式の店舗ページから。札幌本店と札幌東店はURL（sapporo / satsuhigashi）から推定した店舗名。</t>
         </is>
       </c>
     </row>
@@ -1793,213 +1773,222 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>日免オートシステム株式会社</t>
+          <t>株式会社軽自動車館</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>北海道、宮城県</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>美使用軽専門店 江別店、美使用軽専門店 静内店（新ひだか）、美使用軽専門店 小樽店、美使用軽専門店 旭川店、美使用軽専門店 十勝音更店、美使用軽専門店 イオンスーパーセンター三笠店、美使用軽専門店 スーパーアークス新琴似店、カーセブン札幌北店、カーセブン北見店、カーセブン十勝音更店</t>
+          <t>札幌本店、札幌東店、新さっぽろ店、札幌清田店、北見店、旭川店、函館店、苫小牧店、帯広店、釧路店、せんだい店</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>北海道札幌市北区東茨戸1条1丁目8番5号</t>
+          <t>北海道札幌市中央区北5条西6丁目2-2</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>011-774-3111</t>
+          <t>011-200-0312</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>011-775-8906</t>
+          <t>011-200-0357</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>代表取締役社長 安部直人</t>
+          <t>代表取締役社長 阿部章一</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.nichimen-g.co.jp/</t>
+          <t>https://keijidousyakan.com/</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://www.nichimen-g.co.jp/company/contact/</t>
+          <t>https://keijidousyakan.com/contact/（現在お問い合わせ見合わせ中の表示あり）</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/channel/UCtYVtXtEHCIxOCia6QF0nBw</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>自動車の買取（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>117名（2026年1月）</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>https://keijidousyakan.com/about/company/
+https://keijidousyakan.com/shops/</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>店舗名は公式の店舗ページから。札幌本店と札幌東店はURL（sapporo / satsuhigashi）から推定した店舗名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>三共自動車販売株式会社（サンキョウ）</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、千葉県</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>本社ミニバン館（市川）、ミニバン専門店 仙台東インター夢創庫、仙台六丁の目店</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>千葉県市川市相之川2-7-18（本社ミニバン館の所在地）</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>https://compalyze.co.jp/company/6040001026340
+https://car.motor-fan.jp/ucar/shop/0900491</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト未確認。企業情報サイトに「直営10店舗を千葉・宮城・群馬・福島に展開」。確認できた店舗名は3つのみ（群馬・福島の店舗名は不明）。新車販売も扱う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>日免オートシステム株式会社</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>美使用軽専門店 江別店、美使用軽専門店 静内店（新ひだか）、美使用軽専門店 小樽店、美使用軽専門店 旭川店、美使用軽専門店 十勝音更店、美使用軽専門店 イオンスーパーセンター三笠店、美使用軽専門店 スーパーアークス新琴似店、カーセブン札幌北店、カーセブン北見店、カーセブン十勝音更店</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>北海道札幌市北区東茨戸1条1丁目8番5号</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>011-774-3111</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>011-775-8906</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 安部直人</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nichimen-g.co.jp/</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nichimen-g.co.jp/company/contact/</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/nichimen_mishiyou/
 https://www.youtube.com/channel/UC-iuDCLbQ6px8P3WISQrLdg</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>ニチメン買取（買取・査定）あり</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>210名（グループ全体・パート含む）</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>https://www.nichimen-g.co.jp/company/
 https://www.nichimen-g.co.jp/company/stores/
 https://www.nichimen-g.co.jp/mishiyou/</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>ニチメングループ。会社概要の「総店舗数31店舗（北海道内グループ全体）」には、スズキ販売店・レンタカー・整備工場・板金・建機なども含まれる。中古車の販売・買取の店舗として、美使用軽専門店7店舗とカーセブン加盟店3店舗を数えた。新琴似本店・札幌本店の位置づけは未確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ジョブカーズ</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>大阪府</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>ジョブカーズ本店、南港店、枚方東店、枚方南店、枚方北店、枚方インポート店、八尾店、守口店、COOL店、バイパス店</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市茄子作2-33-25</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>072-852-8500</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>072-852-8501</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>吉村浩二</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/contact/</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>70名</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>https://jobcars.net/company/</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>同じ名前の別会社に注意：jobcars.jp は札幌の「ジョブカーズ株式会社」で別会社。枚方の会社の公式サイトは jobcars.net。枚方北店は大型トラック・バス、COOL店とバイパス店は会社概要に住所の記載がない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>株式会社フレックス・ドリーム</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>宮城県、群馬県、埼玉県、東京都、神奈川県、愛知県</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>ランクル調布店、ランクルさいたま北店、ランクル小牧店、ランクル湘南厚木店、ランクル仙台東店、ハイエース小牧店、ハイエース湘南厚木店、ハイエース高崎店、ハイエース仙台東店、ハイエース三郷店</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flexdream.jp/</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flexdream.jp/（503で取得不可。検索結果に表示された店舗一覧の抜粋）
-https://compalyze.co.jp/company/2012401009864（検索結果の抜粋）</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>ランクル・ハイエース・USトヨタ専門店。店舗名は検索結果に表示された公式サイトの店舗一覧の抜粋による（10店舗、これ以上ある可能性）。公式サイトは503で確認できず。フレックス株式会社（FLEX、31店舗以上で除外）とは別会社。同じ敷地のランクル店・ハイエース店を別々に数えている。</t>
         </is>
       </c>
     </row>
@@ -2009,7 +1998,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>株式会社川内自動車</t>
+          <t>株式会社ジョブカーズ</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2017,46 +2006,65 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>ジョブカーズ本店、南港店、枚方東店、枚方南店、枚方北店、枚方インポート店、八尾店、守口店、COOL店、バイパス店</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市茄子作2-33-25</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>072-852-8500</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>072-852-8501</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>吉村浩二</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://k-bacca.com/</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
+          <t>https://jobcars.net/</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://jobcars.net/contact/</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/k_bacca_kawauchi/</t>
-        </is>
-      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>70名</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>https://k-bacca.com/contents/store/index.html
-https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
+          <t>https://jobcars.net/company/</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
+          <t>同じ名前の別会社に注意：jobcars.jp は札幌の「ジョブカーズ株式会社」で別会社。枚方の会社の公式サイトは jobcars.net。枚方北店は大型トラック・バス、COOL店とバイパス店は会社概要に住所の記載がない。</t>
         </is>
       </c>
     </row>
@@ -2066,27 +2074,31 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ティーバイティーガレージ（TxTGARAGE、運営会社未確認）</t>
+          <t>株式会社フレックス・ドリーム</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>宮城県、群馬県、埼玉県、東京都、神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>北海道内8店舗、奥州店</t>
+          <t>ランクル調布店、ランクルさいたま北店、ランクル小牧店、ランクル湘南厚木店、ランクル仙台東店、ハイエース小牧店、ハイエース湘南厚木店、ハイエース高崎店、ハイエース仙台東店、ハイエース三郷店</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flexdream.jp/</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
@@ -2094,7 +2106,8 @@
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事・求人）</t>
+          <t>https://www.flexdream.jp/（503で取得不可。検索結果に表示された店舗一覧の抜粋）
+https://compalyze.co.jp/company/2012401009864（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2104,7 +2117,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>比較記事の「道内8店舗」と、岩手県奥州市の店舗の求人による（奥州店は岩手県）。公式の店舗一覧・運営会社は未確認。</t>
+          <t>ランクル・ハイエース・USトヨタ専門店。店舗名は検索結果に表示された公式サイトの店舗一覧の抜粋による（10店舗、これ以上ある可能性）。公式サイトは503で確認できず。フレックス株式会社（FLEX、31店舗以上で除外）とは別会社。同じ敷地のランクル店・ハイエース店を別々に数えている。</t>
         </is>
       </c>
     </row>
@@ -2114,44 +2127,44 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>株式会社サークルエム</t>
+          <t>株式会社川内自動車</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県、東京都、神奈川県、愛知県、福岡県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>カートルズ越谷店、カートルズ鶴ヶ島店、カートルズ草加店、カートルズ青梅インター店、カートルズ相模原店、カートルズ千葉店、カートルズ岡崎店、カートルズ名古屋店、カートルズ北九州店</t>
+          <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>048-970-2444</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://1190.jp/</t>
+          <t>https://k-bacca.com/</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/k_bacca_kawauchi/</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>https://1190.jp/shop/
-求人情報（検索結果の抜粋：カートルズ草加店【株式会社サークルエム】）</t>
+          <t>https://k-bacca.com/contents/store/index.html
+https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2161,7 +2174,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店「カートルズ」。公式サイトの店舗一覧で販売店9店舗（ほかに整備工場とBlackbunny）。求人では「直営13店舗」とも。運営会社名は草加店の求人表記によるもので、全店が同じ法人かは未確認。</t>
+          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2184,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>株式会社シースペース</t>
+          <t>human joint株式会社</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2179,61 +2192,59 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>京都府、大阪府、兵庫県</t>
+          <t>北海道、岩手県、宮城県、福島県、埼玉県、千葉県、長野県、静岡県、愛知県</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
+          <t>COCOCAR 酒々井店、COCOCAR 加須店、COCOCAR 仙台店、COCOCAR 福島納車センター、COCOCAR 盛岡店、COCOCAR 長野営業所、COCOCAR 名古屋店、COCOCAR 静岡営業所、COCOCAR 札幌営業所</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>大阪府柏原市国分市場2丁目13番1号</t>
+          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>072-978-1263</t>
+          <t>03-4446-7735</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>072-978-1283</t>
+          <t>03-5422-8006</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>代表取締役社長 平松宗彦</t>
+          <t>代表取締役 齊藤博行</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.c-space.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://cococar-hp.net/</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://twitter.com/C_SPACE_U_POHS</t>
+          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>ユーポス事業（車買取）</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
+          <t>中古自動車の販売および買取（事業内容）</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>32名</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/company/
-https://www.c-space.co.jp/shop/
-https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://cococar-hp.net/company/</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2243,7 +2254,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>会社概要に「ユーポス（関西にて現在8店舗）」とある。ユーポス本部のサイトでシースペース運営と表示されるのは7店舗で、久御山店は表示されていない。本社のC-SPACE.（中古車販売）を1店舗として数え、合計9店舗。ほかにニコニコレンタカー5店舗とコバック1店舗（いずれも対象外）を運営。X(Twitter)のURLは検索結果から取得。</t>
+          <t>ブランドはCOCOCAR（自社ローン専門）。会社概要の沿革で第1〜9号店（酒々井・加須・仙台・福島・盛岡・長野・名古屋・静岡・札幌）を確認し、営業所・納車センターを含めて9拠点で計上（2026-10再確認、以前は「店」のみの5で計上）。FC店（ORCAR横浜本店、COCOCAR札幌店）は含めていない。</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2264,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社ジーアフター</t>
+          <t>ティーバイティーガレージ（TxTGARAGE、運営会社未確認）</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2261,58 +2272,37 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>宮城県、栃木県、埼玉県、千葉県、新潟県、岡山県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>MEGA仙台新港店、MEGA佐野厄除大師店、MEGA越谷レイクタウン店、MEGA千葉北インター店、G-BORDER千葉北インター店、成田店、木更津店、MEGA新潟店、MEGA東岡山店</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>東京都中央区日本橋2-12-6 高島屋THビル北館4階</t>
-        </is>
-      </c>
+          <t>北海道内8店舗、奥州店</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 西川佳吾</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.g-after.co.jp/</t>
-        </is>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>車買取専門店（主業）</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>210名（2023年6月期実績）</t>
-        </is>
-      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>https://www.g-after.co.jp/company
-https://www.g-after.co.jp/shop/</t>
+          <t>検索結果の抜粋（比較記事・求人）</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>車買取専門店ジーアフター（MEGA店など）。店舗数は公式サイトの店舗一覧9件。都道府県は店舗名から判断。</t>
+          <t>比較記事の「道内8店舗」と、岩手県奥州市の店舗の求人による（奥州店は岩手県）。公式の店舗一覧・運営会社は未確認。</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2312,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>株式会社リトラス</t>
+          <t>株式会社サークルエム</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2330,29 +2320,29 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
+          <t>埼玉県、千葉県、東京都、神奈川県、愛知県、福岡県</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 津田猛</t>
-        </is>
-      </c>
+          <t>カートルズ越谷店、カートルズ鶴ヶ島店、カートルズ草加店、カートルズ青梅インター店、カートルズ相模原店、カートルズ千葉店、カートルズ岡崎店、カートルズ名古屋店、カートルズ北九州店</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>048-970-2444</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>048-970-2455</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.retrus.co.jp/</t>
+          <t>https://1190.jp/</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -2362,8 +2352,8 @@
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://www.retrus.co.jp/about/office.asp
-https://www.retrus.co.jp/about/</t>
+          <t>https://1190.jp/shop/
+求人情報（検索結果の抜粋：カートルズ草加店【株式会社サークルエム】）</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -2373,7 +2363,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
+          <t>自社ローン専門店「カートルズ」。公式サイトの店舗一覧で販売店9店舗（ほかに整備工場とBlackbunny）。求人では「直営13店舗」とも。運営会社名は草加店の求人表記によるもので、全店が同じ法人かは未確認。</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2373,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>株式会社九州ユーポス</t>
+          <t>株式会社シースペース</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2391,30 +2381,61 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
+          <t>京都府、大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
+          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>大阪府柏原市国分市場2丁目13番1号</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1263</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1283</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 平松宗彦</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/contact/</t>
+        </is>
+      </c>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/C_SPACE_U_POHS</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス事業（車買取）</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/hikarinomori/
-https://www.u-pohs.co.jp/kagoshima
-https://www.u-pohs.co.jp/kumamotominami</t>
+          <t>https://www.c-space.co.jp/company/
+https://www.c-space.co.jp/shop/
+https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -2424,7 +2445,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
+          <t>会社概要に「ユーポス（関西にて現在8店舗）」とある。ユーポス本部のサイトでシースペース運営と表示されるのは7店舗で、久御山店は表示されていない。本社のC-SPACE.（中古車販売）を1店舗として数え、合計9店舗。ほかにニコニコレンタカー5店舗とコバック1店舗（いずれも対象外）を運営。X(Twitter)のURLは検索結果から取得。</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2455,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>株式会社原ホンダ</t>
+          <t>株式会社ジーアフター</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2442,30 +2463,48 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>宮城県、栃木県、埼玉県、千葉県、新潟県、岡山県</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>MEGA仙台新港店、MEGA佐野厄除大師店、MEGA越谷レイクタウン店、MEGA千葉北インター店、G-BORDER千葉北インター店、成田店、木更津店、MEGA新潟店、MEGA東岡山店</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>東京都中央区日本橋2-12-6 高島屋THビル北館4階</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 西川佳吾</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.g-after.co.jp/</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>車買取専門店（主業）</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>210名（2023年6月期実績）</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0031/
-https://www.applenet.co.jp/shop/0033/
-https://www.applenet.co.jp/shop/0042/</t>
+          <t>https://www.g-after.co.jp/company
+https://www.g-after.co.jp/shop/</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -2475,7 +2514,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
+          <t>車買取専門店ジーアフター（MEGA店など）。店舗数は公式サイトの店舗一覧9件。都道府県は店舗名から判断。</t>
         </is>
       </c>
     </row>
@@ -2485,70 +2524,58 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>株式会社TRUCK-ONE</t>
+          <t>株式会社リトラス</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
+          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
+          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>山口県下松市生野屋南3-3-40</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-1100</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-5660</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 津田猛</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-one.com/</t>
+          <t>https://www.retrus.co.jp/</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/truckone_official/</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>買取専用窓口あり（0120-751-519）</t>
-        </is>
-      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-one.com/officelist/
-https://www.truck-one.com/company/</t>
+          <t>https://www.retrus.co.jp/about/office.asp
+https://www.retrus.co.jp/about/</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
+          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
         </is>
       </c>
     </row>
@@ -2558,20 +2585,20 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>株式会社ジャンプジャパン</t>
+          <t>株式会社九州ユーポス</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
+          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
@@ -2586,18 +2613,20 @@
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（日立市・東海村・那珂市・水戸市・つくば市・牛久市・守谷市・龍ヶ崎市に店舗を構えるとの案内）
-https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-</t>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/hikarinomori/
+https://www.u-pohs.co.jp/kagoshima
+https://www.u-pohs.co.jp/kumamotominami</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
         </is>
       </c>
     </row>
@@ -2607,39 +2636,27 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>株式会社ハヤシ</t>
+          <t>株式会社原ホンダ</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>岡山県倉敷市加須山334-4</t>
-        </is>
-      </c>
+          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>http://www.c-hayashi.com/</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
@@ -2647,18 +2664,20 @@
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
-https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0031/
+https://www.applenet.co.jp/shop/0033/
+https://www.applenet.co.jp/shop/0042/</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2687,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>株式会社パッション</t>
+          <t>株式会社TRUCK-ONE</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2676,44 +2695,52 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、愛知県</t>
+          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>愛知県春日井市味美町2丁目122番地</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
+          <t>山口県下松市生野屋南3-3-40</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-1100</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-5660</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+          <t>https://www.truck-one.com/</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/truckone_official/</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>買取専門店ラビット勝川店を運営</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>217名（2025年12月）</t>
-        </is>
-      </c>
+          <t>買取専用窓口あり（0120-751-519）</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/company/outline/
-https://www.1963passion.co.jp/company/access/</t>
+          <t>https://www.truck-one.com/officelist/
+https://www.truck-one.com/company/</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -2723,7 +2750,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
+          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2760,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>株式会社東和モータース販売</t>
+          <t>株式会社ジャンプジャパン</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2741,70 +2768,38 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>東京都杉並区上高井戸1-21-18</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>03-3303-1146</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>03-3302-6600</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 稲葉弘幸</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>https://towa-motors.com/</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>https://towa-motors.com/contact.html</t>
-        </is>
-      </c>
+          <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/towa.motors</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/company.html
-https://towa-motors.com/shop/</t>
+          <t>検索結果の抜粋（日立市・東海村・那珂市・水戸市・つくば市・牛久市・守谷市・龍ヶ崎市に店舗を構えるとの案内）
+https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
+          <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -2814,31 +2809,39 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ツチヤ自動車株式会社</t>
+          <t>株式会社ハヤシ</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>千葉県市川市北方町4-1441-8</t>
+          <t>岡山県倉敷市加須山334-4</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>http://www.c-hayashi.com/</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
@@ -2846,8 +2849,8 @@
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
-https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
+          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
+https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -2857,7 +2860,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
+          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -2867,38 +2870,52 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>株式会社パッション</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>岐阜県、愛知県</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
+          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>愛知県春日井市味美町2丁目122番地</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>買取専門店ラビット勝川店を運営</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>217名（2025年12月）</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0004/
-https://www.applenet.co.jp/shop/0007/
-https://www.applenet.co.jp/shop/0046/</t>
+          <t>https://www.1963passion.co.jp/company/outline/
+https://www.1963passion.co.jp/company/access/</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -2908,7 +2925,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
+          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -2918,74 +2935,78 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヨシダオートサービス</t>
+          <t>株式会社東和モータース販売</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+          <t>東京都杉並区上高井戸1-21-18</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>072-246-0301</t>
+          <t>03-3303-1146</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>072-246-0302</t>
+          <t>03-3302-6600</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>吉田宜史</t>
+          <t>代表取締役社長 稲葉弘幸</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+          <t>https://towa-motors.com/</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/contact/</t>
+          <t>https://towa-motors.com/contact.html</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/towa.motors</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>218名（2025年1月）</t>
+          <t>50名</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
+          <t>https://towa-motors.com/company.html
+https://towa-motors.com/shop/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
+          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
         </is>
       </c>
     </row>
@@ -2995,25 +3016,25 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>ツチヤ自動車株式会社</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
+          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
+          <t>千葉県市川市北方町4-1441-8</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -3027,8 +3048,8 @@
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
+https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -3038,7 +3059,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
         </is>
       </c>
     </row>
@@ -3048,20 +3069,20 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>株式会社アップルカーセールス</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -3077,9 +3098,9 @@
       <c r="P40" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/</t>
+https://www.applenet.co.jp/shop/0004/
+https://www.applenet.co.jp/shop/0007/
+https://www.applenet.co.jp/shop/0046/</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -3089,7 +3110,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
         </is>
       </c>
     </row>
@@ -3099,35 +3120,64 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>松下モータース</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -3137,7 +3187,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3197,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>株式会社AOZORA COMPANY</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3155,17 +3205,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>東京都、新潟県、大阪府、福岡県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
+          <t>浜松市内6店舗</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>新潟県新潟市西区黒鳥5243番地1</t>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -3179,8 +3229,8 @@
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
-厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -3190,7 +3240,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3250,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3208,47 +3258,30 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -3258,7 +3291,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3301,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>松下モータース</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3276,12 +3309,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3296,20 +3329,17 @@
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3349,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社AOZORA COMPANY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3327,23 +3357,23 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都、新潟県、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>新潟県新潟市西区黒鳥5243番地1</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tortoise-k-carlife.com/</t>
-        </is>
-      </c>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
@@ -3351,8 +3381,8 @@
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
-https://www.applenet.co.jp/shop/</t>
+          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
+厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -3362,7 +3392,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。</t>
+          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3402,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>株式会社ナック（ジャック査定センター）</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3380,48 +3410,47 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>京都府、大阪府、兵庫県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
-        </is>
-      </c>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>078-685-0066</t>
-        </is>
-      </c>
+      <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 難波克年</t>
+          <t>代表取締役 石戸宏樹</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://jacnet.jp/</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>中古車の査定買取（主業）</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr"/>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>26名</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>https://jacnet.jp/site/company/?pt=detail
-https://jacnet.jp/site/company/?pt=shop_list</t>
+          <t>https://www.apple-car.jp/company</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -3431,7 +3460,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3470,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3449,12 +3478,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -3469,17 +3498,20 @@
       <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3521,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>株式会社メディアトラスト（クルオク）</t>
+          <t>株式会社コバックインターナショナル（コバックカーズ）</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3497,75 +3529,39 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>岐阜県、愛知県、三重県</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>クルオク 名古屋インター店（本社）、クルオク レスパ岡崎店、クルオク 豊田吉原店、クルオク カーマ21稲沢店、クルオク カインズホーム半田店、クルオク カインズモール蒲郡店</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>愛知県名古屋市名東区高針台1-110</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>0564-58-9609</t>
-        </is>
-      </c>
+          <t>コバックカーズ岐阜店、コバックカーズ岐南店、コバックカーズ軽アウトレット多治見、コバックカーズ春日井東野店、コバックカーズ春日井坂下店、コバックカーズ四日市インター店</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>鬼頭 宏彰</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.9609.biz/</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.9609.biz/contact/</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>info@kuruma094.com</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>https://twitter.com/kuruma094
-https://www.facebook.com/kuruoku/</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>買取あり（事業内容に「国内の中古車の買取り」）</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>正社員4名・パート2名・役員4名（2025年12月現在）</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>https://www.9609.biz/company/
-https://www.9609.biz/store/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0208435
+https://car.motor-fan.jp/ucar/shop/0203980
+https://car.motor-fan.jp/ucar/shop/0208367</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>6拠点のうち5つはショッピングモール・ホームセンターの屋上や駐車場内の常設展示場。従業員は少人数。</t>
+          <t>公式サイト未確認。中古車情報サイト・求人情報の店舗名から6店舗。店舗紹介に「グループ総在庫1500台」「系列店は愛知・岐阜・三重・静岡」とあり静岡の店舗名は不明。運営会社名は求人情報の「株式会社コバックインターナショナル コバックカーズ岐南店」の表記による（全店が同社運営かは未確認）。車検のコバック（FC本部グループ）との関係も未確認。</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3571,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユー・パーク</t>
+          <t>株式会社トータス</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3583,58 +3579,42 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9566</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9590</t>
-        </is>
-      </c>
+          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/</t>
+          <t>https://www.tortoise-k-carlife.com/</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>買取無料査定あり</t>
-        </is>
-      </c>
+      <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/about-us/
-https://www.u-parknet.com/</t>
+          <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
+https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。</t>
         </is>
       </c>
     </row>
@@ -3644,67 +3624,56 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>human joint株式会社</t>
+          <t>株式会社ナック（ジャック査定センター）</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>岩手県、宮城県、埼玉県、千葉県、愛知県</t>
+          <t>京都府、大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>COCOCAR 盛岡店、COCOCAR 仙台店、COCOCAR 加須店、COCOCAR 酒々井店、COCOCAR 名古屋店</t>
+          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>東京都品川区西五反田2-24-4 THE CROSS GOTANDA 3階</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>03-4446-7735</t>
-        </is>
-      </c>
+          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>03-5422-8006</t>
+          <t>078-685-0066</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 齊藤博行</t>
+          <t>代表取締役 難波克年</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/</t>
+          <t>https://jacnet.jp/</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCCe2kjmg9P0sksXmeF1LiMw</t>
-        </is>
-      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>中古自動車の販売および買取（事業内容）</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>32名</t>
-        </is>
-      </c>
+          <t>中古車の査定買取（主業）</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>https://cococar-hp.net/company/</t>
+          <t>https://jacnet.jp/site/company/?pt=detail
+https://jacnet.jp/site/company/?pt=shop_list</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -3714,7 +3683,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>ブランドはCOCOCAR（自社ローン専門）。「店」は5店舗。ほかに札幌・長野・静岡の営業所と福島納車センターがあり、営業所を含めると8拠点。FC1号店ORCAR横浜本店（加盟店）は含めていない。</t>
+          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
         </is>
       </c>
     </row>
@@ -3724,67 +3693,45 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大久自動車販売株式会社</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ダイキュー飯坂店、ダイキュー郡山店、ダイキュー白河中央インター店、ダイキューいわき店、ダイキュー会津若松店</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>福島県福島市本内字北古舘9</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>024-542-1221</t>
-        </is>
-      </c>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daiq-car.jp/</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daiq-car.jp/contact</t>
-        </is>
-      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>https://twitter.com/DaiQ_motors
-https://www.facebook.com/daiq.motors/
-https://www.instagram.com/daiq_motors.official/</t>
-        </is>
-      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>https://www.daiq-car.jp/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店ダイキュー。運営会社名は公式サイトの古物営業法に基づく表示による。店舗は公式サイトの5店舗。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
         </is>
       </c>
     </row>
@@ -3794,55 +3741,73 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>株式会社CIA</t>
+          <t>株式会社メディアトラスト（クルオク）</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+          <t>クルオク 名古屋インター店（本社）、クルオク レスパ岡崎店、クルオク 豊田吉原店、クルオク カーマ21稲沢店、クルオク カインズホーム半田店、クルオク カインズモール蒲郡店</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
+          <t>愛知県名古屋市名東区高針台1-110</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>0564-58-9609</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 大内康弘</t>
+          <t>鬼頭 宏彰</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>https://www.9609.biz/</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.9609.biz/contact/</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>info@kuruma094.com</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/kuruma094
+https://www.facebook.com/kuruoku/</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー買取（買取センター4か所）</t>
+          <t>買取あり（事業内容に「国内の中古車の買取り」）</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>50名</t>
+          <t>正社員4名・パート2名・役員4名（2025年12月現在）</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/company/</t>
+          <t>https://www.9609.biz/company/
+https://www.9609.biz/store/</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -3852,7 +3817,7 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+          <t>6拠点のうち5つはショッピングモール・ホームセンターの屋上や駐車場内の常設展示場。従業員は少人数。</t>
         </is>
       </c>
     </row>
@@ -3862,70 +3827,56 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>株式会社NIIZAWA</t>
+          <t>株式会社ユー・パーク</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>広島県、山口県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
+          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>広島県廿日市市大野原1丁目2-20</t>
+          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0829-30-8103</t>
+          <t>048-798-9566</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0829-30-8104</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
-        </is>
-      </c>
+          <t>048-798-9590</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.kei-market.co.jp/</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kei-market.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://www.u-parknet.com/</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/keimarket.k
-https://www.facebook.com/share/1AhR49eysR
-https://youtube.com/@keimarket398</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>95名（パート含む）</t>
-        </is>
-      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>買取無料査定あり</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>https://www.kei-market.co.jp/company/
-https://www.kei-market.co.jp/store/</t>
+          <t>https://www.u-parknet.com/about-us/
+https://www.u-parknet.com/</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -3935,7 +3886,7 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
+          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
         </is>
       </c>
     </row>
@@ -3945,43 +3896,53 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>株式会社TSC</t>
+          <t>株式会社ロペライオ</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県、千葉県</t>
+          <t>埼玉県、東京都、愛知県、京都府</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>大久保駅前店、千葉北インター店、蘇我インター店、買取直販 つくば店、北本店</t>
+          <t>ロペライオ練馬、ロペライオさいたま、モーターホーム by ロペライオ、東日本買取センター、中部買取センター、西日本買取センター</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>千葉県千葉市美浜区中瀬（番地は未確認）</t>
+          <t>東京都世田谷区太子堂4-1-1 キャロットタワー6F</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>早水 彰</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>https://loperaio.co.jp/</t>
+        </is>
+      </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>買取直販（買取車両を展示販売）</t>
+          <t>買取センター3拠点（東日本・中部・西日本）</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>https://job.rikunabi.com/job_descriptions/82de25d5815e8620/（検索結果の抜粋。現在は404）</t>
+          <t>https://loperaio.co.jp/shop_index.html
+https://loperaio.co.jp/shop_head_office.html
+https://loperaio.co.jp/company_index.html</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -3991,7 +3952,7 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。求人情報の勤務地一覧から5店舗。本社の美浜区中瀬・蘇我インター店の緑区古市場町が、KiND OUTLETのプライバシーポリシー記載会社（NEXTGATE MOTOR SOLUTIONS、美浜区中瀬）・同千葉コンパクトハイブリッド店（緑区古市場町）と近く、同一グループの可能性あり（未確認）。</t>
+          <t>輸入中古車専門店。ショップガイドの住所と店舗名の対応はページの画像代替テキストから推定（買取センターの所在県は住所一覧からの推定）。ほかに本社・セントラルベース・ファクトリーセンター（非販売拠点）、ボランタリーチェーンのロペシティ西宮（うかいや運営）・札幌平岸（三愛自動車工業運営）。健康経営優良法人（大規模法人部門）取得。</t>
         </is>
       </c>
     </row>
@@ -4001,7 +3962,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>株式会社Y's GARAGE</t>
+          <t>大久自動車販売株式会社</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -4009,47 +3970,49 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>京都府、鳥取県、島根県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
+          <t>ダイキュー飯坂店、ダイキュー郡山店、ダイキュー白河中央インター店、ダイキューいわき店、ダイキュー会津若松店</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>京都府宇治市槇島町三十五38-1</t>
+          <t>福島県福島市本内字北古舘9</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0774-25-5557</t>
+          <t>024-542-1221</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 桐畑勇志</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://k-smile.jp/</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr"/>
+          <t>https://www.daiq-car.jp/</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daiq-car.jp/contact</t>
+        </is>
+      </c>
       <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/DaiQ_motors
+https://www.facebook.com/daiq.motors/
+https://www.instagram.com/daiq_motors.official/</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr"/>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>158名（アルバイト含む、令和8年10月）</t>
-        </is>
-      </c>
+      <c r="O55" s="2" t="inlineStr"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>https://k-smile.jp/company/</t>
+          <t>https://www.daiq-car.jp/</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -4059,7 +4022,7 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+          <t>軽自動車専門店ダイキュー。運営会社名は公式サイトの古物営業法に基づく表示による。店舗は公式サイトの5店舗。</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4032,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>株式会社ケーワン（5-STAR）</t>
+          <t>株式会社CIA</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -4077,39 +4040,57 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>5-STAR 越谷店、5-STAR 春日部店、5-STAR 三郷店、5-STAR 土浦店、5-STAR 阿見店</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
+          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 大内康弘</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/</t>
+        </is>
+      </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー買取（買取センター4か所）</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>https://employment.en-japan.com/comp-66249/
-https://car.motor-fan.jp/ucar/shop/3000451
-https://compalyze.co.jp/company/2030001068305</t>
+          <t>https://www.yacco.cc/company/</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。求人情報に「埼玉県・茨城県の5-STAR各店舗（越谷・春日部・三郷・土浦）」、中古車情報サイトに阿見店。ランキング記事では「埼玉県中心に6店舗」。越谷店は越谷市大間野町3-146。</t>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4100,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロイヤルオートサービス</t>
+          <t>株式会社NIIZAWA</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -4127,67 +4108,72 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>広島県、山口県</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>長野県松本市村井町南2-1-5</t>
+          <t>広島県廿日市市大野原1丁目2-20</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>0120-107-817</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
+          <t>0829-30-8103</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8104</t>
+        </is>
+      </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 中田忠章</t>
+          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://carstation.royal-auto.jp/</t>
+          <t>https://www.kei-market.co.jp/</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>https://carstation.royal-auto.jp/contact/</t>
+          <t>https://www.kei-market.co.jp/contact/</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>https://twitter.com/royal_auto_
-https://www.instagram.com/royal_auto_service/?hl=ja
-https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
+          <t>https://www.instagram.com/keimarket.k
+https://www.facebook.com/share/1AhR49eysR
+https://youtube.com/@keimarket398</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>187名</t>
+          <t>95名（パート含む）</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>https://carstation.royal-auto.jp/company/</t>
+          <t>https://www.kei-market.co.jp/company/
+https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
+          <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4183,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>株式会社東部オート（東部オートグループ）</t>
+          <t>株式会社TSC</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -4205,58 +4191,45 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>茨城県、埼玉県、千葉県</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>高前バイパス店、前橋店、小鳥店、ラビット高前バイパス店、ラビット高崎小鳥店</t>
+          <t>大久保駅前店、千葉北インター店、蘇我インター店、買取直販 つくば店、北本店</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>群馬県高崎市小八木町1538</t>
+          <t>千葉県千葉市美浜区中瀬（番地は未確認）</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>田口 治</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tobu-auto.com/</t>
-        </is>
-      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>買取店（ラビット加盟2店舗、買取事業部をLinksより継承）</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>81名</t>
-        </is>
-      </c>
+          <t>買取直販（買取車両を展示販売）</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>https://www.tobu-auto.com/about
-https://www.tobu-auto.com/</t>
+          <t>https://job.rikunabi.com/job_descriptions/82de25d5815e8620/（検索結果の抜粋。現在は404）</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>会社概要の事業所数は10店舗（整備・鈑金拠点等を含むとみられる）。中古車販売3店舗＋ラビット2店舗で計上。グループにBMW正規販売のモトーレン群馬・栃木（別法人）あり。年商59億円（会社概要）。</t>
+          <t>公式サイト未確認。求人情報の勤務地一覧から5店舗。本社の美浜区中瀬・蘇我インター店の緑区古市場町が、KiND OUTLETのプライバシーポリシー記載会社（NEXTGATE MOTOR SOLUTIONS、美浜区中瀬）・同千葉コンパクトハイブリッド店（緑区古市場町）と近く、同一グループの可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4239,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>株式会社横浜ユーポス</t>
+          <t>株式会社Y's GARAGE</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4274,30 +4247,47 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>栃木県、神奈川県</t>
+          <t>京都府、鳥取県、島根県</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>京都府宇治市槇島町三十五38-1</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>0774-25-5557</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 桐畑勇志</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>https://k-smile.jp/</t>
+        </is>
+      </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>158名（アルバイト含む、令和8年10月）</t>
+        </is>
+      </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/kouhoku
-https://www.u-pohs.co.jp/shonanhiratsuka
-https://www.u-pohs.co.jp/tsuzuki</t>
+          <t>https://k-smile.jp/company/</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -4307,7 +4297,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
         </is>
       </c>
     </row>
@@ -4317,54 +4307,73 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>KiND OUTLET（カインドアウトレット）</t>
+          <t>株式会社ウシジマ（UJグループ・ウシトラ）</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>埼玉県、東京都、京都府、福岡県</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>市原店、千葉蘇我インター軽専門店、山武成東店、千葉コンパクトハイブリッド店</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
+          <t>八女本社、福岡支店（展示場）、埼玉支店（展示場）、東京営業所、京都支店</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>福岡県八女市室岡377-10</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>0436-55-9169</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>0943-24-1126</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0943-24-4812</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>牛島 豊晴</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://kindoutlet.jp/</t>
+          <t>https://www.ushitruck.com/</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック買取あり</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>106名（スタッフ数）</t>
+        </is>
+      </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>https://kindoutlet.jp/shop
-https://kindoutlet.jp/privacypolicy</t>
+          <t>https://www.ushitruck.com/truck/corporate</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>千葉県の軽自動車専門店。サイトのプライバシーポリシー記載はNEXTGATE MOTOR SOLUTIONS株式会社（千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F）だが、運営会社かどうかは未確認。電話は市原店。</t>
+          <t>中古トラック販売・買取。拠点数は販売系の本社・支店・営業所で計上（ほかに部品のウシパーツ、レンタル店）。電話・FAXは会社概要記載のもの（本社の番号かは未確認）。</t>
         </is>
       </c>
     </row>
@@ -4374,20 +4383,20 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ニシオ自販</t>
+          <t>株式会社ケーワン（5-STAR）</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>静岡県西部の4店舗</t>
+          <t>5-STAR 越谷店、5-STAR 春日部店、5-STAR 三郷店、5-STAR 土浦店、5-STAR 阿見店</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -4402,7 +4411,9 @@
       <c r="O61" s="2" t="inlineStr"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋</t>
+          <t>https://employment.en-japan.com/comp-66249/
+https://car.motor-fan.jp/ucar/shop/3000451
+https://compalyze.co.jp/company/2030001068305</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -4412,7 +4423,7 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>「静岡県西部に4店舗展開」との掲載による。店舗名・法人格は未確認。</t>
+          <t>公式サイト未確認。求人情報に「埼玉県・茨城県の5-STAR各店舗（越谷・春日部・三郷・土浦）」、中古車情報サイトに阿見店。ランキング記事では「埼玉県中心に6店舗」。越谷店は越谷市大間野町3-146。</t>
         </is>
       </c>
     </row>
@@ -4422,45 +4433,71 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>プルミエ（軽届出済未使用車専門店、運営会社未確認）</t>
+          <t>株式会社トータルカーサービス（ミニクス）</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>兵庫県、広島県</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>豊田、安城、豊橋、四日市</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
+          <t>ミニクス 福山店、ミニクス 福山中央店、ミニクス アウトレット店、ミニクス 姫路店、ミニクス 加古川店</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>広島県福山市南手城町1丁目14-7</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>084-973-1147</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>084-973-1148</t>
+        </is>
+      </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>https://minics.jp/</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>https://minics.jp/contact</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/minics_2021/
+https://www.youtube.com/channel/UCtdVZXmW98t3g6RypKRTXzg</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋</t>
+          <t>https://minics.jp/shop
+https://minics.jp/about</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>同じ4店舗（豊橋・岡崎安城・豊田・四日市）で「CAST」の名称の掲載もあり、同一の運営会社の可能性。</t>
+          <t>軽トラ・軽バン専門店。サイトに「ミニクス運営：株式会社トータルカーサービス」。所在地は福山中央店と同じ住所の記載（本社かどうかは未確認）。</t>
         </is>
       </c>
     </row>
@@ -4470,11 +4507,11 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ミスターシャーマン（運営会社未確認）</t>
+          <t>株式会社ロイヤルオートサービス</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
@@ -4483,22 +4520,52 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>長野県内4店舗</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>長野県松本市村井町南2-1-5</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>0120-107-817</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 中田忠章</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>https://carstation.royal-auto.jp/</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>https://carstation.royal-auto.jp/contact/</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/royal_auto_
+https://www.instagram.com/royal_auto_service/?hl=ja
+https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr"/>
-      <c r="O63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>187名</t>
+        </is>
+      </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事）</t>
+          <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -4508,7 +4575,7 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>車買取。比較記事の「県内4店舗」による。</t>
+          <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
         </is>
       </c>
     </row>
@@ -4518,45 +4585,66 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ムラトミ</t>
+          <t>株式会社東部オート（東部オートグループ）</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>相模原本店、相模原（2店舗目）、海老名店、伊勢原店</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
+          <t>高前バイパス店、前橋店、小鳥店、ラビット高前バイパス店、ラビット高崎小鳥店</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>群馬県高崎市小八木町1538</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>田口 治</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tobu-auto.com/</t>
+        </is>
+      </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>買取店（ラビット加盟2店舗、買取事業部をLinksより継承）</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0530132</t>
+          <t>https://www.tobu-auto.com/about
+https://www.tobu-auto.com/</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイトの店舗紹介に「神奈川県内4店舗（相模原2店、海老名、伊勢原）のロープライスカー専門店」とある。相模原本店は相模原市南区新磯野5-43。運営法人名は未確認。2店舗目の相模原の店名は不明。</t>
+          <t>会社概要の事業所数は10店舗（整備・鈑金拠点等を含むとみられる）。中古車販売3店舗＋ラビット2店舗で計上。グループにBMW正規販売のモトーレン群馬・栃木（別法人）あり。年商59億円（会社概要）。</t>
         </is>
       </c>
     </row>
@@ -4566,20 +4654,20 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昭和礦油株式会社</t>
+          <t>株式会社横浜ユーポス</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県、神奈川県</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
+          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -4594,9 +4682,10 @@
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0282/
-https://www.applenet.co.jp/shop/0290/
-https://www.applenet.co.jp/shop/0291/</t>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/kouhoku
+https://www.u-pohs.co.jp/shonanhiratsuka
+https://www.u-pohs.co.jp/tsuzuki</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -4606,7 +4695,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4705,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>株式会社MARE</t>
+          <t>KiND OUTLET（カインドアウトレット）</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4624,19 +4713,27 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>愛知県、兵庫県、広島県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
+          <t>市原店、千葉蘇我インター軽専門店、山武成東店、千葉コンパクトハイブリッド店</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>0436-55-9169</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>https://kindoutlet.jp/</t>
+        </is>
+      </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
@@ -4644,19 +4741,18 @@
       <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0289/
-https://www.applenet.co.jp/shop/0296/
-https://www.applenet.co.jp/shop/0308/</t>
+          <t>https://kindoutlet.jp/shop
+https://kindoutlet.jp/privacypolicy</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>千葉県の軽自動車専門店。サイトのプライバシーポリシー記載はNEXTGATE MOTOR SOLUTIONS株式会社（千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F）だが、運営会社かどうかは未確認。電話は市原店。</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4762,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>株式会社オリンピア</t>
+          <t>ニシオ自販</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4674,12 +4770,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>栃木県、群馬県、埼玉県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
+          <t>静岡県西部の4店舗</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -4694,19 +4790,17 @@
       <c r="O67" s="2" t="inlineStr"/>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0138/
-https://www.applenet.co.jp/shop/0141/
-https://www.applenet.co.jp/shop/0143/</t>
+          <t>検索結果の抜粋</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>「静岡県西部に4店舗展開」との掲載による。店舗名・法人格は未確認。</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4810,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートスペースアクセル（ASAグループ）</t>
+          <t>プルミエ（軽届出済未使用車専門店、運営会社未確認）</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4724,12 +4818,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>（有）オートフィールドストリーク</t>
+          <t>豊田、安城、豊橋、四日市</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -4744,8 +4838,7 @@
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0510254
-https://biz-maps.com/s/cities/142123/m-inds/378</t>
+          <t>検索結果の抜粋</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -4755,7 +4848,7 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。</t>
+          <t>同じ4店舗（豊橋・岡崎安城・豊田・四日市）で「CAST」の名称の掲載もあり、同一の運営会社の可能性。</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4858,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>株式会社クレタ（北海道軽パーク）</t>
+          <t>ミスターシャーマン（運営会社未確認）</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4773,43 +4866,27 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>札幌店、札幌東店、北広島店、苫小牧店</t>
+          <t>長野県内4店舗</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>https://kereta.jp/</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>https://kereta.jp/contact/</t>
-        </is>
-      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/hokkaido_k_park/
-https://x.com/hokkaido_k_park
-https://www.facebook.com/hokkaidokeipark/
-https://youtube.com/channel/UC2xk0xmuuww2ocTXFsNghcw
-https://www.tiktok.com/@hokkaido_k_park</t>
-        </is>
-      </c>
+      <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr"/>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>https://kereta.jp/</t>
+          <t>検索結果の抜粋（比較記事）</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -4819,7 +4896,7 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。</t>
+          <t>車買取。比較記事の「県内4店舗」による。</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4906,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>株式会社グローバンネット</t>
+          <t>ムラトミ</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4837,23 +4914,19 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
+          <t>相模原本店、相模原（2店舗目）、海老名店、伊勢原店</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>https://pa-cars.com/</t>
-        </is>
-      </c>
+      <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr"/>
@@ -4861,7 +4934,7 @@
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>https://pa-cars.com/shopinfo.html</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0530132</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -4871,7 +4944,7 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。</t>
+          <t>公式サイト未確認。中古車情報サイトの店舗紹介に「神奈川県内4店舗（相模原2店、海老名、伊勢原）のロープライスカー専門店」とある。相模原本店は相模原市南区新磯野5-43。運営法人名は未確認。2店舗目の相模原の店名は不明。</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4954,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>株式会社ダブルツリー</t>
+          <t>昭和礦油株式会社</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4889,22 +4962,18 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
+          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
+      <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
@@ -4913,7 +4982,9 @@
       <c r="O71" s="2" t="inlineStr"/>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/</t>
+          <t>https://www.applenet.co.jp/shop/0282/
+https://www.applenet.co.jp/shop/0290/
+https://www.applenet.co.jp/shop/0291/</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -4923,7 +4994,7 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4933,7 +5004,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビッグワン</t>
+          <t>株式会社GR8（GR8STYLE）</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4941,37 +5012,67 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>販売店（千葉市内4店舗）</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
+          <t>GR8 STYLE 春日井店、名古屋大府店、岡崎店、名古屋港店</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>愛知県春日井市南下原町6丁目2-1</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>0568-41-8828</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0568-41-8839</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>入谷 篤</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gr8style.co.jp/</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gr8style.co.jp/contact/</t>
+        </is>
+      </c>
       <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gr8style/
+https://www.instagram.com/gr8style_japan/</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr"/>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
+          <t>https://www.gr8style.co.jp/company-profile/
+https://www.gr8style.co.jp/</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
+          <t>ハイエース専門店（新車・中古車・カスタム・キャンピング）。</t>
         </is>
       </c>
     </row>
@@ -4981,7 +5082,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミナミシマ自動車販売</t>
+          <t>株式会社MARE</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4989,12 +5090,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>愛知県、兵庫県、広島県</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
+          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -5009,9 +5110,9 @@
       <c r="O73" s="2" t="inlineStr"/>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kashiba/
-https://www.u-pohs.co.jp/kashihara/
-https://www.u-pohs.co.jp/katuragi/</t>
+          <t>https://www.applenet.co.jp/shop/0289/
+https://www.applenet.co.jp/shop/0296/
+https://www.applenet.co.jp/shop/0308/</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -5021,7 +5122,7 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5132,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>株式会社ワークス</t>
+          <t>株式会社T-SPACE</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -5044,32 +5145,63 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
+          <t>SPACE ジムニー館、SPACE-ONE、SPACE-SE、SPACE-ZERO</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県春日部市栄町1-431-1</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>048-797-6699</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>048-797-6644</t>
+        </is>
+      </c>
       <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>https://cardealer-space.com/</t>
+        </is>
+      </c>
       <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>info@cardealer-space.com</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/space_jimny
+https://www.instagram.com/spaceone661
+https://www.instagram.com/spacese6
+https://www.instagram.com/space.zero.kasukabe/</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>買取査定あり</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
+          <t>https://cardealer-space.com/company/</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
+          <t>販売店4（春日部市）。ほかに整備（T-SPACE SERVICE）・鈑金（SPACE-Body Lab.）・レンタカー。</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5211,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>株式会社沖縄ユーポス</t>
+          <t>株式会社エコノミー湘南（奇跡査定センター）</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5087,39 +5219,62 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
+          <t>奇跡査定センター 藤沢六会本店、藤沢橋店、横浜都筑店、相模原16号由野台店</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県藤沢市亀井野2480-3</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>0466-80-3443</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>0466-80-3445</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>桑名 伸</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.satei.net/</t>
+        </is>
+      </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>買取専門（買取センター）</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr"/>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/misato/
-https://www.u-pohs.co.jp/naha-shintoshin
-https://www.u-pohs.co.jp/noborikawa/</t>
+          <t>https://www.satei.net/company-profile/
+https://www.satei.net/</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>車買取専門店。会社概要の沿革に「有限会社エコノミーエンタープライズより営業継承し、株式会社エコノミー湘南を設立」「屋号を奇跡査定センターとし」とあるが、現在の社名欄は確認できず。電話は藤沢六会本店。</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5284,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>株式会社鈴木モータース</t>
+          <t>株式会社オリンピア</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5137,12 +5292,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>栃木県、群馬県、埼玉県</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
+          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -5157,9 +5312,9 @@
       <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0065/
-https://www.applenet.co.jp/shop/0071/
-https://www.applenet.co.jp/shop/0080/</t>
+          <t>https://www.applenet.co.jp/shop/0138/
+https://www.applenet.co.jp/shop/0141/
+https://www.applenet.co.jp/shop/0143/</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -5179,7 +5334,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>買取マウス（運営会社未確認）</t>
+          <t>株式会社オートスペースアクセル（ASAグループ）</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5187,12 +5342,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>新潟市内4店舗</t>
+          <t>（有）オートフィールドストリーク</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -5207,7 +5362,8 @@
       <c r="O77" s="2" t="inlineStr"/>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事）</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0510254
+https://biz-maps.com/s/cities/142123/m-inds/378</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -5217,7 +5373,7 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>車買取。比較記事の「新潟市内に4店舗」による。</t>
+          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。</t>
         </is>
       </c>
     </row>
@@ -5227,20 +5383,20 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Dash（運営会社未確認）</t>
+          <t>株式会社クレタ（北海道軽パーク）</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>名古屋本店、西三河店、三重鈴鹿店</t>
+          <t>札幌店、札幌東店、北広島店、苫小牧店</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -5249,17 +5405,29 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.car-dash.jp/</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
+          <t>https://kereta.jp/</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>https://kereta.jp/contact/</t>
+        </is>
+      </c>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hokkaido_k_park/
+https://x.com/hokkaido_k_park
+https://www.facebook.com/hokkaidokeipark/
+https://youtube.com/channel/UC2xk0xmuuww2ocTXFsNghcw
+https://www.tiktok.com/@hokkaido_k_park</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>https://www.car-dash.jp/</t>
+          <t>https://kereta.jp/</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -5269,7 +5437,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店。</t>
+          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。</t>
         </is>
       </c>
     </row>
@@ -5279,27 +5447,31 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ZERO MOTORS（運営会社未確認）</t>
+          <t>株式会社グローバンネット</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>埼玉県内3店舗</t>
+          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>https://pa-cars.com/</t>
+        </is>
+      </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr"/>
@@ -5307,7 +5479,7 @@
       <c r="O79" s="2" t="inlineStr"/>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://pa-cars.com/shopinfo.html</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -5317,7 +5489,7 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>軽自動車・コンパクトカー専門店。「埼玉県3店舗・総在庫700台以上」との掲載による。</t>
+          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。</t>
         </is>
       </c>
     </row>
@@ -5327,20 +5499,20 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>アビックス大阪株式会社</t>
+          <t>株式会社サンライズモータース（軽プラザサンライズ）</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
+          <t>軽プラザサンライズ 青森本店、軽プラザサンライズ 弘前本店、軽プラザサンライズ 八戸本店、新車市場 サンライズ青森東バイパス店</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -5355,7 +5527,9 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）</t>
+          <t>https://carbell.jp/partner/search?area_code=10
+https://car.motor-fan.jp/ucar/shop/0904135
+https://www.kurumaerabi.com/shop/detail/40016907/</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -5365,7 +5539,7 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>アビックスコーポレーションのグループ会社とみられる。</t>
+          <t>公式サイト未確認。軽未使用車専門店。中古車情報サイトの店舗紹介に青森・弘前・八戸の各店と「グループ総在庫800台」。新車市場の加盟店一覧に「新車市場 サンライズ青森東バイパス店 株式会社サンライズモータース」。青森本店は青森市第二問屋町2丁目5-13（車検のコバック併設）、八戸本店は八戸市城下3-8-6。</t>
         </is>
       </c>
     </row>
@@ -5375,26 +5549,30 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>オニキス千葉（ONIX加盟、運営会社未確認）</t>
+          <t>株式会社ダブルツリー</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>八千代店ほか千葉県内3店舗</t>
+          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
@@ -5403,17 +5581,17 @@
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>https://unusedcar.onix-ns.com/</t>
+          <t>https://www.applenet.co.jp/shop/</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>未使用車専門店。「千葉県で3店舗、総在庫1000台以上」との掲載による。</t>
+          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。</t>
         </is>
       </c>
     </row>
@@ -5423,20 +5601,20 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>トーワオート（運営会社未確認）</t>
+          <t>株式会社ビッグワン</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>宇都宮西店、宇都宮東店、宇都宮南店</t>
+          <t>販売店（千葉市内4店舗）</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -5451,7 +5629,7 @@
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -5461,7 +5639,7 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>宇都宮市内の3店舗。</t>
+          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -5471,20 +5649,20 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>プチモ軽自動車専門店（株式会社ヒューベストオートの可能性）</t>
+          <t>株式会社ミナミシマ自動車販売</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>佐賀店、唐津店、佐世保店</t>
+          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -5499,17 +5677,19 @@
       <c r="O83" s="2" t="inlineStr"/>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（求人・店舗掲載）</t>
+          <t>https://www.u-pohs.co.jp/kashiba/
+https://www.u-pohs.co.jp/kashihara/
+https://www.u-pohs.co.jp/katuragi/</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>佐世保店は長崎県（2025年12月開店）。運営会社は佐世保店の求人の募集元による推定。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。</t>
         </is>
       </c>
     </row>
@@ -5519,49 +5699,66 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>ポケットカーズ（運営会社未確認）</t>
+          <t>株式会社ライズオート（RiSE AUTO）</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>女池店、三条店、長岡店</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>RiSE 四日市北店、RiSE 四日市南店、ガリバーアウトレット 四日市緑地店、ガリバー 稲沢店</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>三重県四日市市日永東3-13-5</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>059-329-5553</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>松村 賢治</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/</t>
+          <t>https://riseauto.jp/</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>買取あり（ガリバー加盟店を運営）</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/shop/</t>
+          <t>https://riseauto.jp/company/
+https://riseauto.jp/</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
+          <t>リョウシンホールディングスグループ。自社ブランドRiSE 2店舗＋ガリバー加盟2店舗。会社概要に「三重県に3店舗と愛知県に1店舗」。</t>
         </is>
       </c>
     </row>
@@ -5571,39 +5768,27 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>古城モータース</t>
+          <t>株式会社ワークス</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>高岡本店、富山店、石川白山店</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>富山県高岡市二塚425番地</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>0120-540-118</t>
-        </is>
-      </c>
+          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kojyo-motors.com/</t>
-        </is>
-      </c>
+      <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
@@ -5611,7 +5796,7 @@
       <c r="O85" s="2" t="inlineStr"/>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/</t>
+          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -5619,7 +5804,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -5627,39 +5816,27 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>株式会社沖縄ユーポス</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8844</t>
-        </is>
-      </c>
+          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.autogallery.co.jp/</t>
-        </is>
-      </c>
+      <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
@@ -5667,8 +5844,9 @@
       <c r="O86" s="2" t="inlineStr"/>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>https://www.u-pohs.co.jp/misato/
+https://www.u-pohs.co.jp/naha-shintoshin
+https://www.u-pohs.co.jp/noborikawa/</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -5678,7 +5856,7 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオートギャラリーグループ（輸入車）。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5688,39 +5866,27 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>株式会社鈴木モータース</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
-        </is>
-      </c>
+          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.csauto.jp/</t>
-        </is>
-      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr"/>
@@ -5728,8 +5894,9 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://www.applenet.co.jp/shop/0065/
+https://www.applenet.co.jp/shop/0071/
+https://www.applenet.co.jp/shop/0080/</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -5739,7 +5906,7 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5749,74 +5916,45 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>株式会社アクセス（カーライフステーション）</t>
+          <t>買取マウス（運営会社未確認）</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>岩槻インター店、上尾店、久喜店</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県さいたま市見沼区宮ケ谷塔91-1</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>0120-344-713</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>048-681-5088</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>黒木 康男</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>https://344860.net/</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>https://344860.net/contact/</t>
-        </is>
-      </c>
+          <t>新潟市内4店舗</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>158人（2019年度）</t>
-        </is>
-      </c>
+      <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>https://344860.net/company/
-https://344860.net/shop/</t>
+          <t>検索結果の抜粋（比較記事）</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車・新車専門店。電話はフリーダイヤル（会社概要記載のもの）。</t>
+          <t>車買取。比較記事の「新潟市内に4店舗」による。</t>
         </is>
       </c>
     </row>
@@ -5826,27 +5964,35 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>鈴木自工株式会社（軽ひろば・くるま広場）</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
+          <t>くるま広場 船橋習志野店、軽ひろば 佐倉王子台店、軽ひろば 千葉貝塚店、軽ひろば 千葉おゆみ店</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>047-406-3259</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>https://kei-hiroba.car-yasui.jp/</t>
+        </is>
+      </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr"/>
@@ -5854,9 +6000,7 @@
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/</t>
+          <t>https://kei-hiroba.car-yasui.jp/</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -5866,7 +6010,7 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>軽自動車（新車・未使用車・中古車）専門店。サイトに「運営：鈴木自工株式会社」。店舗名はサイトのタイトル・本文から。電話はサイト記載のもの（どの店舗かは未確認）。新車の扱いが中心の可能性あり。</t>
         </is>
       </c>
     </row>
@@ -5876,7 +6020,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>Dash（運営会社未確認）</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5884,29 +6028,21 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
-        </is>
-      </c>
+          <t>名古屋本店、西三河店、三重鈴鹿店</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 上武英輝</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
@@ -5916,16 +6052,19 @@
       <c r="O90" s="2" t="inlineStr"/>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R90" s="2" t="inlineStr"/>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>自社ローン専門店。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -5933,7 +6072,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>株式会社クイックモーション（カラーズ）</t>
+          <t>ZERO MOTORS（運営会社未確認）</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5946,7 +6085,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>カラーズKawagoe（川越）、ほか2店舗</t>
+          <t>埼玉県内3店舗</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -5961,7 +6100,7 @@
       <c r="O91" s="2" t="inlineStr"/>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>https://ucar.carview.yahoo.co.jp/shop/saitama/214637003/（検索結果の抜粋）</t>
+          <t>検索結果の抜粋（店舗掲載）</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -5971,7 +6110,7 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>4WD・SUV専門店。「埼玉県を中心に3店舗」との掲載による。</t>
+          <t>軽自動車・コンパクトカー専門店。「埼玉県3店舗・総在庫700台以上」との掲載による。</t>
         </is>
       </c>
     </row>
@@ -5981,7 +6120,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>株式会社コンチネント</t>
+          <t>アビックス大阪株式会社</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -5989,58 +6128,37 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>岡山本店、カーセブン倉敷中島店、カーセブン岡山妹尾店</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>岡山県岡山市南区妹尾4130-2</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>086-281-5544</t>
-        </is>
-      </c>
+          <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>平松 裕</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>https://conti-nent.com/</t>
-        </is>
-      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>買取（カーセブン加盟店）</t>
-        </is>
-      </c>
+      <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>https://conti-nent.com/company/
-https://conti-nent.com/shops/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>会社概要に「3店舗展開 岡山本店・倉敷中島店・岡山妹尾店」。ほかに鈑金塗装工場あり。カーセブンFC加盟。</t>
+          <t>アビックスコーポレーションのグループ会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6168,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>カーライフグループ株式会社</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6058,29 +6176,48 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr"/>
+          <t>TOKYO店、大阪店、福岡店</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>福岡県糟屋郡粕屋町戸原西4丁目8-11</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>0120-038-871</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>092-410-5912</t>
+        </is>
+      </c>
       <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>https://loanok.jp/</t>
+        </is>
+      </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr"/>
-      <c r="O93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>30名</t>
+        </is>
+      </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://loanok.jp/shop000.html
+https://loanok.jp/</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -6090,7 +6227,7 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>自社ローン専門。所在地はサイト記載の住所（本社かどうかは未確認）。</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6237,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>トーワオート（運営会社未確認）</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6108,12 +6245,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+          <t>宇都宮西店、宇都宮東店、宇都宮南店</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -6128,17 +6265,17 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>検索結果の抜粋（店舗掲載）</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>ユーポス以外の事業は未確認。</t>
+          <t>宇都宮市内の3店舗。</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6285,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>プチモ軽自動車専門店（株式会社ヒューベストオートの可能性）</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6156,12 +6293,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>佐賀店、唐津店、佐世保店</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -6176,19 +6313,17 @@
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/</t>
+          <t>検索結果の抜粋（求人・店舗掲載）</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>佐世保店は長崎県（2025年12月開店）。運営会社は佐世保店の求人の募集元による推定。</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6333,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーリンクス</t>
+          <t>ポケットカーズ（運営会社未確認）</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6206,19 +6341,23 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>アラジン二又瀬店、アラジン小倉南店、アラジン飯塚店</t>
+          <t>女池店、三条店、長岡店</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pocketcars.jp/</t>
+        </is>
+      </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
@@ -6226,7 +6365,7 @@
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>https://autoc-one.jp/ullo/shop/3142/（検索結果の抜粋）</t>
+          <t>https://www.pocketcars.jp/shop/</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -6236,7 +6375,7 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>車買取りネットワーク「アラジン」の運営会社の一つ。アラジンは九州中心に複数の運営会社がある（久留米南店は株式会社Alive）。他店舗の運営会社は未確認。</t>
+          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6385,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>古城モータース</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6254,19 +6393,31 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
+          <t>高岡本店、富山店、石川白山店</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>富山県高岡市二塚425番地</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>0120-540-118</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kojyo-motors.com/</t>
+        </is>
+      </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr"/>
@@ -6274,21 +6425,15 @@
       <c r="O97" s="2" t="inlineStr"/>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R97" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -6296,7 +6441,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6304,29 +6449,52 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8845</t>
+        </is>
+      </c>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.autogallery.co.jp/</t>
+        </is>
+      </c>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>inquiry@autogallery.co.jp</t>
+        </is>
+      </c>
       <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>中古車の買取・下取りあり</t>
+        </is>
+      </c>
       <c r="O98" s="2" t="inlineStr"/>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -6336,7 +6504,7 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>輸入車（アメ車等）専門店。サイトの見出しは「東京 神奈川 福岡」で、古物商許可も神奈川県を含むが、店舗情報ページに載っているのは東京・大阪・福岡の3店舗。</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6514,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>良質車専門店ネクスト（運営会社未確認）</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6354,19 +6522,31 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>会津若松店、いわき店、白河店</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
+        </is>
+      </c>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 河野修一</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.csauto.jp/</t>
+        </is>
+      </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr"/>
@@ -6374,17 +6554,18 @@
       <c r="O99" s="2" t="inlineStr"/>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗の在庫掲載）</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車も扱う中古車店。3市の店舗は検索結果の在庫掲載から確認。運営会社名は未確認。</t>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6575,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>軽ステ（運営会社未確認）</t>
+          <t>株式会社アクセス（カーライフステーション）</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6402,37 +6583,66 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>熊本県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>けんぐん東店、うと店、しみず店</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
+          <t>岩槻インター店、上尾店、久喜店</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県さいたま市見沼区宮ケ谷塔91-1</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>0120-344-713</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>048-681-5088</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>黒木 康男</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>https://344860.net/</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>https://344860.net/contact/</t>
+        </is>
+      </c>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>158人（2019年度）</t>
+        </is>
+      </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://344860.net/company/
+https://344860.net/shop/</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>熊本県最大級の軽届出済未使用車専門店（総在庫1,300台）とのこと。運営会社未確認。</t>
+          <t>届出済未使用車・新車専門店。電話はフリーダイヤル（会社概要記載のもの）。</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6652,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>阿部勝自動車工業株式会社</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -6450,23 +6660,19 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>https://k-mishiyo.abekatu.co.jp/</t>
-        </is>
-      </c>
+      <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr"/>
@@ -6474,15 +6680,635 @@
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>株式会社カミタケモータース</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>大阪府、奈良県、大分県</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>枚方本店、奈良店、大分店</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>株式会社クイックモーション（カラーズ）</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>カラーズKawagoe（川越）、ほか2店舗</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>https://ucar.carview.yahoo.co.jp/shop/saitama/214637003/（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>4WD・SUV専門店。「埼玉県を中心に3店舗」との掲載による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>株式会社コンチネント</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>岡山本店、カーセブン倉敷中島店、カーセブン岡山妹尾店</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>岡山県岡山市南区妹尾4130-2</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>086-281-5544</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>平松 裕</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>https://conti-nent.com/</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>買取（カーセブン加盟店）</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>https://conti-nent.com/company/
+https://conti-nent.com/shops/</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>会社概要に「3店舗展開 岡山本店・倉敷中島店・岡山妹尾店」。ほかに鈑金塗装工場あり。カーセブンFC加盟。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>株式会社シマダオート商事</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>株式会社フロンティアモータース</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>大阪府、兵庫県</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス以外の事業は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ベネフィット</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>千葉県、東京都</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ユーリンクス</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>アラジン二又瀬店、アラジン小倉南店、アラジン飯塚店</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>https://autoc-one.jp/ullo/shop/3142/（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>車買取りネットワーク「アラジン」の運営会社の一つ。アラジンは九州中心に複数の運営会社がある（久留米南店は株式会社Alive）。他店舗の運営会社は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>株式会社リフトオフ</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>茨城県、千葉県、東京都</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>株式会社中州自動車</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>大分県</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>良質車専門店ネクスト（運営会社未確認）</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>会津若松店、いわき店、白河店</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>検索結果の抜粋（店舗の在庫掲載）</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>届出済未使用車も扱う中古車店。3市の店舗は検索結果の在庫掲載から確認。運営会社名は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>軽ステ（運営会社未確認）</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>熊本県</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>けんぐん東店、うと店、しみず店</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>検索結果の抜粋（店舗掲載）</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>熊本県最大級の軽届出済未使用車専門店（総在庫1,300台）とのこと。運営会社未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>阿部勝自動車工業株式会社</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>https://k-mishiyo.abekatu.co.jp/</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
           <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）</t>
         </is>
       </c>
-      <c r="Q101" s="2" t="inlineStr">
+      <c r="Q113" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R101" s="2" t="inlineStr"/>
+      <c r="R113" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6495,7 +7321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6528,13 +7354,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6544,127 +7370,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>富山県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>石川県</t>
+          <t>富山県</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>福井県</t>
+          <t>石川県</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6674,17 +7500,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>福井県</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6694,97 +7520,97 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>鳥取県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>島根県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6794,67 +7620,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>徳島県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>香川県</t>
+          <t>徳島県</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>愛媛県</t>
+          <t>香川県</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>高知県</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6864,147 +7690,147 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>高知県</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>長崎県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>熊本県</t>
+          <t>長崎県</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>熊本県</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>鹿児島県</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>鹿児島県</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>沖縄県</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B44" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>本社所在地の都道府県別の社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>都道府県</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>2</v>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -7014,37 +7840,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>富山県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -7054,7 +7880,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>富山県</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -7064,17 +7890,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -7084,47 +7910,47 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -7134,141 +7960,161 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="B69" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>店舗数の分布</t>
         </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>3〜4店舗</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5〜9店舗</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>36</v>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10〜19店舗</t>
+          <t>3〜4店舗</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20〜30店舗</t>
+          <t>5〜9店舗</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>10〜19店舗</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20〜30店舗</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="B77" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>確度別の社数</t>
         </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>確度</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>45</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>確度</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>55</v>
+      <c r="B82" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -9956,7 +10802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10087,22 +10933,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>株式会社アクティブコレクション</t>
+          <t>興和自動車販売（KOWA飯田）</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>リバティの子会社。横浜・大和、グループ総在庫4,000台</t>
+          <t>南信地区</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認。リバティとの関係（子会社）をどう扱うか要判断</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -10112,17 +10958,13 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>株式会社クレタ（北海道軽パーク）</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>苫小牧</t>
-        </is>
-      </c>
+          <t>株式会社佐野自動車商会（トラスト新潟）</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -10137,22 +10979,18 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>軽プラザサンライズ</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>弘前・八戸</t>
-        </is>
-      </c>
+          <t>株式会社Smile Carz</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>未確認（2店舗の可能性）</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -10162,19 +11000,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>興和自動車販売（KOWA飯田）</t>
+          <t>株式会社BIG BRIDGE／株式会社five star</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>南信地区</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>長野県</t>
-        </is>
-      </c>
+          <t>自社ローン</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
@@ -10187,18 +11021,14 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>株式会社佐野自動車商会（トラスト新潟）</t>
+          <t>株式会社ヤマト（島根）／共盛自動車グループ（広島）／株式会社日本カードック（尼崎）／株式会社グランドエンタープライズ（京都）</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>新潟県</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>業態・店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -10208,15 +11038,15 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>株式会社Smile Carz</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>山口県</t>
-        </is>
-      </c>
+          <t>株式会社ルートシックス</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー専門、水戸・埼玉</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
@@ -10229,18 +11059,18 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>株式会社BIG BRIDGE／株式会社five star</t>
+          <t>株式会社タックス横浜／株式会社タックス宮城野／株式会社キリン自動車（ONIX）</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>自社ローン</t>
+          <t>FC加盟店</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>タックス・オニキス本部の店舗一覧が取得できず店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -10250,14 +11080,18 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヤマト（島根）／共盛自動車グループ（広島）／株式会社日本カードック（尼崎）／株式会社グランドエンタープライズ（京都）</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
+          <t>株式会社OSG（ミニバン専門店OSG）／OSINC.／株式会社N.T ART</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>大阪</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>業態・店舗数未確認</t>
+          <t>店舗数未確認（1〜2店舗の可能性）</t>
         </is>
       </c>
     </row>
@@ -10267,18 +11101,18 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>株式会社ルートシックス</t>
+          <t>LACモービル（アネックス・キャンピングカーランド・デルタリンクの3社）</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー専門、水戸・埼玉</t>
+          <t>キャンピングカー。宮城・横浜・埼玉・入間・千葉・名古屋・京都・大阪・倉敷・岐阜・新潟（直営9店舗＋FC）</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>3社の共通ブランドで、どの会社が何店舗を運営しているか未確認（各社4店舗以下の可能性）</t>
         </is>
       </c>
     </row>
@@ -10288,18 +11122,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>株式会社タックス横浜／株式会社タックス宮城野／株式会社キリン自動車（ONIX）</t>
+          <t>株式会社クロカワ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>FC加盟店</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>軽届出済未使用車専門店</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>タックス・オニキス本部の店舗一覧が取得できず店舗数未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -10309,18 +11147,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>株式会社OSG（ミニバン専門店OSG）／OSINC.／株式会社N.T ART</t>
+          <t>株式会社ネクスト（軽スマイル）</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>大阪</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>北九州、39.8万円専門店</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認（1〜2店舗の可能性）</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -10330,18 +11172,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LACモービル（アネックス・キャンピングカーランド・デルタリンクの3社）</t>
+          <t>株式会社モトヤモビリティーズ（軽モール）</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー。宮城・横浜・埼玉・入間・千葉・名古屋・京都・大阪・倉敷・岐阜・新潟（直営9店舗＋FC）</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
+          <t>倉敷</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3社の共通ブランドで、どの会社が何店舗を運営しているか未確認（各社4店舗以下の可能性）</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -10351,22 +11197,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>株式会社クロカワ</t>
+          <t>カーズ松尾自動車</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>軽届出済未使用車専門店</t>
+          <t>小郡・朝倉ほか</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>香川県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -10376,22 +11222,14 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>オートプラネット名古屋</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>輸入中古車</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>愛知県</t>
-        </is>
-      </c>
+          <t>株式会社ネクスト（軽スマイル）／綿仁株式会社（パッカーズ沼津・三島）</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -10401,22 +11239,18 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>株式会社ネクスト（軽スマイル）</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>北九州、39.8万円専門店</t>
-        </is>
-      </c>
+          <t>株式会社Car Service FRIENDS（軽マート）</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -10426,22 +11260,18 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>株式会社モトヤモビリティーズ（軽モール）</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>倉敷</t>
-        </is>
-      </c>
+          <t>トヨオカ自動車グループ（軽市場）</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>未確認</t>
         </is>
       </c>
     </row>
@@ -10451,22 +11281,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>カーズ松尾自動車</t>
+          <t>新生オートプラザグループ</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>小郡・朝倉ほか</t>
+          <t>飯能・坂戸、グループ300台</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>店舗数未確認</t>
+          <t>公式サイトから店舗数を判定できず（2〜3店舗の可能性）</t>
         </is>
       </c>
     </row>
@@ -10476,14 +11306,18 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>株式会社ネクスト（軽スマイル）／綿仁株式会社（パッカーズ沼津・三島）</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
+          <t>GTNET（スポーツカー専門店）</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>GT-R買取・スポーツカー専門、埼玉ほか複数店舗</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>公式サイトが403で取得できず、運営会社・店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -10493,18 +11327,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>株式会社Car Service FRIENDS（軽マート）</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>兵庫県</t>
-        </is>
-      </c>
+          <t>株式会社RIP-OFF／株式会社STK（マーキュリー八王子）</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>輸入車</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -10514,18 +11348,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>トヨオカ自動車グループ（軽市場）</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
+          <t>アップルワールド</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>豊田市、1972年設立</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -10535,12 +11373,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>新生オートプラザグループ</t>
+          <t>Car Shop IKKI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>飯能・坂戸、グループ300台</t>
+          <t>さいたま市北区本社、埼玉県内に複数店舗</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -10550,7 +11388,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>公式サイトから店舗数を判定できず（2〜3店舗の可能性）</t>
+          <t>公式サイトに接続できず、運営会社・店舗数未確認</t>
         </is>
       </c>
     </row>
@@ -10560,18 +11398,18 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GTNET（スポーツカー専門店）</t>
+          <t>30cars（30万以下の中古車専門店）</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GT-R買取・スポーツカー専門、埼玉ほか複数店舗</t>
+          <t>福岡・香川観音寺・宮崎都城・東広島・山口宇部・倉敷・熊本宇土天草・宮崎延岡（予定）など</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>公式サイトが403で取得できず、運営会社・店舗数未確認</t>
+          <t>公式サイト・運営会社が見つからず店舗数未確認（FCの可能性あり）</t>
         </is>
       </c>
     </row>
@@ -10581,93 +11419,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>株式会社クイックモーション（カラーズ、4WD・SUV専門店）</t>
+          <t>株式会社ガイアスジャパン（軽ワーク）</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>埼玉中心に3店舗</t>
+          <t>長野県上田市の軽トラ・軽バン専門店。検索結果に「東信エリアで4店舗」</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3店舗前後で境界未満の可能性</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>株式会社RIP-OFF／株式会社STK（マーキュリー八王子）</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>輸入車</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>店舗数未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>アップルワールド</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>豊田市、1972年設立</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>愛知県</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>店舗数未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Car Shop IKKI</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>さいたま市北区本社、埼玉県内に複数店舗</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>公式サイトに接続できず、運営会社・店舗数未確認</t>
+          <t>4店舗に中古車販売以外の業態が含まれるか未確認</t>
         </is>
       </c>
     </row>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -647,7 +647,11 @@
           <t>オトロン所沢インター店、オトロン土浦店、ほか（関東・東北・中部を中心に展開）</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>千葉県千葉市中央区寒川町3丁目107番地3</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
@@ -663,7 +667,8 @@
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>https://www.otoron.jp/（503で取得不可。検索結果の抜粋）</t>
+          <t>https://www.otoron.jp/（503で取得不可。検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -673,7 +678,7 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店「オトロン」。店舗数21は公式サイトの古い表記（検索結果による）で最新値は未確認。2024年にオートバックスセブンの完全子会社化が発表されている。公式サイトが503でアクセスできない。</t>
+          <t>自社ローン専門店「オトロン」。店舗数21は公式サイトの古い表記（検索結果による）で最新値は未確認。2024年にオートバックスセブンの完全子会社化が発表されている。公式サイトが503でアクセスできない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7040001077985、〒260-0832）。</t>
         </is>
       </c>
     </row>
@@ -699,7 +704,11 @@
           <t>アップル春日井店、アップル尾張旭店、アップル小牧店、アップル多治見店、アップル世田谷店、アップル大垣インター南店、アップル可児店、アップル瀬戸店、アップル恵那店、アップル春日井中央店、アップル各務原店、アップル一宮22号店、アップルかしわ沼南店、アップル岐阜21号店、アップル碧南店、アップル名岐バイパス春日店、アップル常滑店、アップル岐大バイパス大垣店、アップル岩倉店、アップル春日部店</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>愛知県春日井市柏井町4丁目43番地の1</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -714,7 +723,8 @@
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0002/
 https://www.applenet.co.jp/shop/0003/
-https://www.applenet.co.jp/shop/0005/</t>
+https://www.applenet.co.jp/shop/0005/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -724,7 +734,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名にスバルとあるが、アップル1号店を開業した会社と紹介されている（春日井市）。トラック専門店も運営。 参考：店舗の連絡先（アップル春日井店）〒486-0849 愛知県春日井市八田町2丁目1-16 TEL 0568-85-0202 FAX 0568-85-0262。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名にスバルとあるが、アップル1号店を開業した会社と紹介されている（春日井市）。トラック専門店も運営。 参考：店舗の連絡先（アップル春日井店）〒486-0849 愛知県春日井市八田町2丁目1-16 TEL 0568-85-0202 FAX 0568-85-0262。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9180001074091、〒486-0927）。</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1208,11 @@
           <t>AVIX IMPORT 府中店、AVIX IMPORT 多摩センター店、AVIX IMPORT 川崎生田店、AVIX IMPORT 木更津金田インター店、ほか関東9店舗、仙台東インター店、名古屋北店</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>東京都府中市白糸台3丁目18番地の8</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1215,7 +1229,8 @@
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t>https://car.motor-fan.jp/ucar/shop/9510200（検索結果の抜粋）
-https://www.goo-net.com/user_review/0500520/（検索結果の抜粋）</t>
+https://www.goo-net.com/user_review/0500520/（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1225,7 +1240,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店AVIX IMPORT。店舗紹介文の「関東地区13店舗＆関西地区3店舗＆仙台東インター＆名古屋北店」から、関西3店舗（アビックス大阪株式会社の運営）を除いて15店舗とした。仙台・名古屋の運営会社は未確認。公式サイトは接続できず。</t>
+          <t>輸入車専門店AVIX IMPORT。店舗紹介文の「関東地区13店舗＆関西地区3店舗＆仙台東インター＆名古屋北店」から、関西3店舗（アビックス大阪株式会社の運営）を除いて15店舗とした。仙台・名古屋の運営会社は未確認。公式サイトは接続できず。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1012401004866、〒183-0011）。</t>
         </is>
       </c>
     </row>
@@ -1253,13 +1268,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>千葉県佐倉市ユーカリが丘7-21-3</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>千葉県千葉市稲毛区長沼原町52-9</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>043-304-6669</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>043-376-9195</t>
+          <t>043-304-6699</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1305,7 +1324,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>ランクル・ハイエース専門店とアップル加盟店を運営。公式サイトの店舗一覧13件に、アップル本部サイトでKSファクトリー運営と表示される「アップル福岡久留米店」（公式サイトの一覧には無し）を加えて14店舗。本社ページの電話番号欄は空欄。</t>
+          <t>ランクル・ハイエース専門店とアップル加盟店を運営。公式サイトの店舗一覧13件に、アップル本部サイトでKSファクトリー運営と表示される「アップル福岡久留米店」（公式サイトの一覧には無し）を加えて14店舗。本社ページの電話番号欄は空欄。 【2026-10更新】会社概要の所在地は千葉市稲毛区長沼原町52-9（以前は佐倉市ユーカリが丘7-21-3と記載していたのを訂正）。電話・FAXは同住所の店舗のもの。</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1423,11 @@
           <t>アップル津島中央道店、アップル厚木・北129号店、アップル富田302号店、アップル小田原飯泉店、アップル昭和橋通店、アップル桑名七和店、アップル中村畑江通店、アップル稲沢店、アップル西・康生通店、アップル南23号店、アップル桑名大桑店、アップル黒川北41号店</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>愛知県名古屋市中川区昭和橋通3丁目6番地</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1419,7 +1442,8 @@
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0008/
 https://www.applenet.co.jp/shop/0021/
-https://www.applenet.co.jp/shop/0022/</t>
+https://www.applenet.co.jp/shop/0022/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1429,7 +1453,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル津島中央道店）〒496-0005 愛知県津島市神守町字一丁田60 TEL 0567-28-8151 FAX 0567-28-8152。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号4180001020315、〒454-0852）。</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1548,11 @@
           <t>アップル坂戸鶴ヶ島インター店、アップル太田店、アップル川越16号店、アップル郡山インター店、アップル深谷17号店、アップル西那須野店、アップル朝霞店、アップル仙台六丁目店、アップル東松山店、アップル白河店、アップル所沢店、アップル鴻巣店</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>栃木県那須塩原市新南163番地115</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1539,7 +1567,8 @@
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0015/
 https://www.applenet.co.jp/shop/0037/
-https://www.applenet.co.jp/shop/0044/</t>
+https://www.applenet.co.jp/shop/0044/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1549,7 +1578,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル坂戸鶴ヶ島インター店）〒350-2211 埼玉県鶴ヶ島市脚折町5-4-13 TEL 049-279-3500 FAX 049-279-3501。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル坂戸鶴ヶ島インター店）〒350-2211 埼玉県鶴ヶ島市脚折町5-4-13 TEL 049-279-3500 FAX 049-279-3501。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8060001011933、〒329-2704）。</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1685,11 @@
           <t>アップル江田駅前店、アップル江戸川環七店、アップル豊橋佐藤店、アップル248岡崎店、アップル平塚田村店、アップル中山宮の下店、アップル町田南店、アップル岡崎六ッ美店、アップル東戸塚店、アップル蒲郡店、アップル豊川インター店、アップル岡崎緑丘店</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>愛知県岡崎市鴨田南町1番地18</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1671,7 +1704,8 @@
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0013/
 https://www.applenet.co.jp/shop/0014/
-https://www.applenet.co.jp/shop/0024/</t>
+https://www.applenet.co.jp/shop/0024/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -1681,7 +1715,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。軽四専門「メガタウン」（豊田市）も運営しており、実際の店舗数はこれより多い可能性。 参考：店舗の連絡先（アップル江田駅前店）〒225-0013 神奈川県横浜市青葉区荏田町1236-7東急江田駅前ドエリング1F TEL 045-912-7560 FAX 045-912-7566。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。軽四専門「メガタウン」（豊田市）も運営しており、実際の店舗数はこれより多い可能性。 参考：店舗の連絡先（アップル江田駅前店）〒225-0013 神奈川県横浜市青葉区荏田町1236-7東急江田駅前ドエリング1F TEL 045-912-7560 FAX 045-912-7566。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7180301001565、〒444-2123）。</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2124,11 @@
           <t>ランクル調布店、ランクルさいたま北店、ランクル小牧店、ランクル湘南厚木店、ランクル仙台東店、ハイエース小牧店、ハイエース湘南厚木店、ハイエース高崎店、ハイエース仙台東店、ハイエース三郷店</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>東京都調布市国領町1丁目17番1号</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
@@ -2107,7 +2145,8 @@
       <c r="P24" s="2" t="inlineStr">
         <is>
           <t>https://www.flexdream.jp/（503で取得不可。検索結果に表示された店舗一覧の抜粋）
-https://compalyze.co.jp/company/2012401009864（検索結果の抜粋）</t>
+https://compalyze.co.jp/company/2012401009864（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2117,7 +2156,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>ランクル・ハイエース・USトヨタ専門店。店舗名は検索結果に表示された公式サイトの店舗一覧の抜粋による（10店舗、これ以上ある可能性）。公式サイトは503で確認できず。フレックス株式会社（FLEX、31店舗以上で除外）とは別会社。同じ敷地のランクル店・ハイエース店を別々に数えている。</t>
+          <t>ランクル・ハイエース・USトヨタ専門店。店舗名は検索結果に表示された公式サイトの店舗一覧の抜粋による（10店舗、これ以上ある可能性）。公式サイトは503で確認できず。フレックス株式会社（FLEX、31店舗以上で除外）とは別会社。同じ敷地のランクル店・ハイエース店を別々に数えている。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2012401009864、〒182-0022）。</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2182,11 @@
           <t>ケイバッカ新津本店、ケイバッカ 軽4WD新津インター店、ケイバッカ佐渡店、ケイバッカ北新発田店、ケイバッカ新発田店、ケイバッカ姥ヶ山店、ケイバッカ村上店、ケイバッカ空港通り店、ケイバッカ長岡店、ケイバッカ駅南店</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>新潟県新潟市秋葉区朝日45番地5</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2164,7 +2207,8 @@
       <c r="P25" s="2" t="inlineStr">
         <is>
           <t>https://k-bacca.com/contents/store/index.html
-https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）</t>
+https://compalyze.co.jp/company/2110001007114（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2174,7 +2218,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。</t>
+          <t>ブランドは軽自動車専門店ケイバッカ（KAWAUCHI GROUP）。店舗名は公式サイトの店舗一覧のリンク名（10店舗）。運営会社名は企業情報サイトの抜粋で、公式サイト上の会社表記は未確認。福島県郡山市にも店舗があるとの情報あり（未確認）。新車販売も行う。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2110001007114、〒956-0835）。</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2645,11 @@
           <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>福岡県福岡市博多区井相田3丁目3番5号</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2616,7 +2664,8 @@
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/hikarinomori/
 https://www.u-pohs.co.jp/kagoshima
-https://www.u-pohs.co.jp/kumamotominami</t>
+https://www.u-pohs.co.jp/kumamotominami
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -2626,7 +2675,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9290001043548、〒812-0881）。</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2701,11 @@
           <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>長野県飯田市鼎東鼎94番地5</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2667,7 +2720,8 @@
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0031/
 https://www.applenet.co.jp/shop/0033/
-https://www.applenet.co.jp/shop/0042/</t>
+https://www.applenet.co.jp/shop/0042/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -2677,7 +2731,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1100002037120、〒395-0817）。</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2830,11 @@
           <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>茨城県ひたちなか市大字中根896番地2</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2789,7 +2847,8 @@
       <c r="P35" s="2" t="inlineStr">
         <is>
           <t>検索結果の抜粋（日立市・東海村・那珂市・水戸市・つくば市・牛久市・守谷市・龍ヶ崎市に店舗を構えるとの案内）
-https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-</t>
+https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -2799,7 +2858,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。</t>
+          <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3050001004686、〒312-0011）。</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3144,11 @@
           <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>愛知県豊明市三崎町中ノ坪13番地12</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
@@ -3100,7 +3163,8 @@
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0004/
 https://www.applenet.co.jp/shop/0007/
-https://www.applenet.co.jp/shop/0046/</t>
+https://www.applenet.co.jp/shop/0046/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -3110,7 +3174,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001069581、〒470-1125）。</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3330,11 @@
           <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>北海道札幌市北区篠路二条9丁目1番48号</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3281,7 +3349,8 @@
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0246/
 https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/</t>
+https://www.applenet.co.jp/shop/0281/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -3291,7 +3360,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9430001034177、〒002-8022）。</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3487,11 @@
           <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県加古川市平岡町高畑88番地の1</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
@@ -3450,7 +3523,8 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company</t>
+          <t>https://www.apple-car.jp/company
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -3460,7 +3534,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5140001093768、〒675-0103）。</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3560,11 @@
           <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>愛知県名古屋市天白区島田2丁目901番地</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3501,7 +3579,8 @@
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0001/
 https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/</t>
+https://www.applenet.co.jp/shop/0040/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -3511,7 +3590,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001023209、〒468-0056）。</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3616,11 @@
           <t>コバックカーズ岐阜店、コバックカーズ岐南店、コバックカーズ軽アウトレット多治見、コバックカーズ春日井東野店、コバックカーズ春日井坂下店、コバックカーズ四日市インター店</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>愛知県豊田市梅坪町10丁目5番地3</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3551,7 +3634,8 @@
         <is>
           <t>https://car.motor-fan.jp/ucar/shop/0208435
 https://car.motor-fan.jp/ucar/shop/0203980
-https://car.motor-fan.jp/ucar/shop/0208367</t>
+https://car.motor-fan.jp/ucar/shop/0208367
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -3561,7 +3645,7 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイト・求人情報の店舗名から6店舗。店舗紹介に「グループ総在庫1500台」「系列店は愛知・岐阜・三重・静岡」とあり静岡の店舗名は不明。運営会社名は求人情報の「株式会社コバックインターナショナル コバックカーズ岐南店」の表記による（全店が同社運営かは未確認）。車検のコバック（FC本部グループ）との関係も未確認。</t>
+          <t>公式サイト未確認。中古車情報サイト・求人情報の店舗名から6店舗。店舗紹介に「グループ総在庫1500台」「系列店は愛知・岐阜・三重・静岡」とあり静岡の店舗名は不明。運営会社名は求人情報の「株式会社コバックインターナショナル コバックカーズ岐南店」の表記による（全店が同社運営かは未確認）。車検のコバック（FC本部グループ）との関係も未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001062751、〒471-0064）。</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3671,11 @@
           <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県大和市福田7丁目39番地13</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3604,7 +3692,8 @@
       <c r="P49" s="2" t="inlineStr">
         <is>
           <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
-https://www.applenet.co.jp/shop/</t>
+https://www.applenet.co.jp/shop/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -3614,7 +3703,7 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。</t>
+          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1021001025628、〒242-0024）。</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3798,11 @@
           <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県三養基郡みやき町大字原古賀字六本松1902番地2</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3721,7 +3814,8 @@
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -3731,7 +3825,7 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6300001009252、〒849-0101）。</t>
         </is>
       </c>
     </row>
@@ -4053,8 +4147,16 @@
           <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>0297-47-9588</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0297-47-9577</t>
+        </is>
+      </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
           <t>代表取締役 大内康弘</t>
@@ -4090,7 +4192,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。</t>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。 電話・FAXは本社と同住所の守谷店（Yacco本店）のもの。</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4501,11 @@
           <t>5-STAR 越谷店、5-STAR 春日部店、5-STAR 三郷店、5-STAR 土浦店、5-STAR 阿見店</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県越谷市大間野町3丁目146番地</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
@@ -4413,7 +4519,8 @@
         <is>
           <t>https://employment.en-japan.com/comp-66249/
 https://car.motor-fan.jp/ucar/shop/3000451
-https://compalyze.co.jp/company/2030001068305</t>
+https://compalyze.co.jp/company/2030001068305
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -4423,7 +4530,7 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。求人情報に「埼玉県・茨城県の5-STAR各店舗（越谷・春日部・三郷・土浦）」、中古車情報サイトに阿見店。ランキング記事では「埼玉県中心に6店舗」。越谷店は越谷市大間野町3-146。</t>
+          <t>公式サイト未確認。求人情報に「埼玉県・茨城県の5-STAR各店舗（越谷・春日部・三郷・土浦）」、中古車情報サイトに阿見店。ランキング記事では「埼玉県中心に6店舗」。越谷店は越谷市大間野町3-146。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9030001065279、〒343-0844）。</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4777,11 @@
           <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県川崎市高津区二子6丁目14番10号</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4685,7 +4796,8 @@
           <t>https://www.u-pohs.co.jp/search_shop
 https://www.u-pohs.co.jp/kouhoku
 https://www.u-pohs.co.jp/shonanhiratsuka
-https://www.u-pohs.co.jp/tsuzuki</t>
+https://www.u-pohs.co.jp/tsuzuki
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -4695,7 +4807,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6020001091254、〒213-0002）。</t>
         </is>
       </c>
     </row>
@@ -4970,7 +5082,11 @@
           <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>東京都大田区平和島5丁目2番28号</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
@@ -4984,7 +5100,8 @@
         <is>
           <t>https://www.applenet.co.jp/shop/0282/
 https://www.applenet.co.jp/shop/0290/
-https://www.applenet.co.jp/shop/0291/</t>
+https://www.applenet.co.jp/shop/0291/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -4994,7 +5111,7 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7010801005652、〒143-0006）。</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5215,11 @@
           <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>広島県廿日市市下平良365番地1</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
@@ -5112,7 +5233,8 @@
         <is>
           <t>https://www.applenet.co.jp/shop/0289/
 https://www.applenet.co.jp/shop/0296/
-https://www.applenet.co.jp/shop/0308/</t>
+https://www.applenet.co.jp/shop/0308/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -5122,7 +5244,7 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3240001051809、〒738-0023）。</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5422,11 @@
           <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>栃木県宇都宮市石井町3335番地55</t>
+        </is>
+      </c>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
@@ -5314,7 +5440,8 @@
         <is>
           <t>https://www.applenet.co.jp/shop/0138/
 https://www.applenet.co.jp/shop/0141/
-https://www.applenet.co.jp/shop/0143/</t>
+https://www.applenet.co.jp/shop/0143/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -5324,7 +5451,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7060001001092、〒321-0912）。</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5477,11 @@
           <t>（有）オートフィールドストリーク</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県厚木市関口236番地14</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
@@ -5363,7 +5494,8 @@
       <c r="P77" s="2" t="inlineStr">
         <is>
           <t>https://car.motor-fan.jp/ucar/shop/0510254
-https://biz-maps.com/s/cities/142123/m-inds/378</t>
+https://biz-maps.com/s/cities/142123/m-inds/378
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -5373,7 +5505,7 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。</t>
+          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2021001024521、〒243-0804）。</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5531,11 @@
           <t>札幌店、札幌東店、北広島店、苫小牧店</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>北海道苫小牧市沼ノ端中央1丁目14番16号</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
@@ -5427,7 +5563,8 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>https://kereta.jp/</t>
+          <t>https://kereta.jp/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -5437,7 +5574,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。</t>
+          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8430001055026、〒059-1305）。</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5600,11 @@
           <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県所沢市大字坂之下17番地1号</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
@@ -5479,7 +5620,8 @@
       <c r="O79" s="2" t="inlineStr"/>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>https://pa-cars.com/shopinfo.html</t>
+          <t>https://pa-cars.com/shopinfo.html
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -5489,7 +5631,7 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。</t>
+          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1030001025439、〒359-0012）。</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5657,11 @@
           <t>軽プラザサンライズ 青森本店、軽プラザサンライズ 弘前本店、軽プラザサンライズ 八戸本店、新車市場 サンライズ青森東バイパス店</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>青森県青森市大字平新田字池上56番地1</t>
+        </is>
+      </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
@@ -5529,7 +5675,8 @@
         <is>
           <t>https://carbell.jp/partner/search?area_code=10
 https://car.motor-fan.jp/ucar/shop/0904135
-https://www.kurumaerabi.com/shop/detail/40016907/</t>
+https://www.kurumaerabi.com/shop/detail/40016907/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -5539,7 +5686,7 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。軽未使用車専門店。中古車情報サイトの店舗紹介に青森・弘前・八戸の各店と「グループ総在庫800台」。新車市場の加盟店一覧に「新車市場 サンライズ青森東バイパス店 株式会社サンライズモータース」。青森本店は青森市第二問屋町2丁目5-13（車検のコバック併設）、八戸本店は八戸市城下3-8-6。</t>
+          <t>公式サイト未確認。軽未使用車専門店。中古車情報サイトの店舗紹介に青森・弘前・八戸の各店と「グループ総在庫800台」。新車市場の加盟店一覧に「新車市場 サンライズ青森東バイパス店 株式会社サンライズモータース」。青森本店は青森市第二問屋町2丁目5-13（車検のコバック併設）、八戸本店は八戸市城下3-8-6。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6420001004869、〒030-0931）。</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5712,11 @@
           <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>岡山県倉敷市加須山334番地の4</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
@@ -5581,7 +5732,8 @@
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/</t>
+          <t>https://www.applenet.co.jp/shop/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -5591,7 +5743,7 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。</t>
+          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1260001014484、〒710-0026）。</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5769,11 @@
           <t>販売店（千葉市内4店舗）</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>千葉県千葉市花見川区三角町525番地</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
@@ -5629,7 +5785,8 @@
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）</t>
+          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -5639,7 +5796,7 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。</t>
+          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号4040001042513、〒262-0011）。</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5822,11 @@
           <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>奈良県葛城市北花内703番地4</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
@@ -5679,7 +5840,8 @@
         <is>
           <t>https://www.u-pohs.co.jp/kashiba/
 https://www.u-pohs.co.jp/kashihara/
-https://www.u-pohs.co.jp/katuragi/</t>
+https://www.u-pohs.co.jp/katuragi/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -5689,7 +5851,7 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5150001014995、〒639-2113）。</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5946,11 @@
           <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県川越市大字府川23番地4</t>
+        </is>
+      </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
@@ -5796,7 +5962,8 @@
       <c r="O85" s="2" t="inlineStr"/>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）</t>
+          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -5806,7 +5973,7 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。</t>
+          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3030001056861、〒350-0831）。</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5999,11 @@
           <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>沖縄県沖縄市字登川2791番地1</t>
+        </is>
+      </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
@@ -5846,7 +6017,8 @@
         <is>
           <t>https://www.u-pohs.co.jp/misato/
 https://www.u-pohs.co.jp/naha-shintoshin
-https://www.u-pohs.co.jp/noborikawa/</t>
+https://www.u-pohs.co.jp/noborikawa/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -5856,7 +6028,7 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3360001016221、〒904-2142）。</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6209,11 @@
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>052-901-8008</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
@@ -6062,7 +6238,7 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店。</t>
+          <t>自社ローン専門店。 電話は名古屋本店のもの。</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6312,11 @@
           <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市中央区南船場2丁目4番23号</t>
+        </is>
+      </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
@@ -6148,7 +6328,8 @@
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）</t>
+          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -6158,7 +6339,7 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>アビックスコーポレーションのグループ会社とみられる。</t>
+          <t>アビックスコーポレーションのグループ会社とみられる。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7120001231212、〒542-0081）。</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6849,11 @@
           <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>愛知県東海市富木島町内堀17番地の1</t>
+        </is>
+      </c>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
@@ -6682,7 +6867,8 @@
         <is>
           <t>https://www.applenet.co.jp/shop/0076/
 https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/</t>
+https://www.applenet.co.jp/shop/0105/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -6692,7 +6878,7 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8180002087515、〒476-0011）。</t>
         </is>
       </c>
     </row>
@@ -6990,7 +7176,11 @@
           <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>千葉県我孫子市柴崎1554番地</t>
+        </is>
+      </c>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
@@ -7004,7 +7194,8 @@
         <is>
           <t>https://www.applenet.co.jp/shop/0187/
 https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/</t>
+https://www.applenet.co.jp/shop/0217/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -7014,7 +7205,7 @@
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3040001085422、〒270-1177）。</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7231,11 @@
           <t>アラジン二又瀬店、アラジン小倉南店、アラジン飯塚店</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>福岡県福岡市西区小戸3丁目54番39号</t>
+        </is>
+      </c>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
@@ -7052,7 +7247,8 @@
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>https://autoc-one.jp/ullo/shop/3142/（検索結果の抜粋）</t>
+          <t>https://autoc-one.jp/ullo/shop/3142/（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -7062,7 +7258,7 @@
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>車買取りネットワーク「アラジン」の運営会社の一つ。アラジンは九州中心に複数の運営会社がある（久留米南店は株式会社Alive）。他店舗の運営会社は未確認。</t>
+          <t>車買取りネットワーク「アラジン」の運営会社の一つ。アラジンは九州中心に複数の運営会社がある（久留米南店は株式会社Alive）。他店舗の運営会社は未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1290001023128、〒819-0001）。</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7334,11 @@
           <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字市浜807番地の1</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr"/>
@@ -7152,7 +7352,8 @@
         <is>
           <t>https://www.applenet.co.jp/shop/0099/
 https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/</t>
+https://www.applenet.co.jp/shop/0218/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -7162,7 +7363,7 @@
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2320202000383、〒875-0052）。</t>
         </is>
       </c>
     </row>
@@ -7284,8 +7485,16 @@
           <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>宮城県石巻市中浦1丁目2番27号</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>0120-058-012</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr">
@@ -7300,7 +7509,8 @@
       <c r="O113" s="2" t="inlineStr"/>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）</t>
+          <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -7308,7 +7518,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R113" s="2" t="inlineStr"/>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>電話はサイト記載のフリーダイヤル（本社番号かは未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6370301000037、〒986-0847）。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7321,7 +7535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7794,13 +8008,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -7810,17 +8024,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -7830,7 +8044,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -7840,117 +8054,117 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>富山県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>富山県</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -7960,7 +8174,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -7970,150 +8184,220 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3</v>
+      </c>
+    </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>店舗数の分布</t>
-        </is>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3〜4店舗</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5〜9店舗</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10〜19店舗</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20〜30店舗</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="78"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>店舗数の分布</t>
+        </is>
+      </c>
+    </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>確度別の社数</t>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>確度</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
+          <t>3〜4店舗</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>5〜9店舗</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>10〜19店舗</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20〜30店舗</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>確度別の社数</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>確度</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B89" t="n">
         <v>63</v>
       </c>
     </row>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R113"/>
+  <dimension ref="A1:R120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ティーバイティーガレージ（TxTGARAGE、運営会社未確認）</t>
+          <t>クルマテラス株式会社</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2316,37 +2316,61 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>岩手県、千葉県、東京都、静岡県、岡山県、福岡県</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>北海道内8店舗、奥州店</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
+          <t>福岡支店（大野城市）、福岡南支店（柳川市）、岡山支店（倉敷市）、千葉支店（木更津市）、千葉東支店（茂原市）、四街道支店、岩手支店（盛岡市）、八王子支店、静岡支店</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>東京都港区愛宕二丁目5番1号 愛宕グリーンヒルズMORIタワー20階</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>03-6434-9295</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>03-6434-9296</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>https://kuruma-terrace.com/</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>中古車買取あり（事業内容）</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>110名</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事・求人）</t>
+          <t>https://kuruma-terrace.com/company/</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>比較記事の「道内8店舗」と、岩手県奥州市の店舗の求人による（奥州店は岩手県）。公式の店舗一覧・運営会社は未確認。</t>
+          <t>【要判断】信用回復ローン（提携信販会社ローンの取次）が主力で、自動車販売・中古車買取も行う。拠点数は会社概要の支店一覧9（実店舗かどうかは支店ごとに未確認）。</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2380,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>株式会社サークルエム</t>
+          <t>ティーバイティーガレージ（TxTGARAGE、運営会社未確認）</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2364,31 +2388,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県、東京都、神奈川県、愛知県、福岡県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>カートルズ越谷店、カートルズ鶴ヶ島店、カートルズ草加店、カートルズ青梅インター店、カートルズ相模原店、カートルズ千葉店、カートルズ岡崎店、カートルズ名古屋店、カートルズ北九州店</t>
+          <t>北海道内8店舗、奥州店</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>048-970-2444</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>048-970-2455</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>https://1190.jp/</t>
-        </is>
-      </c>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
@@ -2396,8 +2408,7 @@
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://1190.jp/shop/
-求人情報（検索結果の抜粋：カートルズ草加店【株式会社サークルエム】）</t>
+          <t>検索結果の抜粋（比較記事・求人）</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -2407,7 +2418,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店「カートルズ」。公式サイトの店舗一覧で販売店9店舗（ほかに整備工場とBlackbunny）。求人では「直営13店舗」とも。運営会社名は草加店の求人表記によるもので、全店が同じ法人かは未確認。</t>
+          <t>比較記事の「道内8店舗」と、岩手県奥州市の店舗の求人による（奥州店は岩手県）。公式の店舗一覧・運営会社は未確認。</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2428,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>株式会社シースペース</t>
+          <t>株式会社カーサービス山形</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2425,201 +2436,201 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>京都府、大阪府、兵庫県</t>
+          <t>山形県</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
+          <t>山形本店、山形嶋店、アップル山形西バイパス店、山形南店（K-Field）、天童店（CASA DOLCE）、NCF、酒田店（庄内ワンダーランド）、鶴岡店、軽CARリース イオンモール三川店</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>大阪府柏原市国分市場2丁目13番1号</t>
+          <t>山形県山形市上山家町字下宿766-6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>072-978-1263</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>072-978-1283</t>
-        </is>
-      </c>
+          <t>023-631-3711</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>代表取締役社長 平松宗彦</t>
+          <t>小川 大輔</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-space.co.jp/</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.c-space.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://www.cs-yamagata.co.jp/</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>https://twitter.com/C_SPACE_U_POHS</t>
-        </is>
-      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>ユーポス事業（車買取）</t>
+          <t>買取あり（アップル加盟店を運営）</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cs-yamagata.co.jp/company
+https://www.applenet.co.jp/shop/0283/</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>山形県内9店舗（会社案内の店舗一覧）。うちアップル山形西バイパス店はアップルFC加盟店。NCFの業態は未確認。新車販売も行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>株式会社サークルエム</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県、千葉県、東京都、神奈川県、愛知県、福岡県</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>カートルズ越谷店、カートルズ鶴ヶ島店、カートルズ草加店、カートルズ青梅インター店、カートルズ相模原店、カートルズ千葉店、カートルズ岡崎店、カートルズ名古屋店、カートルズ北九州店</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>048-970-2444</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>048-970-2455</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>https://1190.jp/</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>https://1190.jp/shop/
+求人情報（検索結果の抜粋：カートルズ草加店【株式会社サークルエム】）</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>自社ローン専門店「カートルズ」。公式サイトの店舗一覧で販売店9店舗（ほかに整備工場とBlackbunny）。求人では「直営13店舗」とも。運営会社名は草加店の求人表記によるもので、全店が同じ法人かは未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>株式会社シースペース</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>京都府、大阪府、兵庫県</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス25号柏原店、ユーポス25号八尾店、ユーポス和泉中央店、ユーポス310号河内長野店、ユーポス仁和寺店、ユーポス内環豊中店、ユーポス171尼崎店、ユーポス久御山店、本社（C-SPACE. 中古車販売）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>大阪府柏原市国分市場2丁目13番1号</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1263</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>072-978-1283</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 平松宗彦</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.c-space.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/C_SPACE_U_POHS</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス事業（車買取）</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>https://www.c-space.co.jp/company/
 https://www.c-space.co.jp/shop/
 https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>会社概要に「ユーポス（関西にて現在8店舗）」とある。ユーポス本部のサイトでシースペース運営と表示されるのは7店舗で、久御山店は表示されていない。本社のC-SPACE.（中古車販売）を1店舗として数え、合計9店舗。ほかにニコニコレンタカー5店舗とコバック1店舗（いずれも対象外）を運営。X(Twitter)のURLは検索結果から取得。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ジーアフター</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>宮城県、栃木県、埼玉県、千葉県、新潟県、岡山県</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>MEGA仙台新港店、MEGA佐野厄除大師店、MEGA越谷レイクタウン店、MEGA千葉北インター店、G-BORDER千葉北インター店、成田店、木更津店、MEGA新潟店、MEGA東岡山店</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>東京都中央区日本橋2-12-6 高島屋THビル北館4階</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 西川佳吾</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.g-after.co.jp/</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>車買取専門店（主業）</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>210名（2023年6月期実績）</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.g-after.co.jp/company
-https://www.g-after.co.jp/shop/</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>車買取専門店ジーアフター（MEGA店など）。店舗数は公式サイトの店舗一覧9件。都道府県は店舗名から判断。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>株式会社リトラス</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 津田猛</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.retrus.co.jp/</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.retrus.co.jp/about/office.asp
-https://www.retrus.co.jp/about/</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2640,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>株式会社九州ユーポス</t>
+          <t>株式会社ジーアフター</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2637,35 +2648,48 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
+          <t>宮城県、栃木県、埼玉県、千葉県、新潟県、岡山県</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
+          <t>MEGA仙台新港店、MEGA佐野厄除大師店、MEGA越谷レイクタウン店、MEGA千葉北インター店、G-BORDER千葉北インター店、成田店、木更津店、MEGA新潟店、MEGA東岡山店</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>福岡県福岡市博多区井相田3丁目3番5号</t>
+          <t>東京都中央区日本橋2-12-6 高島屋THビル北館4階</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 西川佳吾</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.g-after.co.jp/</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>車買取専門店（主業）</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>210名（2023年6月期実績）</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/hikarinomori/
-https://www.u-pohs.co.jp/kagoshima
-https://www.u-pohs.co.jp/kumamotominami
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.g-after.co.jp/company
+https://www.g-after.co.jp/shop/</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -2675,7 +2699,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9290001043548、〒812-0881）。</t>
+          <t>車買取専門店ジーアフター（MEGA店など）。店舗数は公式サイトの店舗一覧9件。都道府県は店舗名から判断。</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2709,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>株式会社原ホンダ</t>
+          <t>株式会社リトラス</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2693,23 +2717,31 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>北海道、群馬県、埼玉県、福井県、愛知県、福岡県、熊本県、沖縄県</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
+          <t>北海道支店、東北支店、福井支店、埼玉支店、群馬支店、名古屋支店、福岡支店、熊本支店、沖縄支店</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>長野県飯田市鼎東鼎94番地5</t>
+          <t>東京都港区高輪2-18-10 高輪泉岳寺駅前ビル11F</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 津田猛</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.retrus.co.jp/</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
@@ -2717,21 +2749,18 @@
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0031/
-https://www.applenet.co.jp/shop/0033/
-https://www.applenet.co.jp/shop/0042/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.retrus.co.jp/about/office.asp
+https://www.retrus.co.jp/about/</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1100002037120、〒395-0817）。</t>
+          <t>中古トラック販売。「グループ全国9拠点」の表記で、業務提携の企業が集まって設立した経緯がある。沿革によると一部の支店は旧別法人（群馬・千葉・熊本）がリトラスの支店になったもの。全支店が同じ法人かどうかは未確認。東北支店の所在県は未確認。</t>
         </is>
       </c>
     </row>
@@ -2741,60 +2770,43 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>株式会社TRUCK-ONE</t>
+          <t>株式会社九州ユーポス</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
+          <t>山口県、福岡県、佐賀県、長崎県、熊本県、大分県、鹿児島県</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
+          <t>ユーポス光の森、ユーポス鹿児島、ユーポス熊本南、ユーポス大分、ユーポス大村、ユーポス折尾、ユーポス佐賀、ユーポス時津、ユーポス山口</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>山口県下松市生野屋南3-3-40</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-1100</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0833-44-5660</t>
-        </is>
-      </c>
+          <t>福岡県福岡市博多区井相田3丁目3番5号</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.truck-one.com/</t>
-        </is>
-      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/truckone_official/</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>買取専用窓口あり（0120-751-519）</t>
-        </is>
-      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-one.com/officelist/
-https://www.truck-one.com/company/</t>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/hikarinomori/
+https://www.u-pohs.co.jp/kagoshima
+https://www.u-pohs.co.jp/kumamotominami
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -2804,7 +2816,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。九州各店のページに系列店として13店舗前後が並ぶが、本部の店舗一覧で運営会社を確認できたのは9店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9290001043548、〒812-0881）。</t>
         </is>
       </c>
     </row>
@@ -2814,25 +2826,25 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>株式会社ジャンプジャパン</t>
+          <t>株式会社原ホンダ</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
+          <t>アップル塩尻北インター店、アップル諏訪インター店、アップル飯田バイパス店、アップル箕輪バイパス店、アップル松本店、アップル上田18号店、アップル長野南店、アップル駒ヶ根店、アップル須坂店</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>茨城県ひたちなか市大字中根896番地2</t>
+          <t>長野県飯田市鼎東鼎94番地5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -2846,145 +2858,148 @@
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0031/
+https://www.applenet.co.jp/shop/0033/
+https://www.applenet.co.jp/shop/0042/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。創業1918年。四輪・二輪の販売・整備を行う長野の会社で、ホンダ販売店の可能性がある（新車ディーラーなら除外対象）。業態要確認。 参考：店舗の連絡先（アップル塩尻北インター店）〒399-0701 長野県塩尻市広丘吉田785-5 TEL 0263-57-8288 FAX 0263-57-8388。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1100002037120、〒395-0817）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>株式会社TRUCK-ONE</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>千葉県、東京都、愛知県、大阪府、岡山県、山口県、福岡県、沖縄県</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>本社・山口支店、岡山支店、大阪支店、名古屋支店、東京支店、福岡支店、千葉営業所、沖縄営業所</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>山口県下松市生野屋南3-3-40</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-1100</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0833-44-5660</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.truck-one.com/</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/truckone_official/</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>買取専用窓口あり（0120-751-519）</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.truck-one.com/officelist/
+https://www.truck-one.com/company/</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>中古トラックの販売会社。サイトの表記は「全国7拠点」だが、拠点一覧には支店・営業所が8件ある。都道府県はページ上の拠点名から判断しており、支店ごとの住所は一部未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ジャンプジャパン</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>茨城県ひたちなか市大字中根896番地2</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
           <t>検索結果の抜粋（日立市・東海村・那珂市・水戸市・つくば市・牛久市・守谷市・龍ヶ崎市に店舗を構えるとの案内）
 https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3050001004686、〒312-0011）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ハヤシ</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>岡山県、香川県</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>岡山県倉敷市加須山334-4</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>http://www.c-hayashi.com/</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
-https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>株式会社パッション</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>岐阜県、愛知県</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>愛知県春日井市味美町2丁目122番地</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>買取専門店ラビット勝川店を運営</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>217名（2025年12月）</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.1963passion.co.jp/company/outline/
-https://www.1963passion.co.jp/company/access/</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -2994,7 +3009,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>株式会社東和モータース販売</t>
+          <t>株式会社ハヤシ</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -3002,70 +3017,50 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
+          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>東京都杉並区上高井戸1-21-18</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>03-3303-1146</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>03-3302-6600</t>
-        </is>
-      </c>
+          <t>岡山県倉敷市加須山334-4</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>代表取締役社長 稲葉弘幸</t>
+          <t>代表取締役 林和樹</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>https://towa-motors.com/contact.html</t>
-        </is>
-      </c>
+          <t>http://www.c-hayashi.com/</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/towa.motors</t>
-        </is>
-      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+      <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/company.html
-https://towa-motors.com/shop/</t>
+          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
+https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
+          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -3075,50 +3070,62 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ツチヤ自動車株式会社</t>
+          <t>株式会社パッション</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>岐阜県、愛知県</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>千葉県市川市北方町4-1441-8</t>
+          <t>愛知県春日井市味美町2丁目122番地</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>買取専門店ラビット勝川店を運営</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>217名（2025年12月）</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
-https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
+          <t>https://www.1963passion.co.jp/company/outline/
+https://www.1963passion.co.jp/company/access/</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
+          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -3128,43 +3135,68 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>株式会社東和モータース販売</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
+          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>愛知県豊明市三崎町中ノ坪13番地12</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
+          <t>東京都杉並区上高井戸1-21-18</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>03-3303-1146</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>03-3302-6600</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 稲葉弘幸</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>https://towa-motors.com/</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>https://towa-motors.com/contact.html</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/towa.motors</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0004/
-https://www.applenet.co.jp/shop/0007/
-https://www.applenet.co.jp/shop/0046/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://towa-motors.com/company.html
+https://towa-motors.com/shop/</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -3174,7 +3206,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001069581、〒470-1125）。</t>
+          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3216,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヨシダオートサービス</t>
+          <t>ツチヤ自動車株式会社</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -3192,56 +3224,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0301</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>072-246-0302</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>吉田宜史</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/contact/</t>
-        </is>
-      </c>
+          <t>千葉県市川市北方町4-1441-8</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>218名（2025年1月）</t>
-        </is>
-      </c>
+      <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
+          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
+https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -3251,7 +3259,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
+          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
         </is>
       </c>
     </row>
@@ -3261,27 +3269,23 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>ナカジマグループ（運営会社未確認、入間）</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
-        </is>
-      </c>
+          <t>ナカジマ（埼玉県入間市東藤沢4-2-5）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3293,8 +3297,8 @@
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://page.line.me/pgw7767e
+https://car.motor-fan.jp/ucar/shop/0580508</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -3304,7 +3308,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>公式サイト未確認。公式LINEの紹介文に「昭和32年創業、関東圏に7店舗、在庫500台以上」、中古車情報サイトに「グループ関東6店舗」（6か7かは不一致）。確認できた店舗は入間の1店のみ。法人名は未確認。</t>
         </is>
       </c>
     </row>
@@ -3314,25 +3318,25 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>株式会社アップルカーセールス</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>北海道札幌市北区篠路二条9丁目1番48号</t>
+          <t>愛知県豊明市三崎町中ノ坪13番地12</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -3347,9 +3351,9 @@
       <c r="P43" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/
+https://www.applenet.co.jp/shop/0004/
+https://www.applenet.co.jp/shop/0007/
+https://www.applenet.co.jp/shop/0046/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -3360,7 +3364,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9430001034177、〒002-8022）。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001069581、〒470-1125）。</t>
         </is>
       </c>
     </row>
@@ -3370,45 +3374,69 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>松下モータース</t>
+          <t>株式会社トラックオーコク（トラック王国）</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>神奈川県、愛知県、広島県、福岡県</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
+          <t>北関東展示場、神奈川展示場、中部展示場、愛知展示場、関西展示場、広島展示場、福岡展示場</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>東京都渋谷区笹塚1丁目55番7号 マルエスファーストビル</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0120-653-034</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0120-363-526</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>津島 一夫</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.55truck.com/</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>トラック買取あり</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://www.55truck.com/company/</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。</t>
+          <t>中古トラック販売・買取。展示場7か所（北関東・中部・関西は所在県未確認）。電話・FAXはフリーダイヤル。</t>
         </is>
       </c>
     </row>
@@ -3418,40 +3446,64 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>株式会社AOZORA COMPANY</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>東京都、新潟県、大阪府、福岡県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>新潟県新潟市西区黒鳥5243番地1</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
-厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -3461,7 +3513,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3523,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3479,62 +3531,42 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+          <t>浜松市内6店舗</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>兵庫県加古川市平岡町高畑88番地の1</t>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5140001093768、〒675-0103）。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3576,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3552,17 +3584,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>愛知県名古屋市天白区島田2丁目901番地</t>
+          <t>北海道札幌市北区篠路二条9丁目1番48号</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -3577,9 +3609,9 @@
       <c r="P47" s="2" t="inlineStr">
         <is>
           <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -3590,7 +3622,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001023209、〒468-0056）。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9430001034177、〒002-8022）。</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3632,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>株式会社コバックインターナショナル（コバックカーズ）</t>
+          <t>株式会社AOZORA COMPANY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3608,17 +3640,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、愛知県、三重県</t>
+          <t>東京都、新潟県、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>コバックカーズ岐阜店、コバックカーズ岐南店、コバックカーズ軽アウトレット多治見、コバックカーズ春日井東野店、コバックカーズ春日井坂下店、コバックカーズ四日市インター店</t>
+          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>愛知県豊田市梅坪町10丁目5番地3</t>
+          <t>新潟県新潟市西区黒鳥5243番地1</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -3632,10 +3664,8 @@
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0208435
-https://car.motor-fan.jp/ucar/shop/0203980
-https://car.motor-fan.jp/ucar/shop/0208367
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
+厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -3645,7 +3675,7 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイト・求人情報の店舗名から6店舗。店舗紹介に「グループ総在庫1500台」「系列店は愛知・岐阜・三重・静岡」とあり静岡の店舗名は不明。運営会社名は求人情報の「株式会社コバックインターナショナル コバックカーズ岐南店」の表記による（全店が同社運営かは未確認）。車検のコバック（FC本部グループ）との関係も未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001062751、〒471-0064）。</t>
+          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3685,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3663,47 +3693,62 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>神奈川県大和市福田7丁目39番地13</t>
+          <t>兵庫県加古川市平岡町高畑88番地の1</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 石戸宏樹</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://www.tortoise-k-carlife.com/</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>26名</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
-https://www.applenet.co.jp/shop/
+          <t>https://www.apple-car.jp/company
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1021001025628、〒242-0024）。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5140001093768、〒675-0103）。</t>
         </is>
       </c>
     </row>
@@ -3713,7 +3758,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>株式会社ナック（ジャック査定センター）</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3721,48 +3766,35 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>京都府、大阪府、兵庫県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
+          <t>愛知県名古屋市天白区島田2丁目901番地</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>078-685-0066</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 難波克年</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>https://jacnet.jp/</t>
-        </is>
-      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>中古車の査定買取（主業）</t>
-        </is>
-      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>https://jacnet.jp/site/company/?pt=detail
-https://jacnet.jp/site/company/?pt=shop_list</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -3772,7 +3804,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001023209、〒468-0056）。</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3814,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社コバックインターナショナル（コバックカーズ）</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3790,17 +3822,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>岐阜県、愛知県、三重県</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+          <t>コバックカーズ岐阜店、コバックカーズ岐南店、コバックカーズ軽アウトレット多治見、コバックカーズ春日井東野店、コバックカーズ春日井坂下店、コバックカーズ四日市インター店</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>佐賀県三養基郡みやき町大字原古賀字六本松1902番地2</t>
+          <t>愛知県豊田市梅坪町10丁目5番地3</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -3814,7 +3846,9 @@
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）
+          <t>https://car.motor-fan.jp/ucar/shop/0208435
+https://car.motor-fan.jp/ucar/shop/0203980
+https://car.motor-fan.jp/ucar/shop/0208367
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -3825,7 +3859,7 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6300001009252、〒849-0101）。</t>
+          <t>公式サイト未確認。中古車情報サイト・求人情報の店舗名から6店舗。店舗紹介に「グループ総在庫1500台」「系列店は愛知・岐阜・三重・静岡」とあり静岡の店舗名は不明。運営会社名は求人情報の「株式会社コバックインターナショナル コバックカーズ岐南店」の表記による（全店が同社運営かは未確認）。車検のコバック（FC本部グループ）との関係も未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001062751、〒471-0064）。</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3869,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>株式会社メディアトラスト（クルオク）</t>
+          <t>株式会社トータス</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3843,75 +3877,47 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>クルオク 名古屋インター店（本社）、クルオク レスパ岡崎店、クルオク 豊田吉原店、クルオク カーマ21稲沢店、クルオク カインズホーム半田店、クルオク カインズモール蒲郡店</t>
+          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>愛知県名古屋市名東区高針台1-110</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>0564-58-9609</t>
-        </is>
-      </c>
+          <t>神奈川県大和市福田7丁目39番地13</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>鬼頭 宏彰</t>
-        </is>
-      </c>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.9609.biz/</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.9609.biz/contact/</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>info@kuruma094.com</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>https://twitter.com/kuruma094
-https://www.facebook.com/kuruoku/</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>買取あり（事業内容に「国内の中古車の買取り」）</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>正社員4名・パート2名・役員4名（2025年12月現在）</t>
-        </is>
-      </c>
+          <t>https://www.tortoise-k-carlife.com/</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>https://www.9609.biz/company/
-https://www.9609.biz/store/</t>
+          <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
+https://www.applenet.co.jp/shop/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>6拠点のうち5つはショッピングモール・ホームセンターの屋上や駐車場内の常設展示場。従業員は少人数。</t>
+          <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1021001025628、〒242-0024）。</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3927,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユー・パーク</t>
+          <t>株式会社ナック（ジャック査定センター）</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3929,33 +3935,33 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>京都府、大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
+          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9566</t>
-        </is>
-      </c>
+          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>048-798-9590</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+          <t>078-685-0066</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 難波克年</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/</t>
+          <t>https://jacnet.jp/</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
@@ -3963,14 +3969,14 @@
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>買取無料査定あり</t>
+          <t>中古車の査定買取（主業）</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/about-us/
-https://www.u-parknet.com/</t>
+          <t>https://jacnet.jp/site/company/?pt=detail
+https://jacnet.jp/site/company/?pt=shop_list</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -3980,7 +3986,7 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3996,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロペライオ</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3998,45 +4004,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、東京都、愛知県、京都府</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>ロペライオ練馬、ロペライオさいたま、モーターホーム by ロペライオ、東日本買取センター、中部買取センター、西日本買取センター</t>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>東京都世田谷区太子堂4-1-1 キャロットタワー6F</t>
+          <t>佐賀県三養基郡みやき町大字原古賀字六本松1902番地2</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>早水 彰</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>https://loperaio.co.jp/</t>
-        </is>
-      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>買取センター3拠点（東日本・中部・西日本）</t>
-        </is>
-      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>https://loperaio.co.jp/shop_index.html
-https://loperaio.co.jp/shop_head_office.html
-https://loperaio.co.jp/company_index.html</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -4046,7 +4039,7 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>輸入中古車専門店。ショップガイドの住所と店舗名の対応はページの画像代替テキストから推定（買取センターの所在県は住所一覧からの推定）。ほかに本社・セントラルベース・ファクトリーセンター（非販売拠点）、ボランタリーチェーンのロペシティ西宮（うかいや運営）・札幌平岸（三愛自動車工業運営）。健康経営優良法人（大規模法人部門）取得。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6300001009252、〒849-0101）。</t>
         </is>
       </c>
     </row>
@@ -4056,57 +4049,73 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>大久自動車販売株式会社</t>
+          <t>株式会社メディアトラスト（クルオク）</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>ダイキュー飯坂店、ダイキュー郡山店、ダイキュー白河中央インター店、ダイキューいわき店、ダイキュー会津若松店</t>
+          <t>クルオク 名古屋インター店（本社）、クルオク レスパ岡崎店、クルオク 豊田吉原店、クルオク カーマ21稲沢店、クルオク カインズホーム半田店、クルオク カインズモール蒲郡店</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>福島県福島市本内字北古舘9</t>
+          <t>愛知県名古屋市名東区高針台1-110</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>024-542-1221</t>
+          <t>0564-58-9609</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>鬼頭 宏彰</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://www.daiq-car.jp/</t>
+          <t>https://www.9609.biz/</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>https://www.daiq-car.jp/contact</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
+          <t>https://www.9609.biz/contact/</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>info@kuruma094.com</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>https://twitter.com/DaiQ_motors
-https://www.facebook.com/daiq.motors/
-https://www.instagram.com/daiq_motors.official/</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr"/>
-      <c r="O55" s="2" t="inlineStr"/>
+          <t>https://twitter.com/kuruma094
+https://www.facebook.com/kuruoku/</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>買取あり（事業内容に「国内の中古車の買取り」）</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>正社員4名・パート2名・役員4名（2025年12月現在）</t>
+        </is>
+      </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>https://www.daiq-car.jp/</t>
+          <t>https://www.9609.biz/company/
+https://www.9609.biz/store/</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -4116,7 +4125,7 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店ダイキュー。運営会社名は公式サイトの古物営業法に基づく表示による。店舗は公式サイトの5店舗。</t>
+          <t>6拠点のうち5つはショッピングモール・ホームセンターの屋上や駐車場内の常設展示場。従業員は少人数。</t>
         </is>
       </c>
     </row>
@@ -4126,45 +4135,41 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>株式会社CIA</t>
+          <t>株式会社ユー・パーク</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0297-47-9588</t>
+          <t>048-798-9566</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0297-47-9577</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 大内康弘</t>
-        </is>
-      </c>
+          <t>048-798-9590</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/</t>
+          <t>https://www.u-parknet.com/</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
@@ -4172,17 +4177,14 @@
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカー買取（買取センター4か所）</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+          <t>買取無料査定あり</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/company/</t>
+          <t>https://www.u-parknet.com/about-us/
+https://www.u-parknet.com/</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -4192,7 +4194,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。 電話・FAXは本社と同住所の守谷店（Yacco本店）のもの。</t>
+          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4202,409 +4204,400 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
+          <t>株式会社ロペライオ</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県、東京都、愛知県、京都府</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>ロペライオ練馬、ロペライオさいたま、モーターホーム by ロペライオ、東日本買取センター、中部買取センター、西日本買取センター</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>東京都世田谷区太子堂4-1-1 キャロットタワー6F</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>早水 彰</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>https://loperaio.co.jp/</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>買取センター3拠点（東日本・中部・西日本）</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>https://loperaio.co.jp/shop_index.html
+https://loperaio.co.jp/shop_head_office.html
+https://loperaio.co.jp/company_index.html</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>輸入中古車専門店。ショップガイドの住所と店舗名の対応はページの画像代替テキストから推定（買取センターの所在県は住所一覧からの推定）。ほかに本社・セントラルベース・ファクトリーセンター（非販売拠点）、ボランタリーチェーンのロペシティ西宮（うかいや運営）・札幌平岸（三愛自動車工業運営）。健康経営優良法人（大規模法人部門）取得。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>株式会社丸山自動車（ポケットカーズ）</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ポケットカーズ（三条市上須頃）、ポケットカーズ 女池インター店（新潟市中央区女池神明）、ポケットカーズ（長岡市堺町）、ポケットカーズ（新潟市中央区紫竹山）、ポケットカーズ（新潟市西区寺尾）、アップル三条店</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pocketcars.jp/</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pocketcars.jp/shop/
+https://www.pocketcars.jp/shop/
+https://www.applenet.co.jp/shop/0317/
+https://mynavi-agent.jp/corpdetail/40198/</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>軽未使用車専門店。運営会社は、転職サイトの会社紹介「1995年以降は車検のコバック、鈑金のモドーリー、ポケットカーズなどの店舗拡大」と、アップル三条店（運営：株式会社丸山自動車）から判断。ポケットカーズの店舗数は公式サイト店舗一覧の住所5件（店名が取れなかった店舗は所在地で表記）＋アップル1店。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>大久自動車販売株式会社</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>ダイキュー飯坂店、ダイキュー郡山店、ダイキュー白河中央インター店、ダイキューいわき店、ダイキュー会津若松店</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>福島県福島市本内字北古舘9</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>024-542-1221</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daiq-car.jp/</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daiq-car.jp/contact</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/DaiQ_motors
+https://www.facebook.com/daiq.motors/
+https://www.instagram.com/daiq_motors.official/</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daiq-car.jp/</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>軽自動車専門店ダイキュー。運営会社名は公式サイトの古物営業法に基づく表示による。店舗は公式サイトの5店舗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>松下モータース</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ecar.co.jp/</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ecar.co.jp/
+https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。 【2026-10更新】公式サイトに「静岡県内5店舗」とあるため6→5に修正（展示場は本店1拠点）。法人格・会社概要は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>株式会社CIA</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>0297-47-9588</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0297-47-9577</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 大内康弘</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー買取（買取センター4か所）</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/company/</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。 電話・FAXは本社と同住所の守谷店（Yacco本店）のもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>株式会社NIIZAWA</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C62" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>広島県、山口県</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>広島県廿日市市大野原1丁目2-20</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>0829-30-8103</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>0829-30-8104</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/contact/</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keimarket.k
 https://www.facebook.com/share/1AhR49eysR
 https://youtube.com/@keimarket398</t>
         </is>
       </c>
-      <c r="N57" s="2" t="inlineStr"/>
-      <c r="O57" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>95名（パート含む）</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr">
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/company/
 https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr">
+      <c r="Q62" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="R62" s="2" t="inlineStr">
         <is>
           <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>株式会社TSC</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>茨城県、埼玉県、千葉県</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>大久保駅前店、千葉北インター店、蘇我インター店、買取直販 つくば店、北本店</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>千葉県千葉市美浜区中瀬（番地は未確認）</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>買取直販（買取車両を展示販売）</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>https://job.rikunabi.com/job_descriptions/82de25d5815e8620/（検索結果の抜粋。現在は404）</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>公式サイト未確認。求人情報の勤務地一覧から5店舗。本社の美浜区中瀬・蘇我インター店の緑区古市場町が、KiND OUTLETのプライバシーポリシー記載会社（NEXTGATE MOTOR SOLUTIONS、美浜区中瀬）・同千葉コンパクトハイブリッド店（緑区古市場町）と近く、同一グループの可能性あり（未確認）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>株式会社Y's GARAGE</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>京都府、鳥取県、島根県</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>京都府宇治市槇島町三十五38-1</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>0774-25-5557</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 桐畑勇志</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>158名（アルバイト含む、令和8年10月）</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/company/</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ウシジマ（UJグループ・ウシトラ）</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県、東京都、京都府、福岡県</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>八女本社、福岡支店（展示場）、埼玉支店（展示場）、東京営業所、京都支店</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>福岡県八女市室岡377-10</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>0943-24-1126</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0943-24-4812</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>牛島 豊晴</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ushitruck.com/</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック買取あり</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>106名（スタッフ数）</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ushitruck.com/truck/corporate</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック販売・買取。拠点数は販売系の本社・支店・営業所で計上（ほかに部品のウシパーツ、レンタル店）。電話・FAXは会社概要記載のもの（本社の番号かは未確認）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ケーワン（5-STAR）</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>茨城県、埼玉県</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>5-STAR 越谷店、5-STAR 春日部店、5-STAR 三郷店、5-STAR 土浦店、5-STAR 阿見店</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県越谷市大間野町3丁目146番地</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>https://employment.en-japan.com/comp-66249/
-https://car.motor-fan.jp/ucar/shop/3000451
-https://compalyze.co.jp/company/2030001068305
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>公式サイト未確認。求人情報に「埼玉県・茨城県の5-STAR各店舗（越谷・春日部・三郷・土浦）」、中古車情報サイトに阿見店。ランキング記事では「埼玉県中心に6店舗」。越谷店は越谷市大間野町3-146。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9030001065279、〒343-0844）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>株式会社トータルカーサービス（ミニクス）</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>兵庫県、広島県</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>ミニクス 福山店、ミニクス 福山中央店、ミニクス アウトレット店、ミニクス 姫路店、ミニクス 加古川店</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>広島県福山市南手城町1丁目14-7</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>084-973-1147</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>084-973-1148</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>https://minics.jp/</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>https://minics.jp/contact</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/minics_2021/
-https://www.youtube.com/channel/UCtdVZXmW98t3g6RypKRTXzg</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>https://minics.jp/shop
-https://minics.jp/about</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>軽トラ・軽バン専門店。サイトに「ミニクス運営：株式会社トータルカーサービス」。所在地は福山中央店と同じ住所の記載（本社かどうかは未確認）。</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4607,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロイヤルオートサービス</t>
+          <t>株式会社TSC</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4622,57 +4615,35 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>茨城県、埼玉県、千葉県</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+          <t>大久保駅前店、千葉北インター店、蘇我インター店、買取直販 つくば店、北本店</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>長野県松本市村井町南2-1-5</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>0120-107-817</t>
-        </is>
-      </c>
+          <t>千葉県千葉市美浜区中瀬（番地は未確認）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 中田忠章</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>https://carstation.royal-auto.jp/</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>https://carstation.royal-auto.jp/contact/</t>
-        </is>
-      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>https://twitter.com/royal_auto_
-https://www.instagram.com/royal_auto_service/?hl=ja
-https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr"/>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>187名</t>
-        </is>
-      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>買取直販（買取車両を展示販売）</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>https://carstation.royal-auto.jp/company/</t>
+          <t>https://job.rikunabi.com/job_descriptions/82de25d5815e8620/（検索結果の抜粋。現在は404）</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -4682,7 +4653,7 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
+          <t>公式サイト未確認。求人情報の勤務地一覧から5店舗。本社の美浜区中瀬・蘇我インター店の緑区古市場町が、KiND OUTLETのプライバシーポリシー記載会社（NEXTGATE MOTOR SOLUTIONS、美浜区中瀬）・同千葉コンパクトハイブリッド店（緑区古市場町）と近く、同一グループの可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4663,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>株式会社東部オート（東部オートグループ）</t>
+          <t>株式会社Y's GARAGE</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4700,48 +4671,47 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>京都府、鳥取県、島根県</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>高前バイパス店、前橋店、小鳥店、ラビット高前バイパス店、ラビット高崎小鳥店</t>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>群馬県高崎市小八木町1538</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>京都府宇治市槇島町三十五38-1</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>0774-25-5557</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>田口 治</t>
+          <t>代表取締役 桐畑勇志</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.tobu-auto.com/</t>
+          <t>https://k-smile.jp/</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>買取店（ラビット加盟2店舗、買取事業部をLinksより継承）</t>
-        </is>
-      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>81名</t>
+          <t>158名（アルバイト含む、令和8年10月）</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>https://www.tobu-auto.com/about
-https://www.tobu-auto.com/</t>
+          <t>https://k-smile.jp/company/</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -4751,7 +4721,7 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>会社概要の事業所数は10店舗（整備・鈑金拠点等を含むとみられる）。中古車販売3店舗＋ラビット2店舗で計上。グループにBMW正規販売のモトーレン群馬・栃木（別法人）あり。年商59億円（会社概要）。</t>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4731,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>株式会社横浜ユーポス</t>
+          <t>株式会社アールブイランド（RVランド）</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4769,35 +4739,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>栃木県、神奈川県</t>
+          <t>北海道、茨城県、千葉県、佐賀県</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
+          <t>本社（常総市）、RVランド イオンモールつくば店、RVランド コンセプト（流山店）、RVランド 北海道（千歳市）、RVランド 九州 鳥栖展示場</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>神奈川県川崎市高津区二子6丁目14番10号</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
+          <t>茨城県常総市大塚戸町1600-1</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>0297-27-6767</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0297-27-6768</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>阿部 和英</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rvland.co.jp/</t>
+        </is>
+      </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr"/>
-      <c r="O65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>社員67名、パート28名</t>
+        </is>
+      </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/kouhoku
-https://www.u-pohs.co.jp/shonanhiratsuka
-https://www.u-pohs.co.jp/tsuzuki
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.rvland.co.jp/about/gaiyou.php</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -4807,7 +4793,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6020001091254、〒213-0002）。</t>
+          <t>【要判断】キャンピングカー専門（製造・販売、新車・中古車）。会社概要の拠点のうち販売店・展示場を5で計上（ほかに常総市大生郷町・久留米市の拠点あり、業態未確認）。</t>
         </is>
       </c>
     </row>
@@ -4817,54 +4803,73 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>KiND OUTLET（カインドアウトレット）</t>
+          <t>株式会社ウシジマ（UJグループ・ウシトラ）</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>埼玉県、東京都、京都府、福岡県</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>市原店、千葉蘇我インター軽専門店、山武成東店、千葉コンパクトハイブリッド店</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
+          <t>八女本社、福岡支店（展示場）、埼玉支店（展示場）、東京営業所、京都支店</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>福岡県八女市室岡377-10</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>0436-55-9169</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>0943-24-1126</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0943-24-4812</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>牛島 豊晴</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://kindoutlet.jp/</t>
+          <t>https://www.ushitruck.com/</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック買取あり</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>106名（スタッフ数）</t>
+        </is>
+      </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>https://kindoutlet.jp/shop
-https://kindoutlet.jp/privacypolicy</t>
+          <t>https://www.ushitruck.com/truck/corporate</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>千葉県の軽自動車専門店。サイトのプライバシーポリシー記載はNEXTGATE MOTOR SOLUTIONS株式会社（千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F）だが、運営会社かどうかは未確認。電話は市原店。</t>
+          <t>中古トラック販売・買取。拠点数は販売系の本社・支店・営業所で計上（ほかに部品のウシパーツ、レンタル店）。電話・FAXは会社概要記載のもの（本社の番号かは未確認）。</t>
         </is>
       </c>
     </row>
@@ -4874,23 +4879,27 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ニシオ自販</t>
+          <t>株式会社ケーワン（5-STAR）</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>静岡県西部の4店舗</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
+          <t>5-STAR 越谷店、5-STAR 春日部店、5-STAR 三郷店、5-STAR 土浦店、5-STAR 阿見店</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県越谷市大間野町3丁目146番地</t>
+        </is>
+      </c>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
@@ -4902,7 +4911,10 @@
       <c r="O67" s="2" t="inlineStr"/>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋</t>
+          <t>https://employment.en-japan.com/comp-66249/
+https://car.motor-fan.jp/ucar/shop/3000451
+https://compalyze.co.jp/company/2030001068305
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -4912,7 +4924,7 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>「静岡県西部に4店舗展開」との掲載による。店舗名・法人格は未確認。</t>
+          <t>公式サイト未確認。求人情報に「埼玉県・茨城県の5-STAR各店舗（越谷・春日部・三郷・土浦）」、中古車情報サイトに阿見店。ランキング記事では「埼玉県中心に6店舗」。越谷店は越谷市大間野町3-146。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9030001065279、〒343-0844）。</t>
         </is>
       </c>
     </row>
@@ -4922,45 +4934,71 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>プルミエ（軽届出済未使用車専門店、運営会社未確認）</t>
+          <t>株式会社トータルカーサービス（ミニクス）</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>兵庫県、広島県</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>豊田、安城、豊橋、四日市</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
+          <t>ミニクス 福山店、ミニクス 福山中央店、ミニクス アウトレット店、ミニクス 姫路店、ミニクス 加古川店</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>広島県福山市南手城町1丁目14-7</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>084-973-1147</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>084-973-1148</t>
+        </is>
+      </c>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>https://minics.jp/</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>https://minics.jp/contact</t>
+        </is>
+      </c>
       <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/minics_2021/
+https://www.youtube.com/channel/UCtdVZXmW98t3g6RypKRTXzg</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋</t>
+          <t>https://minics.jp/shop
+https://minics.jp/about</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>同じ4店舗（豊橋・岡崎安城・豊田・四日市）で「CAST」の名称の掲載もあり、同一の運営会社の可能性。</t>
+          <t>軽トラ・軽バン専門店。サイトに「ミニクス運営：株式会社トータルカーサービス」。所在地は福山中央店と同じ住所の記載（本社かどうかは未確認）。</t>
         </is>
       </c>
     </row>
@@ -4970,11 +5008,11 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ミスターシャーマン（運営会社未確認）</t>
+          <t>株式会社ロイヤルオートサービス</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
@@ -4983,22 +5021,52 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>長野県内4店舗</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
+          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>長野県松本市村井町南2-1-5</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>0120-107-817</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 中田忠章</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>https://carstation.royal-auto.jp/</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>https://carstation.royal-auto.jp/contact/</t>
+        </is>
+      </c>
       <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/royal_auto_
+https://www.instagram.com/royal_auto_service/?hl=ja
+https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>187名</t>
+        </is>
+      </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事）</t>
+          <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -5008,7 +5076,7 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>車買取。比較記事の「県内4店舗」による。</t>
+          <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
         </is>
       </c>
     </row>
@@ -5018,45 +5086,66 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ムラトミ</t>
+          <t>株式会社東部オート（東部オートグループ）</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>相模原本店、相模原（2店舗目）、海老名店、伊勢原店</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
+          <t>高前バイパス店、前橋店、小鳥店、ラビット高前バイパス店、ラビット高崎小鳥店</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>群馬県高崎市小八木町1538</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>田口 治</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tobu-auto.com/</t>
+        </is>
+      </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>買取店（ラビット加盟2店舗、買取事業部をLinksより継承）</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0530132</t>
+          <t>https://www.tobu-auto.com/about
+https://www.tobu-auto.com/</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイトの店舗紹介に「神奈川県内4店舗（相模原2店、海老名、伊勢原）のロープライスカー専門店」とある。相模原本店は相模原市南区新磯野5-43。運営法人名は未確認。2店舗目の相模原の店名は不明。</t>
+          <t>会社概要の事業所数は10店舗（整備・鈑金拠点等を含むとみられる）。中古車販売3店舗＋ラビット2店舗で計上。グループにBMW正規販売のモトーレン群馬・栃木（別法人）あり。年商59億円（会社概要）。</t>
         </is>
       </c>
     </row>
@@ -5066,25 +5155,25 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>昭和礦油株式会社</t>
+          <t>株式会社横浜ユーポス</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>栃木県、神奈川県</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
+          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>東京都大田区平和島5丁目2番28号</t>
+          <t>神奈川県川崎市高津区二子6丁目14番10号</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -5098,9 +5187,10 @@
       <c r="O71" s="2" t="inlineStr"/>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0282/
-https://www.applenet.co.jp/shop/0290/
-https://www.applenet.co.jp/shop/0291/
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/kouhoku
+https://www.u-pohs.co.jp/shonanhiratsuka
+https://www.u-pohs.co.jp/tsuzuki
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -5111,7 +5201,7 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7010801005652、〒143-0006）。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6020001091254、〒213-0002）。</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5211,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>株式会社GR8（GR8STYLE）</t>
+          <t>KiND OUTLET（カインドアウトレット）</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -5129,67 +5219,46 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>GR8 STYLE 春日井店、名古屋大府店、岡崎店、名古屋港店</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>愛知県春日井市南下原町6丁目2-1</t>
-        </is>
-      </c>
+          <t>市原店、千葉蘇我インター軽専門店、山武成東店、千葉コンパクトハイブリッド店</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>0568-41-8828</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0568-41-8839</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>入谷 篤</t>
-        </is>
-      </c>
+          <t>0436-55-9169</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.gr8style.co.jp/</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gr8style.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://kindoutlet.jp/</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/gr8style/
-https://www.instagram.com/gr8style_japan/</t>
-        </is>
-      </c>
+      <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr"/>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>https://www.gr8style.co.jp/company-profile/
-https://www.gr8style.co.jp/</t>
+          <t>https://kindoutlet.jp/shop
+https://kindoutlet.jp/privacypolicy</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>ハイエース専門店（新車・中古車・カスタム・キャンピング）。</t>
+          <t>千葉県の軽自動車専門店。サイトのプライバシーポリシー記載はNEXTGATE MOTOR SOLUTIONS株式会社（千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F）だが、運営会社かどうかは未確認。電話は市原店。</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5268,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>株式会社MARE</t>
+          <t>ニシオ自販</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -5207,19 +5276,15 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>愛知県、兵庫県、広島県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>広島県廿日市市下平良365番地1</t>
-        </is>
-      </c>
+          <t>静岡県西部の4店舗</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
@@ -5231,20 +5296,17 @@
       <c r="O73" s="2" t="inlineStr"/>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0289/
-https://www.applenet.co.jp/shop/0296/
-https://www.applenet.co.jp/shop/0308/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>検索結果の抜粋</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3240001051809、〒738-0023）。</t>
+          <t>「静岡県西部に4店舗展開」との掲載による。店舗名・法人格は未確認。</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5316,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>株式会社T-SPACE</t>
+          <t>プルミエ（軽届出済未使用車専門店、運営会社未確認）</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -5262,68 +5324,37 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>SPACE ジムニー館、SPACE-ONE、SPACE-SE、SPACE-ZERO</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県春日部市栄町1-431-1</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>048-797-6699</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>048-797-6644</t>
-        </is>
-      </c>
+          <t>豊田、安城、豊橋、四日市</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>https://cardealer-space.com/</t>
-        </is>
-      </c>
+      <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>info@cardealer-space.com</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/space_jimny
-https://www.instagram.com/spaceone661
-https://www.instagram.com/spacese6
-https://www.instagram.com/space.zero.kasukabe/</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>買取査定あり</t>
-        </is>
-      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>https://cardealer-space.com/company/</t>
+          <t>検索結果の抜粋</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>販売店4（春日部市）。ほかに整備（T-SPACE SERVICE）・鈑金（SPACE-Body Lab.）・レンタカー。</t>
+          <t>同じ4店舗（豊橋・岡崎安城・豊田・四日市）で「CAST」の名称の掲載もあり、同一の運営会社の可能性。</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5364,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>株式会社エコノミー湘南（奇跡査定センター）</t>
+          <t>ミスターシャーマン（運営会社未確認）</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5341,52 +5372,27 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>奇跡査定センター 藤沢六会本店、藤沢橋店、横浜都筑店、相模原16号由野台店</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県藤沢市亀井野2480-3</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>0466-80-3443</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>0466-80-3445</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>桑名 伸</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>https://www.satei.net/</t>
-        </is>
-      </c>
+          <t>長野県内4店舗</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>買取専門（買取センター）</t>
-        </is>
-      </c>
+      <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr"/>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>https://www.satei.net/company-profile/
-https://www.satei.net/</t>
+          <t>検索結果の抜粋（比較記事）</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -5396,7 +5402,7 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>車買取専門店。会社概要の沿革に「有限会社エコノミーエンタープライズより営業継承し、株式会社エコノミー湘南を設立」「屋号を奇跡査定センターとし」とあるが、現在の社名欄は確認できず。電話は藤沢六会本店。</t>
+          <t>車買取。比較記事の「県内4店舗」による。</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5412,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>株式会社オリンピア</t>
+          <t>ムラトミ</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5414,19 +5420,15 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>栃木県、群馬県、埼玉県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>栃木県宇都宮市石井町3335番地55</t>
-        </is>
-      </c>
+          <t>相模原本店、相模原（2店舗目）、海老名店、伊勢原店</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
@@ -5438,20 +5440,17 @@
       <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0138/
-https://www.applenet.co.jp/shop/0141/
-https://www.applenet.co.jp/shop/0143/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0530132</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7060001001092、〒321-0912）。</t>
+          <t>公式サイト未確認。中古車情報サイトの店舗紹介に「神奈川県内4店舗（相模原2店、海老名、伊勢原）のロープライスカー専門店」とある。相模原本店は相模原市南区新磯野5-43。運営法人名は未確認。2店舗目の相模原の店名は不明。</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5460,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートスペースアクセル（ASAグループ）</t>
+          <t>昭和礦油株式会社</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5474,12 +5473,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>（有）オートフィールドストリーク</t>
+          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>神奈川県厚木市関口236番地14</t>
+          <t>東京都大田区平和島5丁目2番28号</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
@@ -5493,19 +5492,20 @@
       <c r="O77" s="2" t="inlineStr"/>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0510254
-https://biz-maps.com/s/cities/142123/m-inds/378
+          <t>https://www.applenet.co.jp/shop/0282/
+https://www.applenet.co.jp/shop/0290/
+https://www.applenet.co.jp/shop/0291/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2021001024521、〒243-0804）。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7010801005652、〒143-0006）。</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>株式会社クレタ（北海道軽パーク）</t>
+          <t>株式会社GR8（GR8STYLE）</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5523,58 +5523,67 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>札幌店、札幌東店、北広島店、苫小牧店</t>
+          <t>GR8 STYLE 春日井店、名古屋大府店、岡崎店、名古屋港店</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>北海道苫小牧市沼ノ端中央1丁目14番16号</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
+          <t>愛知県春日井市南下原町6丁目2-1</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>0568-41-8828</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>0568-41-8839</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>入谷 篤</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://kereta.jp/</t>
+          <t>https://www.gr8style.co.jp/</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://kereta.jp/contact/</t>
+          <t>https://www.gr8style.co.jp/contact/</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hokkaido_k_park/
-https://x.com/hokkaido_k_park
-https://www.facebook.com/hokkaidokeipark/
-https://youtube.com/channel/UC2xk0xmuuww2ocTXFsNghcw
-https://www.tiktok.com/@hokkaido_k_park</t>
+          <t>https://www.facebook.com/gr8style/
+https://www.instagram.com/gr8style_japan/</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>https://kereta.jp/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.gr8style.co.jp/company-profile/
+https://www.gr8style.co.jp/</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8430001055026、〒059-1305）。</t>
+          <t>ハイエース専門店（新車・中古車・カスタム・キャンピング）。</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5593,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>株式会社グローバンネット</t>
+          <t>株式会社MARE</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5592,27 +5601,23 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>愛知県、兵庫県、広島県</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
+          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>埼玉県所沢市大字坂之下17番地1号</t>
+          <t>広島県廿日市市下平良365番地1</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>https://pa-cars.com/</t>
-        </is>
-      </c>
+      <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr"/>
@@ -5620,18 +5625,20 @@
       <c r="O79" s="2" t="inlineStr"/>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>https://pa-cars.com/shopinfo.html
+          <t>https://www.applenet.co.jp/shop/0289/
+https://www.applenet.co.jp/shop/0296/
+https://www.applenet.co.jp/shop/0308/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1030001025439、〒359-0012）。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3240001051809、〒738-0023）。</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5648,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>株式会社サンライズモータース（軽プラザサンライズ）</t>
+          <t>株式会社T-SPACE</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5649,44 +5656,68 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>軽プラザサンライズ 青森本店、軽プラザサンライズ 弘前本店、軽プラザサンライズ 八戸本店、新車市場 サンライズ青森東バイパス店</t>
+          <t>SPACE ジムニー館、SPACE-ONE、SPACE-SE、SPACE-ZERO</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>青森県青森市大字平新田字池上56番地1</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
+          <t>埼玉県春日部市栄町1-431-1</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>048-797-6699</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>048-797-6644</t>
+        </is>
+      </c>
       <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>https://cardealer-space.com/</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>info@cardealer-space.com</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/space_jimny
+https://www.instagram.com/spaceone661
+https://www.instagram.com/spacese6
+https://www.instagram.com/space.zero.kasukabe/</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>買取査定あり</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>https://carbell.jp/partner/search?area_code=10
-https://car.motor-fan.jp/ucar/shop/0904135
-https://www.kurumaerabi.com/shop/detail/40016907/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://cardealer-space.com/company/</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。軽未使用車専門店。中古車情報サイトの店舗紹介に青森・弘前・八戸の各店と「グループ総在庫800台」。新車市場の加盟店一覧に「新車市場 サンライズ青森東バイパス店 株式会社サンライズモータース」。青森本店は青森市第二問屋町2丁目5-13（車検のコバック併設）、八戸本店は八戸市城下3-8-6。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6420001004869、〒030-0931）。</t>
+          <t>販売店4（春日部市）。ほかに整備（T-SPACE SERVICE）・鈑金（SPACE-Body Lab.）・レンタカー。</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5727,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>株式会社ダブルツリー</t>
+          <t>株式会社エコノミー湘南（奇跡査定センター）</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5704,46 +5735,62 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
+          <t>奇跡査定センター 藤沢六会本店、藤沢橋店、横浜都筑店、相模原16号由野台店</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>岡山県倉敷市加須山334番地の4</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
+          <t>神奈川県藤沢市亀井野2480-3</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>0466-80-3443</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>0466-80-3445</t>
+        </is>
+      </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr"/>
+          <t>桑名 伸</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.satei.net/</t>
+        </is>
+      </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>買取専門（買取センター）</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.satei.net/company-profile/
+https://www.satei.net/</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1260001014484、〒710-0026）。</t>
+          <t>車買取専門店。会社概要の沿革に「有限会社エコノミーエンタープライズより営業継承し、株式会社エコノミー湘南を設立」「屋号を奇跡査定センターとし」とあるが、現在の社名欄は確認できず。電話は藤沢六会本店。</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5800,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビッグワン</t>
+          <t>株式会社オリンピア</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5761,17 +5808,17 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>栃木県、群馬県、埼玉県</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>販売店（千葉市内4店舗）</t>
+          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>千葉県千葉市花見川区三角町525番地</t>
+          <t>栃木県宇都宮市石井町3335番地55</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
@@ -5785,18 +5832,20 @@
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）
+          <t>https://www.applenet.co.jp/shop/0138/
+https://www.applenet.co.jp/shop/0141/
+https://www.applenet.co.jp/shop/0143/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号4040001042513、〒262-0011）。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7060001001092、〒321-0912）。</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5855,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミナミシマ自動車販売</t>
+          <t>株式会社オートスペースアクセル（ASAグループ）</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5814,17 +5863,17 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
+          <t>（有）オートフィールドストリーク</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>奈良県葛城市北花内703番地4</t>
+          <t>神奈川県厚木市関口236番地14</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
@@ -5838,20 +5887,19 @@
       <c r="O83" s="2" t="inlineStr"/>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kashiba/
-https://www.u-pohs.co.jp/kashihara/
-https://www.u-pohs.co.jp/katuragi/
+          <t>https://car.motor-fan.jp/ucar/shop/0510254
+https://biz-maps.com/s/cities/142123/m-inds/378
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5150001014995、〒639-2113）。</t>
+          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2021001024521、〒243-0804）。</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5909,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>株式会社ライズオート（RiSE AUTO）</t>
+          <t>株式会社クルーズコーポレーション（カーニバル）</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5869,48 +5917,40 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>RiSE 四日市北店、RiSE 四日市南店、ガリバーアウトレット 四日市緑地店、ガリバー 稲沢店</t>
+          <t>カーニバル 久喜インター店、カーニバル 春日部店、カーニバル 岩槻店、カーニバル 上尾店</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>三重県四日市市日永東3-13-5</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>059-329-5553</t>
-        </is>
-      </c>
+          <t>埼玉県久喜市江面1479</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>松村 賢治</t>
+          <t>内田 浩</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://riseauto.jp/</t>
+          <t>https://caniva.jp/</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>買取あり（ガリバー加盟店を運営）</t>
-        </is>
-      </c>
+      <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>https://riseauto.jp/company/
-https://riseauto.jp/</t>
+          <t>https://caniva.jp/company/
+https://caniva.jp/shop/</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -5920,7 +5960,7 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>リョウシンホールディングスグループ。自社ブランドRiSE 2店舗＋ガリバー加盟2店舗。会社概要に「三重県に3店舗と愛知県に1店舗」。</t>
+          <t>新車・未使用車・中古車販売。公式サイトの店舗一覧で4店舗（ほかに春日部サービス工場）。本社は久喜インター店と同じ住所。電話は会社概要に記載なし（店舗へ直接）。</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5970,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>株式会社ワークス</t>
+          <t>株式会社クレタ（北海道軽パーク）</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5938,31 +5978,47 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
+          <t>札幌店、札幌東店、北広島店、苫小牧店</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>埼玉県川越市大字府川23番地4</t>
+          <t>北海道苫小牧市沼ノ端中央1丁目14番16号</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>https://kereta.jp/</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>https://kereta.jp/contact/</t>
+        </is>
+      </c>
       <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hokkaido_k_park/
+https://x.com/hokkaido_k_park
+https://www.facebook.com/hokkaidokeipark/
+https://youtube.com/channel/UC2xk0xmuuww2ocTXFsNghcw
+https://www.tiktok.com/@hokkaido_k_park</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr"/>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）
+          <t>https://kereta.jp/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -5973,7 +6029,7 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3030001056861、〒350-0831）。</t>
+          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8430001055026、〒059-1305）。</t>
         </is>
       </c>
     </row>
@@ -5983,7 +6039,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>株式会社沖縄ユーポス</t>
+          <t>株式会社グローバンネット</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5991,23 +6047,27 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>沖縄県沖縄市字登川2791番地1</t>
+          <t>埼玉県所沢市大字坂之下17番地1号</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>https://pa-cars.com/</t>
+        </is>
+      </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
@@ -6015,20 +6075,18 @@
       <c r="O86" s="2" t="inlineStr"/>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/misato/
-https://www.u-pohs.co.jp/naha-shintoshin
-https://www.u-pohs.co.jp/noborikawa/
+          <t>https://pa-cars.com/shopinfo.html
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3360001016221、〒904-2142）。</t>
+          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1030001025439、〒359-0012）。</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6096,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>株式会社鈴木モータース</t>
+          <t>株式会社サンライズモータース（軽プラザサンライズ）</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -6046,15 +6104,19 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
+          <t>軽プラザサンライズ 青森本店、軽プラザサンライズ 弘前本店、軽プラザサンライズ 八戸本店、新車市場 サンライズ青森東バイパス店</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>青森県青森市大字平新田字池上56番地1</t>
+        </is>
+      </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
@@ -6066,19 +6128,20 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0065/
-https://www.applenet.co.jp/shop/0071/
-https://www.applenet.co.jp/shop/0080/</t>
+          <t>https://carbell.jp/partner/search?area_code=10
+https://car.motor-fan.jp/ucar/shop/0904135
+https://www.kurumaerabi.com/shop/detail/40016907/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>公式サイト未確認。軽未使用車専門店。中古車情報サイトの店舗紹介に青森・弘前・八戸の各店と「グループ総在庫800台」。新車市場の加盟店一覧に「新車市場 サンライズ青森東バイパス店 株式会社サンライズモータース」。青森本店は青森市第二問屋町2丁目5-13（車検のコバック併設）、八戸本店は八戸市城下3-8-6。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6420001004869、〒030-0931）。</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6151,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>買取マウス（運営会社未確認）</t>
+          <t>株式会社ダブルツリー</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -6096,18 +6159,26 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>新潟市内4店舗</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
+          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>岡山県倉敷市加須山334番地の4</t>
+        </is>
+      </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
@@ -6116,17 +6187,18 @@
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事）</t>
+          <t>https://www.applenet.co.jp/shop/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>車買取。比較記事の「新潟市内に4店舗」による。</t>
+          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1260001014484、〒710-0026）。</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6208,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>鈴木自工株式会社（軽ひろば・くるま広場）</t>
+          <t>株式会社ビッグワン</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -6149,22 +6221,18 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>くるま広場 船橋習志野店、軽ひろば 佐倉王子台店、軽ひろば 千葉貝塚店、軽ひろば 千葉おゆみ店</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>047-406-3259</t>
-        </is>
-      </c>
+          <t>販売店（千葉市内4店舗）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>千葉県千葉市花見川区三角町525番地</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>https://kei-hiroba.car-yasui.jp/</t>
-        </is>
-      </c>
+      <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr"/>
@@ -6172,17 +6240,18 @@
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>https://kei-hiroba.car-yasui.jp/</t>
+          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>軽自動車（新車・未使用車・中古車）専門店。サイトに「運営：鈴木自工株式会社」。店舗名はサイトのタイトル・本文から。電話はサイト記載のもの（どの店舗かは未確認）。新車の扱いが中心の可能性あり。</t>
+          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号4040001042513、〒262-0011）。</t>
         </is>
       </c>
     </row>
@@ -6192,35 +6261,31 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Dash（運営会社未確認）</t>
+          <t>株式会社ミナミシマ自動車販売</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>名古屋本店、西三河店、三重鈴鹿店</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>052-901-8008</t>
-        </is>
-      </c>
+          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>奈良県葛城市北花内703番地4</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.car-dash.jp/</t>
-        </is>
-      </c>
+      <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr"/>
@@ -6228,17 +6293,20 @@
       <c r="O90" s="2" t="inlineStr"/>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>https://www.car-dash.jp/</t>
+          <t>https://www.u-pohs.co.jp/kashiba/
+https://www.u-pohs.co.jp/kashihara/
+https://www.u-pohs.co.jp/katuragi/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店。 電話は名古屋本店のもの。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5150001014995、〒639-2113）。</t>
         </is>
       </c>
     </row>
@@ -6248,45 +6316,66 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ZERO MOTORS（運営会社未確認）</t>
+          <t>株式会社ライズオート（RiSE AUTO）</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>埼玉県内3店舗</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+          <t>RiSE 四日市北店、RiSE 四日市南店、ガリバーアウトレット 四日市緑地店、ガリバー 稲沢店</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>三重県四日市市日永東3-13-5</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>059-329-5553</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>松村 賢治</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>https://riseauto.jp/</t>
+        </is>
+      </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>買取あり（ガリバー加盟店を運営）</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr"/>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://riseauto.jp/company/
+https://riseauto.jp/</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>軽自動車・コンパクトカー専門店。「埼玉県3店舗・総在庫700台以上」との掲載による。</t>
+          <t>リョウシンホールディングスグループ。自社ブランドRiSE 2店舗＋ガリバー加盟2店舗。会社概要に「三重県に3店舗と愛知県に1店舗」。</t>
         </is>
       </c>
     </row>
@@ -6296,25 +6385,25 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>アビックス大阪株式会社</t>
+          <t>株式会社ワークス</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
+          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>大阪府大阪市中央区南船場2丁目4番23号</t>
+          <t>埼玉県川越市大字府川23番地4</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
@@ -6328,7 +6417,7 @@
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）
+          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -6339,7 +6428,7 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>アビックスコーポレーションのグループ会社とみられる。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7120001231212、〒542-0081）。</t>
+          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3030001056861、〒350-0831）。</t>
         </is>
       </c>
     </row>
@@ -6349,56 +6438,42 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>カーライフグループ株式会社</t>
+          <t>株式会社沖縄ユーポス</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>TOKYO店、大阪店、福岡店</t>
+          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>福岡県糟屋郡粕屋町戸原西4丁目8-11</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>0120-038-871</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>092-410-5912</t>
-        </is>
-      </c>
+          <t>沖縄県沖縄市字登川2791番地1</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>https://loanok.jp/</t>
-        </is>
-      </c>
+      <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr"/>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>30名</t>
-        </is>
-      </c>
+      <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>https://loanok.jp/shop000.html
-https://loanok.jp/</t>
+          <t>https://www.u-pohs.co.jp/misato/
+https://www.u-pohs.co.jp/naha-shintoshin
+https://www.u-pohs.co.jp/noborikawa/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -6408,7 +6483,7 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門。所在地はサイト記載の住所（本社かどうかは未確認）。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3360001016221、〒904-2142）。</t>
         </is>
       </c>
     </row>
@@ -6418,20 +6493,20 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>トーワオート（運営会社未確認）</t>
+          <t>株式会社鈴木モータース</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>宇都宮西店、宇都宮東店、宇都宮南店</t>
+          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -6446,17 +6521,19 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://www.applenet.co.jp/shop/0065/
+https://www.applenet.co.jp/shop/0071/
+https://www.applenet.co.jp/shop/0080/</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>宇都宮市内の3店舗。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6466,20 +6543,20 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>プチモ軽自動車専門店（株式会社ヒューベストオートの可能性）</t>
+          <t>買取マウス（運営会社未確認）</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>佐賀店、唐津店、佐世保店</t>
+          <t>新潟市内4店舗</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -6494,7 +6571,7 @@
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（求人・店舗掲載）</t>
+          <t>検索結果の抜粋（比較記事）</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -6504,7 +6581,7 @@
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>佐世保店は長崎県（2025年12月開店）。運営会社は佐世保店の求人の募集元による推定。</t>
+          <t>車買取。比較記事の「新潟市内に4店舗」による。</t>
         </is>
       </c>
     </row>
@@ -6514,29 +6591,33 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>ポケットカーズ（運営会社未確認）</t>
+          <t>鈴木自工株式会社（軽ひろば・くるま広場）</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>女池店、三条店、長岡店</t>
+          <t>くるま広場 船橋習志野店、軽ひろば 佐倉王子台店、軽ひろば 千葉貝塚店、軽ひろば 千葉おゆみ店</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>047-406-3259</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/</t>
+          <t>https://kei-hiroba.car-yasui.jp/</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
@@ -6546,17 +6627,17 @@
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>https://www.pocketcars.jp/shop/</t>
+          <t>https://kei-hiroba.car-yasui.jp/</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>軽未使用車専門店。公式の店舗一覧は3店舗（検索結果では4店舗とも）。運営会社名は公式サイトで確認できず（車検のコバックも運営する会社の可能性）。</t>
+          <t>軽自動車（新車・未使用車・中古車）専門店。サイトに「運営：鈴木自工株式会社」。店舗名はサイトのタイトル・本文から。電話はサイト記載のもの（どの店舗かは未確認）。新車の扱いが中心の可能性あり。</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6647,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>古城モータース</t>
+          <t>Dash（運営会社未確認）</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6574,29 +6655,25 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>高岡本店、富山店、石川白山店</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>富山県高岡市二塚425番地</t>
-        </is>
-      </c>
+          <t>名古屋本店、西三河店、三重鈴鹿店</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>0120-540-118</t>
+          <t>052-901-8008</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
@@ -6606,7 +6683,7 @@
       <c r="O97" s="2" t="inlineStr"/>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -6614,7 +6691,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>自社ローン専門店。 電話は名古屋本店のもの。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -6622,7 +6703,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>ZERO MOTORS（運営会社未確認）</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6630,62 +6711,37 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8844</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8845</t>
-        </is>
-      </c>
+          <t>埼玉県内3店舗</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.autogallery.co.jp/</t>
-        </is>
-      </c>
+      <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>inquiry@autogallery.co.jp</t>
-        </is>
-      </c>
+      <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>中古車の買取・下取りあり</t>
-        </is>
-      </c>
+      <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr"/>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>検索結果の抜粋（店舗掲載）</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>輸入車（アメ車等）専門店。サイトの見出しは「東京 神奈川 福岡」で、古物商許可も神奈川県を含むが、店舗情報ページに載っているのは東京・大阪・福岡の3店舗。</t>
+          <t>軽自動車・コンパクトカー専門店。「埼玉県3店舗・総在庫700台以上」との掲載による。</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6751,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>アビックス大阪株式会社</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6703,31 +6759,23 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+          <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
+          <t>大阪府大阪市中央区南船場2丁目4番23号</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.csauto.jp/</t>
-        </is>
-      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr"/>
@@ -6735,18 +6783,18 @@
       <c r="O99" s="2" t="inlineStr"/>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+          <t>アビックスコーポレーションのグループ会社とみられる。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7120001231212、〒542-0081）。</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6804,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>株式会社アクセス（カーライフステーション）</t>
+          <t>エービーエスオート（ABS Auto、運営会社未確認）</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6764,66 +6812,37 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>岩槻インター店、上尾店、久喜店</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県さいたま市見沼区宮ケ谷塔91-1</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>0120-344-713</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>048-681-5088</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>黒木 康男</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>https://344860.net/</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>https://344860.net/contact/</t>
-        </is>
-      </c>
+          <t>藤沢店（藤沢市用田1531-1）、海老名店、綾瀬店</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>158人（2019年度）</t>
-        </is>
-      </c>
+      <c r="O100" s="2" t="inlineStr"/>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>https://344860.net/company/
-https://344860.net/shop/</t>
+          <t>https://www.kurumaerabi.com/shop/detail/29454/</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車・新車専門店。電話はフリーダイヤル（会社概要記載のもの）。</t>
+          <t>中古トラック販売。公式サイト未確認。中古車情報サイトの紹介に「藤沢市用田に1店舗・海老名と綾瀬にも店舗」。</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6852,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>カーライフグループ株式会社</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -6841,34 +6860,48 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
+          <t>TOKYO店、大阪店、福岡店</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>愛知県東海市富木島町内堀17番地の1</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
+          <t>福岡県糟屋郡粕屋町戸原西4丁目8-11</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>0120-038-871</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>092-410-5912</t>
+        </is>
+      </c>
       <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>https://loanok.jp/</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>30名</t>
+        </is>
+      </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://loanok.jp/shop000.html
+https://loanok.jp/</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -6878,7 +6911,7 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8180002087515、〒476-0011）。</t>
+          <t>自社ローン専門。所在地はサイト記載の住所（本社かどうかは未確認）。</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6921,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>トーワオート（運営会社未確認）</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -6896,31 +6929,19 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
-        </is>
-      </c>
+          <t>宇都宮西店、宇都宮東店、宇都宮南店</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 上武英輝</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kamitake.net/</t>
-        </is>
-      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr"/>
@@ -6928,16 +6949,19 @@
       <c r="O102" s="2" t="inlineStr"/>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>検索結果の抜粋（店舗掲載）</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R102" s="2" t="inlineStr"/>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>宇都宮市内の3店舗。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -6945,7 +6969,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>株式会社クイックモーション（カラーズ）</t>
+          <t>プチモ軽自動車専門店（株式会社ヒューベストオートの可能性）</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -6953,12 +6977,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>カラーズKawagoe（川越）、ほか2店舗</t>
+          <t>佐賀店、唐津店、佐世保店</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
@@ -6973,7 +6997,7 @@
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>https://ucar.carview.yahoo.co.jp/shop/saitama/214637003/（検索結果の抜粋）</t>
+          <t>検索結果の抜粋（求人・店舗掲載）</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -6983,7 +7007,7 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>4WD・SUV専門店。「埼玉県を中心に3店舗」との掲載による。</t>
+          <t>佐世保店は長崎県（2025年12月開店）。運営会社は佐世保店の求人の募集元による推定。</t>
         </is>
       </c>
     </row>
@@ -6993,7 +7017,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>株式会社コンチネント</t>
+          <t>古城モータース</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -7001,60 +7025,47 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>岡山本店、カーセブン倉敷中島店、カーセブン岡山妹尾店</t>
+          <t>高岡本店、富山店、石川白山店</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>岡山県岡山市南区妹尾4130-2</t>
+          <t>富山県高岡市二塚425番地</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>086-281-5544</t>
+          <t>0120-540-118</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>平松 裕</t>
-        </is>
-      </c>
+      <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://conti-nent.com/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>買取（カーセブン加盟店）</t>
-        </is>
-      </c>
+      <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr"/>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>https://conti-nent.com/company/
-https://conti-nent.com/shops/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R104" s="2" t="inlineStr">
-        <is>
-          <t>会社概要に「3店舗展開 岡山本店・倉敷中島店・岡山妹尾店」。ほかに鈑金塗装工場あり。カーセブンFC加盟。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -7062,7 +7073,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -7070,29 +7081,52 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr"/>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8845</t>
+        </is>
+      </c>
       <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.autogallery.co.jp/</t>
+        </is>
+      </c>
       <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>inquiry@autogallery.co.jp</t>
+        </is>
+      </c>
       <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>中古車の買取・下取りあり</t>
+        </is>
+      </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -7102,7 +7136,7 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>輸入車（アメ車等）専門店。サイトの見出しは「東京 神奈川 福岡」で、古物商許可も神奈川県を含むが、店舗情報ページに載っているのは東京・大阪・福岡の3店舗。</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7146,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -7120,19 +7154,31 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
+        </is>
+      </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 河野修一</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.csauto.jp/</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr"/>
@@ -7140,7 +7186,8 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -7150,7 +7197,7 @@
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>ユーポス以外の事業は未確認。</t>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7207,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>株式会社アクセス（カーライフステーション）</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -7168,34 +7215,56 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>岩槻インター店、上尾店、久喜店</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>千葉県我孫子市柴崎1554番地</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
+          <t>埼玉県さいたま市見沼区宮ケ谷塔91-1</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>0120-344-713</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>048-681-5088</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>黒木 康男</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>https://344860.net/</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>https://344860.net/contact/</t>
+        </is>
+      </c>
       <c r="L107" s="2" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr"/>
-      <c r="O107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>158人（2019年度）</t>
+        </is>
+      </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://344860.net/company/
+https://344860.net/shop/</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -7205,7 +7274,7 @@
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3040001085422、〒270-1177）。</t>
+          <t>届出済未使用車・新車専門店。電話はフリーダイヤル（会社概要記載のもの）。</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7284,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーリンクス</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -7223,17 +7292,17 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>アラジン二又瀬店、アラジン小倉南店、アラジン飯塚店</t>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>福岡県福岡市西区小戸3丁目54番39号</t>
+          <t>愛知県東海市富木島町内堀17番地の1</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
@@ -7247,18 +7316,20 @@
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>https://autoc-one.jp/ullo/shop/3142/（検索結果の抜粋）
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>車買取りネットワーク「アラジン」の運営会社の一つ。アラジンは九州中心に複数の運営会社がある（久留米南店は株式会社Alive）。他店舗の運営会社は未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1290001023128、〒819-0001）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8180002087515、〒476-0011）。</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7339,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>株式会社カミタケモータース</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -7276,19 +7347,31 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>大阪府、奈良県、大分県</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr"/>
+          <t>枚方本店、奈良店、大分店</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
+        </is>
+      </c>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr"/>
@@ -7296,9 +7379,8 @@
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -7306,11 +7388,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="R109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -7318,7 +7396,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社クイックモーション（カラーズ）</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
@@ -7326,19 +7404,15 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>大分県臼杵市大字市浜807番地の1</t>
-        </is>
-      </c>
+          <t>カラーズKawagoe（川越）、ほか2店舗</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr"/>
@@ -7350,20 +7424,17 @@
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://ucar.carview.yahoo.co.jp/shop/saitama/214637003/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2320202000383、〒875-0052）。</t>
+          <t>4WD・SUV専門店。「埼玉県を中心に3店舗」との掲載による。</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7444,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>良質車専門店ネクスト（運営会社未確認）</t>
+          <t>株式会社コンチネント</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -7381,37 +7452,58 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>会津若松店、いわき店、白河店</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
+          <t>岡山本店、カーセブン倉敷中島店、カーセブン岡山妹尾店</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>岡山県岡山市南区妹尾4130-2</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>086-281-5544</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>平松 裕</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>https://conti-nent.com/</t>
+        </is>
+      </c>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>買取（カーセブン加盟店）</t>
+        </is>
+      </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗の在庫掲載）</t>
+          <t>https://conti-nent.com/company/
+https://conti-nent.com/shops/</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車も扱う中古車店。3市の店舗は検索結果の在庫掲載から確認。運営会社名は未確認。</t>
+          <t>会社概要に「3店舗展開 岡山本店・倉敷中島店・岡山妹尾店」。ほかに鈑金塗装工場あり。カーセブンFC加盟。</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7513,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>軽ステ（運営会社未確認）</t>
+          <t>株式会社シマダオート商事</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -7429,12 +7521,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>熊本県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>けんぐん東店、うと店、しみず店</t>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -7449,17 +7541,19 @@
       <c r="O112" s="2" t="inlineStr"/>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>熊本県最大級の軽届出済未使用車専門店（総在庫1,300台）とのこと。運営会社未確認。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7563,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>阿部勝自動車工業株式会社</t>
+          <t>株式会社フロンティアモータース</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -7477,31 +7571,19 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>宮城県石巻市中浦1丁目2番27号</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>0120-058-012</t>
-        </is>
-      </c>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>https://k-mishiyo.abekatu.co.jp/</t>
-        </is>
-      </c>
+      <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr"/>
       <c r="M113" s="2" t="inlineStr"/>
@@ -7509,16 +7591,385 @@
       <c r="O113" s="2" t="inlineStr"/>
       <c r="P113" s="2" t="inlineStr">
         <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス以外の事業は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ベネフィット</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>千葉県、東京都</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>千葉県我孫子市柴崎1554番地</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3040001085422、〒270-1177）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ユーリンクス</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>アラジン二又瀬店、アラジン小倉南店、アラジン飯塚店</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>福岡県福岡市西区小戸3丁目54番39号</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>https://autoc-one.jp/ullo/shop/3142/（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>車買取りネットワーク「アラジン」の運営会社の一つ。アラジンは九州中心に複数の運営会社がある（久留米南店は株式会社Alive）。他店舗の運営会社は未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1290001023128、〒819-0001）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>株式会社リフトオフ</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>茨城県、千葉県、東京都</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>株式会社中州自動車</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>大分県</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字市浜807番地の1</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr"/>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2320202000383、〒875-0052）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>良質車専門店ネクスト（運営会社未確認）</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>会津若松店、いわき店、白河店</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>検索結果の抜粋（店舗の在庫掲載）</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>届出済未使用車も扱う中古車店。3市の店舗は検索結果の在庫掲載から確認。運営会社名は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>軽ステ（運営会社未確認）</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>熊本県</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>けんぐん東店、うと店、しみず店</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>検索結果の抜粋（店舗掲載）</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>熊本県最大級の軽届出済未使用車専門店（総在庫1,300台）とのこと。運営会社未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>阿部勝自動車工業株式会社</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>宮城県石巻市中浦1丁目2番27号</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>0120-058-012</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>https://k-mishiyo.abekatu.co.jp/</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
           <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q113" s="2" t="inlineStr">
+      <c r="Q120" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R113" s="2" t="inlineStr">
+      <c r="R120" s="2" t="inlineStr">
         <is>
           <t>電話はサイト記載のフリーダイヤル（本社番号かは未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6370301000037、〒986-0847）。</t>
         </is>
@@ -7535,7 +7986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7568,7 +8019,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -7588,7 +8039,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -7604,117 +8055,117 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>山形県</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>富山県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>石川県</t>
+          <t>富山県</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>福井県</t>
+          <t>石川県</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -7724,117 +8175,117 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>福井県</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>鳥取県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>島根県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7844,67 +8295,67 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>徳島県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>香川県</t>
+          <t>徳島県</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>愛媛県</t>
+          <t>香川県</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>高知県</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -7914,117 +8365,117 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>高知県</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>長崎県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>熊本県</t>
+          <t>長崎県</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>熊本県</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>鹿児島県</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>鹿児島県</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>沖縄県</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B45" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>本社所在地の都道府県別の社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>都道府県</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -8034,7 +8485,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -8044,97 +8495,97 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>山形県</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>東京都</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>富山県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -8144,57 +8595,57 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>富山県</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>京都府</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>京都府</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -8204,57 +8655,57 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>山口県</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -8264,17 +8715,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -8284,121 +8735,141 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>大分県</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>沖縄県</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77"/>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="B78" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>店舗数の分布</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>3〜4店舗</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5〜9店舗</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>40</v>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10〜19店舗</t>
+          <t>3〜4店舗</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20〜30店舗</t>
+          <t>5〜9店舗</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>10〜19店舗</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20〜30店舗</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="85"/>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="B86" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>確度別の社数</t>
         </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>確度</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>社数</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>49</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>確度</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>社数</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>63</v>
+      <c r="B91" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R120"/>
+  <dimension ref="A1:R128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>株式会社ジャンプジャパン</t>
+          <t>株式会社シマ商会（グットラックshima）</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2963,19 +2963,15 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>北海道、宮城県、福島県、埼玉県、新潟県、愛知県、大阪府、佐賀県</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>茨城県ひたちなか市大字中根896番地2</t>
-        </is>
-      </c>
+          <t>グットラックshima北海道、グットラックshima宮城、グットラックshima福島、グットラックshima新潟、グットラックshima東京、グットラックshima愛知 中京自動車、グットラックshima大阪、グットラックshima福岡</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2983,23 +2979,25 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（日立市・東海村・那珂市・水戸市・つくば市・牛久市・守谷市・龍ヶ崎市に店舗を構えるとの案内）
-https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3050001004686、〒312-0011）。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：グットラックshima北海道：北海道苫小牧市拓勇東町8丁目7-26（0120-81-9109）、グットラックshima宮城：宮城県名取市堀内字北竹141（0120-81-9109）、グットラックshima福島：福島県福島県南相馬市原町区雫字福田455（0120-81-9109）、グットラックshima新潟：新潟県新潟県新潟市南区茨曽根2031-1（0120-81-9109）、グットラックshima東京：埼玉県久喜市高柳2193-3（0120-81-9109）、グットラックshima愛知 中京自動車：愛知県安城市尾崎町堤下17－2（0566‐93-8070）、グットラックshima大阪：大阪府和泉市和気町1丁目26番1号（0725-40-3155）、グットラックshima福岡：佐賀県三養基郡基山町小倉400-3（0942-85-7567）</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3007,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>株式会社ハヤシ</t>
+          <t>株式会社ジャンプジャパン</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -3017,31 +3015,23 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>茨城県</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
+          <t>日立、東海村、那珂、水戸、つくば、牛久、守谷、龍ヶ崎</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>岡山県倉敷市加須山334-4</t>
+          <t>茨城県ひたちなか市大字中根896番地2</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>http://www.c-hayashi.com/</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
@@ -3049,8 +3039,9 @@
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
-https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
+          <t>検索結果の抜粋（日立市・東海村・那珂市・水戸市・つくば市・牛久市・守谷市・龍ヶ崎市に店舗を構えるとの案内）
+https://map.yahoo.co.jp/v3/place/AraH_Zt_UG-
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -3060,7 +3051,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
+          <t>中古車販売・買取。店舗数は「8市町村に店舗」との案内から1市町村1店舗として数えた（実数は未確認）。ひたちなか店の掲載もある。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3050001004686、〒312-0011）。</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3061,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>株式会社パッション</t>
+          <t>株式会社ハヤシ</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -3078,54 +3069,50 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、愛知県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
+          <t>くるまのハヤシ 倉敷店（本社）、くるまのハヤシ 高松店、くるまのハヤシ 丸亀店、くるまのハヤシ ほか2店舗、エイチプラス 2店舗、フラット7 1店舗</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>愛知県春日井市味美町2丁目122番地</t>
+          <t>岡山県倉敷市加須山334-4</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+          <t>http://www.c-hayashi.com/</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>買取専門店ラビット勝川店を運営</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>217名（2025年12月）</t>
-        </is>
-      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>https://www.1963passion.co.jp/company/outline/
-https://www.1963passion.co.jp/company/access/</t>
+          <t>https://www.r-agent.com/company/86071/（求人情報、検索結果の抜粋）
+https://www.kurumaerabi.com/shop/detail/40023836/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
+          <t>軽自動車専門店「くるまのハヤシ」（1972年設立）。求人情報の内訳「くるまのハヤシ5・エイチプラス2・フラット7 1・車検の速太郎5・板金の速太郎3（計17店舗）」から、販売店8店舗を数えた。公式サイトは接続できず未確認。代表者が同じダブルツリー（アップル加盟店4店舗）はグループ会社とみられる。</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3122,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>株式会社東和モータース販売</t>
+          <t>株式会社パッション</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -3143,60 +3130,44 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
+          <t>岐阜県、愛知県</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
+          <t>パッション 春日井店、パッションプラス 春日井店、パッション 4U（軽39.8万円専門店）、ラビット勝川店（買取）、パッション 南大高店、パッションプラス 南大高店、パッション 豊田店、パッション 土岐店</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>東京都杉並区上高井戸1-21-18</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>03-3303-1146</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>03-3302-6600</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役社長 稲葉弘幸</t>
-        </is>
-      </c>
+          <t>愛知県春日井市味美町2丁目122番地</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>https://towa-motors.com/contact.html</t>
-        </is>
-      </c>
+          <t>https://www.1963passion.co.jp/ / https://kei-passion.com/</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/towa.motors</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>買取専門店ラビット勝川店を運営</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>50名</t>
+          <t>217名（2025年12月）</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://towa-motors.com/company.html
-https://towa-motors.com/shop/</t>
+          <t>https://www.1963passion.co.jp/company/outline/
+https://www.1963passion.co.jp/company/access/</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -3206,7 +3177,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
+          <t>旧社名サンアイ自動車。アクセスページの拠点のうち、販売・買取の店舗だけを数えた（車検の速太郎・パッション車検・板金・保険・コーティングの店は除外）。ラビット勝川店はラビットFCの加盟店。</t>
         </is>
       </c>
     </row>
@@ -3216,50 +3187,78 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ツチヤ自動車株式会社</t>
+          <t>株式会社東和モータース販売</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>北海道、埼玉県、千葉県、東京都、神奈川県</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+          <t>東京本店（杉並）、環八店、入間店、所沢店、本庄店（深谷市）、横浜店（大和市）、千葉店、札幌店</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>千葉県市川市北方町4-1441-8</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
+          <t>東京都杉並区上高井戸1-21-18</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>03-3303-1146</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>03-3302-6600</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役社長 稲葉弘幸</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>https://towa-motors.com/</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>https://towa-motors.com/contact.html</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/towa.motors</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
-https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
+          <t>https://towa-motors.com/company.html
+https://towa-motors.com/shop/</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
+          <t>キャンピングカーの総合ディーラー（新車・中古車・買取・福祉車両）。一般の中古車販売店とは業態が異なる（フジカーズジャパンと同じ扱いで要判断）。店舗数は公式サイトの店舗ページ8件。店舗名はURLと住所から付けた。</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3268,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ナカジマグループ（運営会社未確認、入間）</t>
+          <t>ツチヤ自動車株式会社</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3277,15 +3276,19 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ナカジマ（埼玉県入間市東藤沢4-2-5）</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
+          <t>本社市川、千葉北店、新小岩店&amp;未使用車専門店、茂原店、ほか3店舗（東京・千葉）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>千葉県市川市北方町4-1441-8</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3297,8 +3300,8 @@
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>https://page.line.me/pgw7767e
-https://car.motor-fan.jp/ucar/shop/0580508</t>
+          <t>https://compalyze.co.jp/company/3040001026921（検索結果の抜粋）
+https://car.motor-fan.jp/ucar/shop/0500996（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -3308,7 +3311,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。公式LINEの紹介文に「昭和32年創業、関東圏に7店舗、在庫500台以上」、中古車情報サイトに「グループ関東6店舗」（6か7かは不一致）。確認できた店舗は入間の1店のみ。法人名は未確認。</t>
+          <t>1969年創業の中古車専門会社。店舗数は企業情報サイトの「東京・千葉に7店舗」による（別の掲載では10店舗）。確認できた店舗名は4つ。公式サイト未確認。本社住所は「本社市川」店の住所。</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3321,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルカーセールス</t>
+          <t>ナカジマグループ（運営会社未確認、入間）</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3326,19 +3329,15 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>愛知県豊明市三崎町中ノ坪13番地12</t>
-        </is>
-      </c>
+          <t>ナカジマ（埼玉県入間市東藤沢4-2-5）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3350,6 +3349,59 @@
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
+          <t>https://page.line.me/pgw7767e
+https://car.motor-fan.jp/ucar/shop/0580508</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト未確認。公式LINEの紹介文に「昭和32年創業、関東圏に7店舗、在庫500台以上」、中古車情報サイトに「グループ関東6店舗」（6か7かは不一致）。確認できた店舗は入間の1店のみ。法人名は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>株式会社アップルカーセールス</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>アップル刈谷店、アップル鳴海店、アップル知立インター店、アップル新安城店、アップル法人営業部店、アップル豊田153通店、アップル新野並店</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>愛知県豊明市三崎町中ノ坪13番地12</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
           <t>https://www.applenet.co.jp/shop/
 https://www.applenet.co.jp/shop/0004/
 https://www.applenet.co.jp/shop/0007/
@@ -3357,86 +3409,14 @@
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="inlineStr">
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。本社は愛知県豊明市（検索結果による）。 参考：店舗の連絡先（アップル刈谷店）〒446-0055 愛知県安城市緑町1-16-10 TEL 0566-71-1311 FAX 0566-71-1312。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001069581、〒470-1125）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>株式会社トラックオーコク（トラック王国）</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県、愛知県、広島県、福岡県</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>北関東展示場、神奈川展示場、中部展示場、愛知展示場、関西展示場、広島展示場、福岡展示場</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>東京都渋谷区笹塚1丁目55番7号 マルエスファーストビル</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0120-653-034</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0120-363-526</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>津島 一夫</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.55truck.com/</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>トラック買取あり</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.55truck.com/company/</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック販売・買取。展示場7か所（北関東・中部・関西は所在県未確認）。電話・FAXはフリーダイヤル。</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3426,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>株式会社ヨシダオートサービス</t>
+          <t>株式会社トラックオーコク（トラック王国）</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3454,66 +3434,61 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>神奈川県、愛知県、広島県、福岡県</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
+          <t>北関東展示場、神奈川展示場、中部展示場、愛知展示場、関西展示場、広島展示場、福岡展示場</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+          <t>東京都渋谷区笹塚1丁目55番7号 マルエスファーストビル</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>072-246-0301</t>
+          <t>0120-653-034</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>072-246-0302</t>
+          <t>0120-363-526</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>吉田宜史</t>
+          <t>津島 一夫</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>https://kurumanomori.com/contact/</t>
-        </is>
-      </c>
+          <t>https://www.55truck.com/</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>218名（2025年1月）</t>
-        </is>
-      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>トラック買取あり</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>https://kurumanomori.com/company/
-https://keinomori.com/（検索結果の抜粋）</t>
+          <t>https://www.55truck.com/company/</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
+          <t>中古トラック販売・買取。展示場7か所（北関東・中部・関西は所在県未確認）。電話・FAXはフリーダイヤル。</t>
         </is>
       </c>
     </row>
@@ -3523,40 +3498,64 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>アイワ自動車販売株式会社</t>
+          <t>株式会社ヨシダオートサービス</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>大阪府</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>浜松市内6店舗</t>
+          <t>軽の森 なかもず店、軽の森 泉北店、軽の森 富田林店、軽の森 泉大津店、軽の森 堺鉄砲町店、軽の森アウトレット、車の森 なかもず店</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>静岡県浜松市中央区宮竹町237-1</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>大阪府堺市北区百舌鳥西之町3-541</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0301</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>072-246-0302</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>吉田宜史</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/ / https://keinomori.com/</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>https://kurumanomori.com/contact/</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>218名（2025年1月）</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
-https://mapfan.com/genres/556/22/138</t>
+          <t>https://kurumanomori.com/company/
+https://keinomori.com/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -3566,7 +3565,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
+          <t>ブランドは「軽の森」「車の森」。会社名は車の森サイトの会社概要で確認した。軽の森の公式サイト keinomori.com はアクセス制限（403）で読めなかったため、軽の森の6店舗は検索結果の抜粋に頼っている。堺鉄砲町店は求人では「マッハ堺鉄砲町店」（車検）と表記されており、販売店かどうか要確認。</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3575,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>カーネクスト北海道株式会社</t>
+          <t>アイワ自動車販売株式会社</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3584,17 +3583,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>北海道、栃木県、千葉県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
+          <t>浜松市内6店舗</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>北海道札幌市北区篠路二条9丁目1番48号</t>
+          <t>静岡県浜松市中央区宮竹町237-1</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -3608,21 +3607,18 @@
       <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0246/
-https://www.applenet.co.jp/shop/0268/
-https://www.applenet.co.jp/shop/0281/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.goo-net.com/usedcar_shop/0210070/group.html（検索結果の抜粋）
+https://mapfan.com/genres/556/22/138</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9430001034177、〒002-8022）。</t>
+          <t>輸入車専門店（輸入車センター）。「浜松市内に6店舗」は検索結果の店舗紹介文、別の掲載では5拠点。本社住所は地図サイトの掲載。輸入車の正規ディーラーを兼ねていれば対象外の可能性あり。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3628,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>株式会社AOZORA COMPANY</t>
+          <t>カーネクスト北海道株式会社</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3640,17 +3636,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>東京都、新潟県、大阪府、福岡県</t>
+          <t>北海道、栃木県、千葉県</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
+          <t>アップル札幌篠路店、アップル札幌白石店、アップル小山店、アップル札幌藻岩店、アップル釧路星が浦店、アップル香取佐原店</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>新潟県新潟市西区黒鳥5243番地1</t>
+          <t>北海道札幌市北区篠路二条9丁目1番48号</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -3664,18 +3660,21 @@
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
-厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0246/
+https://www.applenet.co.jp/shop/0268/
+https://www.applenet.co.jp/shop/0281/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。社名が御社（株式会社カーネクスト）と似ているが、関係は未確認。アップルの加盟店。 参考：店舗の連絡先（アップル札幌篠路店）〒002-8022 北海道札幌市北区篠路二条9丁目1番48号 TEL 011-676-4501 FAX 011-676-4502。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9430001034177、〒002-8022）。</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3684,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>株式会社AOZORA COMPANY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3693,62 +3692,42 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>東京都、新潟県、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>兵庫県加古川市平岡町高畑88番地の1</t>
+          <t>新潟県新潟市西区黒鳥5243番地1</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
+厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5140001093768、〒675-0103）。</t>
+          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3737,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3766,34 +3745,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>愛知県名古屋市天白区島田2丁目901番地</t>
+          <t>兵庫県加古川市平岡町高畑88番地の1</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 石戸宏樹</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>26名</t>
+        </is>
+      </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/
+          <t>https://www.apple-car.jp/company
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -3804,7 +3800,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001023209、〒468-0056）。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5140001093768、〒675-0103）。</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3810,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>株式会社コバックインターナショナル（コバックカーズ）</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3822,17 +3818,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、愛知県、三重県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>コバックカーズ岐阜店、コバックカーズ岐南店、コバックカーズ軽アウトレット多治見、コバックカーズ春日井東野店、コバックカーズ春日井坂下店、コバックカーズ四日市インター店</t>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>愛知県豊田市梅坪町10丁目5番地3</t>
+          <t>愛知県名古屋市天白区島田2丁目901番地</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -3846,20 +3842,21 @@
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0208435
-https://car.motor-fan.jp/ucar/shop/0203980
-https://car.motor-fan.jp/ucar/shop/0208367
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイト・求人情報の店舗名から6店舗。店舗紹介に「グループ総在庫1500台」「系列店は愛知・岐阜・三重・静岡」とあり静岡の店舗名は不明。運営会社名は求人情報の「株式会社コバックインターナショナル コバックカーズ岐南店」の表記による（全店が同社運営かは未確認）。車検のコバック（FC本部グループ）との関係も未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001062751、〒471-0064）。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001023209、〒468-0056）。</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3866,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社コバックインターナショナル（コバックカーズ）</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3877,27 +3874,23 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>岐阜県、愛知県、三重県</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+          <t>コバックカーズ岐阜店、コバックカーズ岐南店、コバックカーズ軽アウトレット多治見、コバックカーズ春日井東野店、コバックカーズ春日井坂下店、コバックカーズ四日市インター店</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>神奈川県大和市福田7丁目39番地13</t>
+          <t>愛知県豊田市梅坪町10丁目5番地3</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tortoise-k-carlife.com/</t>
-        </is>
-      </c>
+      <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
@@ -3905,88 +3898,78 @@
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
+          <t>https://car.motor-fan.jp/ucar/shop/0208435
+https://car.motor-fan.jp/ucar/shop/0203980
+https://car.motor-fan.jp/ucar/shop/0208367
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト未確認。中古車情報サイト・求人情報の店舗名から6店舗。店舗紹介に「グループ総在庫1500台」「系列店は愛知・岐阜・三重・静岡」とあり静岡の店舗名は不明。運営会社名は求人情報の「株式会社コバックインターナショナル コバックカーズ岐南店」の表記による（全店が同社運営かは未確認）。車検のコバック（FC本部グループ）との関係も未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001062751、〒471-0064）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>株式会社トータス</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県大和市福田7丁目39番地13</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tortoise-k-carlife.com/</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
           <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
 https://www.applenet.co.jp/shop/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="inlineStr">
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="R53" s="2" t="inlineStr">
         <is>
           <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1021001025628、〒242-0024）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ナック（ジャック査定センター）</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>京都府、大阪府、兵庫県</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>078-685-0066</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 難波克年</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>https://jacnet.jp/</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>中古車の査定買取（主業）</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>https://jacnet.jp/site/company/?pt=detail
-https://jacnet.jp/site/company/?pt=shop_list</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3979,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社ナック（ジャック査定センター）</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -4004,42 +3987,58 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>京都府、大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>佐賀県三養基郡みやき町大字原古賀字六本松1902番地2</t>
+          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>078-685-0066</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 難波克年</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>https://jacnet.jp/</t>
+        </is>
+      </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>中古車の査定買取（主業）</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://jacnet.jp/site/company/?pt=detail
+https://jacnet.jp/site/company/?pt=shop_list</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6300001009252、〒849-0101）。</t>
+          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4048,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>株式会社メディアトラスト（クルオク）</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -4057,75 +4056,42 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>クルオク 名古屋インター店（本社）、クルオク レスパ岡崎店、クルオク 豊田吉原店、クルオク カーマ21稲沢店、クルオク カインズホーム半田店、クルオク カインズモール蒲郡店</t>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>愛知県名古屋市名東区高針台1-110</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>0564-58-9609</t>
-        </is>
-      </c>
+          <t>佐賀県三養基郡みやき町大字原古賀字六本松1902番地2</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>鬼頭 宏彰</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>https://www.9609.biz/</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>https://www.9609.biz/contact/</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>info@kuruma094.com</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>https://twitter.com/kuruma094
-https://www.facebook.com/kuruoku/</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>買取あり（事業内容に「国内の中古車の買取り」）</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>正社員4名・パート2名・役員4名（2025年12月現在）</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>https://www.9609.biz/company/
-https://www.9609.biz/store/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>6拠点のうち5つはショッピングモール・ホームセンターの屋上や駐車場内の常設展示場。従業員は少人数。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6300001009252、〒849-0101）。</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4101,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユー・パーク</t>
+          <t>株式会社メディアトラスト（クルオク）</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -4143,48 +4109,65 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
+          <t>クルオク 名古屋インター店（本社）、クルオク レスパ岡崎店、クルオク 豊田吉原店、クルオク カーマ21稲沢店、クルオク カインズホーム半田店、クルオク カインズモール蒲郡店</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
+          <t>愛知県名古屋市名東区高針台1-110</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>048-798-9566</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9590</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+          <t>0564-58-9609</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>鬼頭 宏彰</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>https://www.9609.biz/</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.9609.biz/contact/</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>info@kuruma094.com</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/kuruma094
+https://www.facebook.com/kuruoku/</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>買取無料査定あり</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr"/>
+          <t>買取あり（事業内容に「国内の中古車の買取り」）</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>正社員4名・パート2名・役員4名（2025年12月現在）</t>
+        </is>
+      </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/about-us/
-https://www.u-parknet.com/</t>
+          <t>https://www.9609.biz/company/
+https://www.9609.biz/store/</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -4194,7 +4177,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+          <t>6拠点のうち5つはショッピングモール・ホームセンターの屋上や駐車場内の常設展示場。従業員は少人数。</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4187,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロペライオ</t>
+          <t>株式会社ユー・パーク</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -4212,29 +4195,33 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、東京都、愛知県、京都府</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ロペライオ練馬、ロペライオさいたま、モーターホーム by ロペライオ、東日本買取センター、中部買取センター、西日本買取センター</t>
+          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>東京都世田谷区太子堂4-1-1 キャロットタワー6F</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>早水 彰</t>
-        </is>
-      </c>
+          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>048-798-9566</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>048-798-9590</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://loperaio.co.jp/</t>
+          <t>https://www.u-parknet.com/</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
@@ -4242,65 +4229,130 @@
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>買取センター3拠点（東日本・中部・西日本）</t>
+          <t>買取無料査定あり</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr"/>
       <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-parknet.com/about-us/
+https://www.u-parknet.com/</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ロペライオ</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県、東京都、愛知県、京都府</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ロペライオ練馬、ロペライオさいたま、モーターホーム by ロペライオ、東日本買取センター、中部買取センター、西日本買取センター</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>東京都世田谷区太子堂4-1-1 キャロットタワー6F</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>早水 彰</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>https://loperaio.co.jp/</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>買取センター3拠点（東日本・中部・西日本）</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>https://loperaio.co.jp/shop_index.html
 https://loperaio.co.jp/shop_head_office.html
 https://loperaio.co.jp/company_index.html</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr">
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>輸入中古車専門店。ショップガイドの住所と店舗名の対応はページの画像代替テキストから推定（買取センターの所在県は住所一覧からの推定）。ほかに本社・セントラルベース・ファクトリーセンター（非販売拠点）、ボランタリーチェーンのロペシティ西宮（うかいや運営）・札幌平岸（三愛自動車工業運営）。健康経営優良法人（大規模法人部門）取得。</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>株式会社丸山自動車（ポケットカーズ）</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C59" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>新潟県</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>ポケットカーズ（三条市上須頃）、ポケットカーズ 女池インター店（新潟市中央区女池神明）、ポケットカーズ（長岡市堺町）、ポケットカーズ（新潟市中央区紫竹山）、ポケットカーズ（新潟市西区寺尾）、アップル三条店</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>https://www.pocketcars.jp/</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr">
         <is>
           <t>https://www.pocketcars.jp/shop/
 https://www.pocketcars.jp/shop/
@@ -4308,137 +4360,84 @@
 https://mynavi-agent.jp/corpdetail/40198/</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr">
+      <c r="Q59" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R58" s="2" t="inlineStr">
+      <c r="R59" s="2" t="inlineStr">
         <is>
           <t>軽未使用車専門店。運営会社は、転職サイトの会社紹介「1995年以降は車検のコバック、鈑金のモドーリー、ポケットカーズなどの店舗拡大」と、アップル三条店（運営：株式会社丸山自動車）から判断。ポケットカーズの店舗数は公式サイト店舗一覧の住所5件（店名が取れなかった店舗は所在地で表記）＋アップル1店。</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>大久自動車販売株式会社</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C60" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>福島県</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>ダイキュー飯坂店、ダイキュー郡山店、ダイキュー白河中央インター店、ダイキューいわき店、ダイキュー会津若松店</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>福島県福島市本内字北古舘9</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>024-542-1221</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>https://www.daiq-car.jp/</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>https://www.daiq-car.jp/contact</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/DaiQ_motors
 https://www.facebook.com/daiq.motors/
 https://www.instagram.com/daiq_motors.official/</t>
         </is>
       </c>
-      <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr"/>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daiq-car.jp/</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>軽自動車専門店ダイキュー。運営会社名は公式サイトの古物営業法に基づく表示による。店舗は公式サイトの5店舗。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>松下モータース</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>静岡県</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ecar.co.jp/</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>https://www.ecar.co.jp/
-https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
+          <t>https://www.daiq-car.jp/</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。 【2026-10更新】公式サイトに「静岡県内5店舗」とあるため6→5に修正（展示場は本店1拠点）。法人格・会社概要は未確認。</t>
+          <t>軽自動車専門店ダイキュー。運営会社名は公式サイトの古物営業法に基づく表示による。店舗は公式サイトの5店舗。</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4447,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>株式会社CIA</t>
+          <t>松下モータース</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4456,65 +4455,42 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>0297-47-9588</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0297-47-9577</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 大内康弘</t>
-        </is>
-      </c>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/</t>
+          <t>https://www.ecar.co.jp/</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>キャンピングカー買取（買取センター4か所）</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/company/</t>
+          <t>https://www.ecar.co.jp/
+https://car.motor-fan.jp/ucar/shop/0600173（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。 電話・FAXは本社と同住所の守谷店（Yacco本店）のもの。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。 【2026-10更新】公式サイトに「静岡県内5店舗」とあるため6→5に修正（展示場は本店1拠点）。法人格・会社概要は未確認。</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4500,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>株式会社NIIZAWA</t>
+          <t>株式会社CIA</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4532,128 +4508,148 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>0297-47-9588</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0297-47-9577</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 大内康弘</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>キャンピングカー買取（買取センター4か所）</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/company/</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。 電話・FAXは本社と同住所の守谷店（Yacco本店）のもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>株式会社NIIZAWA</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
           <t>広島県、山口県</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>広島県廿日市市大野原1丁目2-20</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>0829-30-8103</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>0829-30-8104</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/contact/</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/keimarket.k
 https://www.facebook.com/share/1AhR49eysR
 https://youtube.com/@keimarket398</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>95名（パート含む）</t>
         </is>
       </c>
-      <c r="P62" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>https://www.kei-market.co.jp/company/
 https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
-      <c r="Q62" s="2" t="inlineStr">
+      <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="R63" s="2" t="inlineStr">
         <is>
           <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>株式会社TSC</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>茨城県、埼玉県、千葉県</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>大久保駅前店、千葉北インター店、蘇我インター店、買取直販 つくば店、北本店</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>千葉県千葉市美浜区中瀬（番地は未確認）</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>買取直販（買取車両を展示販売）</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>https://job.rikunabi.com/job_descriptions/82de25d5815e8620/（検索結果の抜粋。現在は404）</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>公式サイト未確認。求人情報の勤務地一覧から5店舗。本社の美浜区中瀬・蘇我インター店の緑区古市場町が、KiND OUTLETのプライバシーポリシー記載会社（NEXTGATE MOTOR SOLUTIONS、美浜区中瀬）・同千葉コンパクトハイブリッド店（緑区古市場町）と近く、同一グループの可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4659,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>株式会社Y's GARAGE</t>
+          <t>株式会社TSC</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4671,57 +4667,45 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>京都府、鳥取県、島根県</t>
+          <t>茨城県、埼玉県、千葉県</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
+          <t>大久保駅前店、千葉北インター店、蘇我インター店、買取直販 つくば店、北本店</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>京都府宇治市槇島町三十五38-1</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>0774-25-5557</t>
-        </is>
-      </c>
+          <t>千葉県千葉市美浜区中瀬（番地は未確認）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 桐畑勇志</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>https://k-smile.jp/</t>
-        </is>
-      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>158名（アルバイト含む、令和8年10月）</t>
-        </is>
-      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>買取直販（買取車両を展示販売）</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>https://k-smile.jp/company/</t>
+          <t>https://job.rikunabi.com/job_descriptions/82de25d5815e8620/（検索結果の抜粋。現在は404）</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+          <t>公式サイト未確認。求人情報の勤務地一覧から5店舗。本社の美浜区中瀬・蘇我インター店の緑区古市場町が、KiND OUTLETのプライバシーポリシー記載会社（NEXTGATE MOTOR SOLUTIONS、美浜区中瀬）・同千葉コンパクトハイブリッド店（緑区古市場町）と近く、同一グループの可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4715,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>株式会社アールブイランド（RVランド）</t>
+          <t>株式会社Y's GARAGE</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4739,37 +4723,33 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>北海道、茨城県、千葉県、佐賀県</t>
+          <t>京都府、鳥取県、島根県</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>本社（常総市）、RVランド イオンモールつくば店、RVランド コンセプト（流山店）、RVランド 北海道（千歳市）、RVランド 九州 鳥栖展示場</t>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>茨城県常総市大塚戸町1600-1</t>
+          <t>京都府宇治市槇島町三十五38-1</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>0297-27-6767</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0297-27-6768</t>
-        </is>
-      </c>
+          <t>0774-25-5557</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>阿部 和英</t>
+          <t>代表取締役 桐畑勇志</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://www.rvland.co.jp/</t>
+          <t>https://k-smile.jp/</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
@@ -4778,12 +4758,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>社員67名、パート28名</t>
+          <t>158名（アルバイト含む、令和8年10月）</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>https://www.rvland.co.jp/about/gaiyou.php</t>
+          <t>https://k-smile.jp/company/</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -4793,7 +4773,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（製造・販売、新車・中古車）。会社概要の拠点のうち販売店・展示場を5で計上（ほかに常総市大生郷町・久留米市の拠点あり、業態未確認）。</t>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4783,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>株式会社ウシジマ（UJグループ・ウシトラ）</t>
+          <t>株式会社アールブイランド（RVランド）</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4811,55 +4791,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、東京都、京都府、福岡県</t>
+          <t>北海道、茨城県、千葉県、佐賀県</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>八女本社、福岡支店（展示場）、埼玉支店（展示場）、東京営業所、京都支店</t>
+          <t>本社（常総市）、RVランド イオンモールつくば店、RVランド コンセプト（流山店）、RVランド 北海道（千歳市）、RVランド 九州 鳥栖展示場</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>福岡県八女市室岡377-10</t>
+          <t>茨城県常総市大塚戸町1600-1</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>0943-24-1126</t>
+          <t>0297-27-6767</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0943-24-4812</t>
+          <t>0297-27-6768</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>牛島 豊晴</t>
+          <t>阿部 和英</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushitruck.com/</t>
+          <t>https://www.rvland.co.jp/</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック買取あり</t>
-        </is>
-      </c>
+      <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>106名（スタッフ数）</t>
+          <t>社員67名、パート28名</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushitruck.com/truck/corporate</t>
+          <t>https://www.rvland.co.jp/about/gaiyou.php</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -4869,7 +4845,7 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売・買取。拠点数は販売系の本社・支店・営業所で計上（ほかに部品のウシパーツ、レンタル店）。電話・FAXは会社概要記載のもの（本社の番号かは未確認）。</t>
+          <t>【要判断】キャンピングカー専門（製造・販売、新車・中古車）。会社概要の拠点のうち販売店・展示場を5で計上（ほかに常総市大生郷町・久留米市の拠点あり、業態未確認）。</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4855,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>株式会社ケーワン（5-STAR）</t>
+          <t>株式会社ウシジマ（UJグループ・ウシトラ）</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4887,29 +4863,105 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>埼玉県、東京都、京都府、福岡県</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>5-STAR 越谷店、5-STAR 春日部店、5-STAR 三郷店、5-STAR 土浦店、5-STAR 阿見店</t>
+          <t>八女本社、福岡支店（展示場）、埼玉支店（展示場）、東京営業所、京都支店</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>埼玉県越谷市大間野町3丁目146番地</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
+          <t>福岡県八女市室岡377-10</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>0943-24-1126</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>0943-24-4812</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>牛島 豊晴</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ushitruck.com/</t>
+        </is>
+      </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr"/>
-      <c r="O67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック買取あり</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>106名（スタッフ数）</t>
+        </is>
+      </c>
       <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ushitruck.com/truck/corporate</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取。拠点数は販売系の本社・支店・営業所で計上（ほかに部品のウシパーツ、レンタル店）。電話・FAXは会社概要記載のもの（本社の番号かは未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ケーワン（5-STAR）</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>茨城県、埼玉県</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>5-STAR 越谷店、5-STAR 春日部店、5-STAR 三郷店、5-STAR 土浦店、5-STAR 阿見店</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県越谷市大間野町3丁目146番地</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr">
         <is>
           <t>https://employment.en-japan.com/comp-66249/
 https://car.motor-fan.jp/ucar/shop/3000451
@@ -4917,88 +4969,14 @@
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q67" s="2" t="inlineStr">
+      <c r="Q68" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R67" s="2" t="inlineStr">
+      <c r="R68" s="2" t="inlineStr">
         <is>
           <t>公式サイト未確認。求人情報に「埼玉県・茨城県の5-STAR各店舗（越谷・春日部・三郷・土浦）」、中古車情報サイトに阿見店。ランキング記事では「埼玉県中心に6店舗」。越谷店は越谷市大間野町3-146。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9030001065279、〒343-0844）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>株式会社トータルカーサービス（ミニクス）</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>兵庫県、広島県</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>ミニクス 福山店、ミニクス 福山中央店、ミニクス アウトレット店、ミニクス 姫路店、ミニクス 加古川店</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>広島県福山市南手城町1丁目14-7</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>084-973-1147</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>084-973-1148</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>https://minics.jp/</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>https://minics.jp/contact</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/minics_2021/
-https://www.youtube.com/channel/UCtdVZXmW98t3g6RypKRTXzg</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>https://minics.jp/shop
-https://minics.jp/about</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>軽トラ・軽バン専門店。サイトに「ミニクス運営：株式会社トータルカーサービス」。所在地は福山中央店と同じ住所の記載（本社かどうかは未確認）。</t>
         </is>
       </c>
     </row>
@@ -5008,7 +4986,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロイヤルオートサービス</t>
+          <t>株式会社トータルカーサービス（ミニクス）</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -5016,136 +4994,141 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>兵庫県、広島県</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+          <t>ミニクス 福山店、ミニクス 福山中央店、ミニクス アウトレット店、ミニクス 姫路店、ミニクス 加古川店</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>長野県松本市村井町南2-1-5</t>
+          <t>広島県福山市南手城町1丁目14-7</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>0120-107-817</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 中田忠章</t>
-        </is>
-      </c>
+          <t>084-973-1147</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>084-973-1148</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>https://carstation.royal-auto.jp/</t>
+          <t>https://minics.jp/</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>https://carstation.royal-auto.jp/contact/</t>
+          <t>https://minics.jp/contact</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/minics_2021/
+https://www.youtube.com/channel/UCtdVZXmW98t3g6RypKRTXzg</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>https://minics.jp/shop
+https://minics.jp/about</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>軽トラ・軽バン専門店。サイトに「ミニクス運営：株式会社トータルカーサービス」。所在地は福山中央店と同じ住所の記載（本社かどうかは未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ロイヤルオートサービス</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>長野県松本市村井町南2-1-5</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>0120-107-817</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 中田忠章</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>https://carstation.royal-auto.jp/</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>https://carstation.royal-auto.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/royal_auto_
 https://www.instagram.com/royal_auto_service/?hl=ja
 https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
         </is>
       </c>
-      <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>187名</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr">
+      <c r="P70" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
-      <c r="Q69" s="2" t="inlineStr">
+      <c r="Q70" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R69" s="2" t="inlineStr">
+      <c r="R70" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>株式会社東部オート（東部オートグループ）</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>群馬県</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>高前バイパス店、前橋店、小鳥店、ラビット高前バイパス店、ラビット高崎小鳥店</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>群馬県高崎市小八木町1538</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>田口 治</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tobu-auto.com/</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>買取店（ラビット加盟2店舗、買取事業部をLinksより継承）</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>81名</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tobu-auto.com/about
-https://www.tobu-auto.com/</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>会社概要の事業所数は10店舗（整備・鈑金拠点等を含むとみられる）。中古車販売3店舗＋ラビット2店舗で計上。グループにBMW正規販売のモトーレン群馬・栃木（別法人）あり。年商59億円（会社概要）。</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5138,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>株式会社横浜ユーポス</t>
+          <t>株式会社東部オート（東部オートグループ）</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -5163,35 +5146,48 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>栃木県、神奈川県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
+          <t>高前バイパス店、前橋店、小鳥店、ラビット高前バイパス店、ラビット高崎小鳥店</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>神奈川県川崎市高津区二子6丁目14番10号</t>
+          <t>群馬県高崎市小八木町1538</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>田口 治</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tobu-auto.com/</t>
+        </is>
+      </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>買取店（ラビット加盟2店舗、買取事業部をLinksより継承）</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/kouhoku
-https://www.u-pohs.co.jp/shonanhiratsuka
-https://www.u-pohs.co.jp/tsuzuki
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.tobu-auto.com/about
+https://www.tobu-auto.com/</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -5201,7 +5197,7 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6020001091254、〒213-0002）。</t>
+          <t>会社概要の事業所数は10店舗（整備・鈑金拠点等を含むとみられる）。中古車販売3店舗＋ラビット2店舗で計上。グループにBMW正規販売のモトーレン群馬・栃木（別法人）あり。年商59億円（会社概要）。</t>
         </is>
       </c>
     </row>
@@ -5211,35 +5207,31 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>KiND OUTLET（カインドアウトレット）</t>
+          <t>株式会社横浜ユーポス</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>栃木県、神奈川県</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>市原店、千葉蘇我インター軽専門店、山武成東店、千葉コンパクトハイブリッド店</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>0436-55-9169</t>
-        </is>
-      </c>
+          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県川崎市高津区二子6丁目14番10号</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>https://kindoutlet.jp/</t>
-        </is>
-      </c>
+      <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr"/>
@@ -5247,18 +5239,21 @@
       <c r="O72" s="2" t="inlineStr"/>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>https://kindoutlet.jp/shop
-https://kindoutlet.jp/privacypolicy</t>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/kouhoku
+https://www.u-pohs.co.jp/shonanhiratsuka
+https://www.u-pohs.co.jp/tsuzuki
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>千葉県の軽自動車専門店。サイトのプライバシーポリシー記載はNEXTGATE MOTOR SOLUTIONS株式会社（千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F）だが、運営会社かどうかは未確認。電話は市原店。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6020001091254、〒213-0002）。</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5263,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ニシオ自販</t>
+          <t>KiND OUTLET（カインドアウトレット）</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -5276,19 +5271,27 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>静岡県西部の4店舗</t>
+          <t>市原店、千葉蘇我インター軽専門店、山武成東店、千葉コンパクトハイブリッド店</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>0436-55-9169</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>https://kindoutlet.jp/</t>
+        </is>
+      </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr"/>
@@ -5296,7 +5299,8 @@
       <c r="O73" s="2" t="inlineStr"/>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋</t>
+          <t>https://kindoutlet.jp/shop
+https://kindoutlet.jp/privacypolicy</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -5306,7 +5310,7 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>「静岡県西部に4店舗展開」との掲載による。店舗名・法人格は未確認。</t>
+          <t>千葉県の軽自動車専門店。サイトのプライバシーポリシー記載はNEXTGATE MOTOR SOLUTIONS株式会社（千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F）だが、運営会社かどうかは未確認。電話は市原店。</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5320,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>プルミエ（軽届出済未使用車専門店、運営会社未確認）</t>
+          <t>ニシオ自販</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -5324,12 +5328,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>豊田、安城、豊橋、四日市</t>
+          <t>静岡県西部の4店舗</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -5354,7 +5358,7 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>同じ4店舗（豊橋・岡崎安城・豊田・四日市）で「CAST」の名称の掲載もあり、同一の運営会社の可能性。</t>
+          <t>「静岡県西部に4店舗展開」との掲載による。店舗名・法人格は未確認。</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5368,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>ミスターシャーマン（運営会社未確認）</t>
+          <t>プルミエ（軽届出済未使用車専門店、運営会社未確認）</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5372,12 +5376,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>長野県内4店舗</t>
+          <t>豊田、安城、豊橋、四日市</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -5392,7 +5396,7 @@
       <c r="O75" s="2" t="inlineStr"/>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事）</t>
+          <t>検索結果の抜粋</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -5402,7 +5406,7 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>車買取。比較記事の「県内4店舗」による。</t>
+          <t>同じ4店舗（豊橋・岡崎安城・豊田・四日市）で「CAST」の名称の掲載もあり、同一の運営会社の可能性。</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5416,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ムラトミ</t>
+          <t>ミスターシャーマン（運営会社未確認）</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5420,12 +5424,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>相模原本店、相模原（2店舗目）、海老名店、伊勢原店</t>
+          <t>長野県内4店舗</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -5440,7 +5444,7 @@
       <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0530132</t>
+          <t>検索結果の抜粋（比較記事）</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -5450,7 +5454,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイトの店舗紹介に「神奈川県内4店舗（相模原2店、海老名、伊勢原）のロープライスカー専門店」とある。相模原本店は相模原市南区新磯野5-43。運営法人名は未確認。2店舗目の相模原の店名は不明。</t>
+          <t>車買取。比較記事の「県内4店舗」による。</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5464,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>昭和礦油株式会社</t>
+          <t>ムラトミ</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5473,14 +5477,10 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>東京都大田区平和島5丁目2番28号</t>
-        </is>
-      </c>
+          <t>相模原本店、相模原（2店舗目）、海老名店、伊勢原店</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
@@ -5492,20 +5492,17 @@
       <c r="O77" s="2" t="inlineStr"/>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0282/
-https://www.applenet.co.jp/shop/0290/
-https://www.applenet.co.jp/shop/0291/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0530132</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7010801005652、〒143-0006）。</t>
+          <t>公式サイト未確認。中古車情報サイトの店舗紹介に「神奈川県内4店舗（相模原2店、海老名、伊勢原）のロープライスカー専門店」とある。相模原本店は相模原市南区新磯野5-43。運営法人名は未確認。2店舗目の相模原の店名は不明。</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5512,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>株式会社GR8（GR8STYLE）</t>
+          <t>上野自動車株式会社</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5523,57 +5520,31 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>埼玉県、岐阜県、兵庫県</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>GR8 STYLE 春日井店、名古屋大府店、岡崎店、名古屋港店</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>愛知県春日井市南下原町6丁目2-1</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>0568-41-8828</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0568-41-8839</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>入谷 篤</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gr8style.co.jp/</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gr8style.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>上野自動車㈱ 関東支店、上野自動車中部支店、上野自動車兵庫園田店、上野自動車㈱兵庫篠山支店</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/gr8style/
-https://www.instagram.com/gr8style_japan/</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>https://www.gr8style.co.jp/company-profile/
-https://www.gr8style.co.jp/</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -5583,7 +5554,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>ハイエース専門店（新車・中古車・カスタム・キャンピング）。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：上野自動車㈱ 関東支店：埼玉県三郷市仁蔵449-1（048-959-9517）、上野自動車中部支店：岐阜県揖斐郡揖斐川町谷汲徳積７３０（0585-56-3088）、上野自動車兵庫園田店：兵庫県尼崎市東園田町2-192（079-590-3003）、上野自動車㈱兵庫篠山支店：兵庫県丹波篠山市今田町佐曽良新田94-1（079-590-3003）</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5564,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>株式会社MARE</t>
+          <t>昭和礦油株式会社</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5601,17 +5572,17 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>愛知県、兵庫県、広島県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
+          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>広島県廿日市市下平良365番地1</t>
+          <t>東京都大田区平和島5丁目2番28号</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
@@ -5625,73 +5596,206 @@
       <c r="O79" s="2" t="inlineStr"/>
       <c r="P79" s="2" t="inlineStr">
         <is>
+          <t>https://www.applenet.co.jp/shop/0282/
+https://www.applenet.co.jp/shop/0290/
+https://www.applenet.co.jp/shop/0291/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7010801005652、〒143-0006）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>株式会社GR8（GR8STYLE）</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>GR8 STYLE 春日井店、名古屋大府店、岡崎店、名古屋港店</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>愛知県春日井市南下原町6丁目2-1</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>0568-41-8828</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0568-41-8839</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>入谷 篤</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gr8style.co.jp/</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gr8style.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gr8style/
+https://www.instagram.com/gr8style_japan/</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gr8style.co.jp/company-profile/
+https://www.gr8style.co.jp/</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>ハイエース専門店（新車・中古車・カスタム・キャンピング）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>株式会社MARE</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>愛知県、兵庫県、広島県</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>広島県廿日市市下平良365番地1</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
           <t>https://www.applenet.co.jp/shop/0289/
 https://www.applenet.co.jp/shop/0296/
 https://www.applenet.co.jp/shop/0308/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q79" s="2" t="inlineStr">
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R79" s="2" t="inlineStr">
+      <c r="R81" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3240001051809、〒738-0023）。</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>株式会社T-SPACE</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
+      <c r="C82" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>埼玉県</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>SPACE ジムニー館、SPACE-ONE、SPACE-SE、SPACE-ZERO</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>埼玉県春日部市栄町1-431-1</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>048-797-6699</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>048-797-6644</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>https://cardealer-space.com/</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>info@cardealer-space.com</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/space_jimny
 https://www.instagram.com/spaceone661
@@ -5699,143 +5803,15 @@
 https://www.instagram.com/space.zero.kasukabe/</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>買取査定あり</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>https://cardealer-space.com/company/</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R80" s="2" t="inlineStr">
-        <is>
-          <t>販売店4（春日部市）。ほかに整備（T-SPACE SERVICE）・鈑金（SPACE-Body Lab.）・レンタカー。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>株式会社エコノミー湘南（奇跡査定センター）</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>奇跡査定センター 藤沢六会本店、藤沢橋店、横浜都筑店、相模原16号由野台店</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県藤沢市亀井野2480-3</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>0466-80-3443</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0466-80-3445</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>桑名 伸</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.satei.net/</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>買取専門（買取センター）</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr"/>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.satei.net/company-profile/
-https://www.satei.net/</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R81" s="2" t="inlineStr">
-        <is>
-          <t>車買取専門店。会社概要の沿革に「有限会社エコノミーエンタープライズより営業継承し、株式会社エコノミー湘南を設立」「屋号を奇跡査定センターとし」とあるが、現在の社名欄は確認できず。電話は藤沢六会本店。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>株式会社オリンピア</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>栃木県、群馬県、埼玉県</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>栃木県宇都宮市石井町3335番地55</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0138/
-https://www.applenet.co.jp/shop/0141/
-https://www.applenet.co.jp/shop/0143/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://cardealer-space.com/company/</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -5845,7 +5821,7 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7060001001092、〒321-0912）。</t>
+          <t>販売店4（春日部市）。ほかに整備（T-SPACE SERVICE）・鈑金（SPACE-Body Lab.）・レンタカー。</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5831,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートスペースアクセル（ASAグループ）</t>
+          <t>株式会社エコノミー湘南（奇跡査定センター）</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5868,28 +5844,47 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>（有）オートフィールドストリーク</t>
+          <t>奇跡査定センター 藤沢六会本店、藤沢橋店、横浜都筑店、相模原16号由野台店</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>神奈川県厚木市関口236番地14</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
+          <t>神奈川県藤沢市亀井野2480-3</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>0466-80-3443</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>0466-80-3445</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>桑名 伸</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.satei.net/</t>
+        </is>
+      </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>買取専門（買取センター）</t>
+        </is>
+      </c>
       <c r="O83" s="2" t="inlineStr"/>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0510254
-https://biz-maps.com/s/cities/142123/m-inds/378
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.satei.net/company-profile/
+https://www.satei.net/</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -5899,7 +5894,7 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2021001024521、〒243-0804）。</t>
+          <t>車買取専門店。会社概要の沿革に「有限会社エコノミーエンタープライズより営業継承し、株式会社エコノミー湘南を設立」「屋号を奇跡査定センターとし」とあるが、現在の社名欄は確認できず。電話は藤沢六会本店。</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5904,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>株式会社クルーズコーポレーション（カーニバル）</t>
+          <t>株式会社オリンピア</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5917,31 +5912,23 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>栃木県、群馬県、埼玉県</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>カーニバル 久喜インター店、カーニバル 春日部店、カーニバル 岩槻店、カーニバル 上尾店</t>
+          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>埼玉県久喜市江面1479</t>
+          <t>栃木県宇都宮市石井町3335番地55</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>内田 浩</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>https://caniva.jp/</t>
-        </is>
-      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr"/>
@@ -5949,8 +5936,10 @@
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>https://caniva.jp/company/
-https://caniva.jp/shop/</t>
+          <t>https://www.applenet.co.jp/shop/0138/
+https://www.applenet.co.jp/shop/0141/
+https://www.applenet.co.jp/shop/0143/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -5960,7 +5949,7 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>新車・未使用車・中古車販売。公式サイトの店舗一覧で4店舗（ほかに春日部サービス工場）。本社は久喜インター店と同じ住所。電話は会社概要に記載なし（店舗へ直接）。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7060001001092、〒321-0912）。</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5959,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>株式会社クレタ（北海道軽パーク）</t>
+          <t>株式会社オートスペースアクセル（ASAグループ）</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5978,47 +5967,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>札幌店、札幌東店、北広島店、苫小牧店</t>
+          <t>（有）オートフィールドストリーク</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>北海道苫小牧市沼ノ端中央1丁目14番16号</t>
+          <t>神奈川県厚木市関口236番地14</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>https://kereta.jp/</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>https://kereta.jp/contact/</t>
-        </is>
-      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/hokkaido_k_park/
-https://x.com/hokkaido_k_park
-https://www.facebook.com/hokkaidokeipark/
-https://youtube.com/channel/UC2xk0xmuuww2ocTXFsNghcw
-https://www.tiktok.com/@hokkaido_k_park</t>
-        </is>
-      </c>
+      <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr"/>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>https://kereta.jp/
+          <t>https://car.motor-fan.jp/ucar/shop/0510254
+https://biz-maps.com/s/cities/142123/m-inds/378
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -6029,7 +6003,7 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8430001055026、〒059-1305）。</t>
+          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2021001024521、〒243-0804）。</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6013,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>株式会社グローバンネット</t>
+          <t>株式会社クルーズコーポレーション（カーニバル）</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -6047,25 +6021,29 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
+          <t>カーニバル 久喜インター店、カーニバル 春日部店、カーニバル 岩槻店、カーニバル 上尾店</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>埼玉県所沢市大字坂之下17番地1号</t>
+          <t>埼玉県久喜市江面1479</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>内田 浩</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://pa-cars.com/</t>
+          <t>https://caniva.jp/</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
@@ -6075,18 +6053,18 @@
       <c r="O86" s="2" t="inlineStr"/>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>https://pa-cars.com/shopinfo.html
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://caniva.jp/company/
+https://caniva.jp/shop/</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1030001025439、〒359-0012）。</t>
+          <t>新車・未使用車・中古車販売。公式サイトの店舗一覧で4店舗（ほかに春日部サービス工場）。本社は久喜インター店と同じ住所。電話は会社概要に記載なし（店舗へ直接）。</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6074,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>株式会社サンライズモータース（軽プラザサンライズ）</t>
+          <t>株式会社クレタ（北海道軽パーク）</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -6104,33 +6082,47 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>軽プラザサンライズ 青森本店、軽プラザサンライズ 弘前本店、軽プラザサンライズ 八戸本店、新車市場 サンライズ青森東バイパス店</t>
+          <t>札幌店、札幌東店、北広島店、苫小牧店</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>青森県青森市大字平新田字池上56番地1</t>
+          <t>北海道苫小牧市沼ノ端中央1丁目14番16号</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>https://kereta.jp/</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>https://kereta.jp/contact/</t>
+        </is>
+      </c>
       <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hokkaido_k_park/
+https://x.com/hokkaido_k_park
+https://www.facebook.com/hokkaidokeipark/
+https://youtube.com/channel/UC2xk0xmuuww2ocTXFsNghcw
+https://www.tiktok.com/@hokkaido_k_park</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>https://carbell.jp/partner/search?area_code=10
-https://car.motor-fan.jp/ucar/shop/0904135
-https://www.kurumaerabi.com/shop/detail/40016907/
+          <t>https://kereta.jp/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -6141,7 +6133,7 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。軽未使用車専門店。中古車情報サイトの店舗紹介に青森・弘前・八戸の各店と「グループ総在庫800台」。新車市場の加盟店一覧に「新車市場 サンライズ青森東バイパス店 株式会社サンライズモータース」。青森本店は青森市第二問屋町2丁目5-13（車検のコバック併設）、八戸本店は八戸市城下3-8-6。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6420001004869、〒030-0931）。</t>
+          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8430001055026、〒059-1305）。</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6143,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>株式会社ダブルツリー</t>
+          <t>株式会社グローバンネット</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -6159,27 +6151,27 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
+          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>岡山県倉敷市加須山334番地の4</t>
+          <t>埼玉県所沢市大字坂之下17番地1号</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>https://pa-cars.com/</t>
+        </is>
+      </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr"/>
@@ -6187,18 +6179,18 @@
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
+          <t>https://pa-cars.com/shopinfo.html
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1260001014484、〒710-0026）。</t>
+          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1030001025439、〒359-0012）。</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6200,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビッグワン</t>
+          <t>株式会社サンライズモータース（軽プラザサンライズ）</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -6216,17 +6208,17 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>販売店（千葉市内4店舗）</t>
+          <t>軽プラザサンライズ 青森本店、軽プラザサンライズ 弘前本店、軽プラザサンライズ 八戸本店、新車市場 サンライズ青森東バイパス店</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>千葉県千葉市花見川区三角町525番地</t>
+          <t>青森県青森市大字平新田字池上56番地1</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
@@ -6240,7 +6232,9 @@
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）
+          <t>https://carbell.jp/partner/search?area_code=10
+https://car.motor-fan.jp/ucar/shop/0904135
+https://www.kurumaerabi.com/shop/detail/40016907/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -6251,7 +6245,7 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号4040001042513、〒262-0011）。</t>
+          <t>公式サイト未確認。軽未使用車専門店。中古車情報サイトの店舗紹介に青森・弘前・八戸の各店と「グループ総在庫800台」。新車市場の加盟店一覧に「新車市場 サンライズ青森東バイパス店 株式会社サンライズモータース」。青森本店は青森市第二問屋町2丁目5-13（車検のコバック併設）、八戸本店は八戸市城下3-8-6。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6420001004869、〒030-0931）。</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6255,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミナミシマ自動車販売</t>
+          <t>株式会社ダブルツリー</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -6269,22 +6263,26 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
+          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>奈良県葛城市北花内703番地4</t>
+          <t>岡山県倉敷市加須山334番地の4</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
@@ -6293,9 +6291,7 @@
       <c r="O90" s="2" t="inlineStr"/>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kashiba/
-https://www.u-pohs.co.jp/kashihara/
-https://www.u-pohs.co.jp/katuragi/
+          <t>https://www.applenet.co.jp/shop/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -6306,7 +6302,7 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5150001014995、〒639-2113）。</t>
+          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1260001014484、〒710-0026）。</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6312,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>株式会社ライズオート（RiSE AUTO）</t>
+          <t>株式会社ビッグワン</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -6324,58 +6320,42 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>RiSE 四日市北店、RiSE 四日市南店、ガリバーアウトレット 四日市緑地店、ガリバー 稲沢店</t>
+          <t>販売店（千葉市内4店舗）</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>三重県四日市市日永東3-13-5</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>059-329-5553</t>
-        </is>
-      </c>
+          <t>千葉県千葉市花見川区三角町525番地</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>松村 賢治</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>https://riseauto.jp/</t>
-        </is>
-      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>買取あり（ガリバー加盟店を運営）</t>
-        </is>
-      </c>
+      <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr"/>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>https://riseauto.jp/company/
-https://riseauto.jp/</t>
+          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>リョウシンホールディングスグループ。自社ブランドRiSE 2店舗＋ガリバー加盟2店舗。会社概要に「三重県に3店舗と愛知県に1店舗」。</t>
+          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号4040001042513、〒262-0011）。</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6365,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>株式会社ワークス</t>
+          <t>株式会社ミナミシマ自動車販売</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6393,17 +6373,17 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
+          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>埼玉県川越市大字府川23番地4</t>
+          <t>奈良県葛城市北花内703番地4</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
@@ -6417,18 +6397,20 @@
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）
+          <t>https://www.u-pohs.co.jp/kashiba/
+https://www.u-pohs.co.jp/kashihara/
+https://www.u-pohs.co.jp/katuragi/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3030001056861、〒350-0831）。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5150001014995、〒639-2113）。</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6420,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>株式会社沖縄ユーポス</t>
+          <t>株式会社ライズオート（RiSE AUTO）</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6446,34 +6428,48 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+          <t>RiSE 四日市北店、RiSE 四日市南店、ガリバーアウトレット 四日市緑地店、ガリバー 稲沢店</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>沖縄県沖縄市字登川2791番地1</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr"/>
+          <t>三重県四日市市日永東3-13-5</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>059-329-5553</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>松村 賢治</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>https://riseauto.jp/</t>
+        </is>
+      </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>買取あり（ガリバー加盟店を運営）</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/misato/
-https://www.u-pohs.co.jp/naha-shintoshin
-https://www.u-pohs.co.jp/noborikawa/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://riseauto.jp/company/
+https://riseauto.jp/</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -6483,7 +6479,7 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3360001016221、〒904-2142）。</t>
+          <t>リョウシンホールディングスグループ。自社ブランドRiSE 2店舗＋ガリバー加盟2店舗。会社概要に「三重県に3店舗と愛知県に1店舗」。</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6489,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>株式会社鈴木モータース</t>
+          <t>株式会社ワークス</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6501,15 +6497,19 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr"/>
+          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県川越市大字府川23番地4</t>
+        </is>
+      </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
@@ -6521,19 +6521,18 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0065/
-https://www.applenet.co.jp/shop/0071/
-https://www.applenet.co.jp/shop/0080/</t>
+          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3030001056861、〒350-0831）。</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6542,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>買取マウス（運営会社未確認）</t>
+          <t>株式会社沖縄ユーポス</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6551,15 +6550,19 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>新潟市内4店舗</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr"/>
+          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>沖縄県沖縄市字登川2791番地1</t>
+        </is>
+      </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
@@ -6571,17 +6574,20 @@
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事）</t>
+          <t>https://www.u-pohs.co.jp/misato/
+https://www.u-pohs.co.jp/naha-shintoshin
+https://www.u-pohs.co.jp/noborikawa/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>車買取。比較記事の「新潟市内に4店舗」による。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3360001016221、〒904-2142）。</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6597,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>鈴木自工株式会社（軽ひろば・くるま広場）</t>
+          <t>株式会社鈴木モータース</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6599,27 +6605,19 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>くるま広場 船橋習志野店、軽ひろば 佐倉王子台店、軽ひろば 千葉貝塚店、軽ひろば 千葉おゆみ店</t>
+          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>047-406-3259</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>https://kei-hiroba.car-yasui.jp/</t>
-        </is>
-      </c>
+      <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
@@ -6627,7 +6625,9 @@
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>https://kei-hiroba.car-yasui.jp/</t>
+          <t>https://www.applenet.co.jp/shop/0065/
+https://www.applenet.co.jp/shop/0071/
+https://www.applenet.co.jp/shop/0080/</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>軽自動車（新車・未使用車・中古車）専門店。サイトに「運営：鈴木自工株式会社」。店舗名はサイトのタイトル・本文から。電話はサイト記載のもの（どの店舗かは未確認）。新車の扱いが中心の可能性あり。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6647,35 +6647,27 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Dash（運営会社未確認）</t>
+          <t>買取マウス（運営会社未確認）</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>名古屋本店、西三河店、三重鈴鹿店</t>
+          <t>新潟市内4店舗</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>052-901-8008</t>
-        </is>
-      </c>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.car-dash.jp/</t>
-        </is>
-      </c>
+      <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr"/>
@@ -6683,7 +6675,7 @@
       <c r="O97" s="2" t="inlineStr"/>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>https://www.car-dash.jp/</t>
+          <t>検索結果の抜粋（比較記事）</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -6693,7 +6685,7 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店。 電話は名古屋本店のもの。</t>
+          <t>車買取。比較記事の「新潟市内に4店舗」による。</t>
         </is>
       </c>
     </row>
@@ -6703,27 +6695,35 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>ZERO MOTORS（運営会社未確認）</t>
+          <t>鈴木自工株式会社（軽ひろば・くるま広場）</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>埼玉県内3店舗</t>
+          <t>くるま広場 船橋習志野店、軽ひろば 佐倉王子台店、軽ひろば 千葉貝塚店、軽ひろば 千葉おゆみ店</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>047-406-3259</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>https://kei-hiroba.car-yasui.jp/</t>
+        </is>
+      </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
@@ -6731,17 +6731,17 @@
       <c r="O98" s="2" t="inlineStr"/>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://kei-hiroba.car-yasui.jp/</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>軽自動車・コンパクトカー専門店。「埼玉県3店舗・総在庫700台以上」との掲載による。</t>
+          <t>軽自動車（新車・未使用車・中古車）専門店。サイトに「運営：鈴木自工株式会社」。店舗名はサイトのタイトル・本文から。電話はサイト記載のもの（どの店舗かは未確認）。新車の扱いが中心の可能性あり。</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>アビックス大阪株式会社</t>
+          <t>Dash（運営会社未確認）</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6759,23 +6759,27 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市中央区南船場2丁目4番23号</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr"/>
+          <t>名古屋本店、西三河店、三重鈴鹿店</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>052-901-8008</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.car-dash.jp/</t>
+        </is>
+      </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr"/>
@@ -6783,8 +6787,7 @@
       <c r="O99" s="2" t="inlineStr"/>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -6794,7 +6797,7 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>アビックスコーポレーションのグループ会社とみられる。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7120001231212、〒542-0081）。</t>
+          <t>自社ローン専門店。 電話は名古屋本店のもの。</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6807,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>エービーエスオート（ABS Auto、運営会社未確認）</t>
+          <t>ZERO MOTORS（運営会社未確認）</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6812,12 +6815,12 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>藤沢店（藤沢市用田1531-1）、海老名店、綾瀬店</t>
+          <t>埼玉県内3店舗</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
@@ -6832,7 +6835,7 @@
       <c r="O100" s="2" t="inlineStr"/>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>https://www.kurumaerabi.com/shop/detail/29454/</t>
+          <t>検索結果の抜粋（店舗掲載）</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -6842,7 +6845,7 @@
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。公式サイト未確認。中古車情報サイトの紹介に「藤沢市用田に1店舗・海老名と綾瀬にも店舗」。</t>
+          <t>軽自動車・コンパクトカー専門店。「埼玉県3店舗・総在庫700台以上」との掲載による。</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6855,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>カーライフグループ株式会社</t>
+          <t>アビックス大阪株式会社</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -6860,58 +6863,42 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>TOKYO店、大阪店、福岡店</t>
+          <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>福岡県糟屋郡粕屋町戸原西4丁目8-11</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>0120-038-871</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>092-410-5912</t>
-        </is>
-      </c>
+          <t>大阪府大阪市中央区南船場2丁目4番23号</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>https://loanok.jp/</t>
-        </is>
-      </c>
+      <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>30名</t>
-        </is>
-      </c>
+      <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>https://loanok.jp/shop000.html
-https://loanok.jp/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門。所在地はサイト記載の住所（本社かどうかは未確認）。</t>
+          <t>アビックスコーポレーションのグループ会社とみられる。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7120001231212、〒542-0081）。</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6908,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>トーワオート（運営会社未確認）</t>
+          <t>エービーエスオート（ABS Auto、運営会社未確認）</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -6929,12 +6916,12 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>宇都宮西店、宇都宮東店、宇都宮南店</t>
+          <t>藤沢店（藤沢市用田1531-1）、海老名店、綾瀬店</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
@@ -6949,7 +6936,7 @@
       <c r="O102" s="2" t="inlineStr"/>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://www.kurumaerabi.com/shop/detail/29454/</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -6959,7 +6946,7 @@
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>宇都宮市内の3店舗。</t>
+          <t>中古トラック販売。公式サイト未確認。中古車情報サイトの紹介に「藤沢市用田に1店舗・海老名と綾瀬にも店舗」。</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6956,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>プチモ軽自動車専門店（株式会社ヒューベストオートの可能性）</t>
+          <t>カーライフグループ株式会社</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -6977,37 +6964,58 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>佐賀店、唐津店、佐世保店</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
+          <t>TOKYO店、大阪店、福岡店</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>福岡県糟屋郡粕屋町戸原西4丁目8-11</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>0120-038-871</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>092-410-5912</t>
+        </is>
+      </c>
       <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>https://loanok.jp/</t>
+        </is>
+      </c>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>30名</t>
+        </is>
+      </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（求人・店舗掲載）</t>
+          <t>https://loanok.jp/shop000.html
+https://loanok.jp/</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>佐世保店は長崎県（2025年12月開店）。運営会社は佐世保店の求人の募集元による推定。</t>
+          <t>自社ローン専門。所在地はサイト記載の住所（本社かどうかは未確認）。</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7025,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>古城モータース</t>
+          <t>トーワオート（運営会社未確認）</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -7025,31 +7033,19 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>高岡本店、富山店、石川白山店</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>富山県高岡市二塚425番地</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>0120-540-118</t>
-        </is>
-      </c>
+          <t>宇都宮西店、宇都宮東店、宇都宮南店</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kojyo-motors.com/</t>
-        </is>
-      </c>
+      <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr"/>
@@ -7057,7 +7053,7 @@
       <c r="O104" s="2" t="inlineStr"/>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/</t>
+          <t>検索結果の抜粋（店舗掲載）</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -7065,7 +7061,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>宇都宮市内の3店舗。</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>プチモ軽自動車専門店（株式会社ヒューベストオートの可能性）</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -7081,62 +7081,37 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8844</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8845</t>
-        </is>
-      </c>
+          <t>佐賀店、唐津店、佐世保店</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.autogallery.co.jp/</t>
-        </is>
-      </c>
+      <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>inquiry@autogallery.co.jp</t>
-        </is>
-      </c>
+      <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>中古車の買取・下取りあり</t>
-        </is>
-      </c>
+      <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>検索結果の抜粋（求人・店舗掲載）</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>輸入車（アメ車等）専門店。サイトの見出しは「東京 神奈川 福岡」で、古物商許可も神奈川県を含むが、店舗情報ページに載っているのは東京・大阪・福岡の3店舗。</t>
+          <t>佐世保店は長崎県（2025年12月開店）。運営会社は佐世保店の求人の募集元による推定。</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7121,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>古城モータース</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -7154,29 +7129,29 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
+          <t>高岡本店、富山店、石川白山店</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
+          <t>富山県高岡市二塚425番地</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>0120-540-118</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
+      <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
@@ -7186,20 +7161,15 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R106" s="2" t="inlineStr">
-        <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -7207,7 +7177,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>株式会社アクセス（カーライフステーション）</t>
+          <t>有限会社カネタ（カネタグループ）</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -7215,56 +7185,31 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>岩槻インター店、上尾店、久喜店</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県さいたま市見沼区宮ケ谷塔91-1</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>0120-344-713</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>048-681-5088</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>黒木 康男</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>https://344860.net/</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>https://344860.net/contact/</t>
-        </is>
-      </c>
+          <t>カネタグループ 旭川トラックセンター、カネタグループ 苫小牧トラックセンター、カネタグループ ２７５トラックセンター</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr"/>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>158人（2019年度）</t>
-        </is>
-      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>https://344860.net/company/
-https://344860.net/shop/</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -7274,7 +7219,7 @@
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車・新車専門店。電話はフリーダイヤル（会社概要記載のもの）。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：カネタグループ 旭川トラックセンター：北海道旭川市末広東一条6丁目1番8号（0166-51-9922）、カネタグループ 苫小牧トラックセンター：北海道苫小牧市字植苗163番地21（0144-51-8282）、カネタグループ ２７５トラックセンター：北海道江別市角山４２６番地１４（011-378-9922）</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7229,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>有限会社中央特車</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -7292,19 +7237,15 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>徳島県、香川県</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>愛知県東海市富木島町内堀17番地の1</t>
-        </is>
-      </c>
+          <t>中央特車(有) 営業所、徳島川内店、香川綾川店</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
@@ -7312,14 +7253,15 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -7329,7 +7271,7 @@
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8180002087515、〒476-0011）。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：中央特車(有) 営業所：徳島県板野郡北島町中村字牛飼原1-1（088-698-6225）、徳島川内店：徳島県徳島市川内町夷野99-1（088-698-6225）、香川綾川店：香川県綾歌郡綾歌町綾川町陶4331（087-899-7683）</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7281,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>栗山自動車工業株式会社</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -7347,40 +7289,31 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>千葉県、東京都、神奈川県</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
-        </is>
-      </c>
+          <t>栗山自動車工業 千葉支店、栗山自動車工業 東京、栗山自動車工業 神奈川支店</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 上武英輝</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kamitake.net/</t>
-        </is>
-      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -7388,7 +7321,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：栗山自動車工業 千葉支店：千葉県佐倉市大作2-12-2（043-498-7974）、栗山自動車工業 東京：東京都江戸川区西瑞江5-3-10（03-3689-7711）、栗山自動車工業 神奈川支店：神奈川県座間市ひばりが丘4-24-12（0120-528-828）</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -7396,7 +7333,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>株式会社クイックモーション（カラーズ）</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
@@ -7404,37 +7341,62 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>カラーズKawagoe（川越）、ほか2店舗</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8845</t>
+        </is>
+      </c>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.autogallery.co.jp/</t>
+        </is>
+      </c>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>inquiry@autogallery.co.jp</t>
+        </is>
+      </c>
       <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>中古車の買取・下取りあり</t>
+        </is>
+      </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>https://ucar.carview.yahoo.co.jp/shop/saitama/214637003/（検索結果の抜粋）</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>4WD・SUV専門店。「埼玉県を中心に3店舗」との掲載による。</t>
+          <t>輸入車（アメ車等）専門店。サイトの見出しは「東京 神奈川 福岡」で、古物商許可も神奈川県を含むが、店舗情報ページに載っているのは東京・大阪・福岡の3店舗。</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7406,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>株式会社コンチネント</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -7452,48 +7414,40 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>岡山本店、カーセブン倉敷中島店、カーセブン岡山妹尾店</t>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>岡山県岡山市南区妹尾4130-2</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>086-281-5544</t>
-        </is>
-      </c>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>平松 裕</t>
+          <t>代表取締役 河野修一</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>https://conti-nent.com/</t>
+          <t>https://www.csauto.jp/</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr">
-        <is>
-          <t>買取（カーセブン加盟店）</t>
-        </is>
-      </c>
+      <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>https://conti-nent.com/company/
-https://conti-nent.com/shops/</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -7503,7 +7457,7 @@
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>会社概要に「3店舗展開 岡山本店・倉敷中島店・岡山妹尾店」。ほかに鈑金塗装工場あり。カーセブンFC加盟。</t>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7467,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>株式会社Noa Corporation（ノアコーポレーション）</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -7521,12 +7475,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
+          <t>ノアコーポレーション、ノアコーポレーション 車両センター、ノアコーポレーション 小山展示場</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -7537,13 +7491,15 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
       <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O112" s="2" t="inlineStr"/>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -7553,7 +7509,7 @@
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：ノアコーポレーション：栃木県さくら市向河原3994-1（028-612-1474）、ノアコーポレーション 車両センター：栃木県宇都宮市宮山田町406-4（028-612-1474）、ノアコーポレーション 小山展示場：栃木県小山市西黒田169-2（028-612-1474）</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7519,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>株式会社アクセス（カーライフステーション）</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -7571,27 +7527,56 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="2" t="inlineStr"/>
+          <t>岩槻インター店、上尾店、久喜店</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県さいたま市見沼区宮ケ谷塔91-1</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>0120-344-713</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>048-681-5088</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>黒木 康男</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>https://344860.net/</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>https://344860.net/contact/</t>
+        </is>
+      </c>
       <c r="L113" s="2" t="inlineStr"/>
       <c r="M113" s="2" t="inlineStr"/>
       <c r="N113" s="2" t="inlineStr"/>
-      <c r="O113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>158人（2019年度）</t>
+        </is>
+      </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://344860.net/company/
+https://344860.net/shop/</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -7601,7 +7586,7 @@
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>ユーポス以外の事業は未確認。</t>
+          <t>届出済未使用車・新車専門店。電話はフリーダイヤル（会社概要記載のもの）。</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7596,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -7619,17 +7604,17 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>千葉県我孫子市柴崎1554番地</t>
+          <t>愛知県東海市富木島町内堀17番地の1</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
@@ -7643,9 +7628,9 @@
       <c r="O114" s="2" t="inlineStr"/>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -7656,7 +7641,7 @@
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3040001085422、〒270-1177）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8180002087515、〒476-0011）。</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7651,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーリンクス</t>
+          <t>株式会社カミタケモータース</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
@@ -7674,23 +7659,31 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>大阪府、奈良県、大分県</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>アラジン二又瀬店、アラジン小倉南店、アラジン飯塚店</t>
+          <t>枚方本店、奈良店、大分店</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>福岡県福岡市西区小戸3丁目54番39号</t>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr"/>
       <c r="M115" s="2" t="inlineStr"/>
@@ -7698,20 +7691,16 @@
       <c r="O115" s="2" t="inlineStr"/>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>https://autoc-one.jp/ullo/shop/3142/（検索結果の抜粋）
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R115" s="2" t="inlineStr">
-        <is>
-          <t>車買取りネットワーク「アラジン」の運営会社の一つ。アラジンは九州中心に複数の運営会社がある（久留米南店は株式会社Alive）。他店舗の運営会社は未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1290001023128、〒819-0001）。</t>
-        </is>
-      </c>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -7719,7 +7708,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>株式会社クイックモーション（カラーズ）</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
@@ -7727,12 +7716,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
+          <t>カラーズKawagoe（川越）、ほか2店舗</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
@@ -7747,19 +7736,17 @@
       <c r="O116" s="2" t="inlineStr"/>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://ucar.carview.yahoo.co.jp/shop/saitama/214637003/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>4WD・SUV専門店。「埼玉県を中心に3店舗」との掲載による。</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7756,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社コンチネント</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -7777,34 +7764,48 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
+          <t>岡山本店、カーセブン倉敷中島店、カーセブン岡山妹尾店</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>大分県臼杵市大字市浜807番地の1</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr"/>
+          <t>岡山県岡山市南区妹尾4130-2</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>086-281-5544</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>平松 裕</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>https://conti-nent.com/</t>
+        </is>
+      </c>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr"/>
       <c r="M117" s="2" t="inlineStr"/>
-      <c r="N117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>買取（カーセブン加盟店）</t>
+        </is>
+      </c>
       <c r="O117" s="2" t="inlineStr"/>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://conti-nent.com/company/
+https://conti-nent.com/shops/</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -7814,7 +7815,7 @@
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2320202000383、〒875-0052）。</t>
+          <t>会社概要に「3店舗展開 岡山本店・倉敷中島店・岡山妹尾店」。ほかに鈑金塗装工場あり。カーセブンFC加盟。</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7825,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>良質車専門店ネクスト（運営会社未確認）</t>
+          <t>株式会社シマダオート商事</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -7832,12 +7833,12 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>会津若松店、いわき店、白河店</t>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -7852,17 +7853,19 @@
       <c r="O118" s="2" t="inlineStr"/>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗の在庫掲載）</t>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車も扱う中古車店。3市の店舗は検索結果の在庫掲載から確認。運営会社名は未確認。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7875,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>軽ステ（運営会社未確認）</t>
+          <t>株式会社ジースタリオン（Gライオン・トラック）</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -7880,12 +7883,12 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>熊本県</t>
+          <t>岐阜県、大阪府、徳島県</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>けんぐん東店、うと店、しみず店</t>
+          <t>Ｇライオン・トラック 岐阜大垣店、Gライオン・トラック 大阪営業所、Ｇライオン・トラック 徳島営業所</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
@@ -7896,21 +7899,25 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr"/>
       <c r="M119" s="2" t="inlineStr"/>
-      <c r="N119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>熊本県最大級の軽届出済未使用車専門店（総在庫1,300台）とのこと。運営会社未確認。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：Ｇライオン・トラック 岐阜大垣店：岐阜県大垣市長沢町5-30（058-447-7708）、Gライオン・トラック 大阪営業所：大阪府泉佐野市湊1-4-38（0724-89-5465）、Ｇライオン・トラック 徳島営業所：徳島県徳島市八万町寺山248－1（088-679-1103）</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7927,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>阿部勝自動車工業株式会社</t>
+          <t>株式会社フロンティアモータース</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -7928,31 +7935,19 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>宮城県石巻市中浦1丁目2番27号</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>0120-058-012</t>
-        </is>
-      </c>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>https://k-mishiyo.abekatu.co.jp/</t>
-        </is>
-      </c>
+      <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
       <c r="M120" s="2" t="inlineStr"/>
@@ -7960,16 +7955,437 @@
       <c r="O120" s="2" t="inlineStr"/>
       <c r="P120" s="2" t="inlineStr">
         <is>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>ユーポス以外の事業は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ベネフィット</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>千葉県、東京都</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>千葉県我孫子市柴崎1554番地</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3040001085422、〒270-1177）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ユーリンクス</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>アラジン二又瀬店、アラジン小倉南店、アラジン飯塚店</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>福岡県福岡市西区小戸3丁目54番39号</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>https://autoc-one.jp/ullo/shop/3142/（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>車買取りネットワーク「アラジン」の運営会社の一つ。アラジンは九州中心に複数の運営会社がある（久留米南店は株式会社Alive）。他店舗の運営会社は未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1290001023128、〒819-0001）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>株式会社リフトオフ</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>茨城県、千葉県、東京都</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>株式会社中州自動車</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>大分県</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字市浜807番地の1</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2320202000383、〒875-0052）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>株式会社丸山自動車（トラック市加盟、仙台・前橋・草加）</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、群馬県、埼玉県</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>トラック市仙台店、丸山自動車 前橋店、埼玉草加店</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：トラック市仙台店：宮城県宮城郡利府町利府新新明前43番地（022-781-6088）、丸山自動車 前橋店：群馬県前橋市宮地町7-1（027-290-3033）、埼玉草加店：埼玉県草加市柿木74（048-933-3111）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>良質車専門店ネクスト（運営会社未確認）</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>会津若松店、いわき店、白河店</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>検索結果の抜粋（店舗の在庫掲載）</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>届出済未使用車も扱う中古車店。3市の店舗は検索結果の在庫掲載から確認。運営会社名は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>軽ステ（運営会社未確認）</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>熊本県</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>けんぐん東店、うと店、しみず店</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>検索結果の抜粋（店舗掲載）</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>熊本県最大級の軽届出済未使用車専門店（総在庫1,300台）とのこと。運営会社未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>阿部勝自動車工業株式会社</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>宮城県石巻市中浦1丁目2番27号</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>0120-058-012</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>https://k-mishiyo.abekatu.co.jp/</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
           <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q120" s="2" t="inlineStr">
+      <c r="Q128" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R120" s="2" t="inlineStr">
+      <c r="R128" s="2" t="inlineStr">
         <is>
           <t>電話はサイト記載のフリーダイヤル（本社番号かは未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6370301000037、〒986-0847）。</t>
         </is>
@@ -8019,7 +8435,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -8049,7 +8465,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -8069,7 +8485,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -8089,7 +8505,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -8099,7 +8515,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -8109,7 +8525,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -8119,7 +8535,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -8129,7 +8545,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -8139,7 +8555,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -8149,7 +8565,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -8199,7 +8615,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -8219,7 +8635,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -8259,7 +8675,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -8269,7 +8685,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -8339,7 +8755,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -8349,7 +8765,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -8389,7 +8805,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -8759,7 +9175,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79"/>
@@ -8789,7 +9205,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83">
@@ -8799,7 +9215,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84">
@@ -8829,7 +9245,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87"/>
@@ -8869,7 +9285,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R155"/>
+  <dimension ref="A1:R159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>株式会社AOZORA COMPANY</t>
+          <t>株式会社ABC</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -4211,42 +4211,61 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>東京都、新潟県、大阪府、福岡県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
+          <t>ABCcars（福山市津之郷町津之郷13-1）、ビナンオート店、TAX福山、Small store、働くクルマ専門店、Self store</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>新潟県新潟市西区黒鳥5243番地1</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
+          <t>広島県福山市津之郷町津之郷13-1</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>084-952-3003</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>佐藤 和伸</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.abc-group.co.jp</t>
+        </is>
+      </c>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>abc-soumu@abc-group.co.jp</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>47名（うち正社員40名）</t>
+        </is>
+      </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
-厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
+          <t>https://www.pref.hiroshima.lg.jp/go-hiroshima-database-kigyo/go-data-01252.html</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
+          <t>広島県の企業データベース「Go!ひろしま」で県内事業所6（福山市内）を確認。新車・未使用車・中古車販売、車検・整備。TAX福山はタックスFC加盟店。年商20億9千万円。</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4275,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>株式会社あっぷる</t>
+          <t>株式会社AOZORA COMPANY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4264,62 +4283,42 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、徳島県</t>
+          <t>東京都、新潟県、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
+          <t>オーシャンデザイン 新潟本社、オーシャンデザイン 八王子店、オーシャンデザイン 大阪和泉店、オーシャンデザイン 行橋店、ほか2店舗</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>兵庫県加古川市平岡町高畑88番地の1</t>
+          <t>新潟県新潟市西区黒鳥5243番地1</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 石戸宏樹</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apple-car.jp/inquiry</t>
-        </is>
-      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>自動車買取サービス（事業内容に記載）</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>26名</t>
-        </is>
-      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>https://www.apple-car.jp/company
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://voix.jp/life/news/74929/（検索結果の抜粋）
+厚生労働省公開PDFの企業リスト（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5140001093768、〒675-0103）。</t>
+          <t>ブランドはオーシャンデザイン（自社ローン対応の中古車販売、レンタカーも運営）。新潟本社の案内に「6店舗合わせてグループ総在庫600台」とある一方、「全国60店舗営業中」との掲載もあり、店舗数の食い違いが大きい（60店舗なら31店舗以上で除外対象）。公式サイト未確認。</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4328,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルコーポレーション</t>
+          <t>株式会社あっぷる</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4337,34 +4336,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県</t>
+          <t>兵庫県、徳島県</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
+          <t>あっぷる神戸西店、あっぷる神戸有馬店、あっぷる東加古川店、あっぷる姫路太子店、あっぷる徳島藍住店、あっぷる西宮夙川店</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>愛知県名古屋市天白区島田2丁目901番地</t>
+          <t>兵庫県加古川市平岡町高畑88番地の1</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 石戸宏樹</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apple-car.jp/inquiry</t>
+        </is>
+      </c>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>自動車買取サービス（事業内容に記載）</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>26名</t>
+        </is>
+      </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-https://www.applenet.co.jp/shop/0001/
-https://www.applenet.co.jp/shop/0020/
-https://www.applenet.co.jp/shop/0040/
+          <t>https://www.apple-car.jp/company
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -4375,7 +4391,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001023209、〒468-0056）。</t>
+          <t>ブランドは「あっぷる関西」。FCの「アップル」（アップルオートネットワーク）とは別の会社。本社所在地は会社概要に記載がない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5140001093768、〒675-0103）。</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4401,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>株式会社コバックインターナショナル（コバックカーズ）</t>
+          <t>株式会社アップルコーポレーション</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4393,17 +4409,17 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、愛知県、三重県</t>
+          <t>神奈川県、愛知県</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>コバックカーズ岐阜店、コバックカーズ岐南店、コバックカーズ軽アウトレット多治見、コバックカーズ春日井東野店、コバックカーズ春日井坂下店、コバックカーズ四日市インター店</t>
+          <t>アップル天白店、アップル横須賀佐原インター店、アップル東郷店、アップル御器所店、アップル日進竹の山店、アップル千種竹越店</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>愛知県豊田市梅坪町10丁目5番地3</t>
+          <t>愛知県名古屋市天白区島田2丁目901番地</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -4417,20 +4433,21 @@
       <c r="O61" s="2" t="inlineStr"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0208435
-https://car.motor-fan.jp/ucar/shop/0203980
-https://car.motor-fan.jp/ucar/shop/0208367
+          <t>https://www.applenet.co.jp/shop/
+https://www.applenet.co.jp/shop/0001/
+https://www.applenet.co.jp/shop/0020/
+https://www.applenet.co.jp/shop/0040/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイト・求人情報の店舗名から6店舗。店舗紹介に「グループ総在庫1500台」「系列店は愛知・岐阜・三重・静岡」とあり静岡の店舗名は不明。運営会社名は求人情報の「株式会社コバックインターナショナル コバックカーズ岐南店」の表記による（全店が同社運営かは未確認）。車検のコバック（FC本部グループ）との関係も未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001062751、〒471-0064）。</t>
+          <t>アップルの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。 参考：店舗の連絡先（アップル天白店）〒468-0056 愛知県名古屋市天白区島田2-901 TEL 052-805-5411 FAX 052-805-5412。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001023209、〒468-0056）。</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4457,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータス</t>
+          <t>株式会社コバックインターナショナル（コバックカーズ）</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4448,27 +4465,23 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>岐阜県、愛知県、三重県</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+          <t>コバックカーズ岐阜店、コバックカーズ岐南店、コバックカーズ軽アウトレット多治見、コバックカーズ春日井東野店、コバックカーズ春日井坂下店、コバックカーズ四日市インター店</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>神奈川県大和市福田7丁目39番地13</t>
+          <t>愛知県豊田市梅坪町10丁目5番地3</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tortoise-k-carlife.com/</t>
-        </is>
-      </c>
+      <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr"/>
@@ -4476,88 +4489,78 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
+          <t>https://car.motor-fan.jp/ucar/shop/0208435
+https://car.motor-fan.jp/ucar/shop/0203980
+https://car.motor-fan.jp/ucar/shop/0208367
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト未確認。中古車情報サイト・求人情報の店舗名から6店舗。店舗紹介に「グループ総在庫1500台」「系列店は愛知・岐阜・三重・静岡」とあり静岡の店舗名は不明。運営会社名は求人情報の「株式会社コバックインターナショナル コバックカーズ岐南店」の表記による（全店が同社運営かは未確認）。車検のコバック（FC本部グループ）との関係も未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6180001062751、〒471-0064）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>株式会社トータス</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>トータス 大和店、トータス 厚木店、トータス 相模原店、トータス 平塚店、アップル大和店、アップル相模原店</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県大和市福田7丁目39番地13</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tortoise-k-carlife.com/</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
           <t>https://www.tortoise-k-carlife.com/（接続できず。検索結果の抜粋）
 https://www.applenet.co.jp/shop/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q62" s="2" t="inlineStr">
+      <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="R63" s="2" t="inlineStr">
         <is>
           <t>軽自動車の中古車・未使用車専門店「トータス」4店舗（検索結果に表示された公式サイトの店舗一覧）と、アップル加盟店2店舗（本部サイトで運営会社「株式会社トータス」を確認）の合計。専門店トータスの運営会社がアップル加盟店と同じ法人かは、公式サイトに接続できず未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1021001025628、〒242-0024）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>株式会社ナック（ジャック査定センター）</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>京都府、大阪府、兵庫県</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>078-685-0066</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 難波克年</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>https://jacnet.jp/</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>中古車の査定買取（主業）</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>https://jacnet.jp/site/company/?pt=detail
-https://jacnet.jp/site/company/?pt=shop_list</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4570,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>株式会社ナッツ</t>
+          <t>株式会社ナック（ジャック査定センター）</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4575,39 +4578,48 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>北海道、埼玉県、神奈川県、愛知県、京都府、福岡県</t>
+          <t>京都府、大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>福岡県の店舗・支店（店名未確認）、北海道の店舗・支店（店名未確認）、埼玉県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、愛知県の店舗・支店（店名未確認）、京都府の店舗・支店（店名未確認）</t>
+          <t>ジャック神戸（本社）、ジャック東灘、ジャック姫路、ジャック箕面、ジャック京都南（伏見）、ジャック京都（右京）</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>福岡県遠賀郡遠賀町尾崎1704-3</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>093-293-8888</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>兵庫県神戸市兵庫区西柳原町4-8</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>078-685-0066</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 難波克年</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://nutsrv.co.jp/</t>
+          <t>https://jacnet.jp/</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>中古車の査定買取（主業）</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>https://www.jrva.com/organization/members/</t>
+          <t>https://jacnet.jp/site/company/?pt=detail
+https://jacnet.jp/site/company/?pt=shop_list</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -4617,7 +4629,7 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
+          <t>車買取専門店JAC（ジャック）。1994年創業で関西で営業。店舗名は店舗一覧の住所から付けた（6店舗）。同名の上場企業「株式会社ナック」（東京）とは別会社なので注意。</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4639,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>株式会社ファインソレイユ</t>
+          <t>株式会社ナッツ</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4635,23 +4647,31 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、長崎県</t>
+          <t>北海道、埼玉県、神奈川県、愛知県、京都府、福岡県</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
+          <t>福岡県の店舗・支店（店名未確認）、北海道の店舗・支店（店名未確認）、埼玉県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、愛知県の店舗・支店（店名未確認）、京都府の店舗・支店（店名未確認）</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>佐賀県三養基郡みやき町大字原古賀字六本松1902番地2</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
+          <t>福岡県遠賀郡遠賀町尾崎1704-3</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>093-293-8888</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>https://nutsrv.co.jp/</t>
+        </is>
+      </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr"/>
@@ -4659,18 +4679,17 @@
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.jrva.com/organization/members/</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6300001009252、〒849-0101）。</t>
+          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4699,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>株式会社メディアトラスト（クルオク）</t>
+          <t>株式会社ファインソレイユ</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4688,75 +4707,42 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>福岡県、佐賀県、長崎県</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>クルオク 名古屋インター店（本社）、クルオク レスパ岡崎店、クルオク 豊田吉原店、クルオク カーマ21稲沢店、クルオク カインズホーム半田店、クルオク カインズモール蒲郡店</t>
+          <t>フレスカー 本店（みやき町）、フレスカー 東脊振インター店、フレスカー 福岡インター店、ほか3店舗（佐賀・長崎・福岡）</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>愛知県名古屋市名東区高針台1-110</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>0564-58-9609</t>
-        </is>
-      </c>
+          <t>佐賀県三養基郡みやき町大字原古賀字六本松1902番地2</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>鬼頭 宏彰</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.9609.biz/</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.9609.biz/contact/</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>info@kuruma094.com</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>https://twitter.com/kuruma094
-https://www.facebook.com/kuruoku/</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>買取あり（事業内容に「国内の中古車の買取り」）</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>正社員4名・パート2名・役員4名（2025年12月現在）</t>
-        </is>
-      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>https://www.9609.biz/company/
-https://www.9609.biz/store/</t>
+          <t>https://www.goo-net.com/usedcar_shop/0802654/showroom.html（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>6拠点のうち5つはショッピングモール・ホームセンターの屋上や駐車場内の常設展示場。従業員は少人数。</t>
+          <t>ブランドはフレスカー。「佐賀・長崎・福岡に6店舗」は検索結果に表示された店舗紹介文による。公式サイトは見つからず、6店舗すべての店舗名は確認できていない。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6300001009252、〒849-0101）。</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4752,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユー・パーク</t>
+          <t>株式会社メディアトラスト（クルオク）</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4774,48 +4760,65 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
+          <t>クルオク 名古屋インター店（本社）、クルオク レスパ岡崎店、クルオク 豊田吉原店、クルオク カーマ21稲沢店、クルオク カインズホーム半田店、クルオク カインズモール蒲郡店</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
+          <t>愛知県名古屋市名東区高針台1-110</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>048-798-9566</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>048-798-9590</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>0564-58-9609</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>鬼頭 宏彰</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>https://www.9609.biz/</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.9609.biz/contact/</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>info@kuruma094.com</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/kuruma094
+https://www.facebook.com/kuruoku/</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>買取無料査定あり</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr"/>
+          <t>買取あり（事業内容に「国内の中古車の買取り」）</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>正社員4名・パート2名・役員4名（2025年12月現在）</t>
+        </is>
+      </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-parknet.com/about-us/
-https://www.u-parknet.com/</t>
+          <t>https://www.9609.biz/company/
+https://www.9609.biz/store/</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -4825,7 +4828,7 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+          <t>6拠点のうち5つはショッピングモール・ホームセンターの屋上や駐車場内の常設展示場。従業員は少人数。</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4838,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロペライオ</t>
+          <t>株式会社ユー・パーク</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4843,29 +4846,33 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、東京都、愛知県、京都府</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>ロペライオ練馬、ロペライオさいたま、モーターホーム by ロペライオ、東日本買取センター、中部買取センター、西日本買取センター</t>
+          <t>本店、ギャラリア店、スクウェアー店、アリーナ店、プラザ店、スタイル店</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>東京都世田谷区太子堂4-1-1 キャロットタワー6F</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>早水 彰</t>
-        </is>
-      </c>
+          <t>埼玉県さいたま市岩槻区釣上新田329-1</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>048-798-9566</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>048-798-9590</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://loperaio.co.jp/</t>
+          <t>https://www.u-parknet.com/</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
@@ -4873,80 +4880,90 @@
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>買取センター3拠点（東日本・中部・西日本）</t>
+          <t>買取無料査定あり</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.u-parknet.com/about-us/
+https://www.u-parknet.com/</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>国産車・輸入車（メルセデス・BMW等）の中古車販売。店舗は公式サイトの店舗情報6店舗（ほかに整備工場2か所）。各店舗の所在県は本社と同じ埼玉県と推定（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ロペライオ</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県、東京都、愛知県、京都府</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>ロペライオ練馬、ロペライオさいたま、モーターホーム by ロペライオ、東日本買取センター、中部買取センター、西日本買取センター</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>東京都世田谷区太子堂4-1-1 キャロットタワー6F</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>早水 彰</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>https://loperaio.co.jp/</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>買取センター3拠点（東日本・中部・西日本）</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr">
         <is>
           <t>https://loperaio.co.jp/shop_index.html
 https://loperaio.co.jp/shop_head_office.html
 https://loperaio.co.jp/company_index.html</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="inlineStr">
+      <c r="Q69" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R68" s="2" t="inlineStr">
+      <c r="R69" s="2" t="inlineStr">
         <is>
           <t>輸入中古車専門店。ショップガイドの住所と店舗名の対応はページの画像代替テキストから推定（買取センターの所在県は住所一覧からの推定）。ほかに本社・セントラルベース・ファクトリーセンター（非販売拠点）、ボランタリーチェーンのロペシティ西宮（うかいや運営）・札幌平岸（三愛自動車工業運営）。健康経営優良法人（大規模法人部門）取得。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>株式会社丸山自動車（ポケットカーズ）</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>新潟県</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>ポケットカーズ（三条市上須頃）、ポケットカーズ 女池インター店（新潟市中央区女池神明）、ポケットカーズ（長岡市堺町）、ポケットカーズ（新潟市中央区紫竹山）、ポケットカーズ（新潟市西区寺尾）、アップル三条店</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pocketcars.jp/</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="2" t="inlineStr"/>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pocketcars.jp/shop/
-https://www.pocketcars.jp/shop/
-https://www.applenet.co.jp/shop/0317/
-https://mynavi-agent.jp/corpdetail/40198/</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>軽未使用車専門店。運営会社は、転職サイトの会社紹介「1995年以降は車検のコバック、鈑金のモドーリー、ポケットカーズなどの店舗拡大」と、アップル三条店（運営：株式会社丸山自動車）から判断。ポケットカーズの店舗数は公式サイト店舗一覧の住所5件（店名が取れなかった店舗は所在地で表記）＋アップル1店。</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4973,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>楠永自動車株式会社（KS-selection）</t>
+          <t>株式会社丸山自動車（ポケットカーズ）</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4964,19 +4981,23 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>大阪府</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KS-selection 和泉店、KS-selection 松原店（松原市立部3-455-1）、KS-selection 堺インター店、KS-selection 高石店</t>
+          <t>ポケットカーズ（三条市上須頃）、ポケットカーズ 女池インター店（新潟市中央区女池神明）、ポケットカーズ（長岡市堺町）、ポケットカーズ（新潟市中央区紫竹山）、ポケットカーズ（新潟市西区寺尾）、アップル三条店</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pocketcars.jp/</t>
+        </is>
+      </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr"/>
@@ -4984,89 +5005,70 @@
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr">
         <is>
+          <t>https://www.pocketcars.jp/shop/
+https://www.pocketcars.jp/shop/
+https://www.applenet.co.jp/shop/0317/
+https://mynavi-agent.jp/corpdetail/40198/</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>軽未使用車専門店。運営会社は、転職サイトの会社紹介「1995年以降は車検のコバック、鈑金のモドーリー、ポケットカーズなどの店舗拡大」と、アップル三条店（運営：株式会社丸山自動車）から判断。ポケットカーズの店舗数は公式サイト店舗一覧の住所5件（店名が取れなかった店舗は所在地で表記）＋アップル1店。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>楠永自動車株式会社（KS-selection）</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>KS-selection 和泉店、KS-selection 松原店（松原市立部3-455-1）、KS-selection 堺インター店、KS-selection 高石店</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
           <t>https://car.motor-fan.jp/ucar/shop/0708174
 https://page.line.me/569icpmb
 https://ctn-net.jp/useful/detail/1258/</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="inlineStr">
+      <c r="Q71" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R70" s="2" t="inlineStr">
+      <c r="R71" s="2" t="inlineStr">
         <is>
           <t>公式サイト未確認。2023年の中古車販売店紹介記事に「大阪の堺・和泉を中心にKS-selectionを6店舗展開」。確認できた店舗は4（和泉・松原・堺インター・高石）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>大久自動車販売株式会社</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>福島県</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>ダイキュー飯坂店、ダイキュー郡山店、ダイキュー白河中央インター店、ダイキューいわき店、ダイキュー会津若松店</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>福島県福島市本内字北古舘9</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>024-542-1221</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daiq-car.jp/</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daiq-car.jp/contact</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>https://twitter.com/DaiQ_motors
-https://www.facebook.com/daiq.motors/
-https://www.instagram.com/daiq_motors.official/</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr"/>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daiq-car.jp/</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="inlineStr">
-        <is>
-          <t>軽自動車専門店ダイキュー。運営会社名は公式サイトの古物営業法に基づく表示による。店舗は公式サイトの5店舗。</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5078,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>有限会社松下モータース</t>
+          <t>三島オート販売株式会社</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -5089,32 +5091,28 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>静岡県掛川市菊浜59-1</t>
-        </is>
-      </c>
+          <t>本店（三島市、国道1号バイパス沿い）、八反畑店（民間車検工場併設）、沼津店、富士店、裾野店</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>0537-72-2583</t>
+          <t>055-971-7743</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0537-72-5067</t>
+          <t>055-971-7764</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>松下 佳正</t>
+          <t>澤田 稔</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.ecar.co.jp/</t>
+          <t>https://www.mishima-auto.jp/</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
@@ -5124,8 +5122,8 @@
       <c r="O72" s="2" t="inlineStr"/>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>https://www.ecar.co.jp/mamo.html
-https://www.ecar.co.jp/</t>
+          <t>https://www.mishima-auto.jp/shop/shopList.aspx
+https://www.mishima-auto.jp/summary/summary.aspx</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -5135,7 +5133,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。 【2026-10更新】公式サイトに「静岡県内5店舗」とあるため6→5に修正（展示場は本店1拠点）。法人格・会社概要は未確認。 会社概要で社名・代表・本社を確認。拠点は本店展示場・本店第二展示場・磐田・掛川ほか（会社概要の拠点一覧）。</t>
+          <t>静岡県東部の中古車量販店（創業58年、展示車両600台）。サイトの表記は「静岡県東部に6店舗」だが、店舗一覧で確認できた中古車店は5（ほかに民間車検工場）。電話は本店。</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5143,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>株式会社CIA</t>
+          <t>大久自動車販売株式会社</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -5153,55 +5151,49 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
+          <t>ダイキュー飯坂店、ダイキュー郡山店、ダイキュー白河中央インター店、ダイキューいわき店、ダイキュー会津若松店</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+          <t>福島県福島市本内字北古舘9</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>0297-47-9588</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>0297-47-9577</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 大内康弘</t>
-        </is>
-      </c>
+          <t>024-542-1221</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr"/>
+          <t>https://www.daiq-car.jp/</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daiq-car.jp/contact</t>
+        </is>
+      </c>
       <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>キャンピングカー買取（買取センター4か所）</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/DaiQ_motors
+https://www.facebook.com/daiq.motors/
+https://www.instagram.com/daiq_motors.official/</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>https://www.yacco.cc/company/</t>
+          <t>https://www.daiq-car.jp/</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -5211,7 +5203,7 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。 電話・FAXは本社と同住所の守谷店（Yacco本店）のもの。</t>
+          <t>軽自動車専門店ダイキュー。運営会社名は公式サイトの古物営業法に基づく表示による。店舗は公式サイトの5店舗。</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5213,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>株式会社NIIZAWA</t>
+          <t>有限会社松下モータース</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -5229,62 +5221,48 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>広島県、山口県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
+          <t>本店（掛川市菊浜）、掛川市内ほか4店舗、磐田店</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>広島県廿日市市大野原1丁目2-20</t>
+          <t>静岡県掛川市菊浜59-1</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>0829-30-8103</t>
+          <t>0537-72-2583</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0829-30-8104</t>
+          <t>0537-72-5067</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
+          <t>松下 佳正</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.kei-market.co.jp/</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kei-market.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>https://www.ecar.co.jp/</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/keimarket.k
-https://www.facebook.com/share/1AhR49eysR
-https://youtube.com/@keimarket398</t>
-        </is>
-      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>95名（パート含む）</t>
-        </is>
-      </c>
+      <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>https://www.kei-market.co.jp/company/
-https://www.kei-market.co.jp/store/</t>
+          <t>https://www.ecar.co.jp/mamo.html
+https://www.ecar.co.jp/</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -5294,7 +5272,7 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
+          <t>未使用車の大型展示場。「静岡県掛川市5店舗、磐田市1店舗」は検索結果に表示された店舗紹介文による。別の掲載では3拠点（本店・掛川店・磐田店）。法人格・会社概要は未確認。 【2026-10更新】公式サイトに「静岡県内5店舗」とあるため6→5に修正（展示場は本店1拠点）。法人格・会社概要は未確認。 会社概要で社名・代表・本社を確認。拠点は本店展示場・本店第二展示場・磐田・掛川ほか（会社概要の拠点一覧）。</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5282,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>株式会社TSC</t>
+          <t>株式会社CIA</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5312,45 +5290,65 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県、千葉県</t>
+          <t>宮城県、茨城県、神奈川県、愛知県、佐賀県</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>大久保駅前店、千葉北インター店、蘇我インター店、買取直販 つくば店、北本店</t>
+          <t>Yacco 守谷店（本店）、仙台買取センター、横浜買取センター、名古屋買取センター、鳥栖買取センター</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>千葉県千葉市美浜区中瀬（番地は未確認）</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
+          <t>茨城県守谷市板戸井1114番地（Yaccoの丘キャンプ場内）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>0297-47-9588</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>0297-47-9577</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 大内康弘</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yacco.cc/</t>
+        </is>
+      </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>買取直販（買取車両を展示販売）</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr"/>
+          <t>キャンピングカー買取（買取センター4か所）</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>https://job.rikunabi.com/job_descriptions/82de25d5815e8620/（検索結果の抜粋。現在は404）</t>
+          <t>https://www.yacco.cc/company/</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。求人情報の勤務地一覧から5店舗。本社の美浜区中瀬・蘇我インター店の緑区古市場町が、KiND OUTLETのプライバシーポリシー記載会社（NEXTGATE MOTOR SOLUTIONS、美浜区中瀬）・同千葉コンパクトハイブリッド店（緑区古市場町）と近く、同一グループの可能性あり（未確認）。</t>
+          <t>ブランドはYacco（キャンピングカー販売・買取）。会社概要の「店舗」欄7件のうち、水海道の工場2か所を除いた5店舗（販売1＋買取センター4）。キャンピングカー専門のため業態は要判断。 電話・FAXは本社と同住所の守谷店（Yacco本店）のもの。</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5358,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>株式会社Y's GARAGE</t>
+          <t>株式会社NIIZAWA</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5368,47 +5366,62 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>京都府、鳥取県、島根県</t>
+          <t>広島県、山口県</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
+          <t>軽マーケット 廿日市店、軽マーケット 大竹店、軽マーケット バン・トラック専門店、ケイマーケット ハイブリッドカー&amp;コンパクトカー専門店、フラット7 岩国店</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>京都府宇治市槇島町三十五38-1</t>
+          <t>広島県廿日市市大野原1丁目2-20</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>0774-25-5557</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
+          <t>0829-30-8103</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0829-30-8104</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 桐畑勇志</t>
+          <t>代表取締役会長 新沢亮二／代表取締役社長 栗原亮太</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://k-smile.jp/</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
+          <t>https://www.kei-market.co.jp/</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kei-market.co.jp/contact/</t>
+        </is>
+      </c>
       <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/keimarket.k
+https://www.facebook.com/share/1AhR49eysR
+https://youtube.com/@keimarket398</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>158名（アルバイト含む、令和8年10月）</t>
+          <t>95名（パート含む）</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>https://k-smile.jp/company/</t>
+          <t>https://www.kei-market.co.jp/company/
+https://www.kei-market.co.jp/store/</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -5418,7 +5431,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
+          <t>ブランドは軽マーケット。公式サイトの「6店舗」には車検のコバック廿日市大野店が含まれるため、販売店は5店舗とした。フラット7はFCブランド。</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5441,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>株式会社アールブイランド（RVランド）</t>
+          <t>株式会社TSC</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5436,51 +5449,49 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>北海道、茨城県、千葉県、佐賀県</t>
+          <t>茨城県、埼玉県、千葉県</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>本社（常総市）、RVランド イオンモールつくば店、RVランド コンセプト（流山店）、RVランド 北海道（千歳市）、RVランド 九州 鳥栖展示場</t>
+          <t>大久保駅前店、千葉北インター店、蘇我インター店、買取直販 つくば店、北本店</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>茨城県常総市大塚戸町1600-1</t>
+          <t>千葉県千葉市美浜区中瀬（番地は未確認）</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>0297-27-6767</t>
+          <t>047-409-0147</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0297-27-6768</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>阿部 和英</t>
-        </is>
-      </c>
+          <t>047-409-0149</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>https://www.rvland.co.jp/</t>
+          <t>https://www.tsc-jp.net/</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr"/>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>社員67名、パート28名</t>
-        </is>
-      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>買取直販（買取車両を展示販売）</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr"/>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>https://www.rvland.co.jp/about/gaiyou.php</t>
+          <t>https://www.tsc-jp.net/
+https://www.tsc-jp.net/company.html
+https://job.rikunabi.com/job_descriptions/82de25d5815e8620/（検索結果の抜粋。現在は404）</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -5490,7 +5501,7 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（製造・販売、新車・中古車）。会社概要の拠点のうち販売店・展示場を5で計上（ほかに常総市大生郷町・久留米市の拠点あり、業態未確認）。</t>
+          <t>【2026-10更新】公式サイト（くるま買取・直販の株式会社TSC）で大久保駅前店・千葉北インター店・蘇我インター店・つくば店の4店舗を確認。北本店は求人情報の勤務地一覧による（公式サイトでは未確認）。本社の美浜区中瀬・蘇我インター店の緑区古市場町が、KiND OUTLET（NEXTGATE MOTORSOLUTIONS、美浜区中瀬）と近く、同一グループの可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5511,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>株式会社ウシジマ（UJグループ・ウシトラ）</t>
+          <t>株式会社Y's GARAGE</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5508,55 +5519,47 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、東京都、京都府、福岡県</t>
+          <t>京都府、鳥取県、島根県</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>八女本社、福岡支店（展示場）、埼玉支店（展示場）、東京営業所、京都支店</t>
+          <t>K-Smile洛西店、K-Smile宇治店、K-Smile伏見店、K-Smile出雲店、K-Smile鳥取店</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>福岡県八女市室岡377-10</t>
+          <t>京都府宇治市槇島町三十五38-1</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>0943-24-1126</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0943-24-4812</t>
-        </is>
-      </c>
+          <t>0774-25-5557</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>牛島 豊晴</t>
+          <t>代表取締役 桐畑勇志</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushitruck.com/</t>
+          <t>https://k-smile.jp/</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック買取あり</t>
-        </is>
-      </c>
+      <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>106名（スタッフ数）</t>
+          <t>158名（アルバイト含む、令和8年10月）</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushitruck.com/truck/corporate</t>
+          <t>https://k-smile.jp/company/</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -5566,7 +5569,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売・買取。拠点数は販売系の本社・支店・営業所で計上（ほかに部品のウシパーツ、レンタル店）。電話・FAXは会社概要記載のもの（本社の番号かは未確認）。</t>
+          <t>ブランドはK-Smile（軽未使用車）。会社概要の店舗情報は5店舗。LINE公式アカウントには「ケイスマイル松江店」もあり、含めると6店舗の可能性。電話番号は宇治店（本社と同じ住所）のもの。</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5579,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>株式会社ケーワン（5-STAR）</t>
+          <t>株式会社アールブイランド（RVランド）</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5584,44 +5587,61 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>北海道、茨城県、千葉県、佐賀県</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>5-STAR 越谷店、5-STAR 春日部店、5-STAR 三郷店、5-STAR 土浦店、5-STAR 阿見店</t>
+          <t>本社（常総市）、RVランド イオンモールつくば店、RVランド コンセプト（流山店）、RVランド 北海道（千歳市）、RVランド 九州 鳥栖展示場</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>埼玉県越谷市大間野町3丁目146番地</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
+          <t>茨城県常総市大塚戸町1600-1</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>0297-27-6767</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>0297-27-6768</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>阿部 和英</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rvland.co.jp/</t>
+        </is>
+      </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr"/>
-      <c r="O79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>社員67名、パート28名</t>
+        </is>
+      </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>https://employment.en-japan.com/comp-66249/
-https://car.motor-fan.jp/ucar/shop/3000451
-https://compalyze.co.jp/company/2030001068305
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.rvland.co.jp/about/gaiyou.php</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。求人情報に「埼玉県・茨城県の5-STAR各店舗（越谷・春日部・三郷・土浦）」、中古車情報サイトに阿見店。ランキング記事では「埼玉県中心に6店舗」。越谷店は越谷市大間野町3-146。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9030001065279、〒343-0844）。</t>
+          <t>【要判断】キャンピングカー専門（製造・販売、新車・中古車）。会社概要の拠点のうち販売店・展示場を5で計上（ほかに常総市大生郷町・久留米市の拠点あり、業態未確認）。</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5651,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>株式会社コバタコーポレーション（カーショップコバタ）</t>
+          <t>株式会社ウシジマ（UJグループ・ウシトラ）</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5639,38 +5659,65 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>福岡県、佐賀県、宮崎県</t>
+          <t>埼玉県、東京都、京都府、福岡県</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>宮崎 ハイブリッド・セダン専門店、カーショップコバタ鳥栖店（鳥栖市幡崎町977-1）、福岡の店舗（店名未確認）</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+          <t>八女本社、福岡支店（展示場）、埼玉支店（展示場）、東京営業所、京都支店</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>福岡県八女市室岡377-10</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>0943-24-1126</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0943-24-4812</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>牛島 豊晴</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ushitruck.com/</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック買取あり</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>106名（スタッフ数）</t>
+        </is>
+      </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>https://autoc-one.jp/used/shop/980/
-https://page.line.me/804olnjj</t>
+          <t>https://www.ushitruck.com/truck/corporate</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。ミニバン・コンパクト・ハイブリッド専門店。宮崎で創業、中古車情報サイトの紹介に「九州で宮崎・佐賀・福岡など5店舗」。確認できた店舗は2。</t>
+          <t>中古トラック販売・買取。拠点数は販売系の本社・支店・営業所で計上（ほかに部品のウシパーツ、レンタル店）。電話・FAXは会社概要記載のもの（本社の番号かは未確認）。</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5727,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>株式会社トップオート（埼玉・福島）</t>
+          <t>株式会社ケーワン（5-STAR）</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5688,15 +5735,19 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>福島県、埼玉県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>トップオート越谷（軽自動車専門店）、TOP AUTO三郷 軽自動車50万円以下専門店、上尾整備工場（求人情報）、福島県の店舗（店名未確認）</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
+          <t>5-STAR 越谷店、5-STAR 春日部店、5-STAR 三郷店、5-STAR 土浦店、5-STAR 阿見店</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県越谷市大間野町3丁目146番地</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
@@ -5708,8 +5759,10 @@
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>https://ctn-net.jp/useful/detail/1258/
-https://www.goo-net.com/usedcar_shop/0504836/detail.html</t>
+          <t>https://employment.en-japan.com/comp-66249/
+https://car.motor-fan.jp/ucar/shop/3000451
+https://compalyze.co.jp/company/2030001068305
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -5719,7 +5772,7 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。2023年の紹介記事に「埼玉県、福島県に計5店舗、ミニバン・ハイエース専門店や軽自動車専門店、4WD専門店など」。確認できた販売店は越谷・三郷の2店（上尾は整備工場）。</t>
+          <t>公式サイト未確認。求人情報に「埼玉県・茨城県の5-STAR各店舗（越谷・春日部・三郷・土浦）」、中古車情報サイトに阿見店。ランキング記事では「埼玉県中心に6店舗」。越谷店は越谷市大間野町3-146。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号9030001065279、〒343-0844）。</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5782,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>株式会社トータルカーサービス（ミニクス）</t>
+          <t>株式会社コバタコーポレーション（カーショップコバタ）</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5737,63 +5790,38 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、広島県</t>
+          <t>福岡県、佐賀県、宮崎県</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>ミニクス 福山店、ミニクス 福山中央店、ミニクス アウトレット店、ミニクス 姫路店、ミニクス 加古川店</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>広島県福山市南手城町1丁目14-7</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>084-973-1147</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>084-973-1148</t>
-        </is>
-      </c>
+          <t>宮崎 ハイブリッド・セダン専門店、カーショップコバタ鳥栖店（鳥栖市幡崎町977-1）、福岡の店舗（店名未確認）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>https://minics.jp/</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>https://minics.jp/contact</t>
-        </is>
-      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/minics_2021/
-https://www.youtube.com/channel/UCtdVZXmW98t3g6RypKRTXzg</t>
-        </is>
-      </c>
+      <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>https://minics.jp/shop
-https://minics.jp/about</t>
+          <t>https://autoc-one.jp/used/shop/980/
+https://page.line.me/804olnjj</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>軽トラ・軽バン専門店。サイトに「ミニクス運営：株式会社トータルカーサービス」。所在地は福山中央店と同じ住所の記載（本社かどうかは未確認）。</t>
+          <t>公式サイト未確認。ミニバン・コンパクト・ハイブリッド専門店。宮崎で創業、中古車情報サイトの紹介に「九州で宮崎・佐賀・福岡など5店舗」。確認できた店舗は2。</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5831,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>株式会社ロイヤルオートサービス</t>
+          <t>株式会社トップオート（埼玉・福島）</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5811,192 +5839,190 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>福島県、埼玉県</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>トップオート越谷（軽自動車専門店）、TOP AUTO三郷 軽自動車50万円以下専門店、上尾整備工場（求人情報）、福島県の店舗（店名未確認）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>https://ctn-net.jp/useful/detail/1258/
+https://www.goo-net.com/usedcar_shop/0504836/detail.html</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト未確認。2023年の紹介記事に「埼玉県、福島県に計5店舗、ミニバン・ハイエース専門店や軽自動車専門店、4WD専門店など」。確認できた販売店は越谷・三郷の2店（上尾は整備工場）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>株式会社トータルカーサービス（ミニクス）</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県、広島県</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>ミニクス 福山店、ミニクス 福山中央店、ミニクス アウトレット店、ミニクス 姫路店、ミニクス 加古川店</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>広島県福山市南手城町1丁目14-7</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>084-973-1147</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>084-973-1148</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>https://minics.jp/</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>https://minics.jp/contact</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/minics_2021/
+https://www.youtube.com/channel/UCtdVZXmW98t3g6RypKRTXzg</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>https://minics.jp/shop
+https://minics.jp/about</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>軽トラ・軽バン専門店。サイトに「ミニクス運営：株式会社トータルカーサービス」。所在地は福山中央店と同じ住所の記載（本社かどうかは未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ロイヤルオートサービス</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
           <t>長野県</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>ロイヤルカーステーション 松本村井店、ロイヤルカーステーション 松本出川店（39.8専門店）、ロイヤルカーステーション 佐久インター店、ロイヤルカーステーション 茅野店、ロイヤルカーステーション 諏訪インター店</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>長野県松本市村井町南2-1-5</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>0120-107-817</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>代表取締役 中田忠章</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/contact/</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>https://twitter.com/royal_auto_
 https://www.instagram.com/royal_auto_service/?hl=ja
 https://www.youtube.com/channel/UCNsrLCF0b44NckH-YN-fH0g/videos</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr"/>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>187名</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr">
+      <c r="P85" s="2" t="inlineStr">
         <is>
           <t>https://carstation.royal-auto.jp/company/</t>
         </is>
       </c>
-      <c r="Q83" s="2" t="inlineStr">
+      <c r="Q85" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R83" s="2" t="inlineStr">
+      <c r="R85" s="2" t="inlineStr">
         <is>
           <t>軽自動車専門店ロイヤルカーステーション。店舗は会社の沿革と検索結果から集めたもので、茅野店と諏訪インター店が同じ店かどうかは未確認（4店舗の可能性）。スズキアリーナ（新車）・車検のコバック・鈑金のモドーリーも運営。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>株式会社東部オート（東部オートグループ）</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>群馬県</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>高前バイパス店、前橋店、小鳥店、ラビット高前バイパス店、ラビット高崎小鳥店</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>群馬県高崎市小八木町1538</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>田口 治</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tobu-auto.com/</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>買取店（ラビット加盟2店舗、買取事業部をLinksより継承）</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>81名</t>
-        </is>
-      </c>
-      <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tobu-auto.com/about
-https://www.tobu-auto.com/</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R84" s="2" t="inlineStr">
-        <is>
-          <t>会社概要の事業所数は10店舗（整備・鈑金拠点等を含むとみられる）。中古車販売3店舗＋ラビット2店舗で計上。グループにBMW正規販売のモトーレン群馬・栃木（別法人）あり。年商59億円（会社概要）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>株式会社横浜ユーポス</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>栃木県、神奈川県</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県川崎市高津区二子6丁目14番10号</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr"/>
-      <c r="O85" s="2" t="inlineStr"/>
-      <c r="P85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.u-pohs.co.jp/search_shop
-https://www.u-pohs.co.jp/kouhoku
-https://www.u-pohs.co.jp/shonanhiratsuka
-https://www.u-pohs.co.jp/tsuzuki
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R85" s="2" t="inlineStr">
-        <is>
-          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6020001091254、〒213-0002）。</t>
         </is>
       </c>
     </row>
@@ -6006,49 +6032,56 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>NEXTGATE MOTORSOLUTIONS株式会社（KiND OUTLET）</t>
+          <t>株式会社東部オート（東部オートグループ）</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>群馬県</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>市原店、千葉蘇我インター軽専門店、山武成東店、千葉コンパクトハイブリッド店</t>
+          <t>高前バイパス店、前橋店、小鳥店、ラビット高前バイパス店、ラビット高崎小鳥店</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>千葉県千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F（プライバシーポリシー記載の所在地）</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>0436-55-9169</t>
-        </is>
-      </c>
+          <t>群馬県高崎市小八木町1538</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>田口 治</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://kindoutlet.jp/</t>
+          <t>https://www.tobu-auto.com/</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>買取店（ラビット加盟2店舗、買取事業部をLinksより継承）</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>81名</t>
+        </is>
+      </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>https://kindoutlet.jp/shop
-https://kindoutlet.jp/privacypolicy
-https://ucar.carview.yahoo.co.jp/shop/chiba/309220005/group/</t>
+          <t>https://www.tobu-auto.com/about
+https://www.tobu-auto.com/</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -6058,7 +6091,7 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>千葉県の軽自動車・コンパクト／ハイブリッド専門店。運営会社は、公式サイトのプライバシーポリシー記載の会社名と、中古車情報サイトの系列店一覧（NEXTGATE MOTORSOLUTIONS株式会社の系列店一覧）で確認。プライバシーポリシー記載の所在地は千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F。電話は市原店。TSCと同一グループの可能性あり（未確認）。</t>
+          <t>会社概要の事業所数は10店舗（整備・鈑金拠点等を含むとみられる）。中古車販売3店舗＋ラビット2店舗で計上。グループにBMW正規販売のモトーレン群馬・栃木（別法人）あり。年商59億円（会社概要）。</t>
         </is>
       </c>
     </row>
@@ -6068,23 +6101,27 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>ニシオ自販</t>
+          <t>株式会社横浜ユーポス</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>栃木県、神奈川県</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>静岡県西部の4店舗</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
+          <t>ユーポス港北店、ユーポス湘南平塚支店、ユーポス都筑支店、ユーポス宇都宮支店、</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県川崎市高津区二子6丁目14番10号</t>
+        </is>
+      </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
@@ -6096,17 +6133,21 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋</t>
+          <t>https://www.u-pohs.co.jp/search_shop
+https://www.u-pohs.co.jp/kouhoku
+https://www.u-pohs.co.jp/shonanhiratsuka
+https://www.u-pohs.co.jp/tsuzuki
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>「静岡県西部に4店舗展開」との掲載による。店舗名・法人格は未確認。</t>
+          <t>ユーポスの加盟店。店舗数は本部サイトの店舗ページで運営会社として表示された店舗の数で、自社ブランドなど他の店舗は未確認（実数はこれ以上の可能性）。公式サイト・本社情報は未取得。1店舗は所在県を取得できなかった。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6020001091254、〒213-0002）。</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6157,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>プルミエ（軽届出済未使用車専門店、運営会社未確認）</t>
+          <t>NEXTGATE MOTORSOLUTIONS株式会社（KiND OUTLET）</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -6124,19 +6165,31 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>豊田、安城、豊橋、四日市</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+          <t>市原店、千葉蘇我インター軽専門店、山武成東店、千葉コンパクトハイブリッド店</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>千葉県千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F（プライバシーポリシー記載の所在地）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>0436-55-9169</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>https://kindoutlet.jp/</t>
+        </is>
+      </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr"/>
@@ -6144,17 +6197,19 @@
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋</t>
+          <t>https://kindoutlet.jp/shop
+https://kindoutlet.jp/privacypolicy
+https://ucar.carview.yahoo.co.jp/shop/chiba/309220005/group/</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>同じ4店舗（豊橋・岡崎安城・豊田・四日市）で「CAST」の名称の掲載もあり、同一の運営会社の可能性。</t>
+          <t>千葉県の軽自動車・コンパクト／ハイブリッド専門店。運営会社は、公式サイトのプライバシーポリシー記載の会社名と、中古車情報サイトの系列店一覧（NEXTGATE MOTORSOLUTIONS株式会社の系列店一覧）で確認。プライバシーポリシー記載の所在地は千葉市美浜区中瀬2-6-1 WBGマリブウエスト30F。電話は市原店。TSCと同一グループの可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6219,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ミスターシャーマン（運営会社未確認）</t>
+          <t>ニシオ自販</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -6172,12 +6227,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>長野県内4店舗</t>
+          <t>静岡県西部の4店舗</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -6192,7 +6247,7 @@
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事）</t>
+          <t>検索結果の抜粋</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -6202,7 +6257,7 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>車買取。比較記事の「県内4店舗」による。</t>
+          <t>「静岡県西部に4店舗展開」との掲載による。店舗名・法人格は未確認。</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6267,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ムラトミ</t>
+          <t>プルミエ（軽届出済未使用車専門店、運営会社未確認）</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -6220,12 +6275,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>相模原本店、相模原（2店舗目）、海老名店、伊勢原店</t>
+          <t>豊田、安城、豊橋、四日市</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -6240,7 +6295,7 @@
       <c r="O90" s="2" t="inlineStr"/>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0530132</t>
+          <t>検索結果の抜粋</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -6250,7 +6305,7 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイトの店舗紹介に「神奈川県内4店舗（相模原2店、海老名、伊勢原）のロープライスカー専門店」とある。相模原本店は相模原市南区新磯野5-43。運営法人名は未確認。2店舗目の相模原の店名は不明。</t>
+          <t>同じ4店舗（豊橋・岡崎安城・豊田・四日市）で「CAST」の名称の掲載もあり、同一の運営会社の可能性。</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6315,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>上野自動車株式会社</t>
+          <t>ミスターシャーマン（運営会社未確認）</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -6268,12 +6323,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、岐阜県、兵庫県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>上野自動車㈱ 関東支店、上野自動車中部支店、上野自動車兵庫園田店、上野自動車㈱兵庫篠山支店</t>
+          <t>長野県内4店舗</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -6284,25 +6339,21 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック販売・買取</t>
-        </is>
-      </c>
+      <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr"/>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-ichi.co.jp/corp/</t>
+          <t>検索結果の抜粋（比較記事）</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：上野自動車㈱ 関東支店：埼玉県三郷市仁蔵449-1（048-959-9517）、上野自動車中部支店：岐阜県揖斐郡揖斐川町谷汲徳積７３０（0585-56-3088）、上野自動車兵庫園田店：兵庫県尼崎市東園田町2-192（079-590-3003）、上野自動車㈱兵庫篠山支店：兵庫県丹波篠山市今田町佐曽良新田94-1（079-590-3003）</t>
+          <t>車買取。比較記事の「県内4店舗」による。</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6363,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>昭和礦油株式会社</t>
+          <t>ムラトミ</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6325,14 +6376,10 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>東京都大田区平和島5丁目2番28号</t>
-        </is>
-      </c>
+          <t>相模原本店、相模原（2店舗目）、海老名店、伊勢原店</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
@@ -6344,20 +6391,17 @@
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0282/
-https://www.applenet.co.jp/shop/0290/
-https://www.applenet.co.jp/shop/0291/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0530132</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7010801005652、〒143-0006）。</t>
+          <t>公式サイト未確認。中古車情報サイトの店舗紹介に「神奈川県内4店舗（相模原2店、海老名、伊勢原）のロープライスカー専門店」とある。相模原本店は相模原市南区新磯野5-43。運営法人名は未確認。2店舗目の相模原の店名は不明。</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6411,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>株式会社GR8（GR8STYLE）</t>
+          <t>上野自動車株式会社</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6375,57 +6419,31 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>埼玉県、岐阜県、兵庫県</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>GR8 STYLE 春日井店、名古屋大府店、岡崎店、名古屋港店</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>愛知県春日井市南下原町6丁目2-1</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>0568-41-8828</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>0568-41-8839</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>入谷 篤</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gr8style.co.jp/</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gr8style.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>上野自動車㈱ 関東支店、上野自動車中部支店、上野自動車兵庫園田店、上野自動車㈱兵庫篠山支店</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/gr8style/
-https://www.instagram.com/gr8style_japan/</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>https://www.gr8style.co.jp/company-profile/
-https://www.gr8style.co.jp/</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -6435,7 +6453,7 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>ハイエース専門店（新車・中古車・カスタム・キャンピング）。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：上野自動車㈱ 関東支店：埼玉県三郷市仁蔵449-1（048-959-9517）、上野自動車中部支店：岐阜県揖斐郡揖斐川町谷汲徳積７３０（0585-56-3088）、上野自動車兵庫園田店：兵庫県尼崎市東園田町2-192（079-590-3003）、上野自動車㈱兵庫篠山支店：兵庫県丹波篠山市今田町佐曽良新田94-1（079-590-3003）</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6463,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>株式会社MARE</t>
+          <t>昭和礦油株式会社</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6453,17 +6471,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>愛知県、兵庫県、広島県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
+          <t>アップル川崎木月店、アップル横浜鶴見店、アップル横浜港南台店、アップル横浜根岸店</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>広島県廿日市市下平良365番地1</t>
+          <t>東京都大田区平和島5丁目2番28号</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
@@ -6477,73 +6495,206 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
+          <t>https://www.applenet.co.jp/shop/0282/
+https://www.applenet.co.jp/shop/0290/
+https://www.applenet.co.jp/shop/0291/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7010801005652、〒143-0006）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>株式会社GR8（GR8STYLE）</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>GR8 STYLE 春日井店、名古屋大府店、岡崎店、名古屋港店</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>愛知県春日井市南下原町6丁目2-1</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>0568-41-8828</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>0568-41-8839</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>入谷 篤</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gr8style.co.jp/</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gr8style.co.jp/contact/</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gr8style/
+https://www.instagram.com/gr8style_japan/</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gr8style.co.jp/company-profile/
+https://www.gr8style.co.jp/</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>ハイエース専門店（新車・中古車・カスタム・キャンピング）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>株式会社MARE</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>愛知県、兵庫県、広島県</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>アップル広島廿日市店、アップル愛知一宮西店、アップル広島福山店、アップル神戸西店</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>広島県廿日市市下平良365番地1</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
           <t>https://www.applenet.co.jp/shop/0289/
 https://www.applenet.co.jp/shop/0296/
 https://www.applenet.co.jp/shop/0308/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q94" s="2" t="inlineStr">
+      <c r="Q96" s="2" t="inlineStr">
         <is>
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R94" s="2" t="inlineStr">
+      <c r="R96" s="2" t="inlineStr">
         <is>
           <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3240001051809、〒738-0023）。</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>株式会社T-SPACE</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="C97" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>埼玉県</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>SPACE ジムニー館、SPACE-ONE、SPACE-SE、SPACE-ZERO</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>埼玉県春日部市栄町1-431-1</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>048-797-6699</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>048-797-6644</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>https://cardealer-space.com/</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>info@cardealer-space.com</t>
         </is>
       </c>
-      <c r="M95" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/space_jimny
 https://www.instagram.com/spaceone661
@@ -6551,143 +6702,15 @@
 https://www.instagram.com/space.zero.kasukabe/</t>
         </is>
       </c>
-      <c r="N95" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>買取査定あり</t>
         </is>
       </c>
-      <c r="O95" s="2" t="inlineStr"/>
-      <c r="P95" s="2" t="inlineStr">
-        <is>
-          <t>https://cardealer-space.com/company/</t>
-        </is>
-      </c>
-      <c r="Q95" s="2" t="inlineStr">
-        <is>
-          <t>高：運営会社名で確認</t>
-        </is>
-      </c>
-      <c r="R95" s="2" t="inlineStr">
-        <is>
-          <t>販売店4（春日部市）。ほかに整備（T-SPACE SERVICE）・鈑金（SPACE-Body Lab.）・レンタカー。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>株式会社エコノミー湘南（奇跡査定センター）</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>奇跡査定センター 藤沢六会本店、藤沢橋店、横浜都筑店、相模原16号由野台店</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>神奈川県藤沢市亀井野2480-3</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>0466-80-3443</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>0466-80-3445</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>桑名 伸</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.satei.net/</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr">
-        <is>
-          <t>買取専門（買取センター）</t>
-        </is>
-      </c>
-      <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.satei.net/company-profile/
-https://www.satei.net/</t>
-        </is>
-      </c>
-      <c r="Q96" s="2" t="inlineStr">
-        <is>
-          <t>中：店舗名からの推定</t>
-        </is>
-      </c>
-      <c r="R96" s="2" t="inlineStr">
-        <is>
-          <t>車買取専門店。会社概要の沿革に「有限会社エコノミーエンタープライズより営業継承し、株式会社エコノミー湘南を設立」「屋号を奇跡査定センターとし」とあるが、現在の社名欄は確認できず。電話は藤沢六会本店。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>株式会社オリンピア</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>栃木県、群馬県、埼玉県</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>栃木県宇都宮市石井町3335番地55</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr"/>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0138/
-https://www.applenet.co.jp/shop/0141/
-https://www.applenet.co.jp/shop/0143/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://cardealer-space.com/company/</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -6697,7 +6720,7 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7060001001092、〒321-0912）。</t>
+          <t>販売店4（春日部市）。ほかに整備（T-SPACE SERVICE）・鈑金（SPACE-Body Lab.）・レンタカー。</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6730,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートスペースアクセル（ASAグループ）</t>
+          <t>株式会社エコノミー湘南（奇跡査定センター）</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6720,28 +6743,47 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>（有）オートフィールドストリーク</t>
+          <t>奇跡査定センター 藤沢六会本店、藤沢橋店、横浜都筑店、相模原16号由野台店</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>神奈川県厚木市関口236番地14</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
+          <t>神奈川県藤沢市亀井野2480-3</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>0466-80-3443</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>0466-80-3445</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>桑名 伸</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.satei.net/</t>
+        </is>
+      </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>買取専門（買取センター）</t>
+        </is>
+      </c>
       <c r="O98" s="2" t="inlineStr"/>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/0510254
-https://biz-maps.com/s/cities/142123/m-inds/378
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.satei.net/company-profile/
+https://www.satei.net/</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -6751,7 +6793,7 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2021001024521、〒243-0804）。</t>
+          <t>車買取専門店。会社概要の沿革に「有限会社エコノミーエンタープライズより営業継承し、株式会社エコノミー湘南を設立」「屋号を奇跡査定センターとし」とあるが、現在の社名欄は確認できず。電話は藤沢六会本店。</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6803,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>株式会社カースーパー（青森）</t>
+          <t>株式会社オリンピア</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6769,15 +6811,19 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>栃木県、群馬県、埼玉県</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>流通団地店、東バイパス店、青森市内の店舗（店名未確認）2店</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
+          <t>アップル羽生122号バイパス店、アップル宇都宮新4号店、アップル伊勢崎西店、アップル館林店</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>栃木県宇都宮市石井町3335番地55</t>
+        </is>
+      </c>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
@@ -6789,17 +6835,20 @@
       <c r="O99" s="2" t="inlineStr"/>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>https://car-mo.jp/mag/category/tips/usedcar/aomori/</t>
+          <t>https://www.applenet.co.jp/shop/0138/
+https://www.applenet.co.jp/shop/0141/
+https://www.applenet.co.jp/shop/0143/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。中古車紹介記事に「青森市内に4店舗、グループ総在庫200台以上」。法人名は求人情報の「株式会社カースーパー 流通団地店」による。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7060001001092、〒321-0912）。</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6858,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>株式会社クルーズコーポレーション（カーニバル）</t>
+          <t>株式会社オートスペースアクセル（ASAグループ）</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6817,31 +6866,23 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>カーニバル 久喜インター店、カーニバル 春日部店、カーニバル 岩槻店、カーニバル 上尾店</t>
+          <t>（有）オートフィールドストリーク</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>埼玉県久喜市江面1479</t>
+          <t>神奈川県厚木市関口236番地14</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>内田 浩</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>https://caniva.jp/</t>
-        </is>
-      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr"/>
@@ -6849,18 +6890,19 @@
       <c r="O100" s="2" t="inlineStr"/>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>https://caniva.jp/company/
-https://caniva.jp/shop/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/0510254
+https://biz-maps.com/s/cities/142123/m-inds/378
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>新車・未使用車・中古車販売。公式サイトの店舗一覧で4店舗（ほかに春日部サービス工場）。本社は久喜インター店と同じ住所。電話は会社概要に記載なし（店舗へ直接）。</t>
+          <t>公式サイト未確認。中古車情報サイトに「4店舗合計400台」、企業情報サイトに「神奈川県内に4店舗」とある。判明している店舗はオートフィールドストリーク（相模原市中央区東淵野辺5-2-20）のみ。他の3店舗名は不明。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2021001024521、〒243-0804）。</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6912,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>株式会社クレタ（北海道軽パーク）</t>
+          <t>株式会社カースーパー（青森）</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -6878,48 +6920,27 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>札幌店、札幌東店、北広島店、苫小牧店</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>北海道苫小牧市沼ノ端中央1丁目14番16号</t>
-        </is>
-      </c>
+          <t>流通団地店、東バイパス店、青森市内の店舗（店名未確認）2店</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>https://kereta.jp/</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>https://kereta.jp/contact/</t>
-        </is>
-      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/hokkaido_k_park/
-https://x.com/hokkaido_k_park
-https://www.facebook.com/hokkaidokeipark/
-https://youtube.com/channel/UC2xk0xmuuww2ocTXFsNghcw
-https://www.tiktok.com/@hokkaido_k_park</t>
-        </is>
-      </c>
+      <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>https://kereta.jp/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://car-mo.jp/mag/category/tips/usedcar/aomori/</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -6929,7 +6950,7 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8430001055026、〒059-1305）。</t>
+          <t>公式サイト未確認。中古車紹介記事に「青森市内に4店舗、グループ総在庫200台以上」。法人名は求人情報の「株式会社カースーパー 流通団地店」による。</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6960,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>株式会社グローバンネット</t>
+          <t>株式会社クルーズコーポレーション（カーニバル）</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -6947,25 +6968,29 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>茨城県、埼玉県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
+          <t>カーニバル 久喜インター店、カーニバル 春日部店、カーニバル 岩槻店、カーニバル 上尾店</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>埼玉県所沢市大字坂之下17番地1号</t>
+          <t>埼玉県久喜市江面1479</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>内田 浩</t>
+        </is>
+      </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>https://pa-cars.com/</t>
+          <t>https://caniva.jp/</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
@@ -6975,18 +7000,18 @@
       <c r="O102" s="2" t="inlineStr"/>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>https://pa-cars.com/shopinfo.html
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://caniva.jp/company/
+https://caniva.jp/shop/</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1030001025439、〒359-0012）。</t>
+          <t>新車・未使用車・中古車販売。公式サイトの店舗一覧で4店舗（ほかに春日部サービス工場）。本社は久喜インター店と同じ住所。電話は会社概要に記載なし（店舗へ直接）。</t>
         </is>
       </c>
     </row>
@@ -6996,7 +7021,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>株式会社サンライズモータース（軽プラザサンライズ）</t>
+          <t>株式会社クレタ（北海道軽パーク）</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -7004,33 +7029,47 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>軽プラザサンライズ 青森本店、軽プラザサンライズ 弘前本店、軽プラザサンライズ 八戸本店、新車市場 サンライズ青森東バイパス店</t>
+          <t>札幌店、札幌東店、北広島店、苫小牧店</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>青森県青森市大字平新田字池上56番地1</t>
+          <t>北海道苫小牧市沼ノ端中央1丁目14番16号</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>https://kereta.jp/</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>https://kereta.jp/contact/</t>
+        </is>
+      </c>
       <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hokkaido_k_park/
+https://x.com/hokkaido_k_park
+https://www.facebook.com/hokkaidokeipark/
+https://youtube.com/channel/UC2xk0xmuuww2ocTXFsNghcw
+https://www.tiktok.com/@hokkaido_k_park</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>https://carbell.jp/partner/search?area_code=10
-https://car.motor-fan.jp/ucar/shop/0904135
-https://www.kurumaerabi.com/shop/detail/40016907/
+          <t>https://kereta.jp/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -7041,7 +7080,7 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。軽未使用車専門店。中古車情報サイトの店舗紹介に青森・弘前・八戸の各店と「グループ総在庫800台」。新車市場の加盟店一覧に「新車市場 サンライズ青森東バイパス店 株式会社サンライズモータース」。青森本店は青森市第二問屋町2丁目5-13（車検のコバック併設）、八戸本店は八戸市城下3-8-6。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6420001004869、〒030-0931）。</t>
+          <t>軽自動車専門店「北海道軽パーク」。店舗は公式サイトの4店舗。運営会社名（株式会社クレタ、本社苫小牧市）は検索結果の抜粋による。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8430001055026、〒059-1305）。</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7090,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>株式会社シンユウ</t>
+          <t>株式会社グローバンネット</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -7059,33 +7098,25 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>徳島県、香川県、愛媛県、高知県</t>
+          <t>茨城県、埼玉県</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>徳島本店（ジョイカル徳島川内店）、高知店（ジョイカル高知大津店）、高松店、松山店（ジョイカル東温田窪店）</t>
+          <t>パッカーズ 所沢新座店、パッカーズ 狭山ヶ丘店、パッカーズ 川越店、パッカーズ つくば店</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>徳島県徳島市川内町中島126（徳島本店）</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>088-665-8150</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>088-665-0814</t>
-        </is>
-      </c>
+          <t>埼玉県所沢市大字坂之下17番地1号</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://sinyu-car.co.jp/</t>
+          <t>https://pa-cars.com/</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
@@ -7095,17 +7126,18 @@
       <c r="O104" s="2" t="inlineStr"/>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>https://sinyu-car.co.jp/店舗案内/</t>
+          <t>https://pa-cars.com/shopinfo.html
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>四国4県に各1店舗。自社ローン（スリークロス）・新車リース（ジョイカル）も扱う。本社所在地は徳島本店の住所。</t>
+          <t>ブランドはパッカーズ（Pa!Cars、届出済未使用車）。運営会社名は求人情報による。親会社はウェルビングループ。ほかに車検の速太郎を運営。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1030001025439、〒359-0012）。</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7147,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>株式会社シーアールエス（CRS）</t>
+          <t>株式会社サンライズモータース（軽プラザサンライズ）</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -7123,31 +7155,23 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>千葉県、神奈川県、大阪府、福岡県</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>大阪府の店舗・支店（店名未確認）、千葉県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、福岡県の店舗・支店（店名未確認）</t>
+          <t>軽プラザサンライズ 青森本店、軽プラザサンライズ 弘前本店、軽プラザサンライズ 八戸本店、新車市場 サンライズ青森東バイパス店</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>大阪府豊中市勝部3-3-18</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>06-6852-9000</t>
-        </is>
-      </c>
+          <t>青森県青森市大字平新田字池上56番地1</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crs9000.com/</t>
-        </is>
-      </c>
+      <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr"/>
@@ -7155,17 +7179,20 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>https://www.jrva.com/organization/members/</t>
+          <t>https://carbell.jp/partner/search?area_code=10
+https://car.motor-fan.jp/ucar/shop/0904135
+https://www.kurumaerabi.com/shop/detail/40016907/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
+          <t>公式サイト未確認。軽未使用車専門店。中古車情報サイトの店舗紹介に青森・弘前・八戸の各店と「グループ総在庫800台」。新車市場の加盟店一覧に「新車市場 サンライズ青森東バイパス店 株式会社サンライズモータース」。青森本店は青森市第二問屋町2丁目5-13（車検のコバック併設）、八戸本店は八戸市城下3-8-6。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6420001004869、〒030-0931）。</t>
         </is>
       </c>
     </row>
@@ -7175,7 +7202,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>株式会社ダブルツリー</t>
+          <t>株式会社シンユウ</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -7183,27 +7210,35 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>岡山県、香川県</t>
+          <t>徳島県、香川県、愛媛県、高知県</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
+          <t>徳島本店（ジョイカル徳島川内店）、高知店（ジョイカル高知大津店）、高松店、松山店（ジョイカル東温田窪店）</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>岡山県倉敷市加須山334番地の4</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 林和樹</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr"/>
+          <t>徳島県徳島市川内町中島126（徳島本店）</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>088-665-8150</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>088-665-0814</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>https://sinyu-car.co.jp/</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr"/>
@@ -7211,8 +7246,7 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://sinyu-car.co.jp/店舗案内/</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -7222,7 +7256,7 @@
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1260001014484、〒710-0026）。</t>
+          <t>四国4県に各1店舗。自社ローン（スリークロス）・新車リース（ジョイカル）も扱う。本社所在地は徳島本店の住所。</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7266,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>株式会社ビッグワン</t>
+          <t>株式会社シーアールエス（CRS）</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -7240,23 +7274,31 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>千葉県、神奈川県、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>販売店（千葉市内4店舗）</t>
+          <t>大阪府の店舗・支店（店名未確認）、千葉県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、福岡県の店舗・支店（店名未確認）</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>千葉県千葉市花見川区三角町525番地</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
+          <t>大阪府豊中市勝部3-3-18</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>06-6852-9000</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crs9000.com/</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr"/>
@@ -7264,18 +7306,17 @@
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.jrva.com/organization/members/</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号4040001042513、〒262-0011）。</t>
+          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7326,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>株式会社ミナミシマ自動車販売</t>
+          <t>株式会社ダブルツリー</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -7293,22 +7334,26 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>岡山県、香川県</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
+          <t>アップル岡山店、アップル東岡山店、アップル高松店、アップル丸亀店</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>奈良県葛城市北花内703番地4</t>
+          <t>岡山県倉敷市加須山334番地の4</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 林和樹</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
@@ -7317,9 +7362,7 @@
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/kashiba/
-https://www.u-pohs.co.jp/kashihara/
-https://www.u-pohs.co.jp/katuragi/
+          <t>https://www.applenet.co.jp/shop/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -7330,7 +7373,7 @@
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5150001014995、〒639-2113）。</t>
+          <t>アップル加盟店4店舗（本部サイトで運営会社を確認）。代表者が同じ株式会社ハヤシ（くるまのハヤシ）は別法人として別の行に記載。グループで見れば12店舗。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号1260001014484、〒710-0026）。</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7383,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>株式会社ライズオート（RiSE AUTO）</t>
+          <t>株式会社ビッグワン</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -7348,58 +7391,42 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>RiSE 四日市北店、RiSE 四日市南店、ガリバーアウトレット 四日市緑地店、ガリバー 稲沢店</t>
+          <t>販売店（千葉市内4店舗）</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>三重県四日市市日永東3-13-5</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>059-329-5553</t>
-        </is>
-      </c>
+          <t>千葉県千葉市花見川区三角町525番地</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>松村 賢治</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>https://riseauto.jp/</t>
-        </is>
-      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr">
-        <is>
-          <t>買取あり（ガリバー加盟店を運営）</t>
-        </is>
-      </c>
+      <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>https://riseauto.jp/company/
-https://riseauto.jp/</t>
+          <t>https://en-gage.net/bigone-web_saiyo/（求人ページ、検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>リョウシンホールディングスグループ。自社ブランドRiSE 2店舗＋ガリバー加盟2店舗。会社概要に「三重県に3店舗と愛知県に1店舗」。</t>
+          <t>求人ページの記載で、千葉市内に販売店4店舗と自社工場2か所（車検場・板金塗装）。同名の別会社が多いので注意（木更津のビッグワンオートは別会社）。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号4040001042513、〒262-0011）。</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7436,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>株式会社ワークス</t>
+          <t>株式会社ミナミシマ自動車販売</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
@@ -7417,17 +7444,17 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>奈良県</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
+          <t>ユーポス香芝店、ユーポス橿原店、ユーポス葛城店、ユーポス大和郡山店</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>埼玉県川越市大字府川23番地4</t>
+          <t>奈良県葛城市北花内703番地4</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
@@ -7441,18 +7468,20 @@
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）
+          <t>https://www.u-pohs.co.jp/kashiba/
+https://www.u-pohs.co.jp/kashihara/
+https://www.u-pohs.co.jp/katuragi/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3030001056861、〒350-0831）。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 スズキ・ダイハツの新車販売店（D-shop橿原など）が本業のため、中古車主業か要確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号5150001014995、〒639-2113）。</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7491,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>株式会社沖縄ユーポス</t>
+          <t>株式会社ライズオート（RiSE AUTO）</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -7470,34 +7499,48 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+          <t>RiSE 四日市北店、RiSE 四日市南店、ガリバーアウトレット 四日市緑地店、ガリバー 稲沢店</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>沖縄県沖縄市字登川2791番地1</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr"/>
+          <t>三重県四日市市日永東3-13-5</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>059-329-5553</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>松村 賢治</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>https://riseauto.jp/</t>
+        </is>
+      </c>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>買取あり（ガリバー加盟店を運営）</t>
+        </is>
+      </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/misato/
-https://www.u-pohs.co.jp/naha-shintoshin
-https://www.u-pohs.co.jp/noborikawa/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://riseauto.jp/company/
+https://riseauto.jp/</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -7507,7 +7550,7 @@
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3360001016221、〒904-2142）。</t>
+          <t>リョウシンホールディングスグループ。自社ブランドRiSE 2店舗＋ガリバー加盟2店舗。会社概要に「三重県に3店舗と愛知県に1店舗」。</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7560,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>株式会社鈴木モータース</t>
+          <t>株式会社ワークス</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -7525,15 +7568,19 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>滋賀県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
+          <t>軽自動車専門店 ワークス（川越市府川）ほか</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県川越市大字府川23番地4</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
@@ -7545,19 +7592,18 @@
       <c r="O112" s="2" t="inlineStr"/>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0065/
-https://www.applenet.co.jp/shop/0071/
-https://www.applenet.co.jp/shop/0080/</t>
+          <t>https://www.r-agent.com/company/c7388/（求人情報、検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>求人情報に「直営4店舗」と「直営5店舗」の2通りの記載あり（境界）。スズキの販売店・アップル車検も運営。公式サイト未確認。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3030001056861、〒350-0831）。</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7613,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>買取マウス（運営会社未確認）</t>
+          <t>株式会社沖縄ユーポス</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -7575,15 +7621,19 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>新潟市内4店舗</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr"/>
+          <t>ユーポス美里店、ユーポス那覇新都心店、ユーポス登川店、ユーポス豊見城店</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>沖縄県沖縄市字登川2791番地1</t>
+        </is>
+      </c>
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
@@ -7595,17 +7645,20 @@
       <c r="O113" s="2" t="inlineStr"/>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（比較記事）</t>
+          <t>https://www.u-pohs.co.jp/misato/
+https://www.u-pohs.co.jp/naha-shintoshin
+https://www.u-pohs.co.jp/noborikawa/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>車買取。比較記事の「新潟市内に4店舗」による。</t>
+          <t>ユーポスの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3360001016221、〒904-2142）。</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7668,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>鈴木自工株式会社（軽ひろば・くるま広場）</t>
+          <t>株式会社鈴木モータース</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -7623,27 +7676,19 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>千葉県</t>
+          <t>滋賀県</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>くるま広場 船橋習志野店、軽ひろば 佐倉王子台店、軽ひろば 千葉貝塚店、軽ひろば 千葉おゆみ店</t>
+          <t>アップル草津店、アップル彦根インター店、アップル守山店、アップル大津店</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>047-406-3259</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>https://kei-hiroba.car-yasui.jp/</t>
-        </is>
-      </c>
+      <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr"/>
@@ -7651,7 +7696,9 @@
       <c r="O114" s="2" t="inlineStr"/>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>https://kei-hiroba.car-yasui.jp/</t>
+          <t>https://www.applenet.co.jp/shop/0065/
+https://www.applenet.co.jp/shop/0071/
+https://www.applenet.co.jp/shop/0080/</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -7661,7 +7708,7 @@
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>軽自動車（新車・未使用車・中古車）専門店。サイトに「運営：鈴木自工株式会社」。店舗名はサイトのタイトル・本文から。電話はサイト記載のもの（どの店舗かは未確認）。新車の扱いが中心の可能性あり。</t>
+          <t>アップルの加盟店として4店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -7671,35 +7718,27 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Dash（運営会社未確認）</t>
+          <t>買取マウス（運営会社未確認）</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>愛知県、三重県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>名古屋本店、西三河店、三重鈴鹿店</t>
+          <t>新潟市内4店舗</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>052-901-8008</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.car-dash.jp/</t>
-        </is>
-      </c>
+      <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr"/>
       <c r="M115" s="2" t="inlineStr"/>
@@ -7707,7 +7746,7 @@
       <c r="O115" s="2" t="inlineStr"/>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>https://www.car-dash.jp/</t>
+          <t>検索結果の抜粋（比較記事）</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -7717,7 +7756,7 @@
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門店。 電話は名古屋本店のもの。</t>
+          <t>車買取。比較記事の「新潟市内に4店舗」による。</t>
         </is>
       </c>
     </row>
@@ -7727,27 +7766,35 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>ZERO MOTORS（運営会社未確認）</t>
+          <t>鈴木自工株式会社（軽ひろば・くるま広場）</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>千葉県</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>埼玉県内3店舗</t>
+          <t>くるま広場 船橋習志野店、軽ひろば 佐倉王子台店、軽ひろば 千葉貝塚店、軽ひろば 千葉おゆみ店</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>047-406-3259</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>https://kei-hiroba.car-yasui.jp/</t>
+        </is>
+      </c>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr"/>
       <c r="M116" s="2" t="inlineStr"/>
@@ -7755,17 +7802,17 @@
       <c r="O116" s="2" t="inlineStr"/>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://kei-hiroba.car-yasui.jp/</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>軽自動車・コンパクトカー専門店。「埼玉県3店舗・総在庫700台以上」との掲載による。</t>
+          <t>軽自動車（新車・未使用車・中古車）専門店。サイトに「運営：鈴木自工株式会社」。店舗名はサイトのタイトル・本文から。電話はサイト記載のもの（どの店舗かは未確認）。新車の扱いが中心の可能性あり。</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7822,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>つしまオート株式会社</t>
+          <t>Dash（運営会社未確認）</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -7783,57 +7830,45 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>愛知県、三重県</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>本店（津島市）、大坪店、北名古屋店</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>愛知県津島市又吉町4丁目16番地</t>
-        </is>
-      </c>
+          <t>名古屋本店、西三河店、三重鈴鹿店</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>0567-26-1351</t>
+          <t>052-901-8008</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>村上 直之</t>
-        </is>
-      </c>
+      <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>https://www.tsushima-auto.com/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr"/>
       <c r="M117" s="2" t="inlineStr"/>
       <c r="N117" s="2" t="inlineStr"/>
-      <c r="O117" s="2" t="inlineStr">
-        <is>
-          <t>54名</t>
-        </is>
-      </c>
+      <c r="O117" s="2" t="inlineStr"/>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>https://www.tsushima-auto.com/company/</t>
+          <t>https://www.car-dash.jp/</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店（軽未使用車）。尾張地区最大級500台在庫をうたう。</t>
+          <t>自社ローン専門店。 電話は名古屋本店のもの。</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7878,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>アビックス大阪株式会社</t>
+          <t>ZERO MOTORS（運営会社未確認）</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -7851,19 +7886,15 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>兵庫県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>大阪府大阪市中央区南船場2丁目4番23号</t>
-        </is>
-      </c>
+          <t>埼玉県内3店舗</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
@@ -7875,8 +7906,7 @@
       <c r="O118" s="2" t="inlineStr"/>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>検索結果の抜粋（店舗掲載）</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -7886,7 +7916,7 @@
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>アビックスコーポレーションのグループ会社とみられる。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7120001231212、〒542-0081）。</t>
+          <t>軽自動車・コンパクトカー専門店。「埼玉県3店舗・総在庫700台以上」との掲載による。</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7926,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ウチダオート株式会社</t>
+          <t>つしまオート株式会社</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -7904,37 +7934,33 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>川口店、岩槻店、川越店</t>
+          <t>本店（津島市）、大坪店、北名古屋店</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>埼玉県川口市西新井宿117</t>
+          <t>愛知県津島市又吉町4丁目16番地</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>048-284-0321</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>048-283-1190</t>
-        </is>
-      </c>
+          <t>0567-26-1351</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>宇野 弘人</t>
+          <t>村上 直之</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>https://www.uchida-auto.co.jp/</t>
+          <t>https://www.tsushima-auto.com/</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr"/>
@@ -7943,13 +7969,12 @@
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>36名（2021年4月現在）</t>
+          <t>54名</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>https://www.uchida-auto.co.jp/
-https://www.uchida-auto.co.jp/info/index.php</t>
+          <t>https://www.tsushima-auto.com/company/</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -7959,7 +7984,7 @@
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>新車・新古車（未使用車）のディスカウント販売。3展示場で常時400台。新車の扱いが中心の可能性あり。</t>
+          <t>軽自動車専門店（軽未使用車）。尾張地区最大級500台在庫をうたう。</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7994,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>エービーエスオート（ABS Auto、運営会社未確認）</t>
+          <t>アビックス大阪株式会社</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -7977,15 +8002,19 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>神奈川県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>藤沢店（藤沢市用田1531-1）、海老名店、綾瀬店</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
+          <t>AVIX IMPORT 宝塚インター店ほか関西3店舗</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市中央区南船場2丁目4番23号</t>
+        </is>
+      </c>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
@@ -7997,7 +8026,8 @@
       <c r="O120" s="2" t="inlineStr"/>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>https://www.kurumaerabi.com/shop/detail/29454/</t>
+          <t>https://car.motor-fan.jp/ucar/shop/9700321（検索結果の抜粋）
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -8007,7 +8037,7 @@
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。公式サイト未確認。中古車情報サイトの紹介に「藤沢市用田に1店舗・海老名と綾瀬にも店舗」。</t>
+          <t>アビックスコーポレーションのグループ会社とみられる。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号7120001231212、〒542-0081）。</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8047,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>カーライフグループ株式会社</t>
+          <t>ウチダオート株式会社</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
@@ -8025,33 +8055,37 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>TOKYO店、大阪店、福岡店</t>
+          <t>川口店、岩槻店、川越店</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>福岡県糟屋郡粕屋町戸原西4丁目8-11</t>
+          <t>埼玉県川口市西新井宿117</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>0120-038-871</t>
+          <t>048-284-0321</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>092-410-5912</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr"/>
+          <t>048-283-1190</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>宇野 弘人</t>
+        </is>
+      </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>https://loanok.jp/</t>
+          <t>https://www.uchida-auto.co.jp/</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr"/>
@@ -8060,13 +8094,13 @@
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>30名</t>
+          <t>36名（2021年4月現在）</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>https://loanok.jp/shop000.html
-https://loanok.jp/</t>
+          <t>https://www.uchida-auto.co.jp/
+https://www.uchida-auto.co.jp/info/index.php</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -8076,7 +8110,7 @@
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>自社ローン専門。所在地はサイト記載の住所（本社かどうかは未確認）。</t>
+          <t>新車・新古車（未使用車）のディスカウント販売。3展示場で常時400台。新車の扱いが中心の可能性あり。</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8120,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>トーワオート（運営会社未確認）</t>
+          <t>エービーエスオート（ABS Auto、運営会社未確認）</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -8094,12 +8128,12 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>宇都宮西店、宇都宮東店、宇都宮南店</t>
+          <t>藤沢店（藤沢市用田1531-1）、海老名店、綾瀬店</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
@@ -8114,7 +8148,7 @@
       <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://www.kurumaerabi.com/shop/detail/29454/</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -8124,7 +8158,7 @@
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>宇都宮市内の3店舗。</t>
+          <t>中古トラック販売。公式サイト未確認。中古車情報サイトの紹介に「藤沢市用田に1店舗・海老名と綾瀬にも店舗」。</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8168,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>プチモ軽自動車専門店（株式会社ヒューベストオートの可能性）</t>
+          <t>カーライフグループ株式会社</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
@@ -8142,37 +8176,58 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>佐賀店、唐津店、佐世保店</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr"/>
+          <t>TOKYO店、大阪店、福岡店</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>福岡県糟屋郡粕屋町戸原西4丁目8-11</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>0120-038-871</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>092-410-5912</t>
+        </is>
+      </c>
       <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>https://loanok.jp/</t>
+        </is>
+      </c>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
       <c r="M123" s="2" t="inlineStr"/>
       <c r="N123" s="2" t="inlineStr"/>
-      <c r="O123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>30名</t>
+        </is>
+      </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（求人・店舗掲載）</t>
+          <t>https://loanok.jp/shop000.html
+https://loanok.jp/</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>佐世保店は長崎県（2025年12月開店）。運営会社は佐世保店の求人の募集元による推定。</t>
+          <t>自社ローン専門。所在地はサイト記載の住所（本社かどうかは未確認）。</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8237,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>古城モータース</t>
+          <t>トーワオート（運営会社未確認）</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
@@ -8190,31 +8245,19 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>高岡本店、富山店、石川白山店</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>富山県高岡市二塚425番地</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>0120-540-118</t>
-        </is>
-      </c>
+          <t>宇都宮西店、宇都宮東店、宇都宮南店</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kojyo-motors.com/</t>
-        </is>
-      </c>
+      <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
       <c r="M124" s="2" t="inlineStr"/>
@@ -8222,7 +8265,7 @@
       <c r="O124" s="2" t="inlineStr"/>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>https://www.kojyo-motors.com/</t>
+          <t>検索結果の抜粋（店舗掲載）</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -8230,7 +8273,11 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>宇都宮市内の3店舗。</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -8238,7 +8285,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>有限会社カネタ（カネタグループ）</t>
+          <t>プチモ軽自動車専門店（株式会社ヒューベストオートの可能性）</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
@@ -8246,12 +8293,12 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>カネタグループ 旭川トラックセンター、カネタグループ 苫小牧トラックセンター、カネタグループ ２７５トラックセンター</t>
+          <t>佐賀店、唐津店、佐世保店</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -8262,25 +8309,21 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr"/>
       <c r="M125" s="2" t="inlineStr"/>
-      <c r="N125" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック販売・買取</t>
-        </is>
-      </c>
+      <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr"/>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-ichi.co.jp/corp/</t>
+          <t>検索結果の抜粋（求人・店舗掲載）</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：カネタグループ 旭川トラックセンター：北海道旭川市末広東一条6丁目1番8号（0166-51-9922）、カネタグループ 苫小牧トラックセンター：北海道苫小牧市字植苗163番地21（0144-51-8282）、カネタグループ ２７５トラックセンター：北海道江別市角山４２６番地１４（011-378-9922）</t>
+          <t>佐世保店は長崎県（2025年12月開店）。運営会社は佐世保店の求人の募集元による推定。</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8333,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>有限会社ナカダ自動車商会</t>
+          <t>古城モータース</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
@@ -8298,19 +8341,31 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>沖縄県</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>本店（沖縄市）、ナカダ自動車商会 うるま店、系列店（店名未確認）</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr"/>
+          <t>高岡本店、富山店、石川白山店</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>富山県高岡市二塚425番地</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>0120-540-118</t>
+        </is>
+      </c>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kojyo-motors.com/</t>
+        </is>
+      </c>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
       <c r="M126" s="2" t="inlineStr"/>
@@ -8318,7 +8373,7 @@
       <c r="O126" s="2" t="inlineStr"/>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>https://annai-center.com/usedcar_shop/s-0120275/group/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -8326,11 +8381,7 @@
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R126" s="2" t="inlineStr">
-        <is>
-          <t>公式サイト未確認。中古車店舗案内サイトの系列店一覧に3店舗（沖縄市の本店、うるま市兼箇段のうるま店ほか）。</t>
-        </is>
-      </c>
+      <c r="R126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -8338,7 +8389,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>有限会社中央特車</t>
+          <t>有限会社カネタ（カネタグループ）</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
@@ -8346,12 +8397,12 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>徳島県、香川県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>中央特車(有) 営業所、徳島川内店、香川綾川店</t>
+          <t>カネタグループ 旭川トラックセンター、カネタグループ 苫小牧トラックセンター、カネタグループ ２７５トラックセンター</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
@@ -8380,7 +8431,7 @@
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：中央特車(有) 営業所：徳島県板野郡北島町中村字牛飼原1-1（088-698-6225）、徳島川内店：徳島県徳島市川内町夷野99-1（088-698-6225）、香川綾川店：香川県綾歌郡綾歌町綾川町陶4331（087-899-7683）</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：カネタグループ 旭川トラックセンター：北海道旭川市末広東一条6丁目1番8号（0166-51-9922）、カネタグループ 苫小牧トラックセンター：北海道苫小牧市字植苗163番地21（0144-51-8282）、カネタグループ ２７５トラックセンター：北海道江別市角山４２６番地１４（011-378-9922）</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8441,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>有限会社輪栄プロダクト（リンエイプロダクト）</t>
+          <t>有限会社ナカダ自動車商会</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
@@ -8398,31 +8449,19 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、岐阜県、大阪府</t>
+          <t>沖縄県</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>埼玉県の店舗・支店（店名未確認）、岐阜県の店舗・支店（店名未確認）、大阪府の店舗・支店（店名未確認）</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>埼玉県川越市福田1040-4</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>049-225-3591</t>
-        </is>
-      </c>
+          <t>本店（沖縄市）、ナカダ自動車商会 うるま店、系列店（店名未確認）</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>http://www.rinei.jp/</t>
-        </is>
-      </c>
+      <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
       <c r="M128" s="2" t="inlineStr"/>
@@ -8430,17 +8469,17 @@
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>https://www.jrva.com/organization/members/</t>
+          <t>https://annai-center.com/usedcar_shop/s-0120275/group/</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
+          <t>公式サイト未確認。中古車店舗案内サイトの系列店一覧に3店舗（沖縄市の本店、うるま市兼箇段のうるま店ほか）。</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8489,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>栗山自動車工業株式会社</t>
+          <t>有限会社中央特車</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
@@ -8458,12 +8497,12 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都、神奈川県</t>
+          <t>徳島県、香川県</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>栗山自動車工業 千葉支店、栗山自動車工業 東京、栗山自動車工業 神奈川支店</t>
+          <t>中央特車(有) 営業所、徳島川内店、香川綾川店</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
@@ -8492,7 +8531,7 @@
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：栗山自動車工業 千葉支店：千葉県佐倉市大作2-12-2（043-498-7974）、栗山自動車工業 東京：東京都江戸川区西瑞江5-3-10（03-3689-7711）、栗山自動車工業 神奈川支店：神奈川県座間市ひばりが丘4-24-12（0120-528-828）</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：中央特車(有) 営業所：徳島県板野郡北島町中村字牛飼原1-1（088-698-6225）、徳島川内店：徳島県徳島市川内町夷野99-1（088-698-6225）、香川綾川店：香川県綾歌郡綾歌町綾川町陶4331（087-899-7683）</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8541,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>株式会社AG</t>
+          <t>有限会社輪栄プロダクト（リンエイプロダクト）</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -8510,52 +8549,39 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>東京都、大阪府、福岡県</t>
+          <t>埼玉県、岐阜県、大阪府</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
+          <t>埼玉県の店舗・支店（店名未確認）、岐阜県の店舗・支店（店名未確認）、大阪府の店舗・支店（店名未確認）</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>大阪府大阪市西区北堀江2-11-18</t>
+          <t>埼玉県川越市福田1040-4</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>06-6538-8844</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>06-6538-8845</t>
-        </is>
-      </c>
+          <t>049-225-3591</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/</t>
+          <t>http://www.rinei.jp/</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="inlineStr">
-        <is>
-          <t>inquiry@autogallery.co.jp</t>
-        </is>
-      </c>
+      <c r="L130" s="2" t="inlineStr"/>
       <c r="M130" s="2" t="inlineStr"/>
-      <c r="N130" s="2" t="inlineStr">
-        <is>
-          <t>中古車の買取・下取りあり</t>
-        </is>
-      </c>
+      <c r="N130" s="2" t="inlineStr"/>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>https://www.autogallery.co.jp/company
-https://www.autogallery.co.jp/shopinfo</t>
+          <t>https://www.jrva.com/organization/members/</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -8565,7 +8591,7 @@
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>輸入車（アメ車等）専門店。サイトの見出しは「東京 神奈川 福岡」で、古物商許可も神奈川県を含むが、店舗情報ページに載っているのは東京・大阪・福岡の3店舗。</t>
+          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8601,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>株式会社CSオートディーラー</t>
+          <t>栗山自動車工業株式会社</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -8583,40 +8609,31 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、千葉県</t>
+          <t>千葉県、東京都、神奈川県</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>東京都渋谷区幡ヶ谷2-21-4</t>
-        </is>
-      </c>
+          <t>栗山自動車工業 千葉支店、栗山自動車工業 東京、栗山自動車工業 神奈川支店</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>代表取締役 河野修一</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>https://www.csauto.jp/</t>
-        </is>
-      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr"/>
       <c r="M131" s="2" t="inlineStr"/>
-      <c r="N131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O131" s="2" t="inlineStr"/>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>https://www.csauto.jp/company
-https://www.csauto.jp/shop</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -8626,7 +8643,7 @@
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：栗山自動車工業 千葉支店：千葉県佐倉市大作2-12-2（043-498-7974）、栗山自動車工業 東京：東京都江戸川区西瑞江5-3-10（03-3689-7711）、栗山自動車工業 神奈川支店：神奈川県座間市ひばりが丘4-24-12（0120-528-828）</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8653,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>株式会社Noa Corporation（ノアコーポレーション）</t>
+          <t>株式会社AG</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -8644,31 +8661,52 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>東京都、大阪府、福岡県</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>ノアコーポレーション、ノアコーポレーション 車両センター、ノアコーポレーション 小山展示場</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr"/>
+          <t>オートギャラリー東京、オートギャラリー大阪、オートギャラリー福岡</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>大阪府大阪市西区北堀江2-11-18</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8844</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>06-6538-8845</t>
+        </is>
+      </c>
       <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.autogallery.co.jp/</t>
+        </is>
+      </c>
       <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>inquiry@autogallery.co.jp</t>
+        </is>
+      </c>
       <c r="M132" s="2" t="inlineStr"/>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売・買取</t>
+          <t>中古車の買取・下取りあり</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr"/>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-ichi.co.jp/corp/</t>
+          <t>https://www.autogallery.co.jp/company
+https://www.autogallery.co.jp/shopinfo</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -8678,7 +8716,7 @@
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：ノアコーポレーション：栃木県さくら市向河原3994-1（028-612-1474）、ノアコーポレーション 車両センター：栃木県宇都宮市宮山田町406-4（028-612-1474）、ノアコーポレーション 小山展示場：栃木県小山市西黒田169-2（028-612-1474）</t>
+          <t>輸入車（アメ車等）専門店。サイトの見出しは「東京 神奈川 福岡」で、古物商許可も神奈川県を含むが、店舗情報ページに載っているのは東京・大阪・福岡の3店舗。</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8726,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>株式会社world of star</t>
+          <t>株式会社CSオートディーラー</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -8696,59 +8734,50 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>埼玉県、千葉県</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>軽自動車専門店 軽ワールド（和歌山市湊）、ハイブリッドワールド（岩出市）、アウトレットワールド（岩出市西野1-1）</t>
+          <t>千葉 柏インター 第一展示場、千葉 柏インター 第二展示場、埼玉 岩槻インター 展示場</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>和歌山県和歌山市湊1820-160</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>073-488-9199</t>
-        </is>
-      </c>
+          <t>東京都渋谷区幡ヶ谷2-21-4</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>中谷 和弘</t>
+          <t>代表取締役 河野修一</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>https://kworld.jp/</t>
+          <t>https://www.csauto.jp/</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr"/>
       <c r="M133" s="2" t="inlineStr"/>
       <c r="N133" s="2" t="inlineStr"/>
-      <c r="O133" s="2" t="inlineStr">
-        <is>
-          <t>50名</t>
-        </is>
-      </c>
+      <c r="O133" s="2" t="inlineStr"/>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>https://kworld.jp/company/
-https://hv-worldofstar.com/
-https://car.motor-fan.jp/ucar/shop/0701226</t>
+          <t>https://www.csauto.jp/company
+https://www.csauto.jp/shop</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
-          <t>【2026-10更新】軽ワールドの会社紹介で運営会社（株式会社world of star）を確認。ハイブリッドワールド（hv-worldofstar.com、岩出市、TEL 0736-63-6700）とアウトレットワールド（岩出市西野、中古車情報サイト掲載）も同グループの店舗とみられるが、運営法人が同一かは未確認。</t>
+          <t>店舗案内には車種別の「専門店」が多数並ぶが、住所は柏インター（野田市）2か所と岩槻インター1か所に集約される。販売協力店フラットオートは別会社とみられ、含めていない。</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8787,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>株式会社アクセス（カーライフステーション）</t>
+          <t>株式会社MIURA（エムステーション）</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -8766,56 +8795,52 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>岩手県、宮城県、山形県</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>岩槻インター店、上尾店、久喜店</t>
+          <t>エムステーション仙台本社店、エムステーション盛岡支店、エムステーション山形支店</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市見沼区宮ケ谷塔91-1</t>
+          <t>宮城県仙台市泉区市名坂字鳥井原18-3</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>0120-344-713</t>
+          <t>022-725-2717</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>048-681-5088</t>
+          <t>022-725-2718</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>黒木 康男</t>
+          <t>三浦 卓也</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>https://344860.net/</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>https://344860.net/contact/</t>
-        </is>
-      </c>
+          <t>https://m-station-tohoku.com/</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr"/>
       <c r="M134" s="2" t="inlineStr"/>
-      <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr">
-        <is>
-          <t>158人（2019年度）</t>
-        </is>
-      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>車買取が主（中古車販売も）</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>https://344860.net/company/
-https://344860.net/shop/</t>
+          <t>https://m-station-tohoku.com/company/
+https://m-station-tohoku.com/shop/</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -8825,7 +8850,7 @@
       </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車・新車専門店。電話はフリーダイヤル（会社概要記載のもの）。</t>
+          <t>車買取・中古車販売のエムステーション。仙台・盛岡・山形に各1店舗。</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8860,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>株式会社アップルグローバルマネージメント</t>
+          <t>株式会社Noa Corporation（ノアコーポレーション）</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -8843,19 +8868,15 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>愛知県東海市富木島町内堀17番地の1</t>
-        </is>
-      </c>
+          <t>ノアコーポレーション、ノアコーポレーション 車両センター、ノアコーポレーション 小山展示場</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr"/>
       <c r="I135" s="2" t="inlineStr"/>
@@ -8863,14 +8884,15 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
       <c r="M135" s="2" t="inlineStr"/>
-      <c r="N135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O135" s="2" t="inlineStr"/>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0076/
-https://www.applenet.co.jp/shop/0077/
-https://www.applenet.co.jp/shop/0105/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -8880,7 +8902,7 @@
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8180002087515、〒476-0011）。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：ノアコーポレーション：栃木県さくら市向河原3994-1（028-612-1474）、ノアコーポレーション 車両センター：栃木県宇都宮市宮山田町406-4（028-612-1474）、ノアコーポレーション 小山展示場：栃木県小山市西黒田169-2（028-612-1474）</t>
         </is>
       </c>
     </row>
@@ -8890,7 +8912,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>株式会社オートパーク（新潟）</t>
+          <t>株式会社world of star</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -8898,32 +8920,49 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>和歌山県</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>オートパーク長岡インター店、オートパーク三条店、新潟市の店舗（店名未確認）</t>
+          <t>軽自動車専門店 軽ワールド（和歌山市湊）、ハイブリッドワールド（岩出市）、アウトレットワールド（岩出市西野1-1）</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>新潟県長岡市下条町803（採用書類の記載、未確認）</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr"/>
+          <t>和歌山県和歌山市湊1820-160</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>073-488-9199</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>中谷 和弘</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>https://kworld.jp/</t>
+        </is>
+      </c>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
       <c r="M136" s="2" t="inlineStr"/>
       <c r="N136" s="2" t="inlineStr"/>
-      <c r="O136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>50名</t>
+        </is>
+      </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>https://map.yahoo.co.jp/v3/place/HYfpeDhMPEg
-https://niigata-chukoshahanbai.info/</t>
+          <t>https://kworld.jp/company/
+https://hv-worldofstar.com/
+https://car.motor-fan.jp/ucar/shop/0701226</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -8933,7 +8972,7 @@
       </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
-          <t>公式サイト未確認。比較記事に「新潟市・三条市・長岡市などに店舗」、中古車販売・買取中心で新車も販売。</t>
+          <t>【2026-10更新】軽ワールドの会社紹介で運営会社（株式会社world of star）を確認。ハイブリッドワールド（hv-worldofstar.com、岩出市、TEL 0736-63-6700）とアウトレットワールド（岩出市西野、中古車情報サイト掲載）も同グループの店舗とみられるが、運営法人が同一かは未確認。</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8982,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>株式会社カミタケモータース</t>
+          <t>株式会社アクセス（カーライフステーション）</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -8951,40 +8990,56 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>大阪府、奈良県、大分県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>枚方本店、奈良店、大分店</t>
+          <t>岩槻インター店、上尾店、久喜店</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>大阪府枚方市池之宮2丁目30-6</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr"/>
+          <t>埼玉県さいたま市見沼区宮ケ谷塔91-1</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>0120-344-713</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>048-681-5088</t>
+        </is>
+      </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>代表取締役 上武英輝</t>
+          <t>黒木 康男</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr"/>
+          <t>https://344860.net/</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>https://344860.net/contact/</t>
+        </is>
+      </c>
       <c r="L137" s="2" t="inlineStr"/>
       <c r="M137" s="2" t="inlineStr"/>
       <c r="N137" s="2" t="inlineStr"/>
-      <c r="O137" s="2" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>158人（2019年度）</t>
+        </is>
+      </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>https://www.kamitake.net/company/
-https://www.kamitake.net/shop/</t>
+          <t>https://344860.net/company/
+https://344860.net/shop/</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -8992,7 +9047,11 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R137" s="2" t="inlineStr"/>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>届出済未使用車・新車専門店。電話はフリーダイヤル（会社概要記載のもの）。</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -9000,7 +9059,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>株式会社クイックモーション（カラーズ）</t>
+          <t>株式会社アップルグローバルマネージメント</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -9008,15 +9067,19 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>カラーズKawagoe（川越）、ほか2店舗</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr"/>
+          <t>アップル大府店、アップル東海ふきしま店、アップル半田店</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>愛知県東海市富木島町内堀17番地の1</t>
+        </is>
+      </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
@@ -9028,17 +9091,20 @@
       <c r="O138" s="2" t="inlineStr"/>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>https://ucar.carview.yahoo.co.jp/shop/saitama/214637003/（検索結果の抜粋）</t>
+          <t>https://www.applenet.co.jp/shop/0076/
+https://www.applenet.co.jp/shop/0077/
+https://www.applenet.co.jp/shop/0105/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R138" s="2" t="inlineStr">
         <is>
-          <t>4WD・SUV専門店。「埼玉県を中心に3店舗」との掲載による。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号8180002087515、〒476-0011）。</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9114,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>株式会社コンチネント</t>
+          <t>株式会社オートパーク（新潟）</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -9056,58 +9122,42 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>新潟県</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>岡山本店、カーセブン倉敷中島店、カーセブン岡山妹尾店</t>
+          <t>オートパーク長岡インター店、オートパーク三条店、新潟市の店舗（店名未確認）</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>岡山県岡山市南区妹尾4130-2</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>086-281-5544</t>
-        </is>
-      </c>
+          <t>新潟県長岡市下条町803（採用書類の記載、未確認）</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>平松 裕</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>https://conti-nent.com/</t>
-        </is>
-      </c>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr"/>
       <c r="M139" s="2" t="inlineStr"/>
-      <c r="N139" s="2" t="inlineStr">
-        <is>
-          <t>買取（カーセブン加盟店）</t>
-        </is>
-      </c>
+      <c r="N139" s="2" t="inlineStr"/>
       <c r="O139" s="2" t="inlineStr"/>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>https://conti-nent.com/company/
-https://conti-nent.com/shops/</t>
+          <t>https://map.yahoo.co.jp/v3/place/HYfpeDhMPEg
+https://niigata-chukoshahanbai.info/</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R139" s="2" t="inlineStr">
         <is>
-          <t>会社概要に「3店舗展開 岡山本店・倉敷中島店・岡山妹尾店」。ほかに鈑金塗装工場あり。カーセブンFC加盟。</t>
+          <t>公式サイト未確認。比較記事に「新潟市・三条市・長岡市などに店舗」、中古車販売・買取中心で新車も販売。</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9167,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>株式会社シマダオート商事</t>
+          <t>株式会社カミタケモータース</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
@@ -9125,19 +9175,31 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>大阪府、奈良県、大分県</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr"/>
+          <t>枚方本店、奈良店、大分店</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>大阪府枚方市池之宮2丁目30-6</t>
+        </is>
+      </c>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>代表取締役 上武英輝</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamitake.net/</t>
+        </is>
+      </c>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr"/>
       <c r="M140" s="2" t="inlineStr"/>
@@ -9145,9 +9207,8 @@
       <c r="O140" s="2" t="inlineStr"/>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0114/
-https://www.applenet.co.jp/shop/0115/
-https://www.applenet.co.jp/shop/0116/</t>
+          <t>https://www.kamitake.net/company/
+https://www.kamitake.net/shop/</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -9155,11 +9216,7 @@
           <t>高：運営会社名で確認</t>
         </is>
       </c>
-      <c r="R140" s="2" t="inlineStr">
-        <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
-        </is>
-      </c>
+      <c r="R140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -9167,7 +9224,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>株式会社ジースタリオン（Gライオン・トラック）</t>
+          <t>株式会社クイックモーション（カラーズ）</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
@@ -9175,12 +9232,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>岐阜県、大阪府、徳島県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Ｇライオン・トラック 岐阜大垣店、Gライオン・トラック 大阪営業所、Ｇライオン・トラック 徳島営業所</t>
+          <t>カラーズKawagoe（川越）、ほか2店舗</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -9191,25 +9248,21 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr"/>
       <c r="M141" s="2" t="inlineStr"/>
-      <c r="N141" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック販売・買取</t>
-        </is>
-      </c>
+      <c r="N141" s="2" t="inlineStr"/>
       <c r="O141" s="2" t="inlineStr"/>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-ichi.co.jp/corp/</t>
+          <t>https://ucar.carview.yahoo.co.jp/shop/saitama/214637003/（検索結果の抜粋）</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認</t>
+          <t>中：店舗名からの推定</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：Ｇライオン・トラック 岐阜大垣店：岐阜県大垣市長沢町5-30（058-447-7708）、Gライオン・トラック 大阪営業所：大阪府泉佐野市湊1-4-38（0724-89-5465）、Ｇライオン・トラック 徳島営業所：徳島県徳島市八万町寺山248－1（088-679-1103）</t>
+          <t>4WD・SUV専門店。「埼玉県を中心に3店舗」との掲載による。</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9272,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>株式会社ダイレクトカーズ（ショールームSUZUKA BASE）</t>
+          <t>株式会社コンチネント</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
@@ -9227,39 +9280,48 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、三重県、福岡県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>三重県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、福岡県の店舗・支店（店名未確認）</t>
+          <t>岡山本店、カーセブン倉敷中島店、カーセブン岡山妹尾店</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>三重県鈴鹿市磯山3－4－1592 DIRECT village</t>
+          <t>岡山県岡山市南区妹尾4130-2</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>059-253-8888</t>
+          <t>086-281-5544</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>平松 裕</t>
+        </is>
+      </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>https://www.cars-drt.com/</t>
+          <t>https://conti-nent.com/</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
       <c r="M142" s="2" t="inlineStr"/>
-      <c r="N142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>買取（カーセブン加盟店）</t>
+        </is>
+      </c>
       <c r="O142" s="2" t="inlineStr"/>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>https://www.jrva.com/organization/members/</t>
+          <t>https://conti-nent.com/company/
+https://conti-nent.com/shops/</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -9269,7 +9331,7 @@
       </c>
       <c r="R142" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー トレーラー レンタルキャンピングカー キャンピングカー用品 その他 JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
+          <t>会社概要に「3店舗展開 岡山本店・倉敷中島店・岡山妹尾店」。ほかに鈑金塗装工場あり。カーセブンFC加盟。</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9341,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>株式会社トイファクトリー</t>
+          <t>株式会社シマダオート商事</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
@@ -9287,31 +9349,19 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>東京都、神奈川県、岐阜県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>岐阜県の店舗・支店（店名未確認）、東京都の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>岐阜県可児市瀬田800-1</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>0574-63-0667</t>
-        </is>
-      </c>
+          <t>アップル四日市金場店、アップル鈴鹿店、アップル名張店</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr"/>
       <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>https://toy-factory.jp/</t>
-        </is>
-      </c>
+      <c r="J143" s="2" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr"/>
       <c r="M143" s="2" t="inlineStr"/>
@@ -9319,7 +9369,9 @@
       <c r="O143" s="2" t="inlineStr"/>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>https://www.jrva.com/organization/members/</t>
+          <t>https://www.applenet.co.jp/shop/0114/
+https://www.applenet.co.jp/shop/0115/
+https://www.applenet.co.jp/shop/0116/</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -9329,7 +9381,7 @@
       </c>
       <c r="R143" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー トレーラー レンタルキャンピングカー キャンピングカー用品 JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9391,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>株式会社バンテック新潟</t>
+          <t>株式会社ジースタリオン（Gライオン・トラック）</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
@@ -9347,39 +9399,31 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、新潟県、石川県</t>
+          <t>岐阜県、大阪府、徳島県</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>新潟県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、石川県の店舗・支店（店名未確認）</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>新潟県上越市七ケ所新田485-4</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>025-524-1224</t>
-        </is>
-      </c>
+          <t>Ｇライオン・トラック 岐阜大垣店、Gライオン・トラック 大阪営業所、Ｇライオン・トラック 徳島営業所</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>http://www.vantech-niigata.com/</t>
-        </is>
-      </c>
+      <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
       <c r="M144" s="2" t="inlineStr"/>
-      <c r="N144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
       <c r="O144" s="2" t="inlineStr"/>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>https://www.jrva.com/organization/members/</t>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -9389,7 +9433,7 @@
       </c>
       <c r="R144" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー トレーラー JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：Ｇライオン・トラック 岐阜大垣店：岐阜県大垣市長沢町5-30（058-447-7708）、Gライオン・トラック 大阪営業所：大阪府泉佐野市湊1-4-38（0724-89-5465）、Ｇライオン・トラック 徳島営業所：徳島県徳島市八万町寺山248－1（088-679-1103）</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9443,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>株式会社フジカーランド上田</t>
+          <t>株式会社ダイレクトカーズ（ショールームSUZUKA BASE）</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
@@ -9407,33 +9451,29 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>神奈川県、三重県、福岡県</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>上田店、佐久店、ONE!店</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr"/>
+          <t>三重県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、福岡県の店舗・支店（店名未確認）</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>三重県鈴鹿市磯山3－4－1592 DIRECT village</t>
+        </is>
+      </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>0120-225-190</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>0268-27-2280</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>羽田 憲史</t>
-        </is>
-      </c>
+          <t>059-253-8888</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>https://www.fujicar.info/</t>
+          <t>https://www.cars-drt.com/</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
@@ -9443,8 +9483,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>https://www.fujicar.info/company/about/
-https://www.fujicar.info/shop</t>
+          <t>https://www.jrva.com/organization/members/</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -9454,7 +9493,7 @@
       </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
-          <t>長野県東信地域の中古車販売店。スズキ副代理店・ダイハツスーパーピット店。電話はフリーダイヤル。</t>
+          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー トレーラー レンタルキャンピングカー キャンピングカー用品 その他 JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9503,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>株式会社フロンティアモータース</t>
+          <t>株式会社トイファクトリー</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
@@ -9472,19 +9511,31 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>大阪府、兵庫県</t>
+          <t>東京都、神奈川県、岐阜県</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr"/>
+          <t>岐阜県の店舗・支店（店名未確認）、東京都の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>岐阜県可児市瀬田800-1</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>0574-63-0667</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>https://toy-factory.jp/</t>
+        </is>
+      </c>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr"/>
       <c r="M146" s="2" t="inlineStr"/>
@@ -9492,7 +9543,7 @@
       <c r="O146" s="2" t="inlineStr"/>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
+          <t>https://www.jrva.com/organization/members/</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -9502,7 +9553,7 @@
       </c>
       <c r="R146" s="2" t="inlineStr">
         <is>
-          <t>ユーポス以外の事業は未確認。</t>
+          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー トレーラー レンタルキャンピングカー キャンピングカー用品 JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9563,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>株式会社ベネフィット</t>
+          <t>株式会社バンテック新潟</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
@@ -9520,23 +9571,31 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>千葉県、東京都</t>
+          <t>神奈川県、新潟県、石川県</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
+          <t>新潟県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、石川県の店舗・支店（店名未確認）</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>千葉県我孫子市柴崎1554番地</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr"/>
+          <t>新潟県上越市七ケ所新田485-4</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>025-524-1224</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>http://www.vantech-niigata.com/</t>
+        </is>
+      </c>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr"/>
       <c r="M147" s="2" t="inlineStr"/>
@@ -9544,10 +9603,7 @@
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0187/
-https://www.applenet.co.jp/shop/0191/
-https://www.applenet.co.jp/shop/0217/
-出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+          <t>https://www.jrva.com/organization/members/</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -9557,7 +9613,7 @@
       </c>
       <c r="R147" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3040001085422、〒270-1177）。</t>
+          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー トレーラー JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9623,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>株式会社ホワイトハウス</t>
+          <t>株式会社フジカーランド上田</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
@@ -9575,29 +9631,33 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>神奈川県、愛知県、福岡県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>愛知県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、福岡県の店舗・支店（店名未確認）</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>愛知県愛知郡東郷町和合北蚊谷29-1 オートプラネット名古屋1Ｆ</t>
-        </is>
-      </c>
+          <t>上田店、佐久店、ONE!店</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>0561-37-5336</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
+          <t>0120-225-190</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0268-27-2280</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>羽田 憲史</t>
+        </is>
+      </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>http://www.whitehousecamper.com/</t>
+          <t>https://www.fujicar.info/</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
@@ -9607,7 +9667,8 @@
       <c r="O148" s="2" t="inlineStr"/>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>https://www.jrva.com/organization/members/</t>
+          <t>https://www.fujicar.info/company/about/
+https://www.fujicar.info/shop</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -9617,7 +9678,7 @@
       </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー キャンピングカー用品 JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。 輸入車の正規販売（新車ディーラー）も行う会社のため、対象に含めるか要判断。</t>
+          <t>長野県東信地域の中古車販売店。スズキ副代理店・ダイハツスーパーピット店。電話はフリーダイヤル。</t>
         </is>
       </c>
     </row>
@@ -9627,7 +9688,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>株式会社ユーアイ（Ui-ビークル）</t>
+          <t>株式会社フリード</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
@@ -9635,39 +9696,51 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、愛知県、大阪府</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>大阪府の店舗・支店（店名未確認）、埼玉県の店舗・支店（店名未確認）、愛知県の店舗・支店（店名未確認）</t>
+          <t>名古屋長久手本店、トヨタインター店、小牧インター店</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>大阪府堺市美原区大饗158-1</t>
+          <t>愛知県長久手市井堀305</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>072-363-8913</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr"/>
+          <t>0561-63-9909</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>0561-63-9991</t>
+        </is>
+      </c>
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>http://www.ui-vehicle.com/</t>
+          <t>https://www.freed.gr.jp/</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr"/>
       <c r="M149" s="2" t="inlineStr"/>
-      <c r="N149" s="2" t="inlineStr"/>
-      <c r="O149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>買取・中古車輸出あり</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>35名（アルバイト・パート含む）</t>
+        </is>
+      </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>https://www.jrva.com/organization/members/</t>
+          <t>https://www.freed.gr.jp/company/</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -9677,7 +9750,7 @@
       </c>
       <c r="R149" s="2" t="inlineStr">
         <is>
-          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー その他 JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
+          <t>会社概要の店舗欄で3店舗。検索結果の紹介文には「愛知県内5店舗」とあったが、公式サイトで確認できたのは3。</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9760,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>株式会社リフトオフ</t>
+          <t>株式会社フロンティアモータース</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
@@ -9695,12 +9768,12 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>茨城県、千葉県、東京都</t>
+          <t>大阪府、兵庫県</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
+          <t>ユーポス東大阪若江店、ユーポス171西宮店、ユーポス神戸西店</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
@@ -9715,9 +9788,7 @@
       <c r="O150" s="2" t="inlineStr"/>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0108/
-https://www.applenet.co.jp/shop/0150/
-https://www.applenet.co.jp/shop/0237/</t>
+          <t>https://www.u-pohs.co.jp/search_shop_pref?p=osaka</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -9727,7 +9798,7 @@
       </c>
       <c r="R150" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
+          <t>ユーポス以外の事業は未確認。</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9808,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>株式会社中州自動車</t>
+          <t>株式会社ベネフィット</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
@@ -9745,17 +9816,17 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>大分県</t>
+          <t>千葉県、東京都</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
+          <t>アップル我孫子6号店、アップル柏中央店、アップル東京中央店</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>大分県臼杵市大字市浜807番地の1</t>
+          <t>千葉県我孫子市柴崎1554番地</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
@@ -9769,9 +9840,9 @@
       <c r="O151" s="2" t="inlineStr"/>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>https://www.applenet.co.jp/shop/0099/
-https://www.applenet.co.jp/shop/0111/
-https://www.applenet.co.jp/shop/0218/
+          <t>https://www.applenet.co.jp/shop/0187/
+https://www.applenet.co.jp/shop/0191/
+https://www.applenet.co.jp/shop/0217/
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
@@ -9782,7 +9853,7 @@
       </c>
       <c r="R151" s="2" t="inlineStr">
         <is>
-          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2320202000383、〒875-0052）。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号3040001085422、〒270-1177）。</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9863,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>株式会社丸山自動車（トラック市加盟、仙台・前橋・草加）</t>
+          <t>株式会社ホワイトハウス</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
@@ -9800,31 +9871,39 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>宮城県、群馬県、埼玉県</t>
+          <t>神奈川県、愛知県、福岡県</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>トラック市仙台店、丸山自動車 前橋店、埼玉草加店</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr"/>
+          <t>愛知県の店舗・支店（店名未確認）、神奈川県の店舗・支店（店名未確認）、福岡県の店舗・支店（店名未確認）</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>愛知県愛知郡東郷町和合北蚊谷29-1 オートプラネット名古屋1Ｆ</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>0561-37-5336</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>http://www.whitehousecamper.com/</t>
+        </is>
+      </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
       <c r="M152" s="2" t="inlineStr"/>
-      <c r="N152" s="2" t="inlineStr">
-        <is>
-          <t>中古トラック販売・買取</t>
-        </is>
-      </c>
+      <c r="N152" s="2" t="inlineStr"/>
       <c r="O152" s="2" t="inlineStr"/>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>https://www.truck-ichi.co.jp/corp/</t>
+          <t>https://www.jrva.com/organization/members/</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -9834,7 +9913,7 @@
       </c>
       <c r="R152" s="2" t="inlineStr">
         <is>
-          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：トラック市仙台店：宮城県宮城郡利府町利府新新明前43番地（022-781-6088）、丸山自動車 前橋店：群馬県前橋市宮地町7-1（027-290-3033）、埼玉草加店：埼玉県草加市柿木74（048-933-3111）</t>
+          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー キャンピングカー用品 JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。 輸入車の正規販売（新車ディーラー）も行う会社のため、対象に含めるか要判断。</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9923,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>良質車専門店ネクスト（運営会社未確認）</t>
+          <t>株式会社ユーアイ（Ui-ビークル）</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
@@ -9852,19 +9931,31 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>埼玉県、愛知県、大阪府</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>会津若松店、いわき店、白河店</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr"/>
+          <t>大阪府の店舗・支店（店名未確認）、埼玉県の店舗・支店（店名未確認）、愛知県の店舗・支店（店名未確認）</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>大阪府堺市美原区大饗158-1</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>072-363-8913</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>http://www.ui-vehicle.com/</t>
+        </is>
+      </c>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr"/>
       <c r="M153" s="2" t="inlineStr"/>
@@ -9872,17 +9963,17 @@
       <c r="O153" s="2" t="inlineStr"/>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗の在庫掲載）</t>
+          <t>https://www.jrva.com/organization/members/</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R153" s="2" t="inlineStr">
         <is>
-          <t>届出済未使用車も扱う中古車店。3市の店舗は検索結果の在庫掲載から確認。運営会社名は未確認。</t>
+          <t>【要判断】キャンピングカー専門（取扱：キャンピングカー その他 JRVA安心サービス登録店）。日本RV協会の協会員一覧（2026年10月5日時点）で会社名・本社所在地・電話と「店舗・支店所在都道府県」を確認。店舗数は所在都道府県の数（実際の店舗数はこれ以上の可能性あり、店名は未確認）。本社所在地・電話は協会員一覧の本社情報。</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9983,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>軽ステ（運営会社未確認）</t>
+          <t>株式会社リフトオフ</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
@@ -9900,12 +9991,12 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>熊本県</t>
+          <t>茨城県、千葉県、東京都</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>けんぐん東店、うと店、しみず店</t>
+          <t>アップル龍ヶ崎店、アップル葛飾店、アップル成田店</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
@@ -9920,17 +10011,19 @@
       <c r="O154" s="2" t="inlineStr"/>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>検索結果の抜粋（店舗掲載）</t>
+          <t>https://www.applenet.co.jp/shop/0108/
+https://www.applenet.co.jp/shop/0150/
+https://www.applenet.co.jp/shop/0237/</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認</t>
         </is>
       </c>
       <c r="R154" s="2" t="inlineStr">
         <is>
-          <t>熊本県最大級の軽届出済未使用車専門店（総在庫1,300台）とのこと。運営会社未確認。</t>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。</t>
         </is>
       </c>
     </row>
@@ -9940,7 +10033,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>阿部勝自動車工業株式会社</t>
+          <t>株式会社中州自動車</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
@@ -9948,31 +10041,23 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>大分県</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+          <t>アップル大分中央店、アップル大分高城店、アップル別府店</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>宮城県石巻市中浦1丁目2番27号</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>0120-058-012</t>
-        </is>
-      </c>
+          <t>大分県臼杵市大字市浜807番地の1</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>https://k-mishiyo.abekatu.co.jp/</t>
-        </is>
-      </c>
+      <c r="J155" s="2" t="inlineStr"/>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr"/>
       <c r="M155" s="2" t="inlineStr"/>
@@ -9980,16 +10065,227 @@
       <c r="O155" s="2" t="inlineStr"/>
       <c r="P155" s="2" t="inlineStr">
         <is>
+          <t>https://www.applenet.co.jp/shop/0099/
+https://www.applenet.co.jp/shop/0111/
+https://www.applenet.co.jp/shop/0218/
+出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>アップルの加盟店として3店舗。自社ブランドなど他の店舗があれば5店舗以上になる可能性あり（未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号2320202000383、〒875-0052）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>株式会社丸山自動車（トラック市加盟、仙台・前橋・草加）</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>宮城県、群馬県、埼玉県</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>トラック市仙台店、丸山自動車 前橋店、埼玉草加店</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売・買取</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr"/>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.truck-ichi.co.jp/corp/</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>高：運営会社名で確認</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>中古トラック販売。トラック市（商用車専門FC）の加盟店一覧で運営会社名と店舗を確認。店舗所在地と電話：トラック市仙台店：宮城県宮城郡利府町利府新新明前43番地（022-781-6088）、丸山自動車 前橋店：群馬県前橋市宮地町7-1（027-290-3033）、埼玉草加店：埼玉県草加市柿木74（048-933-3111）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>良質車専門店ネクスト（運営会社未確認）</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>会津若松店、いわき店、白河店</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr"/>
+      <c r="O157" s="2" t="inlineStr"/>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>検索結果の抜粋（店舗の在庫掲載）</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>届出済未使用車も扱う中古車店。3市の店舗は検索結果の在庫掲載から確認。運営会社名は未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>軽ステ（運営会社未確認）</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>熊本県</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>けんぐん東店、うと店、しみず店</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr"/>
+      <c r="O158" s="2" t="inlineStr"/>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>検索結果の抜粋（店舗掲載）</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>熊本県最大級の軽届出済未使用車専門店（総在庫1,300台）とのこと。運営会社未確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>阿部勝自動車工業株式会社</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>アベカツ石巻店、大崎古川店、名取岩沼店</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>宮城県石巻市中浦1丁目2番27号</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>0120-058-012</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>https://k-mishiyo.abekatu.co.jp/</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr"/>
+      <c r="O159" s="2" t="inlineStr"/>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
           <t>https://k-mishiyo.abekatu.co.jp/（検索結果の抜粋）
 出典：国税庁法人番号公表サイト（国税庁）（https://www.houjin-bangou.nta.go.jp/download/zenken/）を加工して作成</t>
         </is>
       </c>
-      <c r="Q155" s="2" t="inlineStr">
+      <c r="Q159" s="2" t="inlineStr">
         <is>
           <t>中：店舗名からの推定</t>
         </is>
       </c>
-      <c r="R155" s="2" t="inlineStr">
+      <c r="R159" s="2" t="inlineStr">
         <is>
           <t>電話はサイト記載のフリーダイヤル（本社番号かは未確認）。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6370301000037、〒986-0847）。</t>
         </is>
@@ -10059,7 +10355,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -10069,7 +10365,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -10079,7 +10375,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -10239,7 +10535,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -10249,7 +10545,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
@@ -10359,7 +10655,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -10539,7 +10835,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -10689,7 +10985,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70">
@@ -10769,7 +11065,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -10839,7 +11135,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85"/>
@@ -10869,7 +11165,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89">
@@ -10879,7 +11175,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90">
@@ -10909,7 +11205,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="93"/>
@@ -10939,7 +11235,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97">
@@ -10949,7 +11245,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/output/中規模中古車販売会社リスト.xlsx
+++ b/output/中規模中古車販売会社リスト.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R209"/>
+  <dimension ref="A1:R208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>ミニクス（軽トラ・軽バン専門店、運営会社未確認）</t>
+          <t>リッチハート株式会社</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
@@ -10612,37 +10612,51 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>兵庫県、広島県</t>
+          <t>埼玉県、東京都</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>ミニクス福山中央店、ミニクス姫路中央店、ミニクス加古川の店舗（店名未確認）</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr"/>
+          <t>リッチハート株式会社、リッチ東京絆トレード、リッチ東京絆トレード八王子店</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>埼玉県所沢市三ケ島3丁目781番地の9</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>0429978282（リッチハート株式会社・店舗番号）</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr"/>
       <c r="M158" s="2" t="inlineStr"/>
-      <c r="N158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>車買取あり（MOTA車買取加盟）</t>
+        </is>
+      </c>
       <c r="O158" s="2" t="inlineStr"/>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>https://www.goo-net.com/usedcar/spread/goo_sort/17/700100280830241130001.html（検索結果の抜粋のみ、アクセスせず）</t>
+          <t>https://autoc-one.jp/ullo/shop/1719/
+https://autoc-one.jp/ullo/shop/2794/
+https://autoc-one.jp/ullo/shop/3231/</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
         <is>
-          <t>中：店舗名からの推定</t>
+          <t>高：運営会社名で確認（MOTA店舗ページの「運営」欄）</t>
         </is>
       </c>
       <c r="R158" s="2" t="inlineStr">
         <is>
-          <t>【要判断】軽トラ・軽バン専門店。検索結果に表示された掲載文に「福山・姫路・加古川の3拠点」。運営会社名は未確認（グーネットはrobots.txt取得不可のためアクセスしていない）。</t>
+          <t>車買取「リッチハート」「リッチ東京絆トレード」。 店舗数はMOTA車買取に掲載の拠点数（3、所在地の重複は除外）で、MOTA非掲載店舗は含まない下限値。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6030001128344、〒359-1164）。</t>
         </is>
       </c>
     </row>
@@ -10652,7 +10666,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>リッチハート株式会社</t>
+          <t>古城モータース</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
@@ -10660,53 +10674,47 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>埼玉県、東京都</t>
+          <t>富山県、石川県</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>リッチハート株式会社、リッチ東京絆トレード、リッチ東京絆トレード八王子店</t>
+          <t>高岡本店、富山店、石川白山店</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>埼玉県所沢市三ケ島3丁目781番地の9</t>
+          <t>富山県高岡市二塚425番地</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>0429978282（リッチハート株式会社・店舗番号）</t>
+          <t>0120-540-118</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kojyo-motors.com/</t>
+        </is>
+      </c>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr"/>
       <c r="M159" s="2" t="inlineStr"/>
-      <c r="N159" s="2" t="inlineStr">
-        <is>
-          <t>車買取あり（MOTA車買取加盟）</t>
-        </is>
-      </c>
+      <c r="N159" s="2" t="inlineStr"/>
       <c r="O159" s="2" t="inlineStr"/>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>https://autoc-one.jp/ullo/shop/1719/
-https://autoc-one.jp/ullo/shop/2794/
-https://autoc-one.jp/ullo/shop/3231/</t>
+          <t>https://www.kojyo-motors.com/</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
         <is>
-          <t>高：運営会社名で確認（MOTA店舗ページの「運営」欄）</t>
-        </is>
-      </c>
-      <c r="R159" s="2" t="inlineStr">
-        <is>
-          <t>車買取「リッチハート」「リッチ東京絆トレード」。 店舗数はMOTA車買取に掲載の拠点数（3、所在地の重複は除外）で、MOTA非掲載店舗は含まない下限値。 本社所在地は法人番号公表サイトの登記上の本店所在地（法人番号6030001128344、〒359-1164）。</t>
-        </is>
-      </c>
+          <t>中：店舗名からの推定</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -10714,7 +10722,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>古城モータース</t>
+          <t>合同会社ENDLESS</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
@@ -10722,47 +10730,53 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>富山県、石川県</t>
+          <t>神奈川県</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>高岡本店、富山店、石川白山店</t>
+          <t>車買取レンジャー、キングビッド、キングビッド 横浜</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>富山県高岡市二塚425番地</t>
+          <t>神奈川県厚木市飯山4586番地13</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>0120-540-118</t>
+          <t>0462589369（車買取レンジャー・店舗番号）</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr"/>
       <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kojyo-motors.com/</t>
-        </is>
-      </c>
+      <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr"/>
       <c r="M160" s="2" t="inlineStr"/>
-      <c r="N160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>車買取あり（MOTA車買取加盟）</t>
+        </is>
+      </c>
       <c r="O160" s="2" t="inlin